--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -52,6 +52,28 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+默认不填，特殊用不同数字标记</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 属性等级，解锁属性id1_解锁属性id2^_……|属性等级，解锁属性id1_解锁属性id2^_……</t>
         </r>
       </text>
@@ -61,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
   <si>
     <t>属性id</t>
   </si>
@@ -78,6 +100,9 @@
     <t>组内序号</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>等级_激活后解锁属性id</t>
   </si>
   <si>
@@ -99,6 +124,9 @@
     <t>subIdx</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>skillId</t>
   </si>
   <si>
@@ -187,9 +215,6 @@
   </si>
   <si>
     <t>1,10350008</t>
-  </si>
-  <si>
-    <t>h</t>
   </si>
   <si>
     <t>金蛇招财模式20倍以上大奖概率提升</t>
@@ -1254,18 +1279,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="15.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="6" max="7" width="26.875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1284,42 +1309,51 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
@@ -1330,13 +1364,16 @@
         <v>100300</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
@@ -1347,16 +1384,17 @@
         <v>100300</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="5"/>
+      <c r="G6" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
@@ -1367,16 +1405,17 @@
         <v>100300</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="5"/>
+      <c r="G7" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
@@ -1387,13 +1426,13 @@
         <v>100300</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
@@ -1404,13 +1443,13 @@
         <v>100300</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
@@ -1421,13 +1460,13 @@
         <v>100300</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>10340001</v>
       </c>
@@ -1438,10 +1477,13 @@
         <v>103400</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10340002</v>
       </c>
@@ -1452,13 +1494,14 @@
         <v>103400</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>10340003</v>
       </c>
@@ -1469,13 +1512,14 @@
         <v>103400</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>10340004</v>
       </c>
@@ -1486,10 +1530,10 @@
         <v>103400</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>10340005</v>
       </c>
@@ -1500,10 +1544,10 @@
         <v>103400</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>10340006</v>
       </c>
@@ -1514,13 +1558,14 @@
         <v>103400</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>10340007</v>
       </c>
@@ -1531,13 +1576,14 @@
         <v>103400</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>29</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>10340008</v>
       </c>
@@ -1548,10 +1594,10 @@
         <v>103400</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>10340009</v>
       </c>
@@ -1562,10 +1608,10 @@
         <v>103400</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>10350001</v>
       </c>
@@ -1576,10 +1622,13 @@
         <v>103500</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>33</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>10350002</v>
       </c>
@@ -1590,13 +1639,14 @@
         <v>103500</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>10350003</v>
       </c>
@@ -1607,13 +1657,14 @@
         <v>103500</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>36</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>10350004</v>
       </c>
@@ -1624,10 +1675,10 @@
         <v>103500</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>10350005</v>
       </c>
@@ -1638,10 +1689,10 @@
         <v>103500</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>10350006</v>
       </c>
@@ -1652,13 +1703,14 @@
         <v>103500</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>10350007</v>
       </c>
@@ -1669,16 +1721,14 @@
         <v>103500</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M26" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="F26" s="5"/>
+      <c r="G26" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>10350008</v>
       </c>
@@ -1689,10 +1739,10 @@
         <v>103500</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>10350009</v>
       </c>
@@ -1703,10 +1753,10 @@
         <v>103500</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>10170001</v>
       </c>
@@ -1717,10 +1767,13 @@
         <v>101700</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>33</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>10170002</v>
       </c>
@@ -1731,13 +1784,14 @@
         <v>101700</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>10170003</v>
       </c>
@@ -1748,10 +1802,10 @@
         <v>101700</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>10170004</v>
       </c>
@@ -1762,10 +1816,10 @@
         <v>101700</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>10170005</v>
       </c>
@@ -1776,10 +1830,10 @@
         <v>101700</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>10170006</v>
       </c>
@@ -1790,13 +1844,13 @@
         <v>101700</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>10170007</v>
       </c>
@@ -1807,13 +1861,13 @@
         <v>101700</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F35" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>10170008</v>
       </c>
@@ -1824,13 +1878,13 @@
         <v>101700</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F36" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>10170009</v>
       </c>
@@ -1841,10 +1895,10 @@
         <v>101700</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>10170010</v>
       </c>
@@ -1855,10 +1909,10 @@
         <v>101700</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>10180001</v>
       </c>
@@ -1869,10 +1923,13 @@
         <v>101800</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>10180002</v>
       </c>
@@ -1883,13 +1940,13 @@
         <v>101800</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>34</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>10180003</v>
       </c>
@@ -1900,13 +1957,13 @@
         <v>101800</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>10180004</v>
       </c>
@@ -1917,13 +1974,13 @@
         <v>101800</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>47</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>10180005</v>
       </c>
@@ -1934,10 +1991,10 @@
         <v>101800</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>10180006</v>
       </c>
@@ -1948,13 +2005,13 @@
         <v>101800</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>49</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>10180007</v>
       </c>
@@ -1965,13 +2022,13 @@
         <v>101800</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>53</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>10180008</v>
       </c>
@@ -1982,13 +2039,13 @@
         <v>101800</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>10180009</v>
       </c>
@@ -1999,10 +2056,10 @@
         <v>101800</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>10180010</v>
       </c>
@@ -2013,10 +2070,10 @@
         <v>101800</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>10210001</v>
       </c>
@@ -2027,10 +2084,13 @@
         <v>102100</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>10210002</v>
       </c>
@@ -2041,13 +2101,13 @@
         <v>102100</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>34</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>10210003</v>
       </c>
@@ -2058,13 +2118,13 @@
         <v>102100</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>10210004</v>
       </c>
@@ -2075,13 +2135,13 @@
         <v>102100</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>47</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>10210005</v>
       </c>
@@ -2092,10 +2152,10 @@
         <v>102100</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>10210006</v>
       </c>
@@ -2106,13 +2166,13 @@
         <v>102100</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>49</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>10210007</v>
       </c>
@@ -2123,13 +2183,13 @@
         <v>102100</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>53</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>10210008</v>
       </c>
@@ -2140,13 +2200,13 @@
         <v>102100</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>62</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>10210009</v>
       </c>
@@ -2157,10 +2217,10 @@
         <v>102100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>10210010</v>
       </c>
@@ -2171,13 +2231,13 @@
         <v>102100</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F58" s="7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>10210011</v>
       </c>
@@ -2188,13 +2248,13 @@
         <v>102100</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F59" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>10210012</v>
       </c>
@@ -2205,10 +2265,10 @@
         <v>102100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <v>10210013</v>
       </c>
@@ -2219,7 +2279,7 @@
         <v>102100</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,23 +83,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
   <si>
     <t>属性id</t>
   </si>
   <si>
-    <t>组别</t>
-  </si>
-  <si>
     <t>游戏id</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>组内序号</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
@@ -115,15 +109,9 @@
     <t>id</t>
   </si>
   <si>
-    <t>team</t>
-  </si>
-  <si>
     <t>gameType</t>
   </si>
   <si>
-    <t>subIdx</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -154,6 +142,15 @@
     <t>触发jackpot概率提升</t>
   </si>
   <si>
+    <t>自动旋转次数</t>
+  </si>
+  <si>
+    <t>快速旋转</t>
+  </si>
+  <si>
+    <t>5,10030007</t>
+  </si>
+  <si>
     <t>1,10340003</t>
   </si>
   <si>
@@ -184,6 +181,9 @@
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
+    <t>5,10340010</t>
+  </si>
+  <si>
     <t>下注金额增加</t>
   </si>
   <si>
@@ -220,6 +220,9 @@
     <t>金蛇招财模式20倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>5,10350010</t>
+  </si>
+  <si>
     <t>1,10170003_10170004|2,10170005</t>
   </si>
   <si>
@@ -256,6 +259,9 @@
     <t>触发奖池概率提升</t>
   </si>
   <si>
+    <t>5,10170011</t>
+  </si>
+  <si>
     <t>1,10180003</t>
   </si>
   <si>
@@ -280,6 +286,9 @@
     <t>免费模式160倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>5,10180011</t>
+  </si>
+  <si>
     <t>1,10210003</t>
   </si>
   <si>
@@ -311,6 +320,9 @@
   </si>
   <si>
     <t>bonus小游戏40倍以上概率提升</t>
+  </si>
+  <si>
+    <t>5,10210014</t>
   </si>
 </sst>
 </file>
@@ -482,12 +494,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1279,18 +1291,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:E73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="15.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="1" customWidth="1"/>
-    <col min="6" max="7" width="26.875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="26.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,980 +1317,923 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
       <c r="B5" s="1">
+        <v>100300</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
-        <v>100300</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
         <v>100300</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
         <v>100300</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
         <v>100300</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
         <v>100300</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
       <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
         <v>100300</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>10030007</v>
+      </c>
+      <c r="B11" s="1">
+        <v>100300</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
+        <v>10030008</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100300</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
+        <v>10340001</v>
+      </c>
+      <c r="B13" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
+        <v>10340002</v>
+      </c>
+      <c r="B14" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="1">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
+        <v>10340003</v>
+      </c>
+      <c r="B15" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
+        <v>10340004</v>
+      </c>
+      <c r="B16" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
+        <v>10340005</v>
+      </c>
+      <c r="B17" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
+        <v>10340006</v>
+      </c>
+      <c r="B18" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>10340007</v>
+      </c>
+      <c r="B19" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>10340008</v>
+      </c>
+      <c r="B20" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
+        <v>10340009</v>
+      </c>
+      <c r="B21" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>10340010</v>
+      </c>
+      <c r="B22" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
+        <v>10340011</v>
+      </c>
+      <c r="B23" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
+        <v>10350001</v>
+      </c>
+      <c r="B24" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>10340001</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
+        <v>10350002</v>
+      </c>
+      <c r="B25" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
+        <v>10350003</v>
+      </c>
+      <c r="B26" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>10350004</v>
+      </c>
+      <c r="B27" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>10350005</v>
+      </c>
+      <c r="B28" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
+        <v>10350006</v>
+      </c>
+      <c r="B29" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>10350007</v>
+      </c>
+      <c r="B30" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>10350008</v>
+      </c>
+      <c r="B31" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>10350009</v>
+      </c>
+      <c r="B32" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>10350010</v>
+      </c>
+      <c r="B33" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>10350011</v>
+      </c>
+      <c r="B34" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>10170001</v>
+      </c>
+      <c r="B35" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1">
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
+        <v>10170002</v>
+      </c>
+      <c r="B36" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
+        <v>10170003</v>
+      </c>
+      <c r="B37" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>10170004</v>
+      </c>
+      <c r="B38" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>10170005</v>
+      </c>
+      <c r="B39" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
+        <v>10170006</v>
+      </c>
+      <c r="B40" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
+        <v>10170007</v>
+      </c>
+      <c r="B41" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
+        <v>10170008</v>
+      </c>
+      <c r="B42" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>10170009</v>
+      </c>
+      <c r="B43" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>10170010</v>
+      </c>
+      <c r="B44" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
+        <v>10170011</v>
+      </c>
+      <c r="B45" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
+        <v>10170012</v>
+      </c>
+      <c r="B46" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
+        <v>10180001</v>
+      </c>
+      <c r="B47" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>10340002</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>10340003</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>10340004</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1">
-        <v>10340005</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>10340006</v>
-      </c>
-      <c r="B16" s="1">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <v>10340007</v>
-      </c>
-      <c r="B17" s="1">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1">
-        <v>10340008</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1">
-        <v>10340009</v>
-      </c>
-      <c r="B19" s="1">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1">
-        <v>10350001</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
+        <v>10180002</v>
+      </c>
+      <c r="B48" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>10180003</v>
+      </c>
+      <c r="B49" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
+        <v>10180004</v>
+      </c>
+      <c r="B50" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>10180005</v>
+      </c>
+      <c r="B51" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>10180006</v>
+      </c>
+      <c r="B52" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
+        <v>10180007</v>
+      </c>
+      <c r="B53" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
+        <v>10180008</v>
+      </c>
+      <c r="B54" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1">
+        <v>10180009</v>
+      </c>
+      <c r="B55" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1">
+        <v>10180010</v>
+      </c>
+      <c r="B56" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
+        <v>10180011</v>
+      </c>
+      <c r="B57" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
+        <v>10180012</v>
+      </c>
+      <c r="B58" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
+        <v>10210001</v>
+      </c>
+      <c r="B59" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1">
-        <v>10350002</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D21" s="1" t="s">
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
+        <v>10210002</v>
+      </c>
+      <c r="B60" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1">
-        <v>10350003</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1">
-        <v>10350004</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
-        <v>10350005</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1">
-        <v>10350006</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1">
-        <v>10350007</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1">
-        <v>10350008</v>
-      </c>
-      <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1">
-        <v>10350009</v>
-      </c>
-      <c r="B28" s="1">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1">
-        <v>10170001</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1">
-        <v>10170002</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1">
-        <v>10170003</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1">
-        <v>10170004</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E60" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
+        <v>10210003</v>
+      </c>
+      <c r="B61" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="1">
-        <v>10170005</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="E61" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
+        <v>10210004</v>
+      </c>
+      <c r="B62" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="1">
-        <v>10170006</v>
-      </c>
-      <c r="B34" s="1">
-        <v>3</v>
-      </c>
-      <c r="C34" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E62" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
+        <v>10210005</v>
+      </c>
+      <c r="B63" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="7" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
+        <v>10210006</v>
+      </c>
+      <c r="B64" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1">
-        <v>10170007</v>
-      </c>
-      <c r="B35" s="1">
-        <v>3</v>
-      </c>
-      <c r="C35" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="1">
-        <v>10170008</v>
-      </c>
-      <c r="B36" s="1">
-        <v>3</v>
-      </c>
-      <c r="C36" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="7" t="s">
+      <c r="E64" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1">
+        <v>10210007</v>
+      </c>
+      <c r="B65" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="1">
-        <v>10170009</v>
-      </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="C37" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="1">
-        <v>10170010</v>
-      </c>
-      <c r="B38" s="1">
-        <v>4</v>
-      </c>
-      <c r="C38" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="1">
-        <v>10180001</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="1">
-        <v>10180002</v>
-      </c>
-      <c r="B40" s="1">
-        <v>2</v>
-      </c>
-      <c r="C40" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="7" t="s">
+      <c r="E65" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1">
+        <v>10210008</v>
+      </c>
+      <c r="B66" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1">
+        <v>10210009</v>
+      </c>
+      <c r="B67" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1">
+        <v>10210010</v>
+      </c>
+      <c r="B68" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1">
+        <v>10210011</v>
+      </c>
+      <c r="B69" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="1">
+        <v>10210012</v>
+      </c>
+      <c r="B70" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1">
+        <v>10210013</v>
+      </c>
+      <c r="B71" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1">
-        <v>10180003</v>
-      </c>
-      <c r="B41" s="1">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="1">
-        <v>10180004</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="1">
-        <v>10180005</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="1">
-        <v>10180006</v>
-      </c>
-      <c r="B44" s="1">
-        <v>3</v>
-      </c>
-      <c r="C44" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1">
-        <v>10180007</v>
-      </c>
-      <c r="B45" s="1">
-        <v>3</v>
-      </c>
-      <c r="C45" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="1">
-        <v>10180008</v>
-      </c>
-      <c r="B46" s="1">
-        <v>3</v>
-      </c>
-      <c r="C46" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="1">
-        <v>10180009</v>
-      </c>
-      <c r="B47" s="1">
-        <v>3</v>
-      </c>
-      <c r="C47" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="1">
-        <v>10180010</v>
-      </c>
-      <c r="B48" s="1">
-        <v>4</v>
-      </c>
-      <c r="C48" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="1">
-        <v>10210001</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1">
+    <row r="72" spans="1:5">
+      <c r="A72" s="1">
+        <v>10210014</v>
+      </c>
+      <c r="B72" s="1">
         <v>102100</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="1">
-        <v>10210002</v>
-      </c>
-      <c r="B50" s="1">
-        <v>2</v>
-      </c>
-      <c r="C50" s="1">
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1">
+        <v>10210015</v>
+      </c>
+      <c r="B73" s="1">
         <v>102100</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="1">
-        <v>10210003</v>
-      </c>
-      <c r="B51" s="1">
-        <v>2</v>
-      </c>
-      <c r="C51" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="1">
-        <v>10210004</v>
-      </c>
-      <c r="B52" s="1">
-        <v>2</v>
-      </c>
-      <c r="C52" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="1">
-        <v>10210005</v>
-      </c>
-      <c r="B53" s="1">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="1">
-        <v>10210006</v>
-      </c>
-      <c r="B54" s="1">
-        <v>3</v>
-      </c>
-      <c r="C54" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="1">
-        <v>10210007</v>
-      </c>
-      <c r="B55" s="1">
-        <v>3</v>
-      </c>
-      <c r="C55" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="1">
-        <v>10210008</v>
-      </c>
-      <c r="B56" s="1">
-        <v>3</v>
-      </c>
-      <c r="C56" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="1">
-        <v>10210009</v>
-      </c>
-      <c r="B57" s="1">
-        <v>3</v>
-      </c>
-      <c r="C57" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="1">
-        <v>10210010</v>
-      </c>
-      <c r="B58" s="1">
-        <v>4</v>
-      </c>
-      <c r="C58" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="1">
-        <v>10210011</v>
-      </c>
-      <c r="B59" s="1">
-        <v>4</v>
-      </c>
-      <c r="C59" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="1">
-        <v>10210012</v>
-      </c>
-      <c r="B60" s="1">
-        <v>4</v>
-      </c>
-      <c r="C60" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="1">
-        <v>10210013</v>
-      </c>
-      <c r="B61" s="1">
-        <v>5</v>
-      </c>
-      <c r="C61" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>56</v>
+      <c r="C73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
   <si>
     <t>属性id</t>
   </si>
@@ -94,6 +94,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>多语言id</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>gameType</t>
   </si>
   <si>
+    <t>languageID</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -145,10 +151,10 @@
     <t>自动旋转次数</t>
   </si>
   <si>
+    <t>5,10030008</t>
+  </si>
+  <si>
     <t>快速旋转</t>
-  </si>
-  <si>
-    <t>5,10030007</t>
   </si>
   <si>
     <t>1,10340003</t>
@@ -494,12 +500,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -955,14 +961,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1291,17 +1303,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="26.875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="26.875" style="2" customWidth="1"/>
+    <col min="5" max="6" width="26.875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1311,42 +1324,51 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
@@ -1354,13 +1376,16 @@
         <v>100300</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
@@ -1368,14 +1393,17 @@
         <v>100300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
@@ -1383,14 +1411,17 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
@@ -1398,10 +1429,13 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4020005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
@@ -1409,10 +1443,13 @@
         <v>100300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4020006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
@@ -1420,10 +1457,13 @@
         <v>100300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4020007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>10030007</v>
       </c>
@@ -1431,10 +1471,16 @@
         <v>100300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>10030008</v>
       </c>
@@ -1442,13 +1488,14 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>10340001</v>
       </c>
@@ -1456,13 +1503,13 @@
         <v>103400</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>10340002</v>
       </c>
@@ -1470,14 +1517,15 @@
         <v>103400</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>10340003</v>
       </c>
@@ -1485,14 +1533,15 @@
         <v>103400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>10340004</v>
       </c>
@@ -1500,10 +1549,10 @@
         <v>103400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>10340005</v>
       </c>
@@ -1511,10 +1560,10 @@
         <v>103400</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>10340006</v>
       </c>
@@ -1522,14 +1571,15 @@
         <v>103400</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>10340007</v>
       </c>
@@ -1537,14 +1587,15 @@
         <v>103400</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>10340008</v>
       </c>
@@ -1552,10 +1603,10 @@
         <v>103400</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>10340009</v>
       </c>
@@ -1563,10 +1614,10 @@
         <v>103400</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>10340010</v>
       </c>
@@ -1574,10 +1625,10 @@
         <v>103400</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>10340011</v>
       </c>
@@ -1585,13 +1636,13 @@
         <v>103400</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>10350001</v>
       </c>
@@ -1599,13 +1650,13 @@
         <v>103500</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="1">
+        <v>35</v>
+      </c>
+      <c r="E24" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>10350002</v>
       </c>
@@ -1613,14 +1664,15 @@
         <v>103500</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>36</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>10350003</v>
       </c>
@@ -1628,14 +1680,15 @@
         <v>103500</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>38</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>10350004</v>
       </c>
@@ -1643,10 +1696,10 @@
         <v>103500</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>10350005</v>
       </c>
@@ -1654,10 +1707,10 @@
         <v>103500</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>10350006</v>
       </c>
@@ -1665,14 +1718,15 @@
         <v>103500</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>42</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>10350007</v>
       </c>
@@ -1680,14 +1734,15 @@
         <v>103500</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>44</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>10350008</v>
       </c>
@@ -1695,10 +1750,10 @@
         <v>103500</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>10350009</v>
       </c>
@@ -1706,10 +1761,10 @@
         <v>103500</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>10350010</v>
       </c>
@@ -1717,10 +1772,10 @@
         <v>103500</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>10350011</v>
       </c>
@@ -1728,13 +1783,13 @@
         <v>103500</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>10170001</v>
       </c>
@@ -1742,13 +1797,13 @@
         <v>101700</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="1">
+        <v>35</v>
+      </c>
+      <c r="E35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>10170002</v>
       </c>
@@ -1756,14 +1811,15 @@
         <v>101700</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>36</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>10170003</v>
       </c>
@@ -1771,10 +1827,10 @@
         <v>101700</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>10170004</v>
       </c>
@@ -1782,10 +1838,10 @@
         <v>101700</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>10170005</v>
       </c>
@@ -1793,10 +1849,10 @@
         <v>101700</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>10170006</v>
       </c>
@@ -1804,13 +1860,13 @@
         <v>101700</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>52</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>10170007</v>
       </c>
@@ -1818,13 +1874,13 @@
         <v>101700</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>10170008</v>
       </c>
@@ -1832,13 +1888,13 @@
         <v>101700</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>56</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>10170009</v>
       </c>
@@ -1846,10 +1902,10 @@
         <v>101700</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>10170010</v>
       </c>
@@ -1857,10 +1913,10 @@
         <v>101700</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>10170011</v>
       </c>
@@ -1868,13 +1924,13 @@
         <v>101700</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>10170012</v>
       </c>
@@ -1882,10 +1938,10 @@
         <v>101700</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>10180001</v>
       </c>
@@ -1893,13 +1949,13 @@
         <v>101800</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" s="1">
+        <v>35</v>
+      </c>
+      <c r="E47" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>10180002</v>
       </c>
@@ -1907,13 +1963,13 @@
         <v>101800</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>36</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>10180003</v>
       </c>
@@ -1921,13 +1977,13 @@
         <v>101800</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>10180004</v>
       </c>
@@ -1935,13 +1991,13 @@
         <v>101800</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>50</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>10180005</v>
       </c>
@@ -1949,10 +2005,10 @@
         <v>101800</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>10180006</v>
       </c>
@@ -1960,13 +2016,13 @@
         <v>101800</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>52</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="1">
         <v>10180007</v>
       </c>
@@ -1974,13 +2030,13 @@
         <v>101800</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>56</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="1">
         <v>10180008</v>
       </c>
@@ -1988,13 +2044,13 @@
         <v>101800</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>66</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="1">
         <v>10180009</v>
       </c>
@@ -2002,10 +2058,10 @@
         <v>101800</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
         <v>10180010</v>
       </c>
@@ -2013,10 +2069,10 @@
         <v>101800</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="1">
         <v>10180011</v>
       </c>
@@ -2024,10 +2080,10 @@
         <v>101800</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="1">
         <v>10180012</v>
       </c>
@@ -2035,13 +2091,13 @@
         <v>101800</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="1">
         <v>10210001</v>
       </c>
@@ -2049,13 +2105,13 @@
         <v>102100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="1">
+        <v>35</v>
+      </c>
+      <c r="E59" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:6">
       <c r="A60" s="1">
         <v>10210002</v>
       </c>
@@ -2063,13 +2119,13 @@
         <v>102100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>36</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="1">
         <v>10210003</v>
       </c>
@@ -2077,13 +2133,13 @@
         <v>102100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="1">
         <v>10210004</v>
       </c>
@@ -2091,13 +2147,13 @@
         <v>102100</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>50</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="1">
         <v>10210005</v>
       </c>
@@ -2105,10 +2161,10 @@
         <v>102100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>10210006</v>
       </c>
@@ -2116,13 +2172,13 @@
         <v>102100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>52</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>10210007</v>
       </c>
@@ -2130,13 +2186,13 @@
         <v>102100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>56</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>10210008</v>
       </c>
@@ -2144,13 +2200,13 @@
         <v>102100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>66</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>10210009</v>
       </c>
@@ -2158,10 +2214,10 @@
         <v>102100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>10210010</v>
       </c>
@@ -2169,13 +2225,13 @@
         <v>102100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>76</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="1">
         <v>10210011</v>
       </c>
@@ -2183,13 +2239,13 @@
         <v>102100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>78</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="1">
         <v>10210012</v>
       </c>
@@ -2197,10 +2253,10 @@
         <v>102100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="1">
         <v>10210013</v>
       </c>
@@ -2208,10 +2264,10 @@
         <v>102100</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="1">
         <v>10210014</v>
       </c>
@@ -2219,10 +2275,10 @@
         <v>102100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="1">
         <v>10210015</v>
       </c>
@@ -2230,10 +2286,10 @@
         <v>102100</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
   <si>
     <t>属性id</t>
   </si>
@@ -100,13 +100,13 @@
     <t>类型</t>
   </si>
   <si>
-    <t>等级_激活后解锁属性id</t>
+    <t>解锁属性id_等级</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>Map&lt;int{,}list&lt;int&gt;{_}&gt;{|}</t>
+    <t>Map&lt;int{,}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -130,37 +130,31 @@
     <t>中奖概率提升</t>
   </si>
   <si>
-    <t>1,10030003</t>
-  </si>
-  <si>
     <t>常规5-10中奖概率提升</t>
   </si>
   <si>
-    <t>1,10030004</t>
+    <t>10030002,1</t>
   </si>
   <si>
     <t>常规10-20中奖概率提升</t>
   </si>
   <si>
+    <t>10030003,1</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升</t>
   </si>
   <si>
     <t>触发jackpot概率提升</t>
   </si>
   <si>
+    <t>快速旋转</t>
+  </si>
+  <si>
     <t>自动旋转次数</t>
   </si>
   <si>
-    <t>5,10030008</t>
-  </si>
-  <si>
-    <t>快速旋转</t>
-  </si>
-  <si>
-    <t>1,10340003</t>
-  </si>
-  <si>
-    <t>1,10340004_10340005</t>
+    <t>10030007,5</t>
   </si>
   <si>
     <t>常规10-25中奖概率提升</t>
@@ -172,39 +166,24 @@
     <t>触发福马模式概率提升</t>
   </si>
   <si>
-    <t>1,10340007</t>
-  </si>
-  <si>
     <t>福马模式10倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>1,10340008</t>
-  </si>
-  <si>
     <t>福马模式20倍以上大奖概率提升</t>
   </si>
   <si>
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
-    <t>5,10340010</t>
-  </si>
-  <si>
     <t>下注金额增加</t>
   </si>
   <si>
     <t>中奖概率增高</t>
   </si>
   <si>
-    <t>1,10350003</t>
-  </si>
-  <si>
     <t>5-10倍中奖概率增高</t>
   </si>
   <si>
-    <t>1,10350004_10350005</t>
-  </si>
-  <si>
     <t>10-20倍中奖概率增高</t>
   </si>
   <si>
@@ -214,24 +193,12 @@
     <t>触发金蛇招财模式概率提升</t>
   </si>
   <si>
-    <t>1,10350007</t>
-  </si>
-  <si>
     <t>金蛇招财模式10倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>1,10350008</t>
-  </si>
-  <si>
     <t>金蛇招财模式20倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>5,10350010</t>
-  </si>
-  <si>
-    <t>1,10170003_10170004|2,10170005</t>
-  </si>
-  <si>
     <t>5-15倍中奖概率增高</t>
   </si>
   <si>
@@ -244,91 +211,31 @@
     <t>触发免费财模式概率提升</t>
   </si>
   <si>
-    <t>1,10170007</t>
-  </si>
-  <si>
     <t>免费模式20倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>1,10170008</t>
-  </si>
-  <si>
     <t>免费模式40倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>1,10170009</t>
-  </si>
-  <si>
     <t>免费模式100倍以上大奖概率提升</t>
   </si>
   <si>
     <t>触发奖池概率提升</t>
   </si>
   <si>
-    <t>5,10170011</t>
-  </si>
-  <si>
-    <t>1,10180003</t>
-  </si>
-  <si>
-    <t>1,10180004</t>
-  </si>
-  <si>
-    <t>1,10180005</t>
-  </si>
-  <si>
-    <t>1,10180007</t>
-  </si>
-  <si>
-    <t>1,10180008</t>
-  </si>
-  <si>
     <t>免费模式80倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>1,10180009</t>
-  </si>
-  <si>
     <t>免费模式160倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>5,10180011</t>
-  </si>
-  <si>
-    <t>1,10210003</t>
-  </si>
-  <si>
-    <t>1,10210004</t>
-  </si>
-  <si>
-    <t>1,10210005</t>
-  </si>
-  <si>
-    <t>1,10210007</t>
-  </si>
-  <si>
-    <t>1,10210008</t>
-  </si>
-  <si>
-    <t>1,10210009</t>
-  </si>
-  <si>
     <t>触发bonus小游戏概率提升</t>
   </si>
   <si>
-    <t>1,10210011</t>
-  </si>
-  <si>
     <t>bonus小游戏20-40倍奖励概率提升</t>
   </si>
   <si>
-    <t>1,10210012</t>
-  </si>
-  <si>
     <t>bonus小游戏40倍以上概率提升</t>
-  </si>
-  <si>
-    <t>5,10210014</t>
   </si>
 </sst>
 </file>
@@ -984,12 +891,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1311,7 +1212,8 @@
     <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.875" style="2" customWidth="1"/>
     <col min="5" max="6" width="26.875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1399,9 +1301,6 @@
         <v>4020003</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1">
@@ -1411,14 +1310,14 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2">
         <v>4020004</v>
       </c>
       <c r="E7" s="7"/>
-      <c r="F7" s="8" t="s">
-        <v>17</v>
+      <c r="F7" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1429,10 +1328,13 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2">
         <v>4020005</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1474,10 +1376,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="2">
-        <v>4020008</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>22</v>
+        <v>4020009</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1488,12 +1387,14 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2">
-        <v>4020009</v>
-      </c>
-      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1">
@@ -1519,11 +1420,8 @@
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="2"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1">
@@ -1533,13 +1431,10 @@
         <v>103400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>15</v>
+      </c>
       <c r="E15" s="7"/>
-      <c r="F15" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1">
@@ -1549,7 +1444,7 @@
         <v>103400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1560,7 +1455,7 @@
         <v>103400</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1571,13 +1466,10 @@
         <v>103400</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>26</v>
+      </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
@@ -1587,13 +1479,10 @@
         <v>103400</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="2"/>
+        <v>27</v>
+      </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
@@ -1603,7 +1492,7 @@
         <v>103400</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1614,7 +1503,7 @@
         <v>103400</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1625,7 +1514,7 @@
         <v>103400</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1636,11 +1525,9 @@
         <v>103400</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>34</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1">
@@ -1650,7 +1537,7 @@
         <v>103500</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -1664,13 +1551,10 @@
         <v>103500</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="2"/>
+        <v>31</v>
+      </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
@@ -1680,13 +1564,10 @@
         <v>103500</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>32</v>
+      </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
@@ -1696,7 +1577,7 @@
         <v>103500</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1707,7 +1588,7 @@
         <v>103500</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1718,13 +1599,10 @@
         <v>103500</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>35</v>
+      </c>
       <c r="E29" s="7"/>
-      <c r="F29" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
@@ -1734,13 +1612,10 @@
         <v>103500</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="2"/>
+        <v>36</v>
+      </c>
       <c r="E30" s="7"/>
-      <c r="F30" s="8" t="s">
-        <v>45</v>
-      </c>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
@@ -1750,7 +1625,7 @@
         <v>103500</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1761,7 +1636,7 @@
         <v>103500</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1772,7 +1647,7 @@
         <v>103500</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1783,11 +1658,9 @@
         <v>103500</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>47</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
@@ -1797,7 +1670,7 @@
         <v>101700</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -1811,13 +1684,10 @@
         <v>101700</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>31</v>
+      </c>
       <c r="E36" s="7"/>
-      <c r="F36" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
@@ -1827,7 +1697,7 @@
         <v>101700</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1838,7 +1708,7 @@
         <v>101700</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1849,7 +1719,7 @@
         <v>101700</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1860,10 +1730,7 @@
         <v>101700</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1874,10 +1741,7 @@
         <v>101700</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1888,10 +1752,7 @@
         <v>101700</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1902,7 +1763,7 @@
         <v>101700</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1913,7 +1774,7 @@
         <v>101700</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1924,11 +1785,9 @@
         <v>101700</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>60</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F45" s="7"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
@@ -1938,7 +1797,7 @@
         <v>101700</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1949,7 +1808,7 @@
         <v>101800</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -1963,10 +1822,7 @@
         <v>101800</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1977,10 +1833,7 @@
         <v>101800</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1991,10 +1844,7 @@
         <v>101800</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2005,7 +1855,7 @@
         <v>101800</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2016,10 +1866,7 @@
         <v>101800</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2030,10 +1877,7 @@
         <v>101800</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2044,10 +1888,7 @@
         <v>101800</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2058,7 +1899,7 @@
         <v>101800</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2069,7 +1910,7 @@
         <v>101800</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2080,7 +1921,7 @@
         <v>101800</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2091,11 +1932,9 @@
         <v>101800</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>69</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F58" s="7"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1">
@@ -2105,7 +1944,7 @@
         <v>102100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -2119,10 +1958,7 @@
         <v>102100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2133,10 +1969,7 @@
         <v>102100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2147,10 +1980,7 @@
         <v>102100</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2161,7 +1991,7 @@
         <v>102100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2172,10 +2002,7 @@
         <v>102100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2186,10 +2013,7 @@
         <v>102100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2200,10 +2024,7 @@
         <v>102100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2214,7 +2035,7 @@
         <v>102100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2225,10 +2046,7 @@
         <v>102100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2239,10 +2057,7 @@
         <v>102100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2253,7 +2068,7 @@
         <v>102100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2264,7 +2079,7 @@
         <v>102100</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2275,7 +2090,7 @@
         <v>102100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2286,11 +2101,9 @@
         <v>102100</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>81</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F73" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -151,10 +151,10 @@
     <t>快速旋转</t>
   </si>
   <si>
+    <t>10030008,5</t>
+  </si>
+  <si>
     <t>自动旋转次数</t>
-  </si>
-  <si>
-    <t>10030007,5</t>
   </si>
   <si>
     <t>常规10-25中奖概率提升</t>
@@ -1378,6 +1378,9 @@
       <c r="D11" s="2">
         <v>4020009</v>
       </c>
+      <c r="F11" s="7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1">
@@ -1387,14 +1390,12 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2">
         <v>4020008</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1">
@@ -1514,7 +1515,7 @@
         <v>103400</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1647,7 +1648,7 @@
         <v>103500</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1785,7 +1786,7 @@
         <v>101700</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F45" s="7"/>
     </row>
@@ -1921,7 +1922,7 @@
         <v>101800</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2090,7 +2091,7 @@
         <v>102100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6">

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="59">
   <si>
     <t>属性id</t>
   </si>
@@ -97,6 +97,9 @@
     <t>多语言id</t>
   </si>
   <si>
+    <t>属性图标</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>Map&lt;int{,}int&gt;{|}</t>
   </si>
   <si>
@@ -118,6 +124,9 @@
     <t>languageID</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -127,9 +136,15 @@
     <t>金额解锁</t>
   </si>
   <si>
+    <t>yjy_jmtb_4.png</t>
+  </si>
+  <si>
     <t>中奖概率提升</t>
   </si>
   <si>
+    <t>yjy_jmtb_5.png</t>
+  </si>
+  <si>
     <t>常规5-10中奖概率提升</t>
   </si>
   <si>
@@ -145,10 +160,19 @@
     <t>中樱桃符号概率提升</t>
   </si>
   <si>
+    <t>yjy_jmtb_2.png</t>
+  </si>
+  <si>
     <t>触发jackpot概率提升</t>
   </si>
   <si>
+    <t>yjy_jmtb_3.png</t>
+  </si>
+  <si>
     <t>快速旋转</t>
+  </si>
+  <si>
+    <t>yjy_jmtb_1.png</t>
   </si>
   <si>
     <t>10030008,5</t>
@@ -868,7 +892,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -882,6 +906,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1204,19 +1231,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.875" style="2" customWidth="1"/>
-    <col min="5" max="6" width="26.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="5" max="7" width="26.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1235,42 +1262,51 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
@@ -1278,16 +1314,19 @@
         <v>100300</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>4020002</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
@@ -1295,14 +1334,17 @@
         <v>100300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>4020003</v>
       </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
@@ -1310,17 +1352,20 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>4020004</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
@@ -1328,16 +1373,19 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2">
         <v>4020005</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
@@ -1345,13 +1393,16 @@
         <v>100300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
         <v>4020006</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
@@ -1359,13 +1410,16 @@
         <v>100300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2">
         <v>4020007</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>10030007</v>
       </c>
@@ -1373,16 +1427,19 @@
         <v>100300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2">
         <v>4020009</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10030008</v>
       </c>
@@ -1390,14 +1447,17 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2">
         <v>4020008</v>
       </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="E12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>10340001</v>
       </c>
@@ -1405,13 +1465,13 @@
         <v>103400</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="1">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>10340002</v>
       </c>
@@ -1419,12 +1479,13 @@
         <v>103400</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>10340003</v>
       </c>
@@ -1432,12 +1493,13 @@
         <v>103400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6">
+        <v>20</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>10340004</v>
       </c>
@@ -1445,10 +1507,10 @@
         <v>103400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>10340005</v>
       </c>
@@ -1456,10 +1518,10 @@
         <v>103400</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>10340006</v>
       </c>
@@ -1467,12 +1529,13 @@
         <v>103400</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6">
+        <v>34</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>10340007</v>
       </c>
@@ -1480,12 +1543,13 @@
         <v>103400</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6">
+        <v>35</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>10340008</v>
       </c>
@@ -1493,10 +1557,10 @@
         <v>103400</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>10340009</v>
       </c>
@@ -1504,10 +1568,10 @@
         <v>103400</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>10340010</v>
       </c>
@@ -1515,10 +1579,10 @@
         <v>103400</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>10340011</v>
       </c>
@@ -1526,11 +1590,11 @@
         <v>103400</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6">
+        <v>28</v>
+      </c>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>10350001</v>
       </c>
@@ -1538,13 +1602,13 @@
         <v>103500</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="1">
+        <v>38</v>
+      </c>
+      <c r="F24" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>10350002</v>
       </c>
@@ -1552,12 +1616,13 @@
         <v>103500</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6">
+        <v>39</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>10350003</v>
       </c>
@@ -1565,12 +1630,13 @@
         <v>103500</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6">
+        <v>40</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>10350004</v>
       </c>
@@ -1578,10 +1644,10 @@
         <v>103500</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>10350005</v>
       </c>
@@ -1589,10 +1655,10 @@
         <v>103500</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>10350006</v>
       </c>
@@ -1600,12 +1666,13 @@
         <v>103500</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6">
+        <v>43</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>10350007</v>
       </c>
@@ -1613,12 +1680,13 @@
         <v>103500</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6">
+        <v>44</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>10350008</v>
       </c>
@@ -1626,10 +1694,10 @@
         <v>103500</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>10350009</v>
       </c>
@@ -1637,10 +1705,10 @@
         <v>103500</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>10350010</v>
       </c>
@@ -1648,10 +1716,10 @@
         <v>103500</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>10350011</v>
       </c>
@@ -1659,11 +1727,11 @@
         <v>103500</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6">
+        <v>28</v>
+      </c>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>10170001</v>
       </c>
@@ -1671,13 +1739,13 @@
         <v>101700</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1">
+        <v>38</v>
+      </c>
+      <c r="F35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>10170002</v>
       </c>
@@ -1685,12 +1753,13 @@
         <v>101700</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6">
+        <v>39</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>10170003</v>
       </c>
@@ -1698,10 +1767,10 @@
         <v>101700</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>10170004</v>
       </c>
@@ -1709,10 +1778,10 @@
         <v>101700</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>10170005</v>
       </c>
@@ -1720,10 +1789,10 @@
         <v>101700</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>10170006</v>
       </c>
@@ -1731,10 +1800,10 @@
         <v>101700</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>10170007</v>
       </c>
@@ -1742,10 +1811,10 @@
         <v>101700</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>10170008</v>
       </c>
@@ -1753,10 +1822,10 @@
         <v>101700</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>10170009</v>
       </c>
@@ -1764,10 +1833,10 @@
         <v>101700</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>10170010</v>
       </c>
@@ -1775,10 +1844,10 @@
         <v>101700</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>10170011</v>
       </c>
@@ -1786,11 +1855,11 @@
         <v>101700</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6">
+        <v>31</v>
+      </c>
+      <c r="G45" s="8"/>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>10170012</v>
       </c>
@@ -1798,10 +1867,10 @@
         <v>101700</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>10180001</v>
       </c>
@@ -1809,13 +1878,13 @@
         <v>101800</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E47" s="1">
+        <v>38</v>
+      </c>
+      <c r="F47" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>10180002</v>
       </c>
@@ -1823,10 +1892,10 @@
         <v>101800</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>10180003</v>
       </c>
@@ -1834,10 +1903,10 @@
         <v>101800</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>10180004</v>
       </c>
@@ -1845,10 +1914,10 @@
         <v>101800</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>10180005</v>
       </c>
@@ -1856,10 +1925,10 @@
         <v>101800</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>10180006</v>
       </c>
@@ -1867,10 +1936,10 @@
         <v>101800</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>10180007</v>
       </c>
@@ -1878,10 +1947,10 @@
         <v>101800</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>10180008</v>
       </c>
@@ -1889,10 +1958,10 @@
         <v>101800</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>10180009</v>
       </c>
@@ -1900,10 +1969,10 @@
         <v>101800</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>10180010</v>
       </c>
@@ -1911,10 +1980,10 @@
         <v>101800</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>10180011</v>
       </c>
@@ -1922,10 +1991,10 @@
         <v>101800</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>10180012</v>
       </c>
@@ -1933,11 +2002,11 @@
         <v>101800</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" s="7"/>
-    </row>
-    <row r="59" spans="1:6">
+        <v>28</v>
+      </c>
+      <c r="G58" s="8"/>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>10210001</v>
       </c>
@@ -1945,13 +2014,13 @@
         <v>102100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" s="1">
+        <v>38</v>
+      </c>
+      <c r="F59" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>10210002</v>
       </c>
@@ -1959,10 +2028,10 @@
         <v>102100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <v>10210003</v>
       </c>
@@ -1970,10 +2039,10 @@
         <v>102100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="1">
         <v>10210004</v>
       </c>
@@ -1981,10 +2050,10 @@
         <v>102100</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="1">
         <v>10210005</v>
       </c>
@@ -1992,10 +2061,10 @@
         <v>102100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="1">
         <v>10210006</v>
       </c>
@@ -2003,10 +2072,10 @@
         <v>102100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="1">
         <v>10210007</v>
       </c>
@@ -2014,10 +2083,10 @@
         <v>102100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="1">
         <v>10210008</v>
       </c>
@@ -2025,10 +2094,10 @@
         <v>102100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <v>10210009</v>
       </c>
@@ -2036,10 +2105,10 @@
         <v>102100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="1">
         <v>10210010</v>
       </c>
@@ -2047,10 +2116,10 @@
         <v>102100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="1">
         <v>10210011</v>
       </c>
@@ -2058,10 +2127,10 @@
         <v>102100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="1">
         <v>10210012</v>
       </c>
@@ -2069,10 +2138,10 @@
         <v>102100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="1">
         <v>10210013</v>
       </c>
@@ -2080,10 +2149,10 @@
         <v>102100</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="1">
         <v>10210014</v>
       </c>
@@ -2091,10 +2160,10 @@
         <v>102100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="1">
         <v>10210015</v>
       </c>
@@ -2102,9 +2171,9 @@
         <v>102100</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F73" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="G73" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
   <si>
     <t>属性id</t>
   </si>
@@ -181,24 +181,69 @@
     <t>自动旋转次数</t>
   </si>
   <si>
+    <t>10340002,1</t>
+  </si>
+  <si>
     <t>常规10-25中奖概率提升</t>
   </si>
   <si>
+    <t>10340003,1</t>
+  </si>
+  <si>
     <t>常规25倍以上中奖概率提升</t>
   </si>
   <si>
+    <t>10340004,1</t>
+  </si>
+  <si>
     <t>触发福马模式概率提升</t>
   </si>
   <si>
     <t>福马模式10倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>10340006,1</t>
+  </si>
+  <si>
     <t>福马模式20倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>10340007,1</t>
+  </si>
+  <si>
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
+    <t>10340010,5</t>
+  </si>
+  <si>
+    <t>10340102,1</t>
+  </si>
+  <si>
+    <t>10340103,1</t>
+  </si>
+  <si>
+    <t>10340104,1</t>
+  </si>
+  <si>
+    <t>触发虎虎生财模式概率提升</t>
+  </si>
+  <si>
+    <t>虎虎生财模式10倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10340106,1</t>
+  </si>
+  <si>
+    <t>虎虎生财模式20倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10340107,1</t>
+  </si>
+  <si>
+    <t>10340110,5</t>
+  </si>
+  <si>
     <t>下注金额增加</t>
   </si>
   <si>
@@ -208,58 +253,103 @@
     <t>5-10倍中奖概率增高</t>
   </si>
   <si>
+    <t>10350002,1</t>
+  </si>
+  <si>
     <t>10-20倍中奖概率增高</t>
   </si>
   <si>
+    <t>10350003,1</t>
+  </si>
+  <si>
     <t>20倍以上中奖概率增高</t>
   </si>
   <si>
+    <t>10350004,1</t>
+  </si>
+  <si>
     <t>触发金蛇招财模式概率提升</t>
   </si>
   <si>
     <t>金蛇招财模式10倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>10350006,1</t>
+  </si>
+  <si>
     <t>金蛇招财模式20倍以上大奖概率提升</t>
   </si>
   <si>
-    <t>5-15倍中奖概率增高</t>
-  </si>
-  <si>
-    <t>15-30倍中奖概率增高</t>
-  </si>
-  <si>
-    <t>30倍以上中奖概率增高</t>
-  </si>
-  <si>
-    <t>触发免费财模式概率提升</t>
-  </si>
-  <si>
-    <t>免费模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>免费模式40倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>免费模式100倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>触发奖池概率提升</t>
-  </si>
-  <si>
-    <t>免费模式80倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>免费模式160倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>触发bonus小游戏概率提升</t>
-  </si>
-  <si>
-    <t>bonus小游戏20-40倍奖励概率提升</t>
-  </si>
-  <si>
-    <t>bonus小游戏40倍以上概率提升</t>
+    <t>10350007,1</t>
+  </si>
+  <si>
+    <t>10350010,5</t>
+  </si>
+  <si>
+    <t>10350102,1</t>
+  </si>
+  <si>
+    <t>10350103,1</t>
+  </si>
+  <si>
+    <t>10350104,1</t>
+  </si>
+  <si>
+    <t>触发金钱兔模式概率提升</t>
+  </si>
+  <si>
+    <t>金钱兔模式10倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10350106,1</t>
+  </si>
+  <si>
+    <t>金钱兔模式20倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10350107,1</t>
+  </si>
+  <si>
+    <t>10350110,5</t>
+  </si>
+  <si>
+    <t>10140002,1</t>
+  </si>
+  <si>
+    <t>10140003,1</t>
+  </si>
+  <si>
+    <t>10140004,1</t>
+  </si>
+  <si>
+    <t>10140010,5</t>
+  </si>
+  <si>
+    <t>10370002,1</t>
+  </si>
+  <si>
+    <t>10370003,1</t>
+  </si>
+  <si>
+    <t>10370004,1</t>
+  </si>
+  <si>
+    <t>触发福牛模式概率提升</t>
+  </si>
+  <si>
+    <t>福牛模式模式10倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10370006,1</t>
+  </si>
+  <si>
+    <t>福牛模式模式20倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10370007,1</t>
+  </si>
+  <si>
+    <t>10370010,5</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
@@ -1467,6 +1557,12 @@
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="D13" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
@@ -1481,7 +1577,12 @@
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="D14" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
     </row>
@@ -1495,9 +1596,16 @@
       <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="D15" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="G15" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
@@ -1507,7 +1615,16 @@
         <v>103400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4020094</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1518,7 +1635,16 @@
         <v>103400</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4020095</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1529,9 +1655,14 @@
         <v>103400</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4020096</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
@@ -1543,11 +1674,18 @@
         <v>103400</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="D19" s="2">
+        <v>4020097</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="G19" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
@@ -1557,7 +1695,16 @@
         <v>103400</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4020098</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1568,7 +1715,13 @@
         <v>103400</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1581,6 +1734,12 @@
       <c r="C22" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="D22" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1">
@@ -1592,17 +1751,31 @@
       <c r="C23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="8"/>
+      <c r="D23" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1">
-        <v>10350001</v>
+        <v>10340101</v>
       </c>
       <c r="B24" s="1">
-        <v>103500</v>
+        <v>103401</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="D24" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -1610,136 +1783,213 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1">
-        <v>10350002</v>
+        <v>10340102</v>
       </c>
       <c r="B25" s="1">
-        <v>103500</v>
+        <v>103402</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="D25" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1">
-        <v>10350003</v>
+        <v>10340103</v>
       </c>
       <c r="B26" s="1">
-        <v>103500</v>
+        <v>103403</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="D26" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1">
-        <v>10350004</v>
+        <v>10340104</v>
       </c>
       <c r="B27" s="1">
-        <v>103500</v>
+        <v>103404</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4020094</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1">
-        <v>10350005</v>
+        <v>10340105</v>
       </c>
       <c r="B28" s="1">
-        <v>103500</v>
+        <v>103405</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="D28" s="2">
+        <v>4020095</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1">
-        <v>10350006</v>
+        <v>10340106</v>
       </c>
       <c r="B29" s="1">
-        <v>103500</v>
+        <v>103406</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="D29" s="2">
+        <v>4020149</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1">
-        <v>10350007</v>
+        <v>10340107</v>
       </c>
       <c r="B30" s="1">
-        <v>103500</v>
+        <v>103407</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4020150</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="G30" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1">
-        <v>10350008</v>
+        <v>10340108</v>
       </c>
       <c r="B31" s="1">
-        <v>103500</v>
+        <v>103408</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4020151</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
-        <v>10350009</v>
+        <v>10340109</v>
       </c>
       <c r="B32" s="1">
-        <v>103500</v>
+        <v>103409</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">
-        <v>10350010</v>
+        <v>10340110</v>
       </c>
       <c r="B33" s="1">
-        <v>103500</v>
+        <v>103410</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="D33" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1">
-        <v>10350011</v>
+        <v>10340111</v>
       </c>
       <c r="B34" s="1">
-        <v>103500</v>
+        <v>103411</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="8"/>
+      <c r="D34" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <v>10170001</v>
+        <v>10350001</v>
       </c>
       <c r="B35" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
+      </c>
+      <c r="D35" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F35" s="1">
         <v>1</v>
@@ -1747,433 +1997,786 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <v>10170002</v>
+        <v>10350002</v>
       </c>
       <c r="B36" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="8"/>
+        <v>54</v>
+      </c>
+      <c r="D36" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <v>10170003</v>
+        <v>10350003</v>
       </c>
       <c r="B37" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
+      </c>
+      <c r="D37" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="8"/>
+      <c r="G37" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <v>10170004</v>
+        <v>10350004</v>
       </c>
       <c r="B38" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="D38" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <v>10170005</v>
+        <v>10350005</v>
       </c>
       <c r="B39" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
+      </c>
+      <c r="D39" s="2">
+        <v>4020202</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <v>10170006</v>
+        <v>10350006</v>
       </c>
       <c r="B40" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4020203</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <v>10170007</v>
+        <v>10350007</v>
       </c>
       <c r="B41" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4020204</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <v>10170008</v>
+        <v>10350008</v>
       </c>
       <c r="B42" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="D42" s="2">
+        <v>4020205</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <v>10170009</v>
+        <v>10350009</v>
       </c>
       <c r="B43" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <v>10170010</v>
+        <v>10350010</v>
       </c>
       <c r="B44" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
+      </c>
+      <c r="D44" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <v>10170011</v>
+        <v>10350011</v>
       </c>
       <c r="B45" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G45" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="D45" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <v>10170012</v>
+        <v>10350101</v>
       </c>
       <c r="B46" s="1">
-        <v>101700</v>
+        <v>103501</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>28</v>
+        <v>53</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <v>10180001</v>
+        <v>10350102</v>
       </c>
       <c r="B47" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" s="1">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D47" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <v>10180002</v>
+        <v>10350103</v>
       </c>
       <c r="B48" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
+      </c>
+      <c r="D48" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <v>10180003</v>
+        <v>10350104</v>
       </c>
       <c r="B49" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="D49" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1">
-        <v>10180004</v>
+        <v>10350105</v>
       </c>
       <c r="B50" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
+      </c>
+      <c r="D50" s="2">
+        <v>4020202</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1">
-        <v>10180005</v>
+        <v>10350106</v>
       </c>
       <c r="B51" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4020246</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1">
-        <v>10180006</v>
+        <v>10350107</v>
       </c>
       <c r="B52" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>49</v>
+        <v>71</v>
+      </c>
+      <c r="D52" s="2">
+        <v>4020247</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="8"/>
+      <c r="G52" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="1">
-        <v>10180007</v>
+        <v>10350108</v>
       </c>
       <c r="B53" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
+      </c>
+      <c r="D53" s="2">
+        <v>4020248</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1">
-        <v>10180008</v>
+        <v>10350109</v>
       </c>
       <c r="B54" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
+      </c>
+      <c r="D54" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="1">
-        <v>10180009</v>
+        <v>10350110</v>
       </c>
       <c r="B55" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
+      </c>
+      <c r="D55" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1">
-        <v>10180010</v>
+        <v>10350111</v>
       </c>
       <c r="B56" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
+      </c>
+      <c r="D56" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="1">
-        <v>10180011</v>
+        <v>10140001</v>
       </c>
       <c r="B57" s="1">
-        <v>101800</v>
+        <v>101400</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
+      </c>
+      <c r="D57" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1">
-        <v>10180012</v>
+        <v>10140002</v>
       </c>
       <c r="B58" s="1">
-        <v>101800</v>
+        <v>101400</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D58" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="8"/>
       <c r="G58" s="8"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="1">
-        <v>10210001</v>
+        <v>10140003</v>
       </c>
       <c r="B59" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59" s="1">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="D59" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="8"/>
+      <c r="G59" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1">
-        <v>10210002</v>
+        <v>10140004</v>
       </c>
       <c r="B60" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>39</v>
+        <v>57</v>
+      </c>
+      <c r="D60" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="1">
-        <v>10210003</v>
+        <v>10140005</v>
       </c>
       <c r="B61" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
+      </c>
+      <c r="D61" s="2">
+        <v>4020202</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1">
-        <v>10210004</v>
+        <v>10140006</v>
       </c>
       <c r="B62" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="D62" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="1">
-        <v>10210005</v>
+        <v>10140007</v>
       </c>
       <c r="B63" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="D63" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="1">
-        <v>10210006</v>
+        <v>10140008</v>
       </c>
       <c r="B64" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="D64" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
-        <v>10210007</v>
+        <v>10370001</v>
       </c>
       <c r="B65" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="D65" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
-        <v>10210008</v>
+        <v>10370002</v>
       </c>
       <c r="B66" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="D66" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
-        <v>10210009</v>
+        <v>10370003</v>
       </c>
       <c r="B67" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="D67" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="8"/>
+      <c r="G67" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
-        <v>10210010</v>
+        <v>10370004</v>
       </c>
       <c r="B68" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="D68" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
-        <v>10210011</v>
+        <v>10370005</v>
       </c>
       <c r="B69" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="D69" s="2">
+        <v>4020202</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
-        <v>10210012</v>
+        <v>10370006</v>
       </c>
       <c r="B70" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>58</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D70" s="2">
+        <v>4020279</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
-        <v>10210013</v>
+        <v>10370007</v>
       </c>
       <c r="B71" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
+      </c>
+      <c r="D71" s="2">
+        <v>4020280</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="8"/>
+      <c r="G71" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
-        <v>10210014</v>
+        <v>10370008</v>
       </c>
       <c r="B72" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>31</v>
+        <v>86</v>
+      </c>
+      <c r="D72" s="2">
+        <v>4020281</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
-        <v>10210015</v>
+        <v>10370009</v>
       </c>
       <c r="B73" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="1">
+        <v>10370010</v>
+      </c>
+      <c r="B74" s="1">
+        <v>103700</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="1">
+        <v>10370011</v>
+      </c>
+      <c r="B75" s="1">
+        <v>103700</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G73" s="8"/>
+      <c r="D75" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="G80" s="8"/>
+    </row>
+    <row r="95" spans="7:7">
+      <c r="G95" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="121">
   <si>
     <t>属性id</t>
   </si>
@@ -325,12 +325,21 @@
     <t>10140010,5</t>
   </si>
   <si>
+    <t>5-10倍中奖概率提升</t>
+  </si>
+  <si>
     <t>10370002,1</t>
   </si>
   <si>
+    <t>10-20倍中奖概率提升</t>
+  </si>
+  <si>
     <t>10370003,1</t>
   </si>
   <si>
+    <t>20倍以上中奖概率提升</t>
+  </si>
+  <si>
     <t>10370004,1</t>
   </si>
   <si>
@@ -350,6 +359,93 @@
   </si>
   <si>
     <t>10370010,5</t>
+  </si>
+  <si>
+    <t>10360002,1</t>
+  </si>
+  <si>
+    <t>10360003,1</t>
+  </si>
+  <si>
+    <t>10360004,1</t>
+  </si>
+  <si>
+    <t>触发福鼠模式概率提升</t>
+  </si>
+  <si>
+    <t>福鼠模式模式10倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10360006,1</t>
+  </si>
+  <si>
+    <t>福鼠模式模式20倍以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10360007,1</t>
+  </si>
+  <si>
+    <t>10360010,5</t>
+  </si>
+  <si>
+    <t>10070002,1</t>
+  </si>
+  <si>
+    <t>10-25倍中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070003,1</t>
+  </si>
+  <si>
+    <t>25-50倍中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070004,1</t>
+  </si>
+  <si>
+    <t>50倍及以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070005,1</t>
+  </si>
+  <si>
+    <t>触发免费模式概率提升</t>
+  </si>
+  <si>
+    <t>免费模式50倍及以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10070007,1</t>
+  </si>
+  <si>
+    <t>免费模式100倍及以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10070008,1</t>
+  </si>
+  <si>
+    <t>10070010,5</t>
+  </si>
+  <si>
+    <t>10170002,1</t>
+  </si>
+  <si>
+    <t>10170003,1</t>
+  </si>
+  <si>
+    <t>10170004,1</t>
+  </si>
+  <si>
+    <t>10170005,1</t>
+  </si>
+  <si>
+    <t>10170007,1</t>
+  </si>
+  <si>
+    <t>10170008,1</t>
+  </si>
+  <si>
+    <t>10170011,5</t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1417,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
@@ -2604,7 +2700,7 @@
         <v>103700</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D67" s="2">
         <v>4020004</v>
@@ -2614,7 +2710,7 @@
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2625,7 +2721,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D68" s="2">
         <v>4020005</v>
@@ -2634,7 +2730,7 @@
         <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2645,7 +2741,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="D69" s="2">
         <v>4020202</v>
@@ -2653,9 +2749,8 @@
       <c r="E69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F69" s="1"/>
       <c r="G69" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2666,7 +2761,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D70" s="2">
         <v>4020279</v>
@@ -2685,7 +2780,7 @@
         <v>103700</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D71" s="2">
         <v>4020280</v>
@@ -2695,7 +2790,7 @@
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2706,7 +2801,7 @@
         <v>103700</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D72" s="2">
         <v>4020281</v>
@@ -2715,7 +2810,7 @@
         <v>25</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2769,14 +2864,663 @@
         <v>29</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="1">
+        <v>10360001</v>
+      </c>
+      <c r="B76" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D76" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="1">
+        <v>10360002</v>
+      </c>
+      <c r="B77" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D77" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="1">
+        <v>10360003</v>
+      </c>
+      <c r="B78" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="8"/>
+      <c r="G78" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="1">
+        <v>10360004</v>
+      </c>
+      <c r="B79" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="G80" s="8"/>
-    </row>
-    <row r="95" spans="7:7">
-      <c r="G95" s="8"/>
+      <c r="A80" s="1">
+        <v>10360005</v>
+      </c>
+      <c r="B80" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" s="2">
+        <v>4020202</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="1">
+        <v>10360006</v>
+      </c>
+      <c r="B81" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81" s="2">
+        <v>4020312</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="1">
+        <v>10360007</v>
+      </c>
+      <c r="B82" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D82" s="2">
+        <v>4020313</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="8"/>
+      <c r="G82" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="1">
+        <v>10360008</v>
+      </c>
+      <c r="B83" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D83" s="2">
+        <v>4020314</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="1">
+        <v>10360009</v>
+      </c>
+      <c r="B84" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="1">
+        <v>10360010</v>
+      </c>
+      <c r="B85" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D85" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="1">
+        <v>10360011</v>
+      </c>
+      <c r="B86" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="1">
+        <v>10070001</v>
+      </c>
+      <c r="B87" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D87" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="1">
+        <v>10070002</v>
+      </c>
+      <c r="B88" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="8"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="1">
+        <v>10070003</v>
+      </c>
+      <c r="B89" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D89" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="1">
+        <v>10070004</v>
+      </c>
+      <c r="B90" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D90" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="1">
+        <v>10070005</v>
+      </c>
+      <c r="B91" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" s="2">
+        <v>4020345</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="1">
+        <v>10070006</v>
+      </c>
+      <c r="B92" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D92" s="2">
+        <v>4020346</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="1">
+        <v>10070007</v>
+      </c>
+      <c r="B93" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D93" s="2">
+        <v>4020347</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="1">
+        <v>10070008</v>
+      </c>
+      <c r="B94" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D94" s="2">
+        <v>4020349</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="1">
+        <v>10070009</v>
+      </c>
+      <c r="B95" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="2">
+        <v>4020350</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="1">
+        <v>10070010</v>
+      </c>
+      <c r="B96" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="1">
+        <v>10070011</v>
+      </c>
+      <c r="B97" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="1">
+        <v>10170001</v>
+      </c>
+      <c r="B98" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D98" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="1">
+        <v>10170002</v>
+      </c>
+      <c r="B99" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D99" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" s="8"/>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="1">
+        <v>10170003</v>
+      </c>
+      <c r="B100" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D100" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="1">
+        <v>10170004</v>
+      </c>
+      <c r="B101" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" s="2">
+        <v>4020005</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="1">
+        <v>10170005</v>
+      </c>
+      <c r="B102" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="2">
+        <v>4020345</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="1">
+        <v>10170006</v>
+      </c>
+      <c r="B103" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D103" s="2">
+        <v>4020346</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="1">
+        <v>10170007</v>
+      </c>
+      <c r="B104" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D104" s="2">
+        <v>4020347</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="1">
+        <v>10170008</v>
+      </c>
+      <c r="B105" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D105" s="2">
+        <v>4020349</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="1">
+        <v>10170009</v>
+      </c>
+      <c r="B106" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D106" s="2">
+        <v>4020350</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="1">
+        <v>10170010</v>
+      </c>
+      <c r="B107" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D107" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="1">
+        <v>10170011</v>
+      </c>
+      <c r="B108" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D108" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="1">
+        <v>10170012</v>
+      </c>
+      <c r="B109" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D109" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -322,7 +322,7 @@
     <t>10140004,1</t>
   </si>
   <si>
-    <t>10140010,5</t>
+    <t>10140007,5</t>
   </si>
   <si>
     <t>5-10倍中奖概率提升</t>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -1882,7 +1882,7 @@
         <v>10340102</v>
       </c>
       <c r="B25" s="1">
-        <v>103402</v>
+        <v>103401</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
@@ -1901,7 +1901,7 @@
         <v>10340103</v>
       </c>
       <c r="B26" s="1">
-        <v>103403</v>
+        <v>103401</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -1922,7 +1922,7 @@
         <v>10340104</v>
       </c>
       <c r="B27" s="1">
-        <v>103404</v>
+        <v>103401</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>33</v>
@@ -1942,7 +1942,7 @@
         <v>10340105</v>
       </c>
       <c r="B28" s="1">
-        <v>103405</v>
+        <v>103401</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>35</v>
@@ -1962,7 +1962,7 @@
         <v>10340106</v>
       </c>
       <c r="B29" s="1">
-        <v>103406</v>
+        <v>103401</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>47</v>
@@ -1981,7 +1981,7 @@
         <v>10340107</v>
       </c>
       <c r="B30" s="1">
-        <v>103407</v>
+        <v>103401</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>48</v>
@@ -2002,7 +2002,7 @@
         <v>10340108</v>
       </c>
       <c r="B31" s="1">
-        <v>103408</v>
+        <v>103401</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>50</v>
@@ -2022,7 +2022,7 @@
         <v>10340109</v>
       </c>
       <c r="B32" s="1">
-        <v>103409</v>
+        <v>103401</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>42</v>
@@ -2039,7 +2039,7 @@
         <v>10340110</v>
       </c>
       <c r="B33" s="1">
-        <v>103410</v>
+        <v>103401</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>31</v>
@@ -2056,7 +2056,7 @@
         <v>10340111</v>
       </c>
       <c r="B34" s="1">
-        <v>103411</v>
+        <v>103401</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="128">
   <si>
     <t>属性id</t>
   </si>
@@ -446,6 +446,27 @@
   </si>
   <si>
     <t>10170011,5</t>
+  </si>
+  <si>
+    <t>10120002,1</t>
+  </si>
+  <si>
+    <t>10-25倍中奖概率增高</t>
+  </si>
+  <si>
+    <t>10120003,1</t>
+  </si>
+  <si>
+    <t>25倍以上中奖概率增高</t>
+  </si>
+  <si>
+    <t>10120004,1</t>
+  </si>
+  <si>
+    <t>财神到游戏概率提升</t>
+  </si>
+  <si>
+    <t>10120009,5</t>
   </si>
 </sst>
 </file>
@@ -1417,7 +1438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
@@ -3520,6 +3541,176 @@
       </c>
       <c r="G109" s="2" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="B110" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D110" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="B111" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D111" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" s="8"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="B112" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D112" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="8"/>
+      <c r="G112" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="B113" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D113" s="2">
+        <v>4020094</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="B114" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D114" s="2">
+        <v>4020095</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="B115" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D115" s="2">
+        <v>4020401</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="B116" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D116" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="1">
+        <v>10120008</v>
+      </c>
+      <c r="B117" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="B118" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D118" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="110">
   <si>
     <t>属性id</t>
   </si>
@@ -181,292 +181,238 @@
     <t>自动旋转次数</t>
   </si>
   <si>
-    <t>10340002,1</t>
-  </si>
-  <si>
-    <t>常规10-25中奖概率提升</t>
-  </si>
-  <si>
-    <t>10340003,1</t>
-  </si>
-  <si>
-    <t>常规25倍以上中奖概率提升</t>
-  </si>
-  <si>
-    <t>10340004,1</t>
-  </si>
-  <si>
-    <t>触发福马模式概率提升</t>
-  </si>
-  <si>
-    <t>福马模式10倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10340006,1</t>
-  </si>
-  <si>
-    <t>福马模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10340007,1</t>
+    <t>下注金额增加</t>
+  </si>
+  <si>
+    <t>中奖概率增高</t>
+  </si>
+  <si>
+    <t>5-10倍中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070002,1</t>
+  </si>
+  <si>
+    <t>10-25倍中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070003,1</t>
+  </si>
+  <si>
+    <t>25-50倍中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070004,1</t>
+  </si>
+  <si>
+    <t>50倍及以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10070005,1</t>
+  </si>
+  <si>
+    <t>触发免费模式概率提升</t>
+  </si>
+  <si>
+    <t>免费模式50倍及以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10070007,1</t>
+  </si>
+  <si>
+    <t>免费模式100倍及以上大奖概率提升</t>
+  </si>
+  <si>
+    <t>10070008,1</t>
+  </si>
+  <si>
+    <t>10070010,5</t>
+  </si>
+  <si>
+    <t>5-10倍中奖概率增高</t>
+  </si>
+  <si>
+    <t>10120002,1</t>
+  </si>
+  <si>
+    <t>10-25倍中奖概率增高</t>
+  </si>
+  <si>
+    <t>10120003,1</t>
+  </si>
+  <si>
+    <t>25倍以上中奖概率增高</t>
+  </si>
+  <si>
+    <t>10120004,1</t>
+  </si>
+  <si>
+    <t>财神到游戏概率提升</t>
   </si>
   <si>
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
-    <t>10340010,5</t>
-  </si>
-  <si>
-    <t>10340102,1</t>
-  </si>
-  <si>
-    <t>10340103,1</t>
-  </si>
-  <si>
-    <t>10340104,1</t>
-  </si>
-  <si>
-    <t>触发虎虎生财模式概率提升</t>
-  </si>
-  <si>
-    <t>虎虎生财模式10倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10340106,1</t>
-  </si>
-  <si>
-    <t>虎虎生财模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10340107,1</t>
-  </si>
-  <si>
-    <t>10340110,5</t>
-  </si>
-  <si>
-    <t>下注金额增加</t>
-  </si>
-  <si>
-    <t>中奖概率增高</t>
-  </si>
-  <si>
-    <t>5-10倍中奖概率增高</t>
-  </si>
-  <si>
-    <t>10350002,1</t>
-  </si>
-  <si>
-    <t>10-20倍中奖概率增高</t>
-  </si>
-  <si>
-    <t>10350003,1</t>
-  </si>
-  <si>
-    <t>20倍以上中奖概率增高</t>
-  </si>
-  <si>
-    <t>10350004,1</t>
-  </si>
-  <si>
-    <t>触发金蛇招财模式概率提升</t>
-  </si>
-  <si>
-    <t>金蛇招财模式10倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10350006,1</t>
-  </si>
-  <si>
-    <t>金蛇招财模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10350007,1</t>
-  </si>
-  <si>
-    <t>10350010,5</t>
-  </si>
-  <si>
-    <t>10350102,1</t>
-  </si>
-  <si>
-    <t>10350103,1</t>
-  </si>
-  <si>
-    <t>10350104,1</t>
-  </si>
-  <si>
-    <t>触发金钱兔模式概率提升</t>
-  </si>
-  <si>
-    <t>金钱兔模式10倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10350106,1</t>
-  </si>
-  <si>
-    <t>金钱兔模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10350107,1</t>
-  </si>
-  <si>
-    <t>10350110,5</t>
-  </si>
-  <si>
-    <t>10140002,1</t>
-  </si>
-  <si>
-    <t>10140003,1</t>
-  </si>
-  <si>
-    <t>10140004,1</t>
-  </si>
-  <si>
-    <t>10140007,5</t>
-  </si>
-  <si>
-    <t>5-10倍中奖概率提升</t>
-  </si>
-  <si>
-    <t>10370002,1</t>
-  </si>
-  <si>
-    <t>10-20倍中奖概率提升</t>
-  </si>
-  <si>
-    <t>10370003,1</t>
-  </si>
-  <si>
-    <t>20倍以上中奖概率提升</t>
-  </si>
-  <si>
-    <t>10370004,1</t>
-  </si>
-  <si>
-    <t>触发福牛模式概率提升</t>
-  </si>
-  <si>
-    <t>福牛模式模式10倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10370006,1</t>
-  </si>
-  <si>
-    <t>福牛模式模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10370007,1</t>
-  </si>
-  <si>
-    <t>10370010,5</t>
-  </si>
-  <si>
-    <t>10360002,1</t>
-  </si>
-  <si>
-    <t>10360003,1</t>
-  </si>
-  <si>
-    <t>10360004,1</t>
-  </si>
-  <si>
-    <t>触发福鼠模式概率提升</t>
-  </si>
-  <si>
-    <t>福鼠模式模式10倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10360006,1</t>
-  </si>
-  <si>
-    <t>福鼠模式模式20倍以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10360007,1</t>
-  </si>
-  <si>
-    <t>10360010,5</t>
-  </si>
-  <si>
-    <t>10070002,1</t>
-  </si>
-  <si>
-    <t>10-25倍中奖概率提升</t>
-  </si>
-  <si>
-    <t>10070003,1</t>
-  </si>
-  <si>
-    <t>25-50倍中奖概率提升</t>
-  </si>
-  <si>
-    <t>10070004,1</t>
-  </si>
-  <si>
-    <t>50倍及以上中奖概率提升</t>
-  </si>
-  <si>
-    <t>10070005,1</t>
-  </si>
-  <si>
-    <t>触发免费模式概率提升</t>
-  </si>
-  <si>
-    <t>免费模式50倍及以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10070007,1</t>
-  </si>
-  <si>
-    <t>免费模式100倍及以上大奖概率提升</t>
-  </si>
-  <si>
-    <t>10070008,1</t>
-  </si>
-  <si>
-    <t>10070010,5</t>
-  </si>
-  <si>
-    <t>10170002,1</t>
-  </si>
-  <si>
-    <t>10170003,1</t>
-  </si>
-  <si>
-    <t>10170004,1</t>
-  </si>
-  <si>
-    <t>10170005,1</t>
-  </si>
-  <si>
-    <t>10170007,1</t>
-  </si>
-  <si>
-    <t>10170008,1</t>
-  </si>
-  <si>
-    <t>10170011,5</t>
-  </si>
-  <si>
-    <t>10120002,1</t>
-  </si>
-  <si>
-    <t>10-25倍中奖概率增高</t>
-  </si>
-  <si>
-    <t>10120003,1</t>
-  </si>
-  <si>
-    <t>25倍以上中奖概率增高</t>
-  </si>
-  <si>
-    <t>10120004,1</t>
-  </si>
-  <si>
-    <t>财神到游戏概率提升</t>
-  </si>
-  <si>
     <t>10120009,5</t>
+  </si>
+  <si>
+    <t>10180002,1</t>
+  </si>
+  <si>
+    <t>10180003,1</t>
+  </si>
+  <si>
+    <t>10180004,1</t>
+  </si>
+  <si>
+    <t>10180005,1</t>
+  </si>
+  <si>
+    <t>10180007,1</t>
+  </si>
+  <si>
+    <t>10180008,1</t>
+  </si>
+  <si>
+    <t>10180011,5</t>
+  </si>
+  <si>
+    <t>10250002,1</t>
+  </si>
+  <si>
+    <t>10250003,1</t>
+  </si>
+  <si>
+    <t>10250004,1</t>
+  </si>
+  <si>
+    <t>10250005,1</t>
+  </si>
+  <si>
+    <t>10250007,1</t>
+  </si>
+  <si>
+    <t>10250008,1</t>
+  </si>
+  <si>
+    <t>10250011,5</t>
+  </si>
+  <si>
+    <t>10310002,1</t>
+  </si>
+  <si>
+    <t>10310003,1</t>
+  </si>
+  <si>
+    <t>常规20倍以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10310004,1</t>
+  </si>
+  <si>
+    <t>10310006,1</t>
+  </si>
+  <si>
+    <t>10310007,1</t>
+  </si>
+  <si>
+    <t>触发bonus模式概率提升</t>
+  </si>
+  <si>
+    <t>yjy_jmtb_6.png</t>
+  </si>
+  <si>
+    <t>bonus模式25倍及以上奖励提升</t>
+  </si>
+  <si>
+    <t>10310009,1</t>
+  </si>
+  <si>
+    <t>bonus模式50倍及以上奖励提升</t>
+  </si>
+  <si>
+    <t>10310010,1</t>
+  </si>
+  <si>
+    <t>10310013,5</t>
+  </si>
+  <si>
+    <t>10220006,1</t>
+  </si>
+  <si>
+    <t>10220007,1</t>
+  </si>
+  <si>
+    <t>10220010,5</t>
+  </si>
+  <si>
+    <t>10210002,1</t>
+  </si>
+  <si>
+    <t>10210003,1</t>
+  </si>
+  <si>
+    <t>10210004,1</t>
+  </si>
+  <si>
+    <t>10210005,1</t>
+  </si>
+  <si>
+    <t>10210007,1</t>
+  </si>
+  <si>
+    <t>10210008,1</t>
+  </si>
+  <si>
+    <t>102100010,1</t>
+  </si>
+  <si>
+    <t>102100011,1</t>
+  </si>
+  <si>
+    <t>102100014,5</t>
+  </si>
+  <si>
+    <t>10390002,1</t>
+  </si>
+  <si>
+    <t>10390003,1</t>
+  </si>
+  <si>
+    <t>10390004,1</t>
+  </si>
+  <si>
+    <t>10390005,1</t>
+  </si>
+  <si>
+    <t>10390007,1</t>
+  </si>
+  <si>
+    <t>10390008,1</t>
+  </si>
+  <si>
+    <t>10390011,1</t>
+  </si>
+  <si>
+    <t>10200002,1</t>
+  </si>
+  <si>
+    <t>10200003,1</t>
+  </si>
+  <si>
+    <t>10200004,1</t>
+  </si>
+  <si>
+    <t>10200005,1</t>
+  </si>
+  <si>
+    <t>10200007,1</t>
+  </si>
+  <si>
+    <t>10200008,1</t>
+  </si>
+  <si>
+    <t>10200011,1</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
@@ -1666,13 +1612,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
-        <v>10340001</v>
+        <v>10070001</v>
       </c>
       <c r="B13" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
         <v>4020002</v>
@@ -1686,13 +1632,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
-        <v>10340002</v>
+        <v>10070002</v>
       </c>
       <c r="B14" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2">
         <v>4020003</v>
@@ -1701,17 +1647,16 @@
         <v>19</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
-        <v>10340003</v>
+        <v>10070003</v>
       </c>
       <c r="B15" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2">
         <v>4020004</v>
@@ -1719,134 +1664,133 @@
       <c r="E15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="8"/>
       <c r="G15" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
-        <v>10340004</v>
+        <v>10070004</v>
       </c>
       <c r="B16" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2">
-        <v>4020094</v>
+        <v>4020005</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1">
-        <v>10340005</v>
+        <v>10070005</v>
       </c>
       <c r="B17" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
-        <v>4020095</v>
+        <v>4020345</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1">
-        <v>10340006</v>
+        <v>10070006</v>
       </c>
       <c r="B18" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2">
-        <v>4020096</v>
+        <v>4020346</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+        <v>19</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1">
-        <v>10340007</v>
+        <v>10070007</v>
       </c>
       <c r="B19" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2">
-        <v>4020097</v>
+        <v>4020347</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="2" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <v>10340008</v>
+        <v>10070008</v>
       </c>
       <c r="B20" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D20" s="2">
-        <v>4020098</v>
+        <v>4020349</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
-        <v>10340009</v>
+        <v>10070009</v>
       </c>
       <c r="B21" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2">
-        <v>4020007</v>
+        <v>4020350</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
-        <v>10340010</v>
+        <v>10070010</v>
       </c>
       <c r="B22" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>31</v>
@@ -1860,10 +1804,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1">
-        <v>10340011</v>
+        <v>10070011</v>
       </c>
       <c r="B23" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -1875,18 +1819,18 @@
         <v>29</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1">
-        <v>10340101</v>
+        <v>10120001</v>
       </c>
       <c r="B24" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2">
         <v>4020002</v>
@@ -1900,13 +1844,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1">
-        <v>10340102</v>
+        <v>10120002</v>
       </c>
       <c r="B25" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D25" s="2">
         <v>4020003</v>
@@ -1915,17 +1859,16 @@
         <v>19</v>
       </c>
       <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1">
-        <v>10340103</v>
+        <v>10120003</v>
       </c>
       <c r="B26" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D26" s="2">
         <v>4020004</v>
@@ -1935,18 +1878,18 @@
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1">
-        <v>10340104</v>
+        <v>10120004</v>
       </c>
       <c r="B27" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D27" s="2">
         <v>4020094</v>
@@ -1955,18 +1898,18 @@
         <v>19</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1">
-        <v>10340105</v>
+        <v>10120005</v>
       </c>
       <c r="B28" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2">
         <v>4020095</v>
@@ -1975,506 +1918,493 @@
         <v>19</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1">
-        <v>10340106</v>
+        <v>10120006</v>
       </c>
       <c r="B29" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2">
-        <v>4020149</v>
+        <v>4020401</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1">
-        <v>10340107</v>
+        <v>10120007</v>
       </c>
       <c r="B30" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D30" s="2">
-        <v>4020150</v>
+        <v>4020007</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="2" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1">
-        <v>10340108</v>
+        <v>10120008</v>
       </c>
       <c r="B31" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D31" s="2">
-        <v>4020151</v>
+        <v>4020008</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
-        <v>10340109</v>
+        <v>10120009</v>
       </c>
       <c r="B32" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D32" s="2">
-        <v>4020007</v>
+        <v>4020009</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">
-        <v>10340110</v>
+        <v>10180001</v>
       </c>
       <c r="B33" s="1">
-        <v>103401</v>
+        <v>101800</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" s="2">
-        <v>4020008</v>
+        <v>4020002</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1">
-        <v>10340111</v>
+        <v>10180002</v>
       </c>
       <c r="B34" s="1">
-        <v>103401</v>
+        <v>101800</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" s="2">
-        <v>4020009</v>
+        <v>4020003</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <v>10350001</v>
+        <v>10180003</v>
       </c>
       <c r="B35" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D35" s="2">
-        <v>4020002</v>
+        <v>4020004</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <v>10350002</v>
+        <v>10180004</v>
       </c>
       <c r="B36" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D36" s="2">
-        <v>4020003</v>
+        <v>4020005</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="G36" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <v>10350003</v>
+        <v>10180005</v>
       </c>
       <c r="B37" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D37" s="2">
-        <v>4020004</v>
+        <v>4020345</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="8"/>
       <c r="G37" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <v>10350004</v>
+        <v>10180006</v>
       </c>
       <c r="B38" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D38" s="2">
-        <v>4020005</v>
+        <v>4020346</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <v>10350005</v>
+        <v>10180007</v>
       </c>
       <c r="B39" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2">
-        <v>4020202</v>
+        <v>4020347</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <v>10350006</v>
+        <v>10180008</v>
       </c>
       <c r="B40" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D40" s="2">
-        <v>4020203</v>
+        <v>4020349</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="G40" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <v>10350007</v>
+        <v>10180009</v>
       </c>
       <c r="B41" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2">
-        <v>4020204</v>
+        <v>4020350</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F41" s="8"/>
       <c r="G41" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <v>10350008</v>
+        <v>10180010</v>
       </c>
       <c r="B42" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2">
-        <v>4020205</v>
+        <v>4020007</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <v>10350009</v>
+        <v>10180011</v>
       </c>
       <c r="B43" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D43" s="2">
-        <v>4020007</v>
+        <v>4020008</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <v>10350010</v>
+        <v>10180012</v>
       </c>
       <c r="B44" s="1">
-        <v>103500</v>
+        <v>101800</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D44" s="2">
-        <v>4020008</v>
+        <v>4020009</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G44" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <v>10350011</v>
+        <v>10250001</v>
       </c>
       <c r="B45" s="1">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D45" s="2">
-        <v>4020009</v>
+        <v>4020002</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>66</v>
+        <v>17</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <v>10350101</v>
+        <v>10250002</v>
       </c>
       <c r="B46" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D46" s="2">
-        <v>4020002</v>
+        <v>4020003</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="1">
-        <v>1</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <v>10350102</v>
+        <v>10250003</v>
       </c>
       <c r="B47" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D47" s="2">
-        <v>4020003</v>
+        <v>4020004</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="G47" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <v>10350103</v>
+        <v>10250004</v>
       </c>
       <c r="B48" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D48" s="2">
-        <v>4020004</v>
+        <v>4020005</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F48" s="8"/>
       <c r="G48" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <v>10350104</v>
+        <v>10250005</v>
       </c>
       <c r="B49" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D49" s="2">
-        <v>4020005</v>
+        <v>4020345</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1">
-        <v>10350105</v>
+        <v>10250006</v>
       </c>
       <c r="B50" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D50" s="2">
-        <v>4020202</v>
+        <v>4020346</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1">
-        <v>10350106</v>
+        <v>10250007</v>
       </c>
       <c r="B51" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D51" s="2">
-        <v>4020246</v>
+        <v>4020347</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1">
-        <v>10350107</v>
+        <v>10250008</v>
       </c>
       <c r="B52" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D52" s="2">
-        <v>4020247</v>
+        <v>4020349</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F52" s="8"/>
       <c r="G52" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="1">
-        <v>10350108</v>
+        <v>10250009</v>
       </c>
       <c r="B53" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D53" s="2">
-        <v>4020248</v>
+        <v>4020350</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1">
-        <v>10350109</v>
+        <v>10250010</v>
       </c>
       <c r="B54" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D54" s="2">
         <v>4020007</v>
@@ -2485,10 +2415,10 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="1">
-        <v>10350110</v>
+        <v>10250011</v>
       </c>
       <c r="B55" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>31</v>
@@ -2502,10 +2432,10 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1">
-        <v>10350111</v>
+        <v>10250012</v>
       </c>
       <c r="B56" s="1">
-        <v>103501</v>
+        <v>102500</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>28</v>
@@ -2517,18 +2447,18 @@
         <v>29</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="1">
-        <v>10140001</v>
+        <v>10310001</v>
       </c>
       <c r="B57" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D57" s="2">
         <v>4020002</v>
@@ -2542,13 +2472,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1">
-        <v>10140002</v>
+        <v>10310002</v>
       </c>
       <c r="B58" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D58" s="2">
         <v>4020003</v>
@@ -2557,17 +2487,16 @@
         <v>19</v>
       </c>
       <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="1">
-        <v>10140003</v>
+        <v>10310003</v>
       </c>
       <c r="B59" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D59" s="2">
         <v>4020004</v>
@@ -2576,19 +2505,19 @@
         <v>19</v>
       </c>
       <c r="F59" s="8"/>
-      <c r="G59" s="2" t="s">
-        <v>76</v>
+      <c r="G59" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1">
-        <v>10140004</v>
+        <v>10310004</v>
       </c>
       <c r="B60" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="D60" s="2">
         <v>4020005</v>
@@ -2596,19 +2525,19 @@
       <c r="E60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>77</v>
+      <c r="G60" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="1">
-        <v>10140005</v>
+        <v>10310005</v>
       </c>
       <c r="B61" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D61" s="2">
         <v>4020202</v>
@@ -2616,1044 +2545,1020 @@
       <c r="E61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>78</v>
+      <c r="G61" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1">
-        <v>10140006</v>
+        <v>10310006</v>
       </c>
       <c r="B62" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="2">
-        <v>4020007</v>
+        <v>4020347</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="1">
-        <v>10140007</v>
+        <v>10310007</v>
       </c>
       <c r="B63" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D63" s="2">
-        <v>4020008</v>
+        <v>4020349</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="1">
-        <v>10140008</v>
+        <v>10310008</v>
       </c>
       <c r="B64" s="1">
-        <v>101400</v>
+        <v>103100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D64" s="2">
-        <v>4020009</v>
+        <v>4020350</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>79</v>
+        <v>25</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
-        <v>10370001</v>
+        <v>10310009</v>
       </c>
       <c r="B65" s="1">
-        <v>103700</v>
+        <v>103100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2">
-        <v>4020002</v>
+        <v>4020412</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="1">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
-        <v>10370002</v>
+        <v>10310010</v>
       </c>
       <c r="B66" s="1">
-        <v>103700</v>
+        <v>103100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D66" s="2">
-        <v>4020003</v>
+        <v>4020413</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
-        <v>10370003</v>
+        <v>10310011</v>
       </c>
       <c r="B67" s="1">
-        <v>103700</v>
+        <v>103100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D67" s="2">
-        <v>4020004</v>
+        <v>4020414</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" s="8"/>
-      <c r="G67" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
-        <v>10370004</v>
+        <v>10310012</v>
       </c>
       <c r="B68" s="1">
-        <v>103700</v>
+        <v>103100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2">
-        <v>4020005</v>
+        <v>4020007</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
-        <v>10370005</v>
+        <v>10310013</v>
       </c>
       <c r="B69" s="1">
-        <v>103700</v>
+        <v>103100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="D69" s="2">
-        <v>4020202</v>
+        <v>4020008</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
-        <v>10370006</v>
+        <v>10310014</v>
       </c>
       <c r="B70" s="1">
-        <v>103700</v>
+        <v>103100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D70" s="2">
-        <v>4020279</v>
+        <v>4020009</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
-        <v>10370007</v>
+        <v>10220001</v>
       </c>
       <c r="B71" s="1">
-        <v>103700</v>
+        <v>102200</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D71" s="2">
-        <v>4020280</v>
+        <v>4020002</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" s="8"/>
-      <c r="G71" s="2" t="s">
-        <v>88</v>
+        <v>17</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
-        <v>10370008</v>
+        <v>10220002</v>
       </c>
       <c r="B72" s="1">
-        <v>103700</v>
+        <v>102200</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="D72" s="2">
-        <v>4020281</v>
+        <v>4020003</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>90</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F72" s="8"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
-        <v>10370009</v>
+        <v>10220003</v>
       </c>
       <c r="B73" s="1">
-        <v>103700</v>
+        <v>102200</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D73" s="2">
-        <v>4020007</v>
+        <v>4020004</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F73" s="8"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
-        <v>10370010</v>
+        <v>10220004</v>
       </c>
       <c r="B74" s="1">
-        <v>103700</v>
+        <v>102200</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D74" s="2">
-        <v>4020008</v>
+        <v>4020094</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
-        <v>10370011</v>
+        <v>10220005</v>
       </c>
       <c r="B75" s="1">
-        <v>103700</v>
+        <v>102200</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D75" s="2">
-        <v>4020009</v>
+        <v>4020095</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="1">
-        <v>10360001</v>
+        <v>10220006</v>
       </c>
       <c r="B76" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D76" s="2">
-        <v>4020002</v>
+        <v>4020347</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="1">
-        <v>10360002</v>
+        <v>10220007</v>
       </c>
       <c r="B77" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D77" s="2">
-        <v>4020003</v>
+        <v>4020349</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="1">
-        <v>10360003</v>
+        <v>10220008</v>
       </c>
       <c r="B78" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D78" s="2">
-        <v>4020004</v>
+        <v>4020350</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F78" s="8"/>
+        <v>25</v>
+      </c>
       <c r="G78" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1">
-        <v>10360004</v>
+        <v>10220009</v>
       </c>
       <c r="B79" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D79" s="2">
-        <v>4020005</v>
+        <v>4020007</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="1">
-        <v>10360005</v>
+        <v>10220010</v>
       </c>
       <c r="B80" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D80" s="2">
-        <v>4020202</v>
+        <v>4020008</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1">
-        <v>10360006</v>
+        <v>10220011</v>
       </c>
       <c r="B81" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="D81" s="2">
-        <v>4020312</v>
+        <v>4020009</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="1">
-        <v>10360007</v>
+        <v>10210001</v>
       </c>
       <c r="B82" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="D82" s="2">
-        <v>4020313</v>
+        <v>4020002</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" s="8"/>
-      <c r="G82" s="2" t="s">
-        <v>97</v>
+        <v>17</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1">
-        <v>10360008</v>
+        <v>10210002</v>
       </c>
       <c r="B83" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="D83" s="2">
-        <v>4020314</v>
+        <v>4020003</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F83" s="8"/>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="1">
-        <v>10360009</v>
+        <v>10210003</v>
       </c>
       <c r="B84" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D84" s="2">
-        <v>4020007</v>
+        <v>4020004</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="1">
-        <v>10360010</v>
+        <v>10210004</v>
       </c>
       <c r="B85" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D85" s="2">
-        <v>4020008</v>
+        <v>4020005</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="1">
-        <v>10360011</v>
+        <v>10210005</v>
       </c>
       <c r="B86" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D86" s="2">
-        <v>4020009</v>
+        <v>4020345</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="1">
-        <v>10070001</v>
+        <v>10210006</v>
       </c>
       <c r="B87" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D87" s="2">
-        <v>4020002</v>
+        <v>4020346</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" s="1">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="1">
-        <v>10070002</v>
+        <v>10210007</v>
       </c>
       <c r="B88" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D88" s="2">
-        <v>4020003</v>
+        <v>4020347</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88" s="8"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="1">
-        <v>10070003</v>
+        <v>10210008</v>
       </c>
       <c r="B89" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D89" s="2">
-        <v>4020004</v>
+        <v>4020349</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1">
-        <v>10070004</v>
+        <v>10210009</v>
       </c>
       <c r="B90" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="D90" s="2">
-        <v>4020005</v>
+        <v>4020350</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="1">
-        <v>10070005</v>
+        <v>10210010</v>
       </c>
       <c r="B91" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2">
-        <v>4020345</v>
+        <v>4020412</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1">
-        <v>10070006</v>
+        <v>10210011</v>
       </c>
       <c r="B92" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D92" s="2">
-        <v>4020346</v>
+        <v>4020413</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="1">
-        <v>10070007</v>
+        <v>10210012</v>
       </c>
       <c r="B93" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="D93" s="2">
-        <v>4020347</v>
+        <v>4020414</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1">
-        <v>10070008</v>
+        <v>10210013</v>
       </c>
       <c r="B94" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="D94" s="2">
-        <v>4020349</v>
+        <v>4020007</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="1">
-        <v>10070009</v>
+        <v>10210014</v>
       </c>
       <c r="B95" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="D95" s="2">
-        <v>4020350</v>
+        <v>4020008</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
-        <v>10070010</v>
+        <v>10210015</v>
       </c>
       <c r="B96" s="1">
-        <v>100700</v>
+        <v>102100</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D96" s="2">
-        <v>4020008</v>
+        <v>4020009</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G96" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">
-        <v>10070011</v>
+        <v>10390001</v>
       </c>
       <c r="B97" s="1">
-        <v>100700</v>
+        <v>103900</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D97" s="2">
-        <v>4020009</v>
+        <v>4020002</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>113</v>
+        <v>17</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1">
-        <v>10170001</v>
+        <v>10390002</v>
       </c>
       <c r="B98" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D98" s="2">
-        <v>4020002</v>
+        <v>4020003</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="1">
-        <v>1</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F98" s="8"/>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="1">
-        <v>10170002</v>
+        <v>10390003</v>
       </c>
       <c r="B99" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D99" s="2">
-        <v>4020003</v>
+        <v>4020004</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F99" s="8"/>
+      <c r="G99" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1">
-        <v>10170003</v>
+        <v>10390004</v>
       </c>
       <c r="B100" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D100" s="2">
-        <v>4020004</v>
+        <v>4020005</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1">
-        <v>10170004</v>
+        <v>10390005</v>
       </c>
       <c r="B101" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="D101" s="2">
-        <v>4020005</v>
+        <v>4020345</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1">
-        <v>10170005</v>
+        <v>10390006</v>
       </c>
       <c r="B102" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="D102" s="2">
-        <v>4020345</v>
+        <v>4020346</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="1">
-        <v>10170006</v>
+        <v>10390007</v>
       </c>
       <c r="B103" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D103" s="2">
-        <v>4020346</v>
+        <v>4020347</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1">
-        <v>10170007</v>
+        <v>10390008</v>
       </c>
       <c r="B104" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="D104" s="2">
-        <v>4020347</v>
+        <v>4020349</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="G104" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1">
-        <v>10170008</v>
+        <v>10390009</v>
       </c>
       <c r="B105" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="D105" s="2">
-        <v>4020349</v>
+        <v>4020350</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="1">
-        <v>10170009</v>
+        <v>10390010</v>
       </c>
       <c r="B106" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="D106" s="2">
-        <v>4020350</v>
+        <v>4020007</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="1">
-        <v>10170010</v>
+        <v>10390011</v>
       </c>
       <c r="B107" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D107" s="2">
-        <v>4020007</v>
+        <v>4020008</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="1">
-        <v>10170011</v>
+        <v>10390012</v>
       </c>
       <c r="B108" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D108" s="2">
-        <v>4020008</v>
+        <v>4020009</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G108" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="1">
-        <v>10170012</v>
+        <v>10200001</v>
       </c>
       <c r="B109" s="1">
-        <v>101700</v>
+        <v>102000</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D109" s="2">
-        <v>4020009</v>
+        <v>4020002</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="1">
-        <v>10120001</v>
+        <v>10200002</v>
       </c>
       <c r="B110" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D110" s="2">
-        <v>4020002</v>
+        <v>4020003</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F110" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="1">
-        <v>10120002</v>
+        <v>10200003</v>
       </c>
       <c r="B111" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D111" s="2">
-        <v>4020003</v>
+        <v>4020004</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F111" s="8"/>
+      <c r="G111" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1">
-        <v>10120003</v>
+        <v>10200004</v>
       </c>
       <c r="B112" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D112" s="2">
-        <v>4020004</v>
+        <v>4020005</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F112" s="8"/>
       <c r="G112" s="2" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="1">
-        <v>10120004</v>
+        <v>10200005</v>
       </c>
       <c r="B113" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="D113" s="2">
-        <v>4020094</v>
+        <v>4020345</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="1">
-        <v>10120005</v>
+        <v>10200006</v>
       </c>
       <c r="B114" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="D114" s="2">
-        <v>4020095</v>
+        <v>4020346</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="1">
-        <v>10120006</v>
+        <v>10200007</v>
       </c>
       <c r="B115" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="D115" s="2">
-        <v>4020401</v>
+        <v>4020347</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>25</v>
@@ -3661,56 +3566,96 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="1">
-        <v>10120007</v>
+        <v>10200008</v>
       </c>
       <c r="B116" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D116" s="2">
-        <v>4020007</v>
+        <v>4020349</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="1">
-        <v>10120008</v>
+        <v>10200009</v>
       </c>
       <c r="B117" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D117" s="2">
-        <v>4020008</v>
+        <v>4020350</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="1">
-        <v>10120009</v>
+        <v>10200010</v>
       </c>
       <c r="B118" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="C118" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D118" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="1">
+        <v>10200011</v>
+      </c>
+      <c r="B119" s="1">
+        <v>102000</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D119" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="1">
+        <v>10200012</v>
+      </c>
+      <c r="B120" s="1">
+        <v>102000</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D120" s="2">
         <v>4020009</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G118" s="2" t="s">
-        <v>127</v>
+      <c r="G120" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="113">
   <si>
     <t>属性id</t>
   </si>
@@ -335,6 +335,15 @@
   </si>
   <si>
     <t>10310013,5</t>
+  </si>
+  <si>
+    <t>10220002,1</t>
+  </si>
+  <si>
+    <t>10220003,1</t>
+  </si>
+  <si>
+    <t>10220004,1</t>
   </si>
   <si>
     <t>10220006,1</t>
@@ -2772,6 +2781,9 @@
         <v>19</v>
       </c>
       <c r="F73" s="8"/>
+      <c r="G73" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
@@ -2789,6 +2801,9 @@
       <c r="E74" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="G74" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
@@ -2806,6 +2821,9 @@
       <c r="E75" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="G75" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="1">
@@ -2841,7 +2859,7 @@
         <v>25</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2861,7 +2879,7 @@
         <v>25</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2915,7 +2933,7 @@
         <v>29</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2973,7 +2991,7 @@
         <v>19</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2993,7 +3011,7 @@
         <v>19</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3013,7 +3031,7 @@
         <v>19</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3033,7 +3051,7 @@
         <v>19</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3070,7 +3088,7 @@
         <v>25</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3090,7 +3108,7 @@
         <v>25</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3127,7 +3145,7 @@
         <v>78</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3147,7 +3165,7 @@
         <v>78</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3201,7 +3219,7 @@
         <v>29</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3259,7 +3277,7 @@
         <v>19</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3279,7 +3297,7 @@
         <v>19</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3299,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3319,7 +3337,7 @@
         <v>19</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3356,7 +3374,7 @@
         <v>25</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3376,7 +3394,7 @@
         <v>25</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3430,7 +3448,7 @@
         <v>29</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3484,7 +3502,7 @@
         <v>19</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3504,7 +3522,7 @@
         <v>19</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3524,7 +3542,7 @@
         <v>19</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3544,7 +3562,7 @@
         <v>19</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3581,7 +3599,7 @@
         <v>25</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3601,7 +3619,7 @@
         <v>25</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3655,7 +3673,7 @@
         <v>29</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="prop" sheetId="1" r:id="rId1"/>
@@ -1980,6 +1980,9 @@
       <c r="E31" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G31" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
@@ -1997,9 +2000,7 @@
       <c r="E32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -373,10 +373,10 @@
     <t>10210008,1</t>
   </si>
   <si>
-    <t>102100010,1</t>
-  </si>
-  <si>
     <t>102100011,1</t>
+  </si>
+  <si>
+    <t>102100012,1</t>
   </si>
   <si>
     <t>102100014,5</t>
@@ -3128,6 +3128,9 @@
       <c r="E91" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="G91" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1">
@@ -3146,7 +3149,7 @@
         <v>78</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3165,9 +3168,7 @@
       <c r="E93" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="G93" s="2"/>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1">
@@ -3202,6 +3203,9 @@
       <c r="E95" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G95" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
@@ -3219,9 +3223,7 @@
       <c r="E96" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>98</v>
-      </c>
+      <c r="G96" s="2"/>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="prop" sheetId="1" r:id="rId1"/>
@@ -253,7 +253,7 @@
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
-    <t>10120009,5</t>
+    <t>10120008,5</t>
   </si>
   <si>
     <t>10180002,1</t>
@@ -373,10 +373,10 @@
     <t>10210008,1</t>
   </si>
   <si>
+    <t>102100010,1</t>
+  </si>
+  <si>
     <t>102100011,1</t>
-  </si>
-  <si>
-    <t>102100012,1</t>
   </si>
   <si>
     <t>102100014,5</t>
@@ -1980,9 +1980,6 @@
       <c r="E31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
@@ -2000,7 +1997,9 @@
       <c r="E32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">
@@ -3128,9 +3127,6 @@
       <c r="E91" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1">
@@ -3149,7 +3145,7 @@
         <v>78</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3168,7 +3164,9 @@
       <c r="E93" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G93" s="2"/>
+      <c r="G93" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1">
@@ -3203,9 +3201,6 @@
       <c r="E95" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G95" s="1" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
@@ -3223,7 +3218,9 @@
       <c r="E96" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G96" s="2"/>
+      <c r="G96" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -373,13 +373,13 @@
     <t>10210008,1</t>
   </si>
   <si>
-    <t>102100010,1</t>
-  </si>
-  <si>
-    <t>102100011,1</t>
-  </si>
-  <si>
-    <t>102100014,5</t>
+    <t>10210010,1</t>
+  </si>
+  <si>
+    <t>10210011,1</t>
+  </si>
+  <si>
+    <t>10210014,5</t>
   </si>
   <si>
     <t>10390002,1</t>
@@ -1997,7 +1997,7 @@
       <c r="E32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="1" t="s">
         <v>56</v>
       </c>
     </row>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -83,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="148">
   <si>
     <t>属性id</t>
   </si>
@@ -139,6 +144,9 @@
     <t>yjy_jmtb_4.png</t>
   </si>
   <si>
+    <t>10030007,1</t>
+  </si>
+  <si>
     <t>中奖概率提升</t>
   </si>
   <si>
@@ -157,6 +165,18 @@
     <t>10030003,1</t>
   </si>
   <si>
+    <t>常规20-50中奖概率提升</t>
+  </si>
+  <si>
+    <t>10030004,1</t>
+  </si>
+  <si>
+    <t>常规50倍及以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10030005,1</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升</t>
   </si>
   <si>
@@ -184,6 +204,9 @@
     <t>下注金额增加</t>
   </si>
   <si>
+    <t>10070011,1</t>
+  </si>
+  <si>
     <t>中奖概率增高</t>
   </si>
   <si>
@@ -229,6 +252,9 @@
     <t>10070010,5</t>
   </si>
   <si>
+    <t>10120009,1</t>
+  </si>
+  <si>
     <t>5-10倍中奖概率增高</t>
   </si>
   <si>
@@ -256,6 +282,9 @@
     <t>10120008,5</t>
   </si>
   <si>
+    <t>10180012,1</t>
+  </si>
+  <si>
     <t>10180002,1</t>
   </si>
   <si>
@@ -277,6 +306,9 @@
     <t>10180011,5</t>
   </si>
   <si>
+    <t>10250012,1</t>
+  </si>
+  <si>
     <t>10250002,1</t>
   </si>
   <si>
@@ -304,9 +336,6 @@
     <t>10310003,1</t>
   </si>
   <si>
-    <t>常规20倍以上中奖概率提升</t>
-  </si>
-  <si>
     <t>10310004,1</t>
   </si>
   <si>
@@ -334,7 +363,10 @@
     <t>10310010,1</t>
   </si>
   <si>
-    <t>10310013,5</t>
+    <t>10310014,5</t>
+  </si>
+  <si>
+    <t>10220011,1</t>
   </si>
   <si>
     <t>10220002,1</t>
@@ -382,6 +414,9 @@
     <t>10210014,5</t>
   </si>
   <si>
+    <t>10390012,1</t>
+  </si>
+  <si>
     <t>10390002,1</t>
   </si>
   <si>
@@ -400,7 +435,10 @@
     <t>10390008,1</t>
   </si>
   <si>
-    <t>10390011,1</t>
+    <t>10390011,5</t>
+  </si>
+  <si>
+    <t>10200012,1</t>
   </si>
   <si>
     <t>10200002,1</t>
@@ -421,7 +459,79 @@
     <t>10200008,1</t>
   </si>
   <si>
-    <t>10200011,1</t>
+    <t>10200011,5</t>
+  </si>
+  <si>
+    <t>10270011,1</t>
+  </si>
+  <si>
+    <t>10270002,1</t>
+  </si>
+  <si>
+    <t>10270003,1</t>
+  </si>
+  <si>
+    <t>10270004,1</t>
+  </si>
+  <si>
+    <t>10270006,1</t>
+  </si>
+  <si>
+    <t>10270007,1</t>
+  </si>
+  <si>
+    <t>10270010,5</t>
+  </si>
+  <si>
+    <t>10150017,1</t>
+  </si>
+  <si>
+    <t>10150002,1</t>
+  </si>
+  <si>
+    <t>10150003,1</t>
+  </si>
+  <si>
+    <t>10150004,1</t>
+  </si>
+  <si>
+    <t>10150005,1</t>
+  </si>
+  <si>
+    <t>10150007,1</t>
+  </si>
+  <si>
+    <t>10150008,1</t>
+  </si>
+  <si>
+    <t>触发许愿百搭概率提升</t>
+  </si>
+  <si>
+    <t>许愿百搭中奖概率提升</t>
+  </si>
+  <si>
+    <t>10150010,1</t>
+  </si>
+  <si>
+    <t>许愿百搭30倍及以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10150011,1</t>
+  </si>
+  <si>
+    <t>许愿百搭50倍及以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10150012,1</t>
+  </si>
+  <si>
+    <t>许愿百搭100倍及以上中奖概率提升</t>
+  </si>
+  <si>
+    <t>10150013,1</t>
+  </si>
+  <si>
+    <t>10150016,5</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1503,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
@@ -1487,6 +1597,9 @@
       <c r="F5" s="1">
         <v>1</v>
       </c>
+      <c r="G5" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
@@ -1496,13 +1609,13 @@
         <v>100300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2">
         <v>4020003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -1514,17 +1627,17 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2">
         <v>4020004</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1535,16 +1648,16 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>4020005</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1555,13 +1668,16 @@
         <v>100300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2">
-        <v>4020006</v>
+        <v>4020471</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1572,13 +1688,16 @@
         <v>100300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2">
-        <v>4020007</v>
+        <v>4020346</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1589,15 +1708,12 @@
         <v>100300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2">
-        <v>4020009</v>
+        <v>4020006</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1612,955 +1728,964 @@
         <v>31</v>
       </c>
       <c r="D12" s="2">
-        <v>4020008</v>
+        <v>4020007</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="8"/>
+        <v>32</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
-        <v>10070001</v>
+        <v>10030009</v>
       </c>
       <c r="B13" s="1">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2">
-        <v>4020002</v>
+        <v>4020009</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
-        <v>10070002</v>
+        <v>10030010</v>
       </c>
       <c r="B14" s="1">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D14" s="2">
-        <v>4020003</v>
+        <v>4020008</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
-        <v>10070003</v>
+        <v>10070001</v>
       </c>
       <c r="B15" s="1">
         <v>100700</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15" s="2">
-        <v>4020004</v>
+        <v>4020002</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
-        <v>10070004</v>
+        <v>10070002</v>
       </c>
       <c r="B16" s="1">
         <v>100700</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2">
-        <v>4020005</v>
+        <v>4020003</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1">
-        <v>10070005</v>
+        <v>10070003</v>
       </c>
       <c r="B17" s="1">
         <v>100700</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2">
-        <v>4020345</v>
+        <v>4020004</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1">
-        <v>10070006</v>
+        <v>10070004</v>
       </c>
       <c r="B18" s="1">
         <v>100700</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2">
-        <v>4020346</v>
+        <v>4020094</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1">
-        <v>10070007</v>
+        <v>10070005</v>
       </c>
       <c r="B19" s="1">
         <v>100700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" s="2">
-        <v>4020347</v>
+        <v>4020345</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <v>10070008</v>
+        <v>10070006</v>
       </c>
       <c r="B20" s="1">
         <v>100700</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2">
-        <v>4020349</v>
+        <v>4020346</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
-        <v>10070009</v>
+        <v>10070007</v>
       </c>
       <c r="B21" s="1">
         <v>100700</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2">
-        <v>4020350</v>
+        <v>4020347</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
-        <v>10070010</v>
+        <v>10070008</v>
       </c>
       <c r="B22" s="1">
         <v>100700</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D22" s="2">
-        <v>4020008</v>
+        <v>4020349</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1">
-        <v>10070011</v>
+        <v>10070009</v>
       </c>
       <c r="B23" s="1">
         <v>100700</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2">
-        <v>4020009</v>
+        <v>4020350</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1">
-        <v>10120001</v>
+        <v>10070010</v>
       </c>
       <c r="B24" s="1">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D24" s="2">
-        <v>4020002</v>
+        <v>4020008</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1">
-        <v>10120002</v>
+        <v>10070011</v>
       </c>
       <c r="B25" s="1">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D25" s="2">
-        <v>4020003</v>
+        <v>4020009</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1">
-        <v>10120003</v>
+        <v>10120001</v>
       </c>
       <c r="B26" s="1">
         <v>101200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D26" s="2">
-        <v>4020004</v>
+        <v>4020002</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1">
-        <v>10120004</v>
+        <v>10120002</v>
       </c>
       <c r="B27" s="1">
         <v>101200</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2">
-        <v>4020094</v>
+        <v>4020003</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1">
-        <v>10120005</v>
+        <v>10120003</v>
       </c>
       <c r="B28" s="1">
         <v>101200</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2">
-        <v>4020095</v>
+        <v>4020004</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F28" s="8"/>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1">
-        <v>10120006</v>
+        <v>10120004</v>
       </c>
       <c r="B29" s="1">
         <v>101200</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2">
-        <v>4020401</v>
+        <v>4020094</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1">
-        <v>10120007</v>
+        <v>10120005</v>
       </c>
       <c r="B30" s="1">
         <v>101200</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2">
-        <v>4020007</v>
+        <v>4020095</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1">
-        <v>10120008</v>
+        <v>10120006</v>
       </c>
       <c r="B31" s="1">
         <v>101200</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2">
-        <v>4020008</v>
+        <v>4020401</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
-        <v>10120009</v>
+        <v>10120007</v>
       </c>
       <c r="B32" s="1">
         <v>101200</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2">
-        <v>4020009</v>
+        <v>4020007</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">
-        <v>10180001</v>
+        <v>10120008</v>
       </c>
       <c r="B33" s="1">
-        <v>101800</v>
+        <v>101200</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2">
-        <v>4020002</v>
+        <v>4020008</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1">
-        <v>10180002</v>
+        <v>10120009</v>
       </c>
       <c r="B34" s="1">
-        <v>101800</v>
+        <v>101200</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="2">
-        <v>4020003</v>
+        <v>4020009</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <v>10180003</v>
+        <v>10180001</v>
       </c>
       <c r="B35" s="1">
         <v>101800</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D35" s="2">
-        <v>4020004</v>
+        <v>4020002</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <v>10180004</v>
+        <v>10180002</v>
       </c>
       <c r="B36" s="1">
         <v>101800</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2">
-        <v>4020005</v>
+        <v>4020003</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>58</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <v>10180005</v>
+        <v>10180003</v>
       </c>
       <c r="B37" s="1">
         <v>101800</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2">
-        <v>4020345</v>
+        <v>4020004</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <v>10180006</v>
+        <v>10180004</v>
       </c>
       <c r="B38" s="1">
         <v>101800</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2">
-        <v>4020346</v>
+        <v>4020094</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <v>10180007</v>
+        <v>10180005</v>
       </c>
       <c r="B39" s="1">
         <v>101800</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2">
-        <v>4020347</v>
+        <v>4020345</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <v>10180008</v>
+        <v>10180006</v>
       </c>
       <c r="B40" s="1">
         <v>101800</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2">
-        <v>4020349</v>
+        <v>4020346</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <v>10180009</v>
+        <v>10180007</v>
       </c>
       <c r="B41" s="1">
         <v>101800</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D41" s="2">
-        <v>4020350</v>
+        <v>4020347</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <v>10180010</v>
+        <v>10180008</v>
       </c>
       <c r="B42" s="1">
         <v>101800</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D42" s="2">
-        <v>4020007</v>
+        <v>4020349</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <v>10180011</v>
+        <v>10180009</v>
       </c>
       <c r="B43" s="1">
         <v>101800</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D43" s="2">
-        <v>4020008</v>
+        <v>4020350</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <v>10180012</v>
+        <v>10180010</v>
       </c>
       <c r="B44" s="1">
         <v>101800</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2">
-        <v>4020009</v>
+        <v>4020007</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <v>10250001</v>
+        <v>10180011</v>
       </c>
       <c r="B45" s="1">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D45" s="2">
-        <v>4020002</v>
+        <v>4020008</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <v>10250002</v>
+        <v>10180012</v>
       </c>
       <c r="B46" s="1">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D46" s="2">
-        <v>4020003</v>
+        <v>4020009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <v>10250003</v>
+        <v>10250001</v>
       </c>
       <c r="B47" s="1">
         <v>102500</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D47" s="2">
-        <v>4020004</v>
+        <v>4020002</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <v>10250004</v>
+        <v>10250002</v>
       </c>
       <c r="B48" s="1">
         <v>102500</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2">
-        <v>4020005</v>
+        <v>4020003</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <v>10250005</v>
+        <v>10250003</v>
       </c>
       <c r="B49" s="1">
         <v>102500</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D49" s="2">
-        <v>4020345</v>
+        <v>4020004</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1">
-        <v>10250006</v>
+        <v>10250004</v>
       </c>
       <c r="B50" s="1">
         <v>102500</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D50" s="2">
-        <v>4020346</v>
+        <v>4020094</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1">
-        <v>10250007</v>
+        <v>10250005</v>
       </c>
       <c r="B51" s="1">
         <v>102500</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D51" s="2">
-        <v>4020347</v>
+        <v>4020345</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1">
-        <v>10250008</v>
+        <v>10250006</v>
       </c>
       <c r="B52" s="1">
         <v>102500</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2">
-        <v>4020349</v>
+        <v>4020346</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="1">
-        <v>10250009</v>
+        <v>10250007</v>
       </c>
       <c r="B53" s="1">
         <v>102500</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D53" s="2">
-        <v>4020350</v>
+        <v>4020347</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1">
-        <v>10250010</v>
+        <v>10250008</v>
       </c>
       <c r="B54" s="1">
         <v>102500</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2">
-        <v>4020007</v>
+        <v>4020349</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="1">
-        <v>10250011</v>
+        <v>10250009</v>
       </c>
       <c r="B55" s="1">
         <v>102500</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D55" s="2">
-        <v>4020008</v>
+        <v>4020350</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1">
-        <v>10250012</v>
+        <v>10250010</v>
       </c>
       <c r="B56" s="1">
         <v>102500</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D56" s="2">
-        <v>4020009</v>
+        <v>4020007</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="1">
-        <v>10310001</v>
+        <v>10250011</v>
       </c>
       <c r="B57" s="1">
-        <v>103100</v>
+        <v>102500</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D57" s="2">
-        <v>4020002</v>
+        <v>4020008</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1">
-        <v>10310002</v>
+        <v>10250012</v>
       </c>
       <c r="B58" s="1">
-        <v>103100</v>
+        <v>102500</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D58" s="2">
-        <v>4020003</v>
+        <v>4020009</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="1">
-        <v>10310003</v>
+        <v>10310001</v>
       </c>
       <c r="B59" s="1">
         <v>103100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D59" s="2">
-        <v>4020004</v>
+        <v>4020002</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8" t="s">
-        <v>71</v>
+        <v>17</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1">
-        <v>10310004</v>
+        <v>10310002</v>
       </c>
       <c r="B60" s="1">
         <v>103100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D60" s="2">
-        <v>4020005</v>
+        <v>4020003</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>72</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F60" s="8"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="1">
-        <v>10310005</v>
+        <v>10310003</v>
       </c>
       <c r="B61" s="1">
         <v>103100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D61" s="2">
-        <v>4020202</v>
+        <v>4020004</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F61" s="8"/>
       <c r="G61" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1">
-        <v>10310006</v>
+        <v>10310004</v>
       </c>
       <c r="B62" s="1">
         <v>103100</v>
@@ -2569,474 +2694,474 @@
         <v>42</v>
       </c>
       <c r="D62" s="2">
-        <v>4020347</v>
+        <v>4020094</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="1">
-        <v>10310007</v>
+        <v>10310005</v>
       </c>
       <c r="B63" s="1">
         <v>103100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D63" s="2">
-        <v>4020349</v>
+        <v>4020345</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="1">
-        <v>10310008</v>
+        <v>10310006</v>
       </c>
       <c r="B64" s="1">
         <v>103100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D64" s="2">
-        <v>4020350</v>
+        <v>4020346</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
-        <v>10310009</v>
+        <v>10310007</v>
       </c>
       <c r="B65" s="1">
         <v>103100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="D65" s="2">
-        <v>4020412</v>
+        <v>4020347</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
-        <v>10310010</v>
+        <v>10310008</v>
       </c>
       <c r="B66" s="1">
         <v>103100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D66" s="2">
-        <v>4020413</v>
+        <v>4020349</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
-        <v>10310011</v>
+        <v>10310009</v>
       </c>
       <c r="B67" s="1">
         <v>103100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2">
-        <v>4020414</v>
+        <v>4020350</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
-        <v>10310012</v>
+        <v>10310010</v>
       </c>
       <c r="B68" s="1">
         <v>103100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D68" s="2">
-        <v>4020007</v>
+        <v>4020412</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
-        <v>10310013</v>
+        <v>10310011</v>
       </c>
       <c r="B69" s="1">
         <v>103100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="D69" s="2">
-        <v>4020008</v>
+        <v>4020413</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>29</v>
+        <v>86</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
-        <v>10310014</v>
+        <v>10310012</v>
       </c>
       <c r="B70" s="1">
         <v>103100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D70" s="2">
-        <v>4020009</v>
+        <v>4020414</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
-        <v>10220001</v>
+        <v>10310013</v>
       </c>
       <c r="B71" s="1">
-        <v>102200</v>
+        <v>103100</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D71" s="2">
-        <v>4020002</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
-        <v>10220002</v>
+        <v>10310014</v>
       </c>
       <c r="B72" s="1">
-        <v>102200</v>
+        <v>103100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D72" s="2">
-        <v>4020003</v>
+        <v>4020008</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" s="8"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
-        <v>10220003</v>
+        <v>10310015</v>
       </c>
       <c r="B73" s="1">
-        <v>102200</v>
+        <v>103100</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D73" s="2">
-        <v>4020004</v>
+        <v>4020009</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="8"/>
-      <c r="G73" s="2" t="s">
-        <v>84</v>
+        <v>34</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
-        <v>10220004</v>
+        <v>10220001</v>
       </c>
       <c r="B74" s="1">
         <v>102200</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D74" s="2">
-        <v>4020094</v>
+        <v>4020002</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>85</v>
+        <v>17</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
-        <v>10220005</v>
+        <v>10220002</v>
       </c>
       <c r="B75" s="1">
         <v>102200</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D75" s="2">
-        <v>4020095</v>
+        <v>4020003</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F75" s="8"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="1">
-        <v>10220006</v>
+        <v>10220003</v>
       </c>
       <c r="B76" s="1">
         <v>102200</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D76" s="2">
-        <v>4020347</v>
+        <v>4020004</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="F76" s="8"/>
+      <c r="G76" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="1">
-        <v>10220007</v>
+        <v>10220004</v>
       </c>
       <c r="B77" s="1">
         <v>102200</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D77" s="2">
-        <v>4020349</v>
+        <v>4020094</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="1">
-        <v>10220008</v>
+        <v>10220005</v>
       </c>
       <c r="B78" s="1">
         <v>102200</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D78" s="2">
-        <v>4020350</v>
+        <v>4020095</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1">
-        <v>10220009</v>
+        <v>10220006</v>
       </c>
       <c r="B79" s="1">
         <v>102200</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D79" s="2">
-        <v>4020007</v>
+        <v>4020347</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="1">
-        <v>10220010</v>
+        <v>10220007</v>
       </c>
       <c r="B80" s="1">
         <v>102200</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D80" s="2">
-        <v>4020008</v>
+        <v>4020349</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1">
-        <v>10220011</v>
+        <v>10220008</v>
       </c>
       <c r="B81" s="1">
         <v>102200</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D81" s="2">
-        <v>4020009</v>
+        <v>4020350</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="1">
-        <v>10210001</v>
+        <v>10220009</v>
       </c>
       <c r="B82" s="1">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D82" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D82" s="2">
-        <v>4020002</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F82" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1">
-        <v>10210002</v>
+        <v>10220010</v>
       </c>
       <c r="B83" s="1">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D83" s="2">
-        <v>4020003</v>
+        <v>4020008</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" s="8"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="1">
-        <v>10210003</v>
+        <v>10220011</v>
       </c>
       <c r="B84" s="1">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D84" s="2">
-        <v>4020004</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="G84" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="1">
-        <v>10210004</v>
+        <v>10210001</v>
       </c>
       <c r="B85" s="1">
         <v>102100</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D85" s="2">
-        <v>4020005</v>
+        <v>4020002</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>91</v>
+        <v>17</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="1">
-        <v>10210005</v>
+        <v>10210002</v>
       </c>
       <c r="B86" s="1">
         <v>102100</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D86" s="2">
-        <v>4020345</v>
+        <v>4020003</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F86" s="8"/>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="1">
-        <v>10210006</v>
+        <v>10210003</v>
       </c>
       <c r="B87" s="1">
         <v>102100</v>
@@ -3045,18 +3170,18 @@
         <v>40</v>
       </c>
       <c r="D87" s="2">
-        <v>4020346</v>
+        <v>4020004</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="1">
-        <v>10210007</v>
+        <v>10210004</v>
       </c>
       <c r="B88" s="1">
         <v>102100</v>
@@ -3065,264 +3190,267 @@
         <v>42</v>
       </c>
       <c r="D88" s="2">
-        <v>4020347</v>
+        <v>4020094</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="1">
-        <v>10210008</v>
+        <v>10210005</v>
       </c>
       <c r="B89" s="1">
         <v>102100</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D89" s="2">
-        <v>4020349</v>
+        <v>4020345</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1">
-        <v>10210009</v>
+        <v>10210006</v>
       </c>
       <c r="B90" s="1">
         <v>102100</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D90" s="2">
-        <v>4020350</v>
+        <v>4020346</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="1">
-        <v>10210010</v>
+        <v>10210007</v>
       </c>
       <c r="B91" s="1">
         <v>102100</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="D91" s="2">
-        <v>4020412</v>
+        <v>4020347</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1">
-        <v>10210011</v>
+        <v>10210008</v>
       </c>
       <c r="B92" s="1">
         <v>102100</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D92" s="2">
-        <v>4020413</v>
+        <v>4020349</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="1">
-        <v>10210012</v>
+        <v>10210009</v>
       </c>
       <c r="B93" s="1">
         <v>102100</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D93" s="2">
-        <v>4020414</v>
+        <v>4020350</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1">
-        <v>10210013</v>
+        <v>10210010</v>
       </c>
       <c r="B94" s="1">
         <v>102100</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D94" s="2">
-        <v>4020007</v>
+        <v>4020412</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="1">
-        <v>10210014</v>
+        <v>10210011</v>
       </c>
       <c r="B95" s="1">
         <v>102100</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="D95" s="2">
-        <v>4020008</v>
+        <v>4020413</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>29</v>
+        <v>86</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
-        <v>10210015</v>
+        <v>10210012</v>
       </c>
       <c r="B96" s="1">
         <v>102100</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D96" s="2">
-        <v>4020009</v>
+        <v>4020414</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">
-        <v>10390001</v>
+        <v>10210013</v>
       </c>
       <c r="B97" s="1">
-        <v>103900</v>
+        <v>102100</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D97" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D97" s="2">
-        <v>4020002</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F97" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1">
-        <v>10390002</v>
+        <v>10210014</v>
       </c>
       <c r="B98" s="1">
-        <v>103900</v>
+        <v>102100</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D98" s="2">
-        <v>4020003</v>
+        <v>4020008</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" s="8"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="1">
-        <v>10390003</v>
+        <v>10210015</v>
       </c>
       <c r="B99" s="1">
-        <v>103900</v>
+        <v>102100</v>
       </c>
       <c r="C99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D99" s="2">
-        <v>4020004</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>99</v>
+      <c r="G99" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1">
-        <v>10390004</v>
+        <v>10390001</v>
       </c>
       <c r="B100" s="1">
         <v>103900</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D100" s="2">
-        <v>4020005</v>
+        <v>4020002</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="F100" s="1">
+        <v>1</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1">
-        <v>10390005</v>
+        <v>10390002</v>
       </c>
       <c r="B101" s="1">
         <v>103900</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D101" s="2">
-        <v>4020345</v>
+        <v>4020003</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>101</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F101" s="8"/>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1">
-        <v>10390006</v>
+        <v>10390003</v>
       </c>
       <c r="B102" s="1">
         <v>103900</v>
@@ -3331,18 +3459,18 @@
         <v>40</v>
       </c>
       <c r="D102" s="2">
-        <v>4020346</v>
+        <v>4020004</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="1">
-        <v>10390007</v>
+        <v>10390004</v>
       </c>
       <c r="B103" s="1">
         <v>103900</v>
@@ -3351,203 +3479,209 @@
         <v>42</v>
       </c>
       <c r="D103" s="2">
-        <v>4020347</v>
+        <v>4020094</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1">
-        <v>10390008</v>
+        <v>10390005</v>
       </c>
       <c r="B104" s="1">
         <v>103900</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D104" s="2">
-        <v>4020349</v>
+        <v>4020345</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1">
-        <v>10390009</v>
+        <v>10390006</v>
       </c>
       <c r="B105" s="1">
         <v>103900</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D105" s="2">
-        <v>4020350</v>
+        <v>4020346</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="1">
-        <v>10390010</v>
+        <v>10390007</v>
       </c>
       <c r="B106" s="1">
         <v>103900</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D106" s="2">
-        <v>4020007</v>
+        <v>4020347</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="1">
-        <v>10390011</v>
+        <v>10390008</v>
       </c>
       <c r="B107" s="1">
         <v>103900</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D107" s="2">
-        <v>4020008</v>
+        <v>4020349</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="1">
-        <v>10390012</v>
+        <v>10390009</v>
       </c>
       <c r="B108" s="1">
         <v>103900</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D108" s="2">
-        <v>4020009</v>
+        <v>4020350</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="1">
-        <v>10200001</v>
+        <v>10390010</v>
       </c>
       <c r="B109" s="1">
-        <v>102000</v>
+        <v>103900</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D109" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D109" s="2">
-        <v>4020002</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="1">
-        <v>10200002</v>
+        <v>10390011</v>
       </c>
       <c r="B110" s="1">
-        <v>102000</v>
+        <v>103900</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D110" s="2">
-        <v>4020003</v>
+        <v>4020008</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="1">
-        <v>10200003</v>
+        <v>10390012</v>
       </c>
       <c r="B111" s="1">
-        <v>102000</v>
+        <v>103900</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D111" s="2">
-        <v>4020004</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="G111" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1">
-        <v>10200004</v>
+        <v>10200001</v>
       </c>
       <c r="B112" s="1">
         <v>102000</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D112" s="2">
-        <v>4020005</v>
+        <v>4020002</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="F112" s="1">
+        <v>1</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="1">
-        <v>10200005</v>
+        <v>10200002</v>
       </c>
       <c r="B113" s="1">
         <v>102000</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D113" s="2">
-        <v>4020345</v>
+        <v>4020003</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="1">
-        <v>10200006</v>
+        <v>10200003</v>
       </c>
       <c r="B114" s="1">
         <v>102000</v>
@@ -3556,18 +3690,18 @@
         <v>40</v>
       </c>
       <c r="D114" s="2">
-        <v>4020346</v>
+        <v>4020004</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="1">
-        <v>10200007</v>
+        <v>10200004</v>
       </c>
       <c r="B115" s="1">
         <v>102000</v>
@@ -3576,104 +3710,703 @@
         <v>42</v>
       </c>
       <c r="D115" s="2">
-        <v>4020347</v>
+        <v>4020005</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="1">
-        <v>10200008</v>
+        <v>10200005</v>
       </c>
       <c r="B116" s="1">
         <v>102000</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D116" s="2">
-        <v>4020349</v>
+        <v>4020345</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="1">
-        <v>10200009</v>
+        <v>10200006</v>
       </c>
       <c r="B117" s="1">
         <v>102000</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D117" s="2">
-        <v>4020350</v>
+        <v>4020346</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="1">
-        <v>10200010</v>
+        <v>10200007</v>
       </c>
       <c r="B118" s="1">
         <v>102000</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D118" s="2">
-        <v>4020007</v>
+        <v>4020347</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="1">
-        <v>10200011</v>
+        <v>10200008</v>
       </c>
       <c r="B119" s="1">
         <v>102000</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D119" s="2">
-        <v>4020008</v>
+        <v>4020349</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="1">
-        <v>10200012</v>
+        <v>10200009</v>
       </c>
       <c r="B120" s="1">
         <v>102000</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D120" s="2">
+        <v>4020350</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="1">
+        <v>10200010</v>
+      </c>
+      <c r="B121" s="1">
+        <v>102000</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D121" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="1">
+        <v>10200011</v>
+      </c>
+      <c r="B122" s="1">
+        <v>102000</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D122" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="1">
+        <v>10200012</v>
+      </c>
+      <c r="B123" s="1">
+        <v>102000</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D123" s="2">
         <v>4020009</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>112</v>
+      <c r="E123" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="1">
+        <v>10270001</v>
+      </c>
+      <c r="B124" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="1">
+        <v>1</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="1">
+        <v>10270002</v>
+      </c>
+      <c r="B125" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D125" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="1">
+        <v>10270003</v>
+      </c>
+      <c r="B126" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D126" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="1">
+        <v>10270004</v>
+      </c>
+      <c r="B127" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D127" s="2">
+        <v>4020094</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="1">
+        <v>10270005</v>
+      </c>
+      <c r="B128" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D128" s="2">
+        <v>4020095</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="1">
+        <v>10270006</v>
+      </c>
+      <c r="B129" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D129" s="2">
+        <v>4020347</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="1">
+        <v>10270007</v>
+      </c>
+      <c r="B130" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D130" s="2">
+        <v>4020349</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="1">
+        <v>10270008</v>
+      </c>
+      <c r="B131" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D131" s="2">
+        <v>4020350</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="1">
+        <v>10270009</v>
+      </c>
+      <c r="B132" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D132" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="1">
+        <v>10270010</v>
+      </c>
+      <c r="B133" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D133" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="1">
+        <v>10270011</v>
+      </c>
+      <c r="B134" s="1">
+        <v>102700</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D134" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="1">
+        <v>10150001</v>
+      </c>
+      <c r="B135" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D135" s="2">
+        <v>4020002</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="1">
+        <v>1</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="1">
+        <v>10150002</v>
+      </c>
+      <c r="B136" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D136" s="2">
+        <v>4020003</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="1">
+        <v>10150003</v>
+      </c>
+      <c r="B137" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D137" s="2">
+        <v>4020004</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="1">
+        <v>10150004</v>
+      </c>
+      <c r="B138" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" s="2">
+        <v>4020094</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="1">
+        <v>10150005</v>
+      </c>
+      <c r="B139" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" s="2">
+        <v>4020345</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="1">
+        <v>10150006</v>
+      </c>
+      <c r="B140" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D140" s="2">
+        <v>4020346</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="1">
+        <v>10150007</v>
+      </c>
+      <c r="B141" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D141" s="2">
+        <v>4020347</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="1">
+        <v>10150008</v>
+      </c>
+      <c r="B142" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D142" s="2">
+        <v>4020349</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="1">
+        <v>10150009</v>
+      </c>
+      <c r="B143" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D143" s="2">
+        <v>4020350</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="1">
+        <v>10150010</v>
+      </c>
+      <c r="B144" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D144" s="2">
+        <v>4020466</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="1">
+        <v>10150011</v>
+      </c>
+      <c r="B145" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D145" s="2">
+        <v>4020467</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="1">
+        <v>10150012</v>
+      </c>
+      <c r="B146" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D146" s="2">
+        <v>4020468</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="1">
+        <v>10150013</v>
+      </c>
+      <c r="B147" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D147" s="2">
+        <v>4020469</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="1">
+        <v>10150014</v>
+      </c>
+      <c r="B148" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D148" s="2">
+        <v>4020470</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="1">
+        <v>10150015</v>
+      </c>
+      <c r="B149" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D149" s="2">
+        <v>4020007</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="1">
+        <v>10150016</v>
+      </c>
+      <c r="B150" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D150" s="2">
+        <v>4020008</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="1">
+        <v>10150017</v>
+      </c>
+      <c r="B151" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D151" s="2">
+        <v>4020009</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="138">
   <si>
     <t>属性id</t>
   </si>
@@ -144,9 +144,6 @@
     <t>yjy_jmtb_4.png</t>
   </si>
   <si>
-    <t>10030007,1</t>
-  </si>
-  <si>
     <t>中奖概率提升</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
     <t>下注金额增加</t>
   </si>
   <si>
-    <t>10070011,1</t>
-  </si>
-  <si>
     <t>中奖概率增高</t>
   </si>
   <si>
@@ -252,9 +246,6 @@
     <t>10070010,5</t>
   </si>
   <si>
-    <t>10120009,1</t>
-  </si>
-  <si>
     <t>5-10倍中奖概率增高</t>
   </si>
   <si>
@@ -282,9 +273,6 @@
     <t>10120008,5</t>
   </si>
   <si>
-    <t>10180012,1</t>
-  </si>
-  <si>
     <t>10180002,1</t>
   </si>
   <si>
@@ -306,9 +294,6 @@
     <t>10180011,5</t>
   </si>
   <si>
-    <t>10250012,1</t>
-  </si>
-  <si>
     <t>10250002,1</t>
   </si>
   <si>
@@ -366,9 +351,6 @@
     <t>10310014,5</t>
   </si>
   <si>
-    <t>10220011,1</t>
-  </si>
-  <si>
     <t>10220002,1</t>
   </si>
   <si>
@@ -414,9 +396,6 @@
     <t>10210014,5</t>
   </si>
   <si>
-    <t>10390012,1</t>
-  </si>
-  <si>
     <t>10390002,1</t>
   </si>
   <si>
@@ -438,9 +417,6 @@
     <t>10390011,5</t>
   </si>
   <si>
-    <t>10200012,1</t>
-  </si>
-  <si>
     <t>10200002,1</t>
   </si>
   <si>
@@ -462,9 +438,6 @@
     <t>10200011,5</t>
   </si>
   <si>
-    <t>10270011,1</t>
-  </si>
-  <si>
     <t>10270002,1</t>
   </si>
   <si>
@@ -481,9 +454,6 @@
   </si>
   <si>
     <t>10270010,5</t>
-  </si>
-  <si>
-    <t>10150017,1</t>
   </si>
   <si>
     <t>10150002,1</t>
@@ -1597,9 +1567,7 @@
       <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
@@ -1609,13 +1577,13 @@
         <v>100300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>4020003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -1627,17 +1595,17 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>4020004</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1648,16 +1616,16 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2">
         <v>4020005</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1668,16 +1636,16 @@
         <v>100300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
         <v>4020471</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1688,16 +1656,16 @@
         <v>100300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2">
         <v>4020346</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1708,13 +1676,13 @@
         <v>100300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2">
         <v>4020006</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1725,13 +1693,13 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2">
         <v>4020007</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1742,16 +1710,16 @@
         <v>100300</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
         <v>4020009</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1762,13 +1730,13 @@
         <v>100300</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>4020008</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" s="8"/>
     </row>
@@ -1780,7 +1748,7 @@
         <v>100700</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2">
         <v>4020002</v>
@@ -1791,9 +1759,7 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
@@ -1803,13 +1769,13 @@
         <v>100700</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
         <v>4020003</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="8"/>
     </row>
@@ -1821,16 +1787,16 @@
         <v>100700</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
         <v>4020004</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1841,16 +1807,16 @@
         <v>100700</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2">
         <v>4020094</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1861,16 +1827,16 @@
         <v>100700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2">
         <v>4020345</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1881,16 +1847,16 @@
         <v>100700</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D20" s="2">
         <v>4020346</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1901,13 +1867,13 @@
         <v>100700</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2">
         <v>4020347</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1918,16 +1884,16 @@
         <v>100700</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22" s="2">
         <v>4020349</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1938,16 +1904,16 @@
         <v>100700</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2">
         <v>4020350</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1958,13 +1924,13 @@
         <v>100700</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2">
         <v>4020008</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1975,16 +1941,16 @@
         <v>100700</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2">
         <v>4020009</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1995,7 +1961,7 @@
         <v>101200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" s="2">
         <v>4020002</v>
@@ -2005,9 +1971,6 @@
       </c>
       <c r="F26" s="1">
         <v>1</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2018,13 +1981,13 @@
         <v>101200</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D27" s="2">
         <v>4020003</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" s="8"/>
     </row>
@@ -2036,17 +1999,17 @@
         <v>101200</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2">
         <v>4020004</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2057,16 +2020,16 @@
         <v>101200</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2">
         <v>4020094</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2077,16 +2040,16 @@
         <v>101200</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D30" s="2">
         <v>4020095</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2097,13 +2060,13 @@
         <v>101200</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D31" s="2">
         <v>4020401</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2114,13 +2077,13 @@
         <v>101200</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2">
         <v>4020007</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2131,13 +2094,13 @@
         <v>101200</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2">
         <v>4020008</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2148,16 +2111,16 @@
         <v>101200</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2">
         <v>4020009</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2168,7 +2131,7 @@
         <v>101800</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2">
         <v>4020002</v>
@@ -2179,9 +2142,7 @@
       <c r="F35" s="1">
         <v>1</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
@@ -2191,13 +2152,13 @@
         <v>101800</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D36" s="2">
         <v>4020003</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F36" s="8"/>
     </row>
@@ -2209,16 +2170,16 @@
         <v>101800</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D37" s="2">
         <v>4020004</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2229,16 +2190,16 @@
         <v>101800</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D38" s="2">
         <v>4020094</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2249,16 +2210,16 @@
         <v>101800</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2">
         <v>4020345</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2269,16 +2230,16 @@
         <v>101800</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D40" s="2">
         <v>4020346</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2289,13 +2250,13 @@
         <v>101800</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D41" s="2">
         <v>4020347</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2306,16 +2267,16 @@
         <v>101800</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2">
         <v>4020349</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2326,16 +2287,16 @@
         <v>101800</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D43" s="2">
         <v>4020350</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2346,13 +2307,13 @@
         <v>101800</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2">
         <v>4020007</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2363,13 +2324,13 @@
         <v>101800</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2">
         <v>4020008</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2380,16 +2341,16 @@
         <v>101800</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D46" s="2">
         <v>4020009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2400,7 +2361,7 @@
         <v>102500</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D47" s="2">
         <v>4020002</v>
@@ -2411,9 +2372,7 @@
       <c r="F47" s="1">
         <v>1</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
@@ -2423,13 +2382,13 @@
         <v>102500</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D48" s="2">
         <v>4020003</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F48" s="8"/>
     </row>
@@ -2441,16 +2400,16 @@
         <v>102500</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D49" s="2">
         <v>4020004</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2461,16 +2420,16 @@
         <v>102500</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D50" s="2">
         <v>4020094</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2481,16 +2440,16 @@
         <v>102500</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D51" s="2">
         <v>4020345</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2501,16 +2460,16 @@
         <v>102500</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D52" s="2">
         <v>4020346</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2521,13 +2480,13 @@
         <v>102500</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D53" s="2">
         <v>4020347</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2538,16 +2497,16 @@
         <v>102500</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D54" s="2">
         <v>4020349</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2558,16 +2517,16 @@
         <v>102500</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D55" s="2">
         <v>4020350</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2578,13 +2537,13 @@
         <v>102500</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2">
         <v>4020007</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2595,13 +2554,13 @@
         <v>102500</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D57" s="2">
         <v>4020008</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2612,16 +2571,16 @@
         <v>102500</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D58" s="2">
         <v>4020009</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2632,7 +2591,7 @@
         <v>103100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D59" s="2">
         <v>4020002</v>
@@ -2652,13 +2611,13 @@
         <v>103100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D60" s="2">
         <v>4020003</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F60" s="8"/>
     </row>
@@ -2670,17 +2629,17 @@
         <v>103100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D61" s="2">
         <v>4020004</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2691,16 +2650,16 @@
         <v>103100</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D62" s="2">
         <v>4020094</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2711,16 +2670,16 @@
         <v>103100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D63" s="2">
         <v>4020345</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2731,13 +2690,13 @@
         <v>103100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D64" s="2">
         <v>4020346</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2748,13 +2707,13 @@
         <v>103100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D65" s="2">
         <v>4020347</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2765,16 +2724,16 @@
         <v>103100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2">
         <v>4020349</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2785,16 +2744,16 @@
         <v>103100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2">
         <v>4020350</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2805,13 +2764,13 @@
         <v>103100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D68" s="2">
         <v>4020412</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2822,16 +2781,16 @@
         <v>103100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D69" s="2">
         <v>4020413</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2842,16 +2801,16 @@
         <v>103100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D70" s="2">
         <v>4020414</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2862,13 +2821,13 @@
         <v>103100</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2">
         <v>4020007</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2879,13 +2838,13 @@
         <v>103100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D72" s="2">
         <v>4020008</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2896,16 +2855,16 @@
         <v>103100</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D73" s="2">
         <v>4020009</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2916,7 +2875,7 @@
         <v>102200</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D74" s="2">
         <v>4020002</v>
@@ -2926,9 +2885,6 @@
       </c>
       <c r="F74" s="1">
         <v>1</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2939,13 +2895,13 @@
         <v>102200</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D75" s="2">
         <v>4020003</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F75" s="8"/>
     </row>
@@ -2957,17 +2913,17 @@
         <v>102200</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D76" s="2">
         <v>4020004</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2978,16 +2934,16 @@
         <v>102200</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D77" s="2">
         <v>4020094</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2998,16 +2954,16 @@
         <v>102200</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D78" s="2">
         <v>4020095</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3018,13 +2974,13 @@
         <v>102200</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D79" s="2">
         <v>4020347</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3035,16 +2991,16 @@
         <v>102200</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D80" s="2">
         <v>4020349</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3055,16 +3011,16 @@
         <v>102200</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D81" s="2">
         <v>4020350</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3075,13 +3031,13 @@
         <v>102200</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D82" s="2">
         <v>4020007</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3092,13 +3048,13 @@
         <v>102200</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D83" s="2">
         <v>4020008</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3109,16 +3065,16 @@
         <v>102200</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D84" s="2">
         <v>4020009</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3129,7 +3085,7 @@
         <v>102100</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D85" s="2">
         <v>4020002</v>
@@ -3149,13 +3105,13 @@
         <v>102100</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D86" s="2">
         <v>4020003</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F86" s="8"/>
     </row>
@@ -3167,16 +3123,16 @@
         <v>102100</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D87" s="2">
         <v>4020004</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3187,16 +3143,16 @@
         <v>102100</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D88" s="2">
         <v>4020094</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3207,16 +3163,16 @@
         <v>102100</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D89" s="2">
         <v>4020345</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3227,16 +3183,16 @@
         <v>102100</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D90" s="2">
         <v>4020346</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3247,13 +3203,13 @@
         <v>102100</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D91" s="2">
         <v>4020347</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3264,16 +3220,16 @@
         <v>102100</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D92" s="2">
         <v>4020349</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3284,16 +3240,16 @@
         <v>102100</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D93" s="2">
         <v>4020350</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3304,13 +3260,13 @@
         <v>102100</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D94" s="2">
         <v>4020412</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3321,16 +3277,16 @@
         <v>102100</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D95" s="2">
         <v>4020413</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3341,16 +3297,16 @@
         <v>102100</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D96" s="2">
         <v>4020414</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3361,13 +3317,13 @@
         <v>102100</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D97" s="2">
         <v>4020007</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3378,13 +3334,13 @@
         <v>102100</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D98" s="2">
         <v>4020008</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3395,16 +3351,16 @@
         <v>102100</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D99" s="2">
         <v>4020009</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3415,7 +3371,7 @@
         <v>103900</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D100" s="2">
         <v>4020002</v>
@@ -3426,9 +3382,7 @@
       <c r="F100" s="1">
         <v>1</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>108</v>
-      </c>
+      <c r="G100" s="2"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1">
@@ -3438,13 +3392,13 @@
         <v>103900</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D101" s="2">
         <v>4020003</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F101" s="8"/>
     </row>
@@ -3456,16 +3410,16 @@
         <v>103900</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D102" s="2">
         <v>4020004</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3476,16 +3430,16 @@
         <v>103900</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D103" s="2">
         <v>4020094</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3496,16 +3450,16 @@
         <v>103900</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D104" s="2">
         <v>4020345</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3516,16 +3470,16 @@
         <v>103900</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D105" s="2">
         <v>4020346</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3536,13 +3490,13 @@
         <v>103900</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D106" s="2">
         <v>4020347</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3553,16 +3507,16 @@
         <v>103900</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D107" s="2">
         <v>4020349</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3573,16 +3527,16 @@
         <v>103900</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D108" s="2">
         <v>4020350</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3593,13 +3547,13 @@
         <v>103900</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2">
         <v>4020007</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3610,13 +3564,13 @@
         <v>103900</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D110" s="2">
         <v>4020008</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3627,16 +3581,16 @@
         <v>103900</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D111" s="2">
         <v>4020009</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3647,7 +3601,7 @@
         <v>102000</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D112" s="2">
         <v>4020002</v>
@@ -3658,9 +3612,7 @@
       <c r="F112" s="1">
         <v>1</v>
       </c>
-      <c r="G112" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="G112" s="2"/>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="1">
@@ -3670,13 +3622,13 @@
         <v>102000</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D113" s="2">
         <v>4020003</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3687,16 +3639,16 @@
         <v>102000</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D114" s="2">
         <v>4020004</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3707,16 +3659,16 @@
         <v>102000</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D115" s="2">
         <v>4020005</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3727,16 +3679,16 @@
         <v>102000</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D116" s="2">
         <v>4020345</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3747,16 +3699,16 @@
         <v>102000</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D117" s="2">
         <v>4020346</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3767,13 +3719,13 @@
         <v>102000</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D118" s="2">
         <v>4020347</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3784,16 +3736,16 @@
         <v>102000</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D119" s="2">
         <v>4020349</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3804,16 +3756,16 @@
         <v>102000</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D120" s="2">
         <v>4020350</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3824,13 +3776,13 @@
         <v>102000</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2">
         <v>4020007</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3841,13 +3793,13 @@
         <v>102000</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D122" s="2">
         <v>4020008</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3858,16 +3810,16 @@
         <v>102000</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D123" s="2">
         <v>4020009</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3878,7 +3830,7 @@
         <v>102700</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D124" s="2">
         <v>4020002</v>
@@ -3888,9 +3840,6 @@
       </c>
       <c r="F124" s="1">
         <v>1</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3901,13 +3850,13 @@
         <v>102700</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D125" s="2">
         <v>4020003</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3918,16 +3867,16 @@
         <v>102700</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D126" s="2">
         <v>4020004</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3938,16 +3887,16 @@
         <v>102700</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D127" s="2">
         <v>4020094</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3958,16 +3907,16 @@
         <v>102700</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D128" s="2">
         <v>4020095</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3978,13 +3927,13 @@
         <v>102700</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D129" s="2">
         <v>4020347</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3995,16 +3944,16 @@
         <v>102700</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D130" s="2">
         <v>4020349</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4015,16 +3964,16 @@
         <v>102700</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D131" s="2">
         <v>4020350</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4035,13 +3984,13 @@
         <v>102700</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D132" s="2">
         <v>4020007</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4052,13 +4001,13 @@
         <v>102700</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D133" s="2">
         <v>4020008</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4069,16 +4018,16 @@
         <v>102700</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D134" s="2">
         <v>4020009</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4089,7 +4038,7 @@
         <v>101500</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D135" s="2">
         <v>4020002</v>
@@ -4099,9 +4048,6 @@
       </c>
       <c r="F135" s="1">
         <v>1</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4112,13 +4058,13 @@
         <v>101500</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D136" s="2">
         <v>4020003</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4129,16 +4075,16 @@
         <v>101500</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D137" s="2">
         <v>4020004</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4149,16 +4095,16 @@
         <v>101500</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D138" s="2">
         <v>4020094</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4169,16 +4115,16 @@
         <v>101500</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D139" s="2">
         <v>4020345</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4189,16 +4135,16 @@
         <v>101500</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D140" s="2">
         <v>4020346</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4209,13 +4155,13 @@
         <v>101500</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D141" s="2">
         <v>4020347</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4226,16 +4172,16 @@
         <v>101500</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D142" s="2">
         <v>4020349</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4246,16 +4192,16 @@
         <v>101500</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D143" s="2">
         <v>4020350</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4266,13 +4212,13 @@
         <v>101500</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D144" s="2">
         <v>4020466</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4283,16 +4229,16 @@
         <v>101500</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D145" s="2">
         <v>4020467</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4303,16 +4249,16 @@
         <v>101500</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D146" s="2">
         <v>4020468</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4323,16 +4269,16 @@
         <v>101500</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D147" s="2">
         <v>4020469</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4343,16 +4289,16 @@
         <v>101500</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D148" s="2">
         <v>4020470</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4363,13 +4309,13 @@
         <v>101500</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D149" s="2">
         <v>4020007</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4380,13 +4326,13 @@
         <v>101500</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D150" s="2">
         <v>4020008</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4397,16 +4343,16 @@
         <v>101500</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D151" s="2">
         <v>4020009</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="140">
   <si>
     <t>属性id</t>
   </si>
@@ -111,6 +111,9 @@
     <t>解锁属性id_等级</t>
   </si>
   <si>
+    <t>位置排序</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
   </si>
   <si>
     <t>skillId</t>
+  </si>
+  <si>
+    <t>SortOrder</t>
   </si>
   <si>
     <t>金额解锁</t>
@@ -1134,7 +1140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1143,6 +1149,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1473,19 +1482,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G151"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H151"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.875" style="2" customWidth="1"/>
     <col min="5" max="7" width="26.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="8" max="9" width="16.25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1507,48 +1516,57 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
@@ -1556,20 +1574,23 @@
         <v>100300</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
         <v>4020002</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5" s="9"/>
+      <c r="H5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
@@ -1577,17 +1598,20 @@
         <v>100300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
         <v>4020003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
@@ -1595,20 +1619,23 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2">
         <v>4020004</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
@@ -1616,19 +1643,22 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2">
         <v>4020005</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
@@ -1636,19 +1666,22 @@
         <v>100300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2">
         <v>4020471</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
@@ -1656,19 +1689,22 @@
         <v>100300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2">
         <v>4020346</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10030007</v>
       </c>
@@ -1676,16 +1712,19 @@
         <v>100300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2">
         <v>4020006</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>10030008</v>
       </c>
@@ -1693,16 +1732,19 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2">
         <v>4020007</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>10030009</v>
       </c>
@@ -1710,19 +1752,22 @@
         <v>100300</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2">
         <v>4020009</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>10030010</v>
       </c>
@@ -1730,17 +1775,20 @@
         <v>100300</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2">
         <v>4020008</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>10070001</v>
       </c>
@@ -1748,20 +1796,23 @@
         <v>100700</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2">
         <v>4020002</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
       </c>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>10070002</v>
       </c>
@@ -1769,17 +1820,20 @@
         <v>100700</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2">
         <v>4020003</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>10070003</v>
       </c>
@@ -1787,19 +1841,22 @@
         <v>100700</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2">
         <v>4020004</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>41</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>10070004</v>
       </c>
@@ -1807,19 +1864,22 @@
         <v>100700</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2">
         <v>4020094</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>10070005</v>
       </c>
@@ -1827,19 +1887,22 @@
         <v>100700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" s="2">
         <v>4020345</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>45</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>10070006</v>
       </c>
@@ -1847,19 +1910,22 @@
         <v>100700</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2">
         <v>4020346</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>47</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>10070007</v>
       </c>
@@ -1867,16 +1933,19 @@
         <v>100700</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2">
         <v>4020347</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H21" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>10070008</v>
       </c>
@@ -1884,19 +1953,22 @@
         <v>100700</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D22" s="2">
         <v>4020349</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>50</v>
+      </c>
+      <c r="H22" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>10070009</v>
       </c>
@@ -1904,19 +1976,22 @@
         <v>100700</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2">
         <v>4020350</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>52</v>
+      </c>
+      <c r="H23" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>10070010</v>
       </c>
@@ -1924,16 +1999,19 @@
         <v>100700</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="2">
         <v>4020008</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>10070011</v>
       </c>
@@ -1941,19 +2019,22 @@
         <v>100700</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2">
         <v>4020009</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>53</v>
+      </c>
+      <c r="H25" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>10120001</v>
       </c>
@@ -1961,19 +2042,22 @@
         <v>101200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2">
         <v>4020002</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>10120002</v>
       </c>
@@ -1981,17 +2065,20 @@
         <v>101200</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2">
         <v>4020003</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>10120003</v>
       </c>
@@ -1999,20 +2086,23 @@
         <v>101200</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2">
         <v>4020004</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="F28" s="9"/>
       <c r="G28" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>55</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>10120004</v>
       </c>
@@ -2020,19 +2110,22 @@
         <v>101200</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2">
         <v>4020094</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>57</v>
+      </c>
+      <c r="H29" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>10120005</v>
       </c>
@@ -2040,19 +2133,22 @@
         <v>101200</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D30" s="2">
         <v>4020095</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>59</v>
+      </c>
+      <c r="H30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>10120006</v>
       </c>
@@ -2060,16 +2156,19 @@
         <v>101200</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D31" s="2">
         <v>4020401</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H31" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>10120007</v>
       </c>
@@ -2077,16 +2176,19 @@
         <v>101200</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D32" s="2">
         <v>4020007</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H32" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>10120008</v>
       </c>
@@ -2094,16 +2196,19 @@
         <v>101200</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2">
         <v>4020008</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H33" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>10120009</v>
       </c>
@@ -2111,19 +2216,22 @@
         <v>101200</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D34" s="2">
         <v>4020009</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="H34" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>10180001</v>
       </c>
@@ -2131,20 +2239,23 @@
         <v>101800</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D35" s="2">
         <v>4020002</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1">
         <v>1</v>
       </c>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>10180002</v>
       </c>
@@ -2152,17 +2263,20 @@
         <v>101800</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2">
         <v>4020003</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>10180003</v>
       </c>
@@ -2170,19 +2284,22 @@
         <v>101800</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2">
         <v>4020004</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>63</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>10180004</v>
       </c>
@@ -2190,19 +2307,22 @@
         <v>101800</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2">
         <v>4020094</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>64</v>
+      </c>
+      <c r="H38" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>10180005</v>
       </c>
@@ -2210,19 +2330,22 @@
         <v>101800</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2">
         <v>4020345</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>65</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>10180006</v>
       </c>
@@ -2230,19 +2353,22 @@
         <v>101800</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2">
         <v>4020346</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>66</v>
+      </c>
+      <c r="H40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>10180007</v>
       </c>
@@ -2250,16 +2376,19 @@
         <v>101800</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="2">
         <v>4020347</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H41" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>10180008</v>
       </c>
@@ -2267,19 +2396,22 @@
         <v>101800</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="2">
         <v>4020349</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>67</v>
+      </c>
+      <c r="H42" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>10180009</v>
       </c>
@@ -2287,19 +2419,22 @@
         <v>101800</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D43" s="2">
         <v>4020350</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>68</v>
+      </c>
+      <c r="H43" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>10180010</v>
       </c>
@@ -2307,16 +2442,19 @@
         <v>101800</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D44" s="2">
         <v>4020007</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H44" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>10180011</v>
       </c>
@@ -2324,16 +2462,19 @@
         <v>101800</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D45" s="2">
         <v>4020008</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H45" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>10180012</v>
       </c>
@@ -2341,19 +2482,22 @@
         <v>101800</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D46" s="2">
         <v>4020009</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>69</v>
+      </c>
+      <c r="H46" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1">
         <v>10250001</v>
       </c>
@@ -2361,20 +2505,23 @@
         <v>102500</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D47" s="2">
         <v>4020002</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
       </c>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>10250002</v>
       </c>
@@ -2382,17 +2529,20 @@
         <v>102500</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2">
         <v>4020003</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>10250003</v>
       </c>
@@ -2400,19 +2550,22 @@
         <v>102500</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D49" s="2">
         <v>4020004</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>70</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>10250004</v>
       </c>
@@ -2420,19 +2573,22 @@
         <v>102500</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D50" s="2">
         <v>4020094</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>71</v>
+      </c>
+      <c r="H50" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>10250005</v>
       </c>
@@ -2440,19 +2596,22 @@
         <v>102500</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D51" s="2">
         <v>4020345</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>72</v>
+      </c>
+      <c r="H51" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>10250006</v>
       </c>
@@ -2460,19 +2619,22 @@
         <v>102500</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2">
         <v>4020346</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>73</v>
+      </c>
+      <c r="H52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>10250007</v>
       </c>
@@ -2480,16 +2642,19 @@
         <v>102500</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D53" s="2">
         <v>4020347</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H53" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>10250008</v>
       </c>
@@ -2497,19 +2662,22 @@
         <v>102500</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2">
         <v>4020349</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>74</v>
+      </c>
+      <c r="H54" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>10250009</v>
       </c>
@@ -2517,19 +2685,22 @@
         <v>102500</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D55" s="2">
         <v>4020350</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>75</v>
+      </c>
+      <c r="H55" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>10250010</v>
       </c>
@@ -2537,16 +2708,19 @@
         <v>102500</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D56" s="2">
         <v>4020007</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H56" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>10250011</v>
       </c>
@@ -2554,16 +2728,19 @@
         <v>102500</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D57" s="2">
         <v>4020008</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H57" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>10250012</v>
       </c>
@@ -2571,19 +2748,22 @@
         <v>102500</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D58" s="2">
         <v>4020009</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>76</v>
+      </c>
+      <c r="H58" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>10310001</v>
       </c>
@@ -2591,19 +2771,22 @@
         <v>103100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D59" s="2">
         <v>4020002</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F59" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>10310002</v>
       </c>
@@ -2611,17 +2794,20 @@
         <v>103100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D60" s="2">
         <v>4020003</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F60" s="9"/>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="1">
         <v>10310003</v>
       </c>
@@ -2629,20 +2815,23 @@
         <v>103100</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D61" s="2">
         <v>4020004</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>10310004</v>
       </c>
@@ -2650,19 +2839,22 @@
         <v>103100</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D62" s="2">
         <v>4020094</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H62" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>10310005</v>
       </c>
@@ -2670,19 +2862,22 @@
         <v>103100</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D63" s="2">
         <v>4020345</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H63" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>10310006</v>
       </c>
@@ -2690,16 +2885,19 @@
         <v>103100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D64" s="2">
         <v>4020346</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="H64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>10310007</v>
       </c>
@@ -2707,16 +2905,19 @@
         <v>103100</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D65" s="2">
         <v>4020347</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H65" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>10310008</v>
       </c>
@@ -2724,19 +2925,22 @@
         <v>103100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D66" s="2">
         <v>4020349</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H66" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>10310009</v>
       </c>
@@ -2744,19 +2948,22 @@
         <v>103100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2">
         <v>4020350</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H67" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1">
         <v>10310010</v>
       </c>
@@ -2764,16 +2971,19 @@
         <v>103100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D68" s="2">
         <v>4020412</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="H68" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>10310011</v>
       </c>
@@ -2781,19 +2991,22 @@
         <v>103100</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D69" s="2">
         <v>4020413</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G69" s="8" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="G69" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>10310012</v>
       </c>
@@ -2801,19 +3014,22 @@
         <v>103100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D70" s="2">
         <v>4020414</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H70" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>10310013</v>
       </c>
@@ -2821,16 +3037,19 @@
         <v>103100</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D71" s="2">
         <v>4020007</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H71" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>10310014</v>
       </c>
@@ -2838,16 +3057,19 @@
         <v>103100</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D72" s="2">
         <v>4020008</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H72" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>10310015</v>
       </c>
@@ -2855,19 +3077,22 @@
         <v>103100</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D73" s="2">
         <v>4020009</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H73" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>10220001</v>
       </c>
@@ -2875,19 +3100,22 @@
         <v>102200</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D74" s="2">
         <v>4020002</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F74" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>10220002</v>
       </c>
@@ -2895,17 +3123,20 @@
         <v>102200</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D75" s="2">
         <v>4020003</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F75" s="9"/>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="1">
         <v>10220003</v>
       </c>
@@ -2913,20 +3144,23 @@
         <v>102200</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D76" s="2">
         <v>4020004</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="F76" s="9"/>
       <c r="G76" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>89</v>
+      </c>
+      <c r="H76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>10220004</v>
       </c>
@@ -2934,19 +3168,22 @@
         <v>102200</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D77" s="2">
         <v>4020094</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>90</v>
+      </c>
+      <c r="H77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>10220005</v>
       </c>
@@ -2954,19 +3191,22 @@
         <v>102200</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D78" s="2">
         <v>4020095</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>91</v>
+      </c>
+      <c r="H78" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>10220006</v>
       </c>
@@ -2974,16 +3214,19 @@
         <v>102200</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D79" s="2">
         <v>4020347</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H79" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>10220007</v>
       </c>
@@ -2991,19 +3234,22 @@
         <v>102200</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D80" s="2">
         <v>4020349</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>92</v>
+      </c>
+      <c r="H80" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>10220008</v>
       </c>
@@ -3011,19 +3257,22 @@
         <v>102200</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D81" s="2">
         <v>4020350</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>93</v>
+      </c>
+      <c r="H81" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>10220009</v>
       </c>
@@ -3031,16 +3280,19 @@
         <v>102200</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D82" s="2">
         <v>4020007</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H82" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>10220010</v>
       </c>
@@ -3048,16 +3300,19 @@
         <v>102200</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D83" s="2">
         <v>4020008</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H83" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="1">
         <v>10220011</v>
       </c>
@@ -3065,19 +3320,22 @@
         <v>102200</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D84" s="2">
         <v>4020009</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="H84" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="1">
         <v>10210001</v>
       </c>
@@ -3085,19 +3343,22 @@
         <v>102100</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D85" s="2">
         <v>4020002</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F85" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>10210002</v>
       </c>
@@ -3105,17 +3366,20 @@
         <v>102100</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D86" s="2">
         <v>4020003</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" s="8"/>
-    </row>
-    <row r="87" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F86" s="9"/>
+      <c r="H86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1">
         <v>10210003</v>
       </c>
@@ -3123,19 +3387,22 @@
         <v>102100</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D87" s="2">
         <v>4020004</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>95</v>
+      </c>
+      <c r="H87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>10210004</v>
       </c>
@@ -3143,19 +3410,22 @@
         <v>102100</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D88" s="2">
         <v>4020094</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>96</v>
+      </c>
+      <c r="H88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>10210005</v>
       </c>
@@ -3163,19 +3433,22 @@
         <v>102100</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D89" s="2">
         <v>4020345</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>97</v>
+      </c>
+      <c r="H89" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>10210006</v>
       </c>
@@ -3183,19 +3456,22 @@
         <v>102100</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D90" s="2">
         <v>4020346</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>98</v>
+      </c>
+      <c r="H90" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="1">
         <v>10210007</v>
       </c>
@@ -3203,16 +3479,19 @@
         <v>102100</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D91" s="2">
         <v>4020347</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H91" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>10210008</v>
       </c>
@@ -3220,19 +3499,22 @@
         <v>102100</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D92" s="2">
         <v>4020349</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>99</v>
+      </c>
+      <c r="H92" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>10210009</v>
       </c>
@@ -3240,19 +3522,22 @@
         <v>102100</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D93" s="2">
         <v>4020350</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>100</v>
+      </c>
+      <c r="H93" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="1">
         <v>10210010</v>
       </c>
@@ -3260,16 +3545,19 @@
         <v>102100</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D94" s="2">
         <v>4020412</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="H94" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>10210011</v>
       </c>
@@ -3277,19 +3565,22 @@
         <v>102100</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D95" s="2">
         <v>4020413</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>101</v>
+      </c>
+      <c r="H95" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>10210012</v>
       </c>
@@ -3297,19 +3588,22 @@
         <v>102100</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D96" s="2">
         <v>4020414</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>102</v>
+      </c>
+      <c r="H96" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="1">
         <v>10210013</v>
       </c>
@@ -3317,16 +3611,19 @@
         <v>102100</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D97" s="2">
         <v>4020007</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H97" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>10210014</v>
       </c>
@@ -3334,16 +3631,19 @@
         <v>102100</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D98" s="2">
         <v>4020008</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H98" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>10210015</v>
       </c>
@@ -3351,19 +3651,22 @@
         <v>102100</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D99" s="2">
         <v>4020009</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H99" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>10390001</v>
       </c>
@@ -3371,20 +3674,23 @@
         <v>103900</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D100" s="2">
         <v>4020002</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
       </c>
       <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="H100" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>10390002</v>
       </c>
@@ -3392,17 +3698,20 @@
         <v>103900</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D101" s="2">
         <v>4020003</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F101" s="8"/>
-    </row>
-    <row r="102" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F101" s="9"/>
+      <c r="H101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>10390003</v>
       </c>
@@ -3410,19 +3719,22 @@
         <v>103900</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D102" s="2">
         <v>4020004</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>104</v>
+      </c>
+      <c r="H102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>10390004</v>
       </c>
@@ -3430,19 +3742,22 @@
         <v>103900</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D103" s="2">
         <v>4020094</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>105</v>
+      </c>
+      <c r="H103" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>10390005</v>
       </c>
@@ -3450,19 +3765,22 @@
         <v>103900</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D104" s="2">
         <v>4020345</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>106</v>
+      </c>
+      <c r="H104" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>10390006</v>
       </c>
@@ -3470,19 +3788,22 @@
         <v>103900</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D105" s="2">
         <v>4020346</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>107</v>
+      </c>
+      <c r="H105" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>10390007</v>
       </c>
@@ -3490,16 +3811,19 @@
         <v>103900</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D106" s="2">
         <v>4020347</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H106" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>10390008</v>
       </c>
@@ -3507,19 +3831,22 @@
         <v>103900</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D107" s="2">
         <v>4020349</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>108</v>
+      </c>
+      <c r="H107" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>10390009</v>
       </c>
@@ -3527,19 +3854,22 @@
         <v>103900</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D108" s="2">
         <v>4020350</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>109</v>
+      </c>
+      <c r="H108" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>10390010</v>
       </c>
@@ -3547,16 +3877,19 @@
         <v>103900</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D109" s="2">
         <v>4020007</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H109" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>10390011</v>
       </c>
@@ -3564,16 +3897,19 @@
         <v>103900</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D110" s="2">
         <v>4020008</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H110" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>10390012</v>
       </c>
@@ -3581,19 +3917,22 @@
         <v>103900</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D111" s="2">
         <v>4020009</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>110</v>
+      </c>
+      <c r="H111" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>10200001</v>
       </c>
@@ -3601,20 +3940,23 @@
         <v>102000</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D112" s="2">
         <v>4020002</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
       </c>
       <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="H112" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>10200002</v>
       </c>
@@ -3622,16 +3964,19 @@
         <v>102000</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D113" s="2">
         <v>4020003</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>10200003</v>
       </c>
@@ -3639,19 +3984,22 @@
         <v>102000</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D114" s="2">
         <v>4020004</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>111</v>
+      </c>
+      <c r="H114" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>10200004</v>
       </c>
@@ -3659,19 +4007,22 @@
         <v>102000</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D115" s="2">
         <v>4020005</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>112</v>
+      </c>
+      <c r="H115" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>10200005</v>
       </c>
@@ -3679,19 +4030,22 @@
         <v>102000</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D116" s="2">
         <v>4020345</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>113</v>
+      </c>
+      <c r="H116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>10200006</v>
       </c>
@@ -3699,19 +4053,22 @@
         <v>102000</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D117" s="2">
         <v>4020346</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="H117" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>10200007</v>
       </c>
@@ -3719,16 +4076,19 @@
         <v>102000</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D118" s="2">
         <v>4020347</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H118" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>10200008</v>
       </c>
@@ -3736,19 +4096,22 @@
         <v>102000</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D119" s="2">
         <v>4020349</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="H119" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>10200009</v>
       </c>
@@ -3756,19 +4119,22 @@
         <v>102000</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D120" s="2">
         <v>4020350</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>116</v>
+      </c>
+      <c r="H120" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>10200010</v>
       </c>
@@ -3776,16 +4142,19 @@
         <v>102000</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D121" s="2">
         <v>4020007</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H121" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" s="1">
         <v>10200011</v>
       </c>
@@ -3793,16 +4162,19 @@
         <v>102000</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D122" s="2">
         <v>4020008</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H122" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>10200012</v>
       </c>
@@ -3810,19 +4182,22 @@
         <v>102000</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D123" s="2">
         <v>4020009</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>117</v>
+      </c>
+      <c r="H123" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>10270001</v>
       </c>
@@ -3830,19 +4205,22 @@
         <v>102700</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D124" s="2">
         <v>4020002</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="H124" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" s="1">
         <v>10270002</v>
       </c>
@@ -3850,16 +4228,19 @@
         <v>102700</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D125" s="2">
         <v>4020003</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="H125" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" s="1">
         <v>10270003</v>
       </c>
@@ -3867,19 +4248,22 @@
         <v>102700</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D126" s="2">
         <v>4020004</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>118</v>
+      </c>
+      <c r="H126" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>10270004</v>
       </c>
@@ -3887,19 +4271,22 @@
         <v>102700</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D127" s="2">
         <v>4020094</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="H127" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>10270005</v>
       </c>
@@ -3907,19 +4294,22 @@
         <v>102700</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D128" s="2">
         <v>4020095</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>120</v>
+      </c>
+      <c r="H128" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>10270006</v>
       </c>
@@ -3927,16 +4317,19 @@
         <v>102700</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D129" s="2">
         <v>4020347</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H129" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="1">
         <v>10270007</v>
       </c>
@@ -3944,19 +4337,22 @@
         <v>102700</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D130" s="2">
         <v>4020349</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>121</v>
+      </c>
+      <c r="H130" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>10270008</v>
       </c>
@@ -3964,19 +4360,22 @@
         <v>102700</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D131" s="2">
         <v>4020350</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>122</v>
+      </c>
+      <c r="H131" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>10270009</v>
       </c>
@@ -3984,16 +4383,19 @@
         <v>102700</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D132" s="2">
         <v>4020007</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H132" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>10270010</v>
       </c>
@@ -4001,16 +4403,19 @@
         <v>102700</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D133" s="2">
         <v>4020008</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H133" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>10270011</v>
       </c>
@@ -4018,19 +4423,22 @@
         <v>102700</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D134" s="2">
         <v>4020009</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>123</v>
+      </c>
+      <c r="H134" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>10150001</v>
       </c>
@@ -4038,19 +4446,22 @@
         <v>101500</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D135" s="2">
         <v>4020002</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F135" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="H135" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>10150002</v>
       </c>
@@ -4058,16 +4469,19 @@
         <v>101500</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D136" s="2">
         <v>4020003</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="H136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>10150003</v>
       </c>
@@ -4075,19 +4489,22 @@
         <v>101500</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D137" s="2">
         <v>4020004</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>124</v>
+      </c>
+      <c r="H137" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="1">
         <v>10150004</v>
       </c>
@@ -4095,19 +4512,22 @@
         <v>101500</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D138" s="2">
         <v>4020094</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>125</v>
+      </c>
+      <c r="H138" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="1">
         <v>10150005</v>
       </c>
@@ -4115,19 +4535,22 @@
         <v>101500</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D139" s="2">
         <v>4020345</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>126</v>
+      </c>
+      <c r="H139" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="1">
         <v>10150006</v>
       </c>
@@ -4135,19 +4558,22 @@
         <v>101500</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D140" s="2">
         <v>4020346</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>127</v>
+      </c>
+      <c r="H140" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="1">
         <v>10150007</v>
       </c>
@@ -4155,16 +4581,19 @@
         <v>101500</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D141" s="2">
         <v>4020347</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H141" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="1">
         <v>10150008</v>
       </c>
@@ -4172,19 +4601,22 @@
         <v>101500</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D142" s="2">
         <v>4020349</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>128</v>
+      </c>
+      <c r="H142" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="1">
         <v>10150009</v>
       </c>
@@ -4192,19 +4624,22 @@
         <v>101500</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D143" s="2">
         <v>4020350</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>129</v>
+      </c>
+      <c r="H143" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="1">
         <v>10150010</v>
       </c>
@@ -4212,16 +4647,19 @@
         <v>101500</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D144" s="2">
         <v>4020466</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="H144" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="1">
         <v>10150011</v>
       </c>
@@ -4229,19 +4667,22 @@
         <v>101500</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D145" s="2">
         <v>4020467</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+        <v>132</v>
+      </c>
+      <c r="H145" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="1">
         <v>10150012</v>
       </c>
@@ -4249,19 +4690,22 @@
         <v>101500</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D146" s="2">
         <v>4020468</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H146" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" s="1">
         <v>10150013</v>
       </c>
@@ -4269,19 +4713,22 @@
         <v>101500</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D147" s="2">
         <v>4020469</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+        <v>136</v>
+      </c>
+      <c r="H147" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" s="1">
         <v>10150014</v>
       </c>
@@ -4289,19 +4736,22 @@
         <v>101500</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D148" s="2">
         <v>4020470</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+        <v>138</v>
+      </c>
+      <c r="H148" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="1">
         <v>10150015</v>
       </c>
@@ -4309,16 +4759,19 @@
         <v>101500</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D149" s="2">
         <v>4020007</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H149" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="1">
         <v>10150016</v>
       </c>
@@ -4326,16 +4779,19 @@
         <v>101500</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D150" s="2">
         <v>4020008</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H150" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="1">
         <v>10150017</v>
       </c>
@@ -4343,16 +4799,19 @@
         <v>101500</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D151" s="2">
         <v>4020009</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="H151" s="1">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\模拟经营数值相关\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -195,25 +195,25 @@
     <t>常规5-10中奖概率提升</t>
   </si>
   <si>
-    <t>10030001,10</t>
+    <t>10030002,10</t>
   </si>
   <si>
     <t>常规10-20中奖概率提升</t>
   </si>
   <si>
-    <t>10030002,10</t>
+    <t>10030003,10</t>
   </si>
   <si>
     <t>常规20-50中奖概率提升</t>
   </si>
   <si>
-    <t>10030003,10</t>
+    <t>10030004,10</t>
   </si>
   <si>
     <t>常规50倍及以上中奖概率提升</t>
   </si>
   <si>
-    <t>10030004,10</t>
+    <t>10030005,10</t>
   </si>
   <si>
     <t>中樱桃符号概率提升</t>
@@ -228,7 +228,7 @@
     <t>yjy_jmtb_3.png</t>
   </si>
   <si>
-    <t>10030006,10</t>
+    <t>10030007,10</t>
   </si>
   <si>
     <t>中奖提成比例</t>
@@ -249,25 +249,25 @@
     <t>5-10倍中奖概率提升</t>
   </si>
   <si>
-    <t>10070001,10</t>
+    <t>10070002,10</t>
   </si>
   <si>
     <t>10-25倍中奖概率提升</t>
   </si>
   <si>
-    <t>10070002,10</t>
+    <t>10070003,10</t>
   </si>
   <si>
     <t>25-50倍中奖概率提升</t>
   </si>
   <si>
-    <t>10070003,10</t>
+    <t>10070004,10</t>
   </si>
   <si>
     <t>50倍及以上中奖概率提升</t>
   </si>
   <si>
-    <t>10070004,10</t>
+    <t>10070005,10</t>
   </si>
   <si>
     <t>触发免费模式概率提升</t>
@@ -276,31 +276,31 @@
     <t>免费模式50倍及以上大奖概率提升</t>
   </si>
   <si>
-    <t>10070006,10</t>
+    <t>10070007,10</t>
   </si>
   <si>
     <t>免费模式100倍及以上大奖概率提升</t>
   </si>
   <si>
-    <t>10070007,10</t>
+    <t>10070008,10</t>
   </si>
   <si>
     <t>5-10倍中奖概率增高</t>
   </si>
   <si>
-    <t>10120001,10</t>
+    <t>10120002,10</t>
   </si>
   <si>
     <t>10-25倍中奖概率增高</t>
   </si>
   <si>
-    <t>10120002,10</t>
+    <t>10120003,10</t>
   </si>
   <si>
     <t>25倍以上中奖概率增高</t>
   </si>
   <si>
-    <t>10120003,10</t>
+    <t>10120004,10</t>
   </si>
   <si>
     <t>财神到游戏概率提升</t>
@@ -309,10 +309,7 @@
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
-    <t>10120005,10</t>
-  </si>
-  <si>
-    <t>10180001,10</t>
+    <t>10120006,10</t>
   </si>
   <si>
     <t>10180002,10</t>
@@ -324,7 +321,7 @@
     <t>10180004,10</t>
   </si>
   <si>
-    <t>10180006,10</t>
+    <t>10180005,10</t>
   </si>
   <si>
     <t>10180007,10</t>
@@ -333,7 +330,7 @@
     <t>10180008,10</t>
   </si>
   <si>
-    <t>10250001,10</t>
+    <t>10180009,10</t>
   </si>
   <si>
     <t>10250002,10</t>
@@ -345,7 +342,7 @@
     <t>10250004,10</t>
   </si>
   <si>
-    <t>10250006,10</t>
+    <t>10250005,10</t>
   </si>
   <si>
     <t>10250007,10</t>
@@ -354,7 +351,7 @@
     <t>10250008,10</t>
   </si>
   <si>
-    <t>10310001,10</t>
+    <t>10250009,10</t>
   </si>
   <si>
     <t>10310002,10</t>
@@ -366,12 +363,15 @@
     <t>10310004,10</t>
   </si>
   <si>
-    <t>10310006,10</t>
+    <t>10310005,10</t>
   </si>
   <si>
     <t>10310007,10</t>
   </si>
   <si>
+    <t>10310008,10</t>
+  </si>
+  <si>
     <t>触发bonus模式概率提升</t>
   </si>
   <si>
@@ -381,19 +381,16 @@
     <t>bonus模式25倍及以上奖励提升</t>
   </si>
   <si>
-    <t>10310009,10</t>
+    <t>10310010,10</t>
   </si>
   <si>
     <t>bonus模式50倍及以上奖励提升</t>
   </si>
   <si>
-    <t>10310010,10</t>
-  </si>
-  <si>
     <t>10310011,10</t>
   </si>
   <si>
-    <t>10220001,10</t>
+    <t>10310012,10</t>
   </si>
   <si>
     <t>10220002,10</t>
@@ -402,7 +399,7 @@
     <t>10220003,10</t>
   </si>
   <si>
-    <t>10220005,10</t>
+    <t>10220004,10</t>
   </si>
   <si>
     <t>10220006,10</t>
@@ -411,7 +408,7 @@
     <t>10220007,10</t>
   </si>
   <si>
-    <t>10210001,10</t>
+    <t>10220008,10</t>
   </si>
   <si>
     <t>10210002,10</t>
@@ -423,13 +420,13 @@
     <t>10210004,10</t>
   </si>
   <si>
-    <t>10210006,10</t>
+    <t>10210005,10</t>
   </si>
   <si>
     <t>10210007,10</t>
   </si>
   <si>
-    <t>10210009,10</t>
+    <t>10210008,10</t>
   </si>
   <si>
     <t>10210010,10</t>
@@ -438,7 +435,7 @@
     <t>10210011,10</t>
   </si>
   <si>
-    <t>10390001,10</t>
+    <t>10210012,10</t>
   </si>
   <si>
     <t>10390002,10</t>
@@ -450,7 +447,7 @@
     <t>10390004,10</t>
   </si>
   <si>
-    <t>10390006,10</t>
+    <t>10390005,10</t>
   </si>
   <si>
     <t>10390007,10</t>
@@ -459,7 +456,7 @@
     <t>10390008,10</t>
   </si>
   <si>
-    <t>10200001,10</t>
+    <t>10390009,10</t>
   </si>
   <si>
     <t>10200002,10</t>
@@ -471,7 +468,7 @@
     <t>10200004,10</t>
   </si>
   <si>
-    <t>10200006,10</t>
+    <t>10200005,10</t>
   </si>
   <si>
     <t>10200007,10</t>
@@ -480,7 +477,7 @@
     <t>10200008,10</t>
   </si>
   <si>
-    <t>10270001,10</t>
+    <t>10200009,10</t>
   </si>
   <si>
     <t>10270002,10</t>
@@ -489,7 +486,7 @@
     <t>10270003,10</t>
   </si>
   <si>
-    <t>10270005,10</t>
+    <t>10270004,10</t>
   </si>
   <si>
     <t>10270006,10</t>
@@ -498,7 +495,7 @@
     <t>10270007,10</t>
   </si>
   <si>
-    <t>10150001,10</t>
+    <t>10270008,10</t>
   </si>
   <si>
     <t>10150002,10</t>
@@ -510,40 +507,43 @@
     <t>10150004,10</t>
   </si>
   <si>
-    <t>10150006,10</t>
+    <t>10150005,10</t>
   </si>
   <si>
     <t>10150007,10</t>
   </si>
   <si>
+    <t>10150008,10</t>
+  </si>
+  <si>
     <t>触发许愿百搭概率提升</t>
   </si>
   <si>
     <t>许愿百搭中奖概率提升</t>
   </si>
   <si>
-    <t>10150009,10</t>
+    <t>10150010,10</t>
   </si>
   <si>
     <t>许愿百搭30倍及以上中奖概率提升</t>
   </si>
   <si>
-    <t>10150010,10</t>
+    <t>10150011,10</t>
   </si>
   <si>
     <t>许愿百搭50倍及以上中奖概率提升</t>
   </si>
   <si>
-    <t>10150011,10</t>
+    <t>10150012,10</t>
   </si>
   <si>
     <t>许愿百搭100倍及以上中奖概率提升</t>
   </si>
   <si>
-    <t>10150012,10</t>
-  </si>
-  <si>
     <t>10150013,10</t>
+  </si>
+  <si>
+    <t>10150014,10</t>
   </si>
 </sst>
 </file>
@@ -715,12 +715,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -112,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="151">
   <si>
     <t>属性id</t>
   </si>
@@ -438,19 +433,34 @@
     <t>10210012,10</t>
   </si>
   <si>
+    <t>10390004,10</t>
+  </si>
+  <si>
+    <t>sweet win中奖概率提升</t>
+  </si>
+  <si>
+    <t>big win中奖概率提升</t>
+  </si>
+  <si>
+    <t>10390003,10</t>
+  </si>
+  <si>
+    <t>mega win中奖概率提升</t>
+  </si>
+  <si>
     <t>10390002,10</t>
   </si>
   <si>
-    <t>10390003,10</t>
-  </si>
-  <si>
-    <t>10390004,10</t>
+    <t>epic win中奖概率提升</t>
   </si>
   <si>
     <t>10390005,10</t>
   </si>
   <si>
-    <t>10390007,10</t>
+    <t>legendary win中奖概率提升</t>
+  </si>
+  <si>
+    <t>10390006,10</t>
   </si>
   <si>
     <t>10390008,10</t>
@@ -459,6 +469,9 @@
     <t>10390009,10</t>
   </si>
   <si>
+    <t>10390010,10</t>
+  </si>
+  <si>
     <t>10200002,10</t>
   </si>
   <si>
@@ -480,13 +493,16 @@
     <t>10200009,10</t>
   </si>
   <si>
+    <t>10270004,10</t>
+  </si>
+  <si>
+    <t>10270003,10</t>
+  </si>
+  <si>
     <t>10270002,10</t>
   </si>
   <si>
-    <t>10270003,10</t>
-  </si>
-  <si>
-    <t>10270004,10</t>
+    <t>10270005,10</t>
   </si>
   <si>
     <t>10270006,10</t>
@@ -556,7 +572,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,6 +583,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1088,137 +1110,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1307,6 +1329,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1620,7 +1648,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="8" customWidth="1"/>
@@ -4076,6 +4104,9 @@
       <c r="G87" s="3">
         <v>2</v>
       </c>
+      <c r="H87" s="20" t="s">
+        <v>108</v>
+      </c>
       <c r="I87" s="3">
         <v>1</v>
       </c>
@@ -4090,11 +4121,11 @@
       <c r="B88" s="3">
         <v>103900</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>44</v>
+      <c r="C88" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="D88" s="20">
-        <v>4020004</v>
+        <v>4020640</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>25</v>
@@ -4102,9 +4133,7 @@
       <c r="G88" s="20">
         <v>2</v>
       </c>
-      <c r="H88" s="20" t="s">
-        <v>108</v>
-      </c>
+      <c r="H88" s="20"/>
       <c r="I88" s="3">
         <v>2</v>
       </c>
@@ -4119,11 +4148,11 @@
       <c r="B89" s="3">
         <v>103900</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>46</v>
+      <c r="C89" s="30" t="s">
+        <v>110</v>
       </c>
       <c r="D89" s="20">
-        <v>4020094</v>
+        <v>4020641</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>25</v>
@@ -4132,7 +4161,7 @@
         <v>2</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I89" s="3">
         <v>3</v>
@@ -4148,11 +4177,11 @@
       <c r="B90" s="3">
         <v>103900</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>48</v>
+      <c r="C90" s="30" t="s">
+        <v>112</v>
       </c>
       <c r="D90" s="20">
-        <v>4020345</v>
+        <v>4020642</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>25</v>
@@ -4161,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I90" s="3">
         <v>4</v>
@@ -4177,11 +4206,11 @@
       <c r="B91" s="3">
         <v>103900</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>50</v>
+      <c r="C91" s="30" t="s">
+        <v>114</v>
       </c>
       <c r="D91" s="20">
-        <v>4020346</v>
+        <v>4020643</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>25</v>
@@ -4190,7 +4219,7 @@
         <v>2</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I91" s="3">
         <v>5</v>
@@ -4206,17 +4235,20 @@
       <c r="B92" s="3">
         <v>103900</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>52</v>
+      <c r="C92" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="D92" s="20">
-        <v>4020347</v>
+        <v>4020644</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G92" s="20">
         <v>2</v>
+      </c>
+      <c r="H92" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="I92" s="3">
         <v>6</v>
@@ -4233,19 +4265,16 @@
         <v>103900</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D93" s="20">
-        <v>4020349</v>
+        <v>4020347</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G93" s="3">
-        <v>2</v>
-      </c>
-      <c r="H93" s="20" t="s">
-        <v>112</v>
+      <c r="G93" s="20">
+        <v>2</v>
       </c>
       <c r="I93" s="3">
         <v>7</v>
@@ -4262,19 +4291,19 @@
         <v>103900</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D94" s="20">
-        <v>4020350</v>
+        <v>4020349</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G94" s="20">
+      <c r="G94" s="3">
         <v>2</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I94" s="3">
         <v>8</v>
@@ -4291,19 +4320,19 @@
         <v>103900</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D95" s="20">
-        <v>4020007</v>
+        <v>4020350</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G95" s="3">
+        <v>35</v>
+      </c>
+      <c r="G95" s="20">
         <v>2</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I95" s="3">
         <v>9</v>
@@ -4312,85 +4341,85 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" s="4" customFormat="1" spans="1:10">
-      <c r="A96" s="4">
-        <v>10200001</v>
-      </c>
-      <c r="B96" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D96" s="22">
-        <v>4020002</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F96" s="4">
-        <v>1</v>
-      </c>
-      <c r="G96" s="4">
-        <v>2</v>
-      </c>
-      <c r="I96" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J96" s="4">
-        <v>0</v>
+    <row r="96" s="3" customFormat="1" spans="1:10">
+      <c r="A96" s="3">
+        <v>10390011</v>
+      </c>
+      <c r="B96" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D96" s="20">
+        <v>4020007</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2</v>
+      </c>
+      <c r="H96" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I96" s="3">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="97" s="4" customFormat="1" spans="1:10">
       <c r="A97" s="4">
-        <v>10200002</v>
+        <v>10200001</v>
       </c>
       <c r="B97" s="4">
         <v>102000</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D97" s="22">
-        <v>4020003</v>
+        <v>4020002</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1</v>
       </c>
       <c r="G97" s="4">
         <v>2</v>
       </c>
       <c r="I97" s="4">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J97" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" s="4" customFormat="1" spans="1:10">
       <c r="A98" s="4">
-        <v>10200003</v>
+        <v>10200002</v>
       </c>
       <c r="B98" s="4">
         <v>102000</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D98" s="22">
-        <v>4020004</v>
+        <v>4020003</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G98" s="22">
-        <v>2</v>
-      </c>
-      <c r="H98" s="22" t="s">
-        <v>115</v>
+      <c r="G98" s="4">
+        <v>2</v>
       </c>
       <c r="I98" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" s="4">
         <v>100</v>
@@ -4398,28 +4427,28 @@
     </row>
     <row r="99" s="4" customFormat="1" spans="1:10">
       <c r="A99" s="4">
-        <v>10200004</v>
+        <v>10200003</v>
       </c>
       <c r="B99" s="4">
         <v>102000</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D99" s="22">
-        <v>4020005</v>
+        <v>4020004</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="22">
         <v>2</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I99" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J99" s="4">
         <v>100</v>
@@ -4427,28 +4456,28 @@
     </row>
     <row r="100" s="4" customFormat="1" spans="1:10">
       <c r="A100" s="4">
-        <v>10200005</v>
+        <v>10200004</v>
       </c>
       <c r="B100" s="4">
         <v>102000</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D100" s="22">
-        <v>4020345</v>
+        <v>4020005</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G100" s="22">
+      <c r="G100" s="4">
         <v>2</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I100" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J100" s="4">
         <v>100</v>
@@ -4456,28 +4485,28 @@
     </row>
     <row r="101" s="4" customFormat="1" spans="1:10">
       <c r="A101" s="4">
-        <v>10200006</v>
+        <v>10200005</v>
       </c>
       <c r="B101" s="4">
         <v>102000</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D101" s="22">
-        <v>4020346</v>
+        <v>4020345</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G101" s="22">
         <v>2</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I101" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J101" s="4">
         <v>100</v>
@@ -4485,25 +4514,28 @@
     </row>
     <row r="102" s="4" customFormat="1" spans="1:10">
       <c r="A102" s="4">
-        <v>10200007</v>
+        <v>10200006</v>
       </c>
       <c r="B102" s="4">
         <v>102000</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D102" s="22">
-        <v>4020347</v>
+        <v>4020346</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G102" s="22">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="G102" s="4">
+        <v>2</v>
+      </c>
+      <c r="H102" s="22" t="s">
+        <v>124</v>
       </c>
       <c r="I102" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J102" s="4">
         <v>100</v>
@@ -4511,28 +4543,25 @@
     </row>
     <row r="103" s="4" customFormat="1" spans="1:10">
       <c r="A103" s="4">
-        <v>10200008</v>
+        <v>10200007</v>
       </c>
       <c r="B103" s="4">
         <v>102000</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D103" s="22">
-        <v>4020349</v>
+        <v>4020347</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G103" s="4">
-        <v>2</v>
-      </c>
-      <c r="H103" s="22" t="s">
-        <v>119</v>
+      <c r="G103" s="22">
+        <v>2</v>
       </c>
       <c r="I103" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J103" s="4">
         <v>100</v>
@@ -4540,28 +4569,28 @@
     </row>
     <row r="104" s="4" customFormat="1" spans="1:10">
       <c r="A104" s="4">
-        <v>10200009</v>
+        <v>10200008</v>
       </c>
       <c r="B104" s="4">
         <v>102000</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D104" s="22">
-        <v>4020350</v>
+        <v>4020349</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G104" s="22">
+      <c r="G104" s="4">
         <v>2</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I104" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J104" s="4">
         <v>100</v>
@@ -4569,100 +4598,103 @@
     </row>
     <row r="105" s="4" customFormat="1" spans="1:10">
       <c r="A105" s="4">
-        <v>10200010</v>
+        <v>10200009</v>
       </c>
       <c r="B105" s="4">
         <v>102000</v>
       </c>
       <c r="C105" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D105" s="22">
+        <v>4020350</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G105" s="22">
+        <v>2</v>
+      </c>
+      <c r="H105" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="I105" s="4">
+        <v>8</v>
+      </c>
+      <c r="J105" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" s="4" customFormat="1" spans="1:10">
+      <c r="A106" s="4">
+        <v>10200010</v>
+      </c>
+      <c r="B106" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C106" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="22">
+      <c r="D106" s="22">
         <v>4020007</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="E106" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G105" s="4">
-        <v>2</v>
-      </c>
-      <c r="H105" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="I105" s="4">
+      <c r="G106" s="4">
+        <v>2</v>
+      </c>
+      <c r="H106" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="I106" s="4">
         <v>9</v>
       </c>
-      <c r="J105" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="106" s="5" customFormat="1" spans="1:10">
-      <c r="A106" s="5">
-        <v>10270001</v>
-      </c>
-      <c r="B106" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D106" s="24">
-        <v>4020002</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F106" s="5">
-        <v>1</v>
-      </c>
-      <c r="G106" s="5">
-        <v>2</v>
-      </c>
-      <c r="I106" s="5">
-        <v>-1</v>
-      </c>
-      <c r="J106" s="5">
-        <v>0</v>
+      <c r="J106" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="107" s="5" customFormat="1" spans="1:10">
       <c r="A107" s="5">
-        <v>10270002</v>
+        <v>10270001</v>
       </c>
       <c r="B107" s="5">
         <v>102700</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D107" s="24">
-        <v>4020003</v>
+        <v>4020002</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F107" s="5">
+        <v>1</v>
       </c>
       <c r="G107" s="5">
         <v>2</v>
       </c>
       <c r="I107" s="5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J107" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" s="5" customFormat="1" spans="1:10">
       <c r="A108" s="5">
-        <v>10270003</v>
+        <v>10270002</v>
       </c>
       <c r="B108" s="5">
         <v>102700</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D108" s="24">
-        <v>4020004</v>
+        <v>4020003</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>25</v>
@@ -4671,10 +4703,10 @@
         <v>2</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I108" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="5">
         <v>100</v>
@@ -4682,16 +4714,16 @@
     </row>
     <row r="109" s="5" customFormat="1" spans="1:10">
       <c r="A109" s="5">
-        <v>10270004</v>
+        <v>10270003</v>
       </c>
       <c r="B109" s="5">
         <v>102700</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>59</v>
+      <c r="C109" s="31" t="s">
+        <v>109</v>
       </c>
       <c r="D109" s="24">
-        <v>4020094</v>
+        <v>4020640</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>25</v>
@@ -4699,11 +4731,9 @@
       <c r="G109" s="5">
         <v>2</v>
       </c>
-      <c r="H109" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="H109" s="5"/>
       <c r="I109" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J109" s="5">
         <v>100</v>
@@ -4711,16 +4741,16 @@
     </row>
     <row r="110" s="5" customFormat="1" spans="1:10">
       <c r="A110" s="5">
-        <v>10270005</v>
+        <v>10270004</v>
       </c>
       <c r="B110" s="5">
         <v>102700</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>61</v>
+      <c r="C110" s="31" t="s">
+        <v>110</v>
       </c>
       <c r="D110" s="24">
-        <v>4020095</v>
+        <v>4020641</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>25</v>
@@ -4729,10 +4759,10 @@
         <v>2</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I110" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J110" s="5">
         <v>100</v>
@@ -4740,25 +4770,28 @@
     </row>
     <row r="111" s="5" customFormat="1" spans="1:10">
       <c r="A111" s="5">
-        <v>10270006</v>
+        <v>10270005</v>
       </c>
       <c r="B111" s="5">
         <v>102700</v>
       </c>
-      <c r="C111" s="5" t="s">
-        <v>52</v>
+      <c r="C111" s="31" t="s">
+        <v>112</v>
       </c>
       <c r="D111" s="24">
-        <v>4020347</v>
+        <v>4020642</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G111" s="5">
         <v>2</v>
       </c>
+      <c r="H111" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="I111" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J111" s="5">
         <v>100</v>
@@ -4766,28 +4799,28 @@
     </row>
     <row r="112" s="5" customFormat="1" spans="1:10">
       <c r="A112" s="5">
-        <v>10270007</v>
+        <v>10270006</v>
       </c>
       <c r="B112" s="5">
         <v>102700</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>53</v>
+      <c r="C112" s="31" t="s">
+        <v>114</v>
       </c>
       <c r="D112" s="24">
-        <v>4020349</v>
+        <v>4020643</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G112" s="5">
         <v>2</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I112" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J112" s="5">
         <v>100</v>
@@ -4795,28 +4828,28 @@
     </row>
     <row r="113" s="5" customFormat="1" spans="1:10">
       <c r="A113" s="5">
-        <v>10270008</v>
+        <v>10270007</v>
       </c>
       <c r="B113" s="5">
         <v>102700</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>55</v>
+      <c r="C113" s="31" t="s">
+        <v>116</v>
       </c>
       <c r="D113" s="24">
-        <v>4020350</v>
+        <v>4020644</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G113" s="5">
         <v>2</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I113" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J113" s="5">
         <v>100</v>
@@ -4824,158 +4857,158 @@
     </row>
     <row r="114" s="5" customFormat="1" spans="1:10">
       <c r="A114" s="5">
-        <v>10270009</v>
+        <v>10270008</v>
       </c>
       <c r="B114" s="5">
         <v>102700</v>
       </c>
       <c r="C114" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D114" s="24">
+        <v>4020347</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G114" s="5">
+        <v>2</v>
+      </c>
+      <c r="I114" s="5">
+        <v>7</v>
+      </c>
+      <c r="J114" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" s="5" customFormat="1" spans="1:10">
+      <c r="A115" s="5">
+        <v>10270009</v>
+      </c>
+      <c r="B115" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D115" s="24">
+        <v>4020349</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G115" s="5">
+        <v>2</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I115" s="5">
+        <v>8</v>
+      </c>
+      <c r="J115" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" s="5" customFormat="1" spans="1:10">
+      <c r="A116" s="5">
+        <v>10270010</v>
+      </c>
+      <c r="B116" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D116" s="24">
+        <v>4020350</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G116" s="5">
+        <v>2</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I116" s="5">
+        <v>9</v>
+      </c>
+      <c r="J116" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" s="5" customFormat="1" spans="1:10">
+      <c r="A117" s="5">
+        <v>10270011</v>
+      </c>
+      <c r="B117" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D114" s="24">
+      <c r="D117" s="24">
         <v>4020007</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E117" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G114" s="5">
-        <v>2</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="I114" s="5">
-        <v>8</v>
-      </c>
-      <c r="J114" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="115" s="1" customFormat="1" spans="1:10">
-      <c r="A115" s="1">
-        <v>10150001</v>
-      </c>
-      <c r="B115" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D115" s="16">
-        <v>4020002</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F115" s="1">
-        <v>1</v>
-      </c>
-      <c r="G115" s="1">
-        <v>2</v>
-      </c>
-      <c r="I115" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J115" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="1" spans="1:10">
-      <c r="A116" s="1">
-        <v>10150002</v>
-      </c>
-      <c r="B116" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D116" s="16">
-        <v>4020003</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G116" s="1">
-        <v>2</v>
-      </c>
-      <c r="I116" s="1">
-        <v>1</v>
-      </c>
-      <c r="J116" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="1" spans="1:10">
-      <c r="A117" s="1">
-        <v>10150003</v>
-      </c>
-      <c r="B117" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D117" s="16">
-        <v>4020004</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G117" s="1">
-        <v>2</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I117" s="1">
-        <v>2</v>
-      </c>
-      <c r="J117" s="1">
+      <c r="G117" s="5">
+        <v>2</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I117" s="5">
+        <v>10</v>
+      </c>
+      <c r="J117" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" spans="1:10">
       <c r="A118" s="1">
-        <v>10150004</v>
+        <v>10150001</v>
       </c>
       <c r="B118" s="1">
         <v>101500</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D118" s="16">
-        <v>4020094</v>
+        <v>4020002</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F118" s="1">
+        <v>1</v>
       </c>
       <c r="G118" s="1">
         <v>2</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="I118" s="1">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="J118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" spans="1:10">
       <c r="A119" s="1">
-        <v>10150005</v>
+        <v>10150002</v>
       </c>
       <c r="B119" s="1">
         <v>101500</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D119" s="16">
-        <v>4020345</v>
+        <v>4020003</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>25</v>
@@ -4983,11 +5016,8 @@
       <c r="G119" s="1">
         <v>2</v>
       </c>
-      <c r="H119" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="I119" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J119" s="1">
         <v>100</v>
@@ -4995,16 +5025,16 @@
     </row>
     <row r="120" s="1" customFormat="1" spans="1:10">
       <c r="A120" s="1">
-        <v>10150006</v>
+        <v>10150003</v>
       </c>
       <c r="B120" s="1">
         <v>101500</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D120" s="16">
-        <v>4020346</v>
+        <v>4020004</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>25</v>
@@ -5013,10 +5043,10 @@
         <v>2</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I120" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J120" s="1">
         <v>100</v>
@@ -5024,25 +5054,28 @@
     </row>
     <row r="121" s="1" customFormat="1" spans="1:10">
       <c r="A121" s="1">
-        <v>10150007</v>
+        <v>10150004</v>
       </c>
       <c r="B121" s="1">
         <v>101500</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D121" s="16">
-        <v>4020347</v>
+        <v>4020094</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G121" s="1">
         <v>2</v>
       </c>
+      <c r="H121" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="I121" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J121" s="1">
         <v>100</v>
@@ -5050,28 +5083,28 @@
     </row>
     <row r="122" s="1" customFormat="1" spans="1:10">
       <c r="A122" s="1">
-        <v>10150008</v>
+        <v>10150005</v>
       </c>
       <c r="B122" s="1">
         <v>101500</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D122" s="16">
-        <v>4020349</v>
+        <v>4020345</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G122" s="1">
         <v>2</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I122" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J122" s="1">
         <v>100</v>
@@ -5079,28 +5112,28 @@
     </row>
     <row r="123" s="1" customFormat="1" spans="1:10">
       <c r="A123" s="1">
-        <v>10150009</v>
+        <v>10150006</v>
       </c>
       <c r="B123" s="1">
         <v>101500</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D123" s="16">
-        <v>4020350</v>
+        <v>4020346</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G123" s="1">
         <v>2</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I123" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J123" s="1">
         <v>100</v>
@@ -5108,25 +5141,25 @@
     </row>
     <row r="124" s="1" customFormat="1" spans="1:10">
       <c r="A124" s="1">
-        <v>10150010</v>
+        <v>10150007</v>
       </c>
       <c r="B124" s="1">
         <v>101500</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="D124" s="16">
-        <v>4020466</v>
+        <v>4020347</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="G124" s="1">
         <v>2</v>
       </c>
       <c r="I124" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J124" s="1">
         <v>100</v>
@@ -5134,28 +5167,28 @@
     </row>
     <row r="125" s="1" customFormat="1" spans="1:10">
       <c r="A125" s="1">
-        <v>10150011</v>
+        <v>10150008</v>
       </c>
       <c r="B125" s="1">
         <v>101500</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="D125" s="16">
-        <v>4020467</v>
+        <v>4020349</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="G125" s="1">
         <v>2</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I125" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J125" s="1">
         <v>100</v>
@@ -5163,28 +5196,28 @@
     </row>
     <row r="126" s="1" customFormat="1" spans="1:10">
       <c r="A126" s="1">
-        <v>10150012</v>
+        <v>10150009</v>
       </c>
       <c r="B126" s="1">
         <v>101500</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="D126" s="16">
-        <v>4020468</v>
+        <v>4020350</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="G126" s="1">
         <v>2</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I126" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J126" s="1">
         <v>100</v>
@@ -5192,16 +5225,16 @@
     </row>
     <row r="127" s="1" customFormat="1" spans="1:10">
       <c r="A127" s="1">
-        <v>10150013</v>
+        <v>10150010</v>
       </c>
       <c r="B127" s="1">
         <v>101500</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D127" s="16">
-        <v>4020469</v>
+        <v>4020466</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>87</v>
@@ -5209,11 +5242,8 @@
       <c r="G127" s="1">
         <v>2</v>
       </c>
-      <c r="H127" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="I127" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J127" s="1">
         <v>100</v>
@@ -5221,16 +5251,16 @@
     </row>
     <row r="128" s="1" customFormat="1" spans="1:10">
       <c r="A128" s="1">
-        <v>10150014</v>
+        <v>10150011</v>
       </c>
       <c r="B128" s="1">
         <v>101500</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D128" s="16">
-        <v>4020470</v>
+        <v>4020467</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>87</v>
@@ -5239,10 +5269,10 @@
         <v>2</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I128" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J128" s="1">
         <v>100</v>
@@ -5250,30 +5280,117 @@
     </row>
     <row r="129" s="1" customFormat="1" spans="1:10">
       <c r="A129" s="1">
-        <v>10150015</v>
+        <v>10150012</v>
       </c>
       <c r="B129" s="1">
         <v>101500</v>
       </c>
       <c r="C129" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D129" s="16">
+        <v>4020468</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G129" s="1">
+        <v>2</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I129" s="1">
+        <v>12</v>
+      </c>
+      <c r="J129" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="1" spans="1:10">
+      <c r="A130" s="1">
+        <v>10150013</v>
+      </c>
+      <c r="B130" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D130" s="16">
+        <v>4020469</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G130" s="1">
+        <v>2</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I130" s="1">
+        <v>13</v>
+      </c>
+      <c r="J130" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="1" spans="1:10">
+      <c r="A131" s="1">
+        <v>10150014</v>
+      </c>
+      <c r="B131" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D131" s="16">
+        <v>4020470</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G131" s="1">
+        <v>2</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I131" s="1">
+        <v>14</v>
+      </c>
+      <c r="J131" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" s="1" customFormat="1" spans="1:10">
+      <c r="A132" s="1">
+        <v>10150015</v>
+      </c>
+      <c r="B132" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D129" s="16">
+      <c r="D132" s="16">
         <v>4020007</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G129" s="1">
-        <v>2</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I129" s="1">
+      <c r="G132" s="1">
+        <v>2</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I132" s="1">
         <v>15</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J132" s="1">
         <v>100</v>
       </c>
     </row>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -107,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="159">
   <si>
     <t>属性id</t>
   </si>
@@ -433,43 +438,67 @@
     <t>10210012,10</t>
   </si>
   <si>
+    <t>10390006,10</t>
+  </si>
+  <si>
+    <t>解锁sweet win奖励</t>
+  </si>
+  <si>
+    <t>sweet win中奖概率提升</t>
+  </si>
+  <si>
+    <t>10390003,1</t>
+  </si>
+  <si>
+    <t>解锁big win奖励</t>
+  </si>
+  <si>
     <t>10390004,10</t>
   </si>
   <si>
-    <t>sweet win中奖概率提升</t>
-  </si>
-  <si>
     <t>big win中奖概率提升</t>
   </si>
   <si>
-    <t>10390003,10</t>
+    <t>10390005,1</t>
+  </si>
+  <si>
+    <t>解锁mega win奖励</t>
+  </si>
+  <si>
+    <t>10390000,10</t>
   </si>
   <si>
     <t>mega win中奖概率提升</t>
   </si>
   <si>
-    <t>10390002,10</t>
+    <t>10390007,1</t>
+  </si>
+  <si>
+    <t>解锁epic win奖励</t>
+  </si>
+  <si>
+    <t>10390008,10</t>
   </si>
   <si>
     <t>epic win中奖概率提升</t>
   </si>
   <si>
-    <t>10390005,10</t>
+    <t>10390009,1</t>
+  </si>
+  <si>
+    <t>解锁legendary win奖励</t>
+  </si>
+  <si>
+    <t>10390010,10</t>
   </si>
   <si>
     <t>legendary win中奖概率提升</t>
   </si>
   <si>
-    <t>10390006,10</t>
-  </si>
-  <si>
-    <t>10390008,10</t>
+    <t>10390011,1</t>
   </si>
   <si>
     <t>10390009,10</t>
-  </si>
-  <si>
-    <t>10390010,10</t>
   </si>
   <si>
     <t>10200002,10</t>
@@ -1648,12 +1677,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="8" customWidth="1"/>
     <col min="2" max="2" width="16" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="23.625" style="8" customWidth="1"/>
     <col min="4" max="4" width="26.875" style="9" customWidth="1"/>
     <col min="5" max="8" width="26.875" style="8" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="8" customWidth="1"/>
@@ -4114,7 +4143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" s="3" customFormat="1" spans="1:10">
+    <row r="88" s="3" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A88" s="3">
         <v>10390003</v>
       </c>
@@ -4124,9 +4153,7 @@
       <c r="C88" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="D88" s="20">
-        <v>4020640</v>
-      </c>
+      <c r="D88" s="20"/>
       <c r="E88" s="3" t="s">
         <v>25</v>
       </c>
@@ -4136,9 +4163,6 @@
       <c r="H88" s="20"/>
       <c r="I88" s="3">
         <v>2</v>
-      </c>
-      <c r="J88" s="3">
-        <v>100</v>
       </c>
     </row>
     <row r="89" s="3" customFormat="1" spans="1:10">
@@ -4152,12 +4176,12 @@
         <v>110</v>
       </c>
       <c r="D89" s="20">
-        <v>4020641</v>
+        <v>4020640</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="20">
         <v>2</v>
       </c>
       <c r="H89" s="20" t="s">
@@ -4180,13 +4204,11 @@
       <c r="C90" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D90" s="20">
-        <v>4020642</v>
-      </c>
+      <c r="D90" s="20"/>
       <c r="E90" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G90" s="20">
+      <c r="G90" s="3">
         <v>2</v>
       </c>
       <c r="H90" s="20" t="s">
@@ -4194,9 +4216,6 @@
       </c>
       <c r="I90" s="3">
         <v>4</v>
-      </c>
-      <c r="J90" s="3">
-        <v>100</v>
       </c>
     </row>
     <row r="91" s="3" customFormat="1" spans="1:10">
@@ -4210,7 +4229,7 @@
         <v>114</v>
       </c>
       <c r="D91" s="20">
-        <v>4020643</v>
+        <v>4020641</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>25</v>
@@ -4238,13 +4257,11 @@
       <c r="C92" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D92" s="20">
-        <v>4020644</v>
-      </c>
+      <c r="D92" s="20"/>
       <c r="E92" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G92" s="20">
+      <c r="G92" s="3">
         <v>2</v>
       </c>
       <c r="H92" s="20" t="s">
@@ -4252,9 +4269,6 @@
       </c>
       <c r="I92" s="3">
         <v>6</v>
-      </c>
-      <c r="J92" s="3">
-        <v>100</v>
       </c>
     </row>
     <row r="93" s="3" customFormat="1" spans="1:10">
@@ -4264,17 +4278,20 @@
       <c r="B93" s="3">
         <v>103900</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>52</v>
+      <c r="C93" s="30" t="s">
+        <v>118</v>
       </c>
       <c r="D93" s="20">
-        <v>4020347</v>
+        <v>4020642</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G93" s="20">
         <v>2</v>
+      </c>
+      <c r="H93" s="20" t="s">
+        <v>119</v>
       </c>
       <c r="I93" s="3">
         <v>7</v>
@@ -4290,26 +4307,21 @@
       <c r="B94" s="3">
         <v>103900</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D94" s="20">
-        <v>4020349</v>
-      </c>
+      <c r="C94" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" s="20"/>
       <c r="E94" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G94" s="3">
         <v>2</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I94" s="3">
         <v>8</v>
-      </c>
-      <c r="J94" s="3">
-        <v>100</v>
       </c>
     </row>
     <row r="95" s="3" customFormat="1" spans="1:10">
@@ -4319,20 +4331,20 @@
       <c r="B95" s="3">
         <v>103900</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>55</v>
+      <c r="C95" s="30" t="s">
+        <v>122</v>
       </c>
       <c r="D95" s="20">
-        <v>4020350</v>
+        <v>4020643</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G95" s="20">
+        <v>25</v>
+      </c>
+      <c r="G95" s="3">
         <v>2</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I95" s="3">
         <v>9</v>
@@ -4348,220 +4360,215 @@
       <c r="B96" s="3">
         <v>103900</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D96" s="20">
-        <v>4020007</v>
-      </c>
+      <c r="C96" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96" s="20"/>
       <c r="E96" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G96" s="3">
         <v>2</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I96" s="3">
         <v>10</v>
       </c>
-      <c r="J96" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" s="4" customFormat="1" spans="1:10">
-      <c r="A97" s="4">
-        <v>10200001</v>
-      </c>
-      <c r="B97" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D97" s="22">
-        <v>4020002</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F97" s="4">
-        <v>1</v>
-      </c>
-      <c r="G97" s="4">
-        <v>2</v>
-      </c>
-      <c r="I97" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J97" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" s="4" customFormat="1" spans="1:10">
-      <c r="A98" s="4">
-        <v>10200002</v>
-      </c>
-      <c r="B98" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D98" s="22">
-        <v>4020003</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G98" s="4">
-        <v>2</v>
-      </c>
-      <c r="I98" s="4">
-        <v>1</v>
-      </c>
-      <c r="J98" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="99" s="4" customFormat="1" spans="1:10">
-      <c r="A99" s="4">
-        <v>10200003</v>
-      </c>
-      <c r="B99" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" s="22">
-        <v>4020004</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G99" s="22">
-        <v>2</v>
-      </c>
-      <c r="H99" s="22" t="s">
+    </row>
+    <row r="97" s="3" customFormat="1" spans="1:10">
+      <c r="A97" s="3">
+        <v>10390012</v>
+      </c>
+      <c r="B97" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C97" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D97" s="20">
+        <v>4020644</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="20">
+        <v>2</v>
+      </c>
+      <c r="H97" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="I97" s="3">
+        <v>11</v>
+      </c>
+      <c r="J97" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" s="3" customFormat="1" spans="1:10">
+      <c r="A98" s="3">
+        <v>10390013</v>
+      </c>
+      <c r="B98" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D98" s="20">
+        <v>4020347</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G98" s="20">
+        <v>2</v>
+      </c>
+      <c r="I98" s="3">
+        <v>12</v>
+      </c>
+      <c r="J98" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" s="3" customFormat="1" spans="1:10">
+      <c r="A99" s="3">
+        <v>10390014</v>
+      </c>
+      <c r="B99" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D99" s="20">
+        <v>4020349</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G99" s="3">
+        <v>2</v>
+      </c>
+      <c r="H99" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="I99" s="4">
-        <v>2</v>
-      </c>
-      <c r="J99" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" s="4" customFormat="1" spans="1:10">
-      <c r="A100" s="4">
-        <v>10200004</v>
-      </c>
-      <c r="B100" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D100" s="22">
-        <v>4020005</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G100" s="4">
-        <v>2</v>
-      </c>
-      <c r="H100" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="I100" s="4">
-        <v>3</v>
-      </c>
-      <c r="J100" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" s="4" customFormat="1" spans="1:10">
-      <c r="A101" s="4">
-        <v>10200005</v>
-      </c>
-      <c r="B101" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D101" s="22">
-        <v>4020345</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G101" s="22">
-        <v>2</v>
-      </c>
-      <c r="H101" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="I101" s="4">
-        <v>4</v>
-      </c>
-      <c r="J101" s="4">
+      <c r="I99" s="3">
+        <v>13</v>
+      </c>
+      <c r="J99" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" s="3" customFormat="1" spans="1:10">
+      <c r="A100" s="3">
+        <v>10390015</v>
+      </c>
+      <c r="B100" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D100" s="20">
+        <v>4020350</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G100" s="20">
+        <v>2</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="I100" s="3">
+        <v>14</v>
+      </c>
+      <c r="J100" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" s="3" customFormat="1" spans="1:10">
+      <c r="A101" s="3">
+        <v>10390016</v>
+      </c>
+      <c r="B101" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D101" s="20">
+        <v>4020007</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2</v>
+      </c>
+      <c r="H101" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="I101" s="3">
+        <v>15</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="102" s="4" customFormat="1" spans="1:10">
       <c r="A102" s="4">
-        <v>10200006</v>
+        <v>10200001</v>
       </c>
       <c r="B102" s="4">
         <v>102000</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D102" s="22">
-        <v>4020346</v>
+        <v>4020002</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F102" s="4">
+        <v>1</v>
       </c>
       <c r="G102" s="4">
         <v>2</v>
       </c>
-      <c r="H102" s="22" t="s">
-        <v>124</v>
-      </c>
       <c r="I102" s="4">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J102" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" s="4" customFormat="1" spans="1:10">
       <c r="A103" s="4">
-        <v>10200007</v>
+        <v>10200002</v>
       </c>
       <c r="B103" s="4">
         <v>102000</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D103" s="22">
-        <v>4020347</v>
+        <v>4020003</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G103" s="22">
+        <v>25</v>
+      </c>
+      <c r="G103" s="4">
         <v>2</v>
       </c>
       <c r="I103" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J103" s="4">
         <v>100</v>
@@ -4569,28 +4576,28 @@
     </row>
     <row r="104" s="4" customFormat="1" spans="1:10">
       <c r="A104" s="4">
-        <v>10200008</v>
+        <v>10200003</v>
       </c>
       <c r="B104" s="4">
         <v>102000</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D104" s="22">
-        <v>4020349</v>
+        <v>4020004</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G104" s="4">
+        <v>25</v>
+      </c>
+      <c r="G104" s="22">
         <v>2</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I104" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J104" s="4">
         <v>100</v>
@@ -4598,28 +4605,28 @@
     </row>
     <row r="105" s="4" customFormat="1" spans="1:10">
       <c r="A105" s="4">
-        <v>10200009</v>
+        <v>10200004</v>
       </c>
       <c r="B105" s="4">
         <v>102000</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D105" s="22">
-        <v>4020350</v>
+        <v>4020005</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G105" s="22">
+        <v>25</v>
+      </c>
+      <c r="G105" s="4">
         <v>2</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I105" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J105" s="4">
         <v>100</v>
@@ -4627,217 +4634,216 @@
     </row>
     <row r="106" s="4" customFormat="1" spans="1:10">
       <c r="A106" s="4">
-        <v>10200010</v>
+        <v>10200005</v>
       </c>
       <c r="B106" s="4">
         <v>102000</v>
       </c>
       <c r="C106" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D106" s="22">
+        <v>4020345</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" s="22">
+        <v>2</v>
+      </c>
+      <c r="H106" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="I106" s="4">
+        <v>4</v>
+      </c>
+      <c r="J106" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" s="4" customFormat="1" spans="1:10">
+      <c r="A107" s="4">
+        <v>10200006</v>
+      </c>
+      <c r="B107" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D107" s="22">
+        <v>4020346</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="I107" s="4">
+        <v>5</v>
+      </c>
+      <c r="J107" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" s="4" customFormat="1" spans="1:10">
+      <c r="A108" s="4">
+        <v>10200007</v>
+      </c>
+      <c r="B108" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108" s="22">
+        <v>4020347</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" s="22">
+        <v>2</v>
+      </c>
+      <c r="I108" s="4">
+        <v>6</v>
+      </c>
+      <c r="J108" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" s="4" customFormat="1" spans="1:10">
+      <c r="A109" s="4">
+        <v>10200008</v>
+      </c>
+      <c r="B109" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D109" s="22">
+        <v>4020349</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G109" s="4">
+        <v>2</v>
+      </c>
+      <c r="H109" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="I109" s="4">
+        <v>7</v>
+      </c>
+      <c r="J109" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" s="4" customFormat="1" spans="1:10">
+      <c r="A110" s="4">
+        <v>10200009</v>
+      </c>
+      <c r="B110" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D110" s="22">
+        <v>4020350</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" s="22">
+        <v>2</v>
+      </c>
+      <c r="H110" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="I110" s="4">
+        <v>8</v>
+      </c>
+      <c r="J110" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" s="4" customFormat="1" spans="1:10">
+      <c r="A111" s="4">
+        <v>10200010</v>
+      </c>
+      <c r="B111" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D106" s="22">
+      <c r="D111" s="22">
         <v>4020007</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E111" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G106" s="4">
-        <v>2</v>
-      </c>
-      <c r="H106" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="I106" s="4">
+      <c r="G111" s="4">
+        <v>2</v>
+      </c>
+      <c r="H111" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="I111" s="4">
         <v>9</v>
       </c>
-      <c r="J106" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" s="5" customFormat="1" spans="1:10">
-      <c r="A107" s="5">
-        <v>10270001</v>
-      </c>
-      <c r="B107" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D107" s="24">
-        <v>4020002</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F107" s="5">
-        <v>1</v>
-      </c>
-      <c r="G107" s="5">
-        <v>2</v>
-      </c>
-      <c r="I107" s="5">
-        <v>-1</v>
-      </c>
-      <c r="J107" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" s="5" customFormat="1" spans="1:10">
-      <c r="A108" s="5">
-        <v>10270002</v>
-      </c>
-      <c r="B108" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D108" s="24">
-        <v>4020003</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G108" s="5">
-        <v>2</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="I108" s="5">
-        <v>1</v>
-      </c>
-      <c r="J108" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="109" s="5" customFormat="1" spans="1:10">
-      <c r="A109" s="5">
-        <v>10270003</v>
-      </c>
-      <c r="B109" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C109" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D109" s="24">
-        <v>4020640</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G109" s="5">
-        <v>2</v>
-      </c>
-      <c r="H109" s="5"/>
-      <c r="I109" s="5">
-        <v>2</v>
-      </c>
-      <c r="J109" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" s="5" customFormat="1" spans="1:10">
-      <c r="A110" s="5">
-        <v>10270004</v>
-      </c>
-      <c r="B110" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C110" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="D110" s="24">
-        <v>4020641</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G110" s="5">
-        <v>2</v>
-      </c>
-      <c r="H110" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I110" s="5">
-        <v>3</v>
-      </c>
-      <c r="J110" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="111" s="5" customFormat="1" spans="1:10">
-      <c r="A111" s="5">
-        <v>10270005</v>
-      </c>
-      <c r="B111" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C111" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D111" s="24">
-        <v>4020642</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G111" s="5">
-        <v>2</v>
-      </c>
-      <c r="H111" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="I111" s="5">
-        <v>4</v>
-      </c>
-      <c r="J111" s="5">
+      <c r="J111" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="112" s="5" customFormat="1" spans="1:10">
       <c r="A112" s="5">
-        <v>10270006</v>
+        <v>10270001</v>
       </c>
       <c r="B112" s="5">
         <v>102700</v>
       </c>
-      <c r="C112" s="31" t="s">
-        <v>114</v>
+      <c r="C112" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D112" s="24">
-        <v>4020643</v>
+        <v>4020002</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1</v>
       </c>
       <c r="G112" s="5">
         <v>2</v>
       </c>
-      <c r="H112" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="I112" s="5">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J112" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" s="5" customFormat="1" spans="1:10">
       <c r="A113" s="5">
-        <v>10270007</v>
+        <v>10270002</v>
       </c>
       <c r="B113" s="5">
         <v>102700</v>
       </c>
-      <c r="C113" s="31" t="s">
-        <v>116</v>
+      <c r="C113" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D113" s="24">
-        <v>4020644</v>
+        <v>4020003</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>25</v>
@@ -4846,10 +4852,10 @@
         <v>2</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I113" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J113" s="5">
         <v>100</v>
@@ -4857,25 +4863,26 @@
     </row>
     <row r="114" s="5" customFormat="1" spans="1:10">
       <c r="A114" s="5">
-        <v>10270008</v>
+        <v>10270003</v>
       </c>
       <c r="B114" s="5">
         <v>102700</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>52</v>
+      <c r="C114" s="31" t="s">
+        <v>110</v>
       </c>
       <c r="D114" s="24">
-        <v>4020347</v>
+        <v>4020640</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G114" s="5">
         <v>2</v>
       </c>
+      <c r="H114" s="5"/>
       <c r="I114" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J114" s="5">
         <v>100</v>
@@ -4883,28 +4890,28 @@
     </row>
     <row r="115" s="5" customFormat="1" spans="1:10">
       <c r="A115" s="5">
-        <v>10270009</v>
+        <v>10270004</v>
       </c>
       <c r="B115" s="5">
         <v>102700</v>
       </c>
-      <c r="C115" s="5" t="s">
-        <v>53</v>
+      <c r="C115" s="31" t="s">
+        <v>114</v>
       </c>
       <c r="D115" s="24">
-        <v>4020349</v>
+        <v>4020641</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G115" s="5">
         <v>2</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I115" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J115" s="5">
         <v>100</v>
@@ -4912,28 +4919,28 @@
     </row>
     <row r="116" s="5" customFormat="1" spans="1:10">
       <c r="A116" s="5">
-        <v>10270010</v>
+        <v>10270005</v>
       </c>
       <c r="B116" s="5">
         <v>102700</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>55</v>
+      <c r="C116" s="31" t="s">
+        <v>118</v>
       </c>
       <c r="D116" s="24">
-        <v>4020350</v>
+        <v>4020642</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G116" s="5">
         <v>2</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I116" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J116" s="5">
         <v>100</v>
@@ -4941,225 +4948,225 @@
     </row>
     <row r="117" s="5" customFormat="1" spans="1:10">
       <c r="A117" s="5">
-        <v>10270011</v>
+        <v>10270006</v>
       </c>
       <c r="B117" s="5">
         <v>102700</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C117" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D117" s="24">
+        <v>4020643</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G117" s="5">
+        <v>2</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I117" s="5">
+        <v>5</v>
+      </c>
+      <c r="J117" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" s="5" customFormat="1" spans="1:10">
+      <c r="A118" s="5">
+        <v>10270007</v>
+      </c>
+      <c r="B118" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C118" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D118" s="24">
+        <v>4020644</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G118" s="5">
+        <v>2</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I118" s="5">
+        <v>6</v>
+      </c>
+      <c r="J118" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" s="5" customFormat="1" spans="1:10">
+      <c r="A119" s="5">
+        <v>10270008</v>
+      </c>
+      <c r="B119" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D119" s="24">
+        <v>4020347</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119" s="5">
+        <v>2</v>
+      </c>
+      <c r="I119" s="5">
+        <v>7</v>
+      </c>
+      <c r="J119" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" s="5" customFormat="1" spans="1:10">
+      <c r="A120" s="5">
+        <v>10270009</v>
+      </c>
+      <c r="B120" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D120" s="24">
+        <v>4020349</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" s="5">
+        <v>2</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I120" s="5">
+        <v>8</v>
+      </c>
+      <c r="J120" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" s="5" customFormat="1" spans="1:10">
+      <c r="A121" s="5">
+        <v>10270010</v>
+      </c>
+      <c r="B121" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D121" s="24">
+        <v>4020350</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G121" s="5">
+        <v>2</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I121" s="5">
+        <v>9</v>
+      </c>
+      <c r="J121" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" s="5" customFormat="1" spans="1:10">
+      <c r="A122" s="5">
+        <v>10270011</v>
+      </c>
+      <c r="B122" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C122" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D117" s="24">
+      <c r="D122" s="24">
         <v>4020007</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E122" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G117" s="5">
-        <v>2</v>
-      </c>
-      <c r="H117" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I117" s="5">
+      <c r="G122" s="5">
+        <v>2</v>
+      </c>
+      <c r="H122" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I122" s="5">
         <v>10</v>
       </c>
-      <c r="J117" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="1" spans="1:10">
-      <c r="A118" s="1">
-        <v>10150001</v>
-      </c>
-      <c r="B118" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D118" s="16">
-        <v>4020002</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F118" s="1">
-        <v>1</v>
-      </c>
-      <c r="G118" s="1">
-        <v>2</v>
-      </c>
-      <c r="I118" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J118" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" s="1" customFormat="1" spans="1:10">
-      <c r="A119" s="1">
-        <v>10150002</v>
-      </c>
-      <c r="B119" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D119" s="16">
-        <v>4020003</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G119" s="1">
-        <v>2</v>
-      </c>
-      <c r="I119" s="1">
-        <v>1</v>
-      </c>
-      <c r="J119" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="1" spans="1:10">
-      <c r="A120" s="1">
-        <v>10150003</v>
-      </c>
-      <c r="B120" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D120" s="16">
-        <v>4020004</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G120" s="1">
-        <v>2</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I120" s="1">
-        <v>2</v>
-      </c>
-      <c r="J120" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="121" s="1" customFormat="1" spans="1:10">
-      <c r="A121" s="1">
-        <v>10150004</v>
-      </c>
-      <c r="B121" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D121" s="16">
-        <v>4020094</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G121" s="1">
-        <v>2</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I121" s="1">
-        <v>3</v>
-      </c>
-      <c r="J121" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="122" s="1" customFormat="1" spans="1:10">
-      <c r="A122" s="1">
-        <v>10150005</v>
-      </c>
-      <c r="B122" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D122" s="16">
-        <v>4020345</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G122" s="1">
-        <v>2</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I122" s="1">
-        <v>4</v>
-      </c>
-      <c r="J122" s="1">
+      <c r="J122" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="1:10">
       <c r="A123" s="1">
-        <v>10150006</v>
+        <v>10150001</v>
       </c>
       <c r="B123" s="1">
         <v>101500</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D123" s="16">
-        <v>4020346</v>
+        <v>4020002</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F123" s="1">
+        <v>1</v>
       </c>
       <c r="G123" s="1">
         <v>2</v>
       </c>
-      <c r="H123" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="I123" s="1">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J123" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="1:10">
       <c r="A124" s="1">
-        <v>10150007</v>
+        <v>10150002</v>
       </c>
       <c r="B124" s="1">
         <v>101500</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D124" s="16">
-        <v>4020347</v>
+        <v>4020003</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G124" s="1">
         <v>2</v>
       </c>
       <c r="I124" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J124" s="1">
         <v>100</v>
@@ -5167,28 +5174,28 @@
     </row>
     <row r="125" s="1" customFormat="1" spans="1:10">
       <c r="A125" s="1">
-        <v>10150008</v>
+        <v>10150003</v>
       </c>
       <c r="B125" s="1">
         <v>101500</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D125" s="16">
-        <v>4020349</v>
+        <v>4020004</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G125" s="1">
         <v>2</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I125" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J125" s="1">
         <v>100</v>
@@ -5196,28 +5203,28 @@
     </row>
     <row r="126" s="1" customFormat="1" spans="1:10">
       <c r="A126" s="1">
-        <v>10150009</v>
+        <v>10150004</v>
       </c>
       <c r="B126" s="1">
         <v>101500</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D126" s="16">
-        <v>4020350</v>
+        <v>4020094</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G126" s="1">
         <v>2</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I126" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J126" s="1">
         <v>100</v>
@@ -5225,25 +5232,28 @@
     </row>
     <row r="127" s="1" customFormat="1" spans="1:10">
       <c r="A127" s="1">
-        <v>10150010</v>
+        <v>10150005</v>
       </c>
       <c r="B127" s="1">
         <v>101500</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="D127" s="16">
-        <v>4020466</v>
+        <v>4020345</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="G127" s="1">
         <v>2</v>
       </c>
+      <c r="H127" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I127" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J127" s="1">
         <v>100</v>
@@ -5251,28 +5261,28 @@
     </row>
     <row r="128" s="1" customFormat="1" spans="1:10">
       <c r="A128" s="1">
-        <v>10150011</v>
+        <v>10150006</v>
       </c>
       <c r="B128" s="1">
         <v>101500</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="D128" s="16">
-        <v>4020467</v>
+        <v>4020346</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="G128" s="1">
         <v>2</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I128" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J128" s="1">
         <v>100</v>
@@ -5280,28 +5290,25 @@
     </row>
     <row r="129" s="1" customFormat="1" spans="1:10">
       <c r="A129" s="1">
-        <v>10150012</v>
+        <v>10150007</v>
       </c>
       <c r="B129" s="1">
         <v>101500</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D129" s="16">
-        <v>4020468</v>
+        <v>4020347</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="G129" s="1">
         <v>2</v>
       </c>
-      <c r="H129" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="I129" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J129" s="1">
         <v>100</v>
@@ -5309,19 +5316,19 @@
     </row>
     <row r="130" s="1" customFormat="1" spans="1:10">
       <c r="A130" s="1">
-        <v>10150013</v>
+        <v>10150008</v>
       </c>
       <c r="B130" s="1">
         <v>101500</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>146</v>
+        <v>53</v>
       </c>
       <c r="D130" s="16">
-        <v>4020469</v>
+        <v>4020349</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="G130" s="1">
         <v>2</v>
@@ -5330,7 +5337,7 @@
         <v>147</v>
       </c>
       <c r="I130" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J130" s="1">
         <v>100</v>
@@ -5338,28 +5345,28 @@
     </row>
     <row r="131" s="1" customFormat="1" spans="1:10">
       <c r="A131" s="1">
-        <v>10150014</v>
+        <v>10150009</v>
       </c>
       <c r="B131" s="1">
         <v>101500</v>
       </c>
       <c r="C131" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D131" s="16">
+        <v>4020350</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G131" s="1">
+        <v>2</v>
+      </c>
+      <c r="H131" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D131" s="16">
-        <v>4020470</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G131" s="1">
-        <v>2</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="I131" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J131" s="1">
         <v>100</v>
@@ -5367,30 +5374,172 @@
     </row>
     <row r="132" s="1" customFormat="1" spans="1:10">
       <c r="A132" s="1">
-        <v>10150015</v>
+        <v>10150010</v>
       </c>
       <c r="B132" s="1">
         <v>101500</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D132" s="16">
+        <v>4020466</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G132" s="1">
+        <v>2</v>
+      </c>
+      <c r="I132" s="1">
+        <v>10</v>
+      </c>
+      <c r="J132" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" s="1" customFormat="1" spans="1:10">
+      <c r="A133" s="1">
+        <v>10150011</v>
+      </c>
+      <c r="B133" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D133" s="16">
+        <v>4020467</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G133" s="1">
+        <v>2</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I133" s="1">
+        <v>11</v>
+      </c>
+      <c r="J133" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" s="1" customFormat="1" spans="1:10">
+      <c r="A134" s="1">
+        <v>10150012</v>
+      </c>
+      <c r="B134" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D134" s="16">
+        <v>4020468</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G134" s="1">
+        <v>2</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I134" s="1">
+        <v>12</v>
+      </c>
+      <c r="J134" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" spans="1:10">
+      <c r="A135" s="1">
+        <v>10150013</v>
+      </c>
+      <c r="B135" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D135" s="16">
+        <v>4020469</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I135" s="1">
+        <v>13</v>
+      </c>
+      <c r="J135" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="1" spans="1:10">
+      <c r="A136" s="1">
+        <v>10150014</v>
+      </c>
+      <c r="B136" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D136" s="16">
+        <v>4020470</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G136" s="1">
+        <v>2</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I136" s="1">
+        <v>14</v>
+      </c>
+      <c r="J136" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="1" spans="1:10">
+      <c r="A137" s="1">
+        <v>10150015</v>
+      </c>
+      <c r="B137" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D132" s="16">
+      <c r="D137" s="16">
         <v>4020007</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E137" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G132" s="1">
-        <v>2</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I132" s="1">
+      <c r="G137" s="1">
+        <v>2</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I137" s="1">
         <v>15</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J137" s="1">
         <v>100</v>
       </c>
     </row>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="185">
   <si>
     <t>属性id</t>
   </si>
@@ -138,6 +138,9 @@
     <t>解锁属性id_等级</t>
   </si>
   <si>
+    <t>特效名称</t>
+  </si>
+  <si>
     <t>位置排序</t>
   </si>
   <si>
@@ -174,6 +177,9 @@
     <t>skillId</t>
   </si>
   <si>
+    <t>EffectName</t>
+  </si>
+  <si>
     <t>SortOrder</t>
   </si>
   <si>
@@ -444,6 +450,9 @@
     <t>解锁sweet win奖励</t>
   </si>
   <si>
+    <t>PetSquadsweet</t>
+  </si>
+  <si>
     <t>sweet win中奖概率提升</t>
   </si>
   <si>
@@ -456,6 +465,9 @@
     <t>10390004,10</t>
   </si>
   <si>
+    <t>PetSquadbig</t>
+  </si>
+  <si>
     <t>big win中奖概率提升</t>
   </si>
   <si>
@@ -465,7 +477,10 @@
     <t>解锁mega win奖励</t>
   </si>
   <si>
-    <t>10390000,10</t>
+    <t>10390002,10</t>
+  </si>
+  <si>
+    <t>PetSquadmega</t>
   </si>
   <si>
     <t>mega win中奖概率提升</t>
@@ -480,6 +495,9 @@
     <t>10390008,10</t>
   </si>
   <si>
+    <t>PetSquadepic</t>
+  </si>
+  <si>
     <t>epic win中奖概率提升</t>
   </si>
   <si>
@@ -492,13 +510,34 @@
     <t>10390010,10</t>
   </si>
   <si>
+    <t>PetSquadlegendary</t>
+  </si>
+  <si>
     <t>legendary win中奖概率提升</t>
   </si>
   <si>
     <t>10390011,1</t>
   </si>
   <si>
-    <t>10390009,10</t>
+    <t>解锁免费模式</t>
+  </si>
+  <si>
+    <t>PetSquadFree</t>
+  </si>
+  <si>
+    <t>10390013,1</t>
+  </si>
+  <si>
+    <t>10390014,10</t>
+  </si>
+  <si>
+    <t>解锁jackpot大奖</t>
+  </si>
+  <si>
+    <t>10390015,10</t>
+  </si>
+  <si>
+    <t>PetSquadjackpot</t>
   </si>
   <si>
     <t>10200002,10</t>
@@ -522,25 +561,64 @@
     <t>10200009,10</t>
   </si>
   <si>
+    <t>10270006,10</t>
+  </si>
+  <si>
+    <t>ElephantFortunesweet</t>
+  </si>
+  <si>
+    <t>10270003,1</t>
+  </si>
+  <si>
     <t>10270004,10</t>
   </si>
   <si>
-    <t>10270003,10</t>
+    <t>ElephantFortunebig</t>
+  </si>
+  <si>
+    <t>10270005,1</t>
   </si>
   <si>
     <t>10270002,10</t>
   </si>
   <si>
-    <t>10270005,10</t>
-  </si>
-  <si>
-    <t>10270006,10</t>
-  </si>
-  <si>
-    <t>10270007,10</t>
+    <t>ElephantFortunemega</t>
+  </si>
+  <si>
+    <t>10270007,1</t>
   </si>
   <si>
     <t>10270008,10</t>
+  </si>
+  <si>
+    <t>ElephantFortuneepic</t>
+  </si>
+  <si>
+    <t>10270009,1</t>
+  </si>
+  <si>
+    <t>10270010,10</t>
+  </si>
+  <si>
+    <t>ElephantFortunelegendary</t>
+  </si>
+  <si>
+    <t>10270011,1</t>
+  </si>
+  <si>
+    <t>ElephantFortuneFree</t>
+  </si>
+  <si>
+    <t>10270013,1</t>
+  </si>
+  <si>
+    <t>10270014,10</t>
+  </si>
+  <si>
+    <t>10270015,10</t>
+  </si>
+  <si>
+    <t>ElephantFortunejackpot</t>
   </si>
   <si>
     <t>10150002,10</t>
@@ -1677,20 +1755,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="8" customWidth="1"/>
     <col min="2" max="2" width="16" style="8" customWidth="1"/>
     <col min="3" max="3" width="23.625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="26.875" style="9" customWidth="1"/>
-    <col min="5" max="8" width="26.875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="8" customWidth="1"/>
-    <col min="10" max="10" width="24.125" style="8" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="8"/>
+    <col min="4" max="4" width="16.75" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.75" style="8" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="26.875" style="8" customWidth="1"/>
+    <col min="9" max="10" width="16.25" style="8" customWidth="1"/>
+    <col min="11" max="11" width="24.125" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1721,66 +1802,75 @@
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="J2" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>11</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="J3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
@@ -1788,13 +1878,13 @@
         <v>100300</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="16">
         <v>4020002</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1803,14 +1893,14 @@
         <v>2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>-1</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
+    <row r="6" s="1" customFormat="1" spans="1:11">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
@@ -1818,26 +1908,26 @@
         <v>100300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="16">
         <v>4020003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="J6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:10">
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
@@ -1845,29 +1935,29 @@
         <v>100300</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="16">
         <v>4020004</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17">
         <v>2</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="1">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:11">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
@@ -1875,28 +1965,28 @@
         <v>100300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="16">
         <v>4020005</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1">
+        <v>31</v>
+      </c>
+      <c r="J8" s="1">
         <v>3</v>
       </c>
-      <c r="J8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:10">
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:11">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
@@ -1904,28 +1994,28 @@
         <v>100300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="16">
         <v>4020471</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" s="17">
         <v>2</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="1">
+        <v>33</v>
+      </c>
+      <c r="J9" s="1">
         <v>4</v>
       </c>
-      <c r="J9" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:10">
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:11">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
@@ -1933,28 +2023,28 @@
         <v>100300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="16">
         <v>4020346</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="1">
+        <v>35</v>
+      </c>
+      <c r="J10" s="1">
         <v>5</v>
       </c>
-      <c r="J10" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:10">
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:11">
       <c r="A11" s="1">
         <v>10030007</v>
       </c>
@@ -1962,25 +2052,25 @@
         <v>100300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="16">
         <v>4020006</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" s="17">
         <v>2</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>6</v>
       </c>
-      <c r="J11" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:10">
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:11">
       <c r="A12" s="1">
         <v>10030008</v>
       </c>
@@ -1988,28 +2078,28 @@
         <v>100300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" s="16">
         <v>4020007</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="1">
+        <v>40</v>
+      </c>
+      <c r="J12" s="1">
         <v>7</v>
       </c>
-      <c r="J12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:10">
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:11">
       <c r="A13" s="1">
         <v>10030009</v>
       </c>
@@ -2017,26 +2107,26 @@
         <v>100300</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="16">
         <v>4020607</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" s="16">
         <v>1</v>
       </c>
       <c r="H13" s="16"/>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>1</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:10">
+    <row r="14" s="1" customFormat="1" spans="1:11">
       <c r="A14" s="1">
         <v>10030010</v>
       </c>
@@ -2044,26 +2134,26 @@
         <v>100300</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" s="16">
         <v>4020608</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G14" s="16">
         <v>1</v>
       </c>
       <c r="H14" s="16"/>
-      <c r="I14" s="1">
-        <v>2</v>
-      </c>
       <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
+    <row r="15" s="2" customFormat="1" spans="1:11">
       <c r="A15" s="2">
         <v>10070001</v>
       </c>
@@ -2071,13 +2161,13 @@
         <v>100700</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" s="18">
         <v>4020002</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -2085,14 +2175,14 @@
       <c r="G15" s="2">
         <v>2</v>
       </c>
-      <c r="I15" s="2">
+      <c r="J15" s="2">
         <v>-1</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
+    <row r="16" s="2" customFormat="1" spans="1:11">
       <c r="A16" s="2">
         <v>10070002</v>
       </c>
@@ -2100,26 +2190,26 @@
         <v>100700</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16" s="18">
         <v>4020003</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="2">
         <v>2</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="2">
         <v>1</v>
       </c>
-      <c r="J16" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:10">
+      <c r="K16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:11">
       <c r="A17" s="2">
         <v>10070003</v>
       </c>
@@ -2127,28 +2217,28 @@
         <v>100700</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" s="18">
         <v>4020004</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G17" s="18">
         <v>2</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="2">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J17" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:11">
       <c r="A18" s="2">
         <v>10070004</v>
       </c>
@@ -2156,28 +2246,28 @@
         <v>100700</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" s="18">
         <v>4020094</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="2">
+        <v>49</v>
+      </c>
+      <c r="J18" s="2">
         <v>3</v>
       </c>
-      <c r="J18" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:10">
+      <c r="K18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:11">
       <c r="A19" s="2">
         <v>10070005</v>
       </c>
@@ -2185,28 +2275,28 @@
         <v>100700</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" s="18">
         <v>4020345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G19" s="18">
         <v>2</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" s="2">
+        <v>51</v>
+      </c>
+      <c r="J19" s="2">
         <v>4</v>
       </c>
-      <c r="J19" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:10">
+      <c r="K19" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:11">
       <c r="A20" s="2">
         <v>10070006</v>
       </c>
@@ -2214,28 +2304,28 @@
         <v>100700</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" s="18">
         <v>4020346</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G20" s="2">
         <v>2</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="2">
+        <v>53</v>
+      </c>
+      <c r="J20" s="2">
         <v>5</v>
       </c>
-      <c r="J20" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:10">
+      <c r="K20" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:11">
       <c r="A21" s="2">
         <v>10070007</v>
       </c>
@@ -2243,25 +2333,25 @@
         <v>100700</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21" s="18">
         <v>4020347</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" s="18">
         <v>2</v>
       </c>
-      <c r="I21" s="2">
+      <c r="J21" s="2">
         <v>6</v>
       </c>
-      <c r="J21" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:10">
+      <c r="K21" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:11">
       <c r="A22" s="2">
         <v>10070008</v>
       </c>
@@ -2269,28 +2359,28 @@
         <v>100700</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D22" s="18">
         <v>4020349</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="2">
+        <v>56</v>
+      </c>
+      <c r="J22" s="2">
         <v>7</v>
       </c>
-      <c r="J22" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:10">
+      <c r="K22" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:11">
       <c r="A23" s="2">
         <v>10070009</v>
       </c>
@@ -2298,28 +2388,28 @@
         <v>100700</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="18">
         <v>4020350</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G23" s="18">
         <v>2</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="I23" s="2">
+        <v>58</v>
+      </c>
+      <c r="J23" s="2">
         <v>8</v>
       </c>
-      <c r="J23" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:10">
+      <c r="K23" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:11">
       <c r="A24" s="3">
         <v>10120001</v>
       </c>
@@ -2327,13 +2417,13 @@
         <v>101200</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D24" s="20">
         <v>4020002</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -2341,14 +2431,14 @@
       <c r="G24" s="3">
         <v>2</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:10">
+    <row r="25" s="3" customFormat="1" spans="1:11">
       <c r="A25" s="3">
         <v>10120002</v>
       </c>
@@ -2356,26 +2446,26 @@
         <v>101200</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>4020003</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="3">
         <v>2</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J25" s="3">
         <v>1</v>
       </c>
-      <c r="J25" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:10">
+      <c r="K25" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:11">
       <c r="A26" s="3">
         <v>10120003</v>
       </c>
@@ -2383,29 +2473,29 @@
         <v>101200</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26" s="20">
         <v>4020004</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="21"/>
       <c r="G26" s="20">
         <v>2</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="J26" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" spans="1:11">
       <c r="A27" s="3">
         <v>10120004</v>
       </c>
@@ -2413,28 +2503,28 @@
         <v>101200</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D27" s="20">
         <v>4020094</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G27" s="3">
         <v>2</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="3">
+        <v>62</v>
+      </c>
+      <c r="J27" s="3">
         <v>3</v>
       </c>
-      <c r="J27" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:10">
+      <c r="K27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:11">
       <c r="A28" s="3">
         <v>10120005</v>
       </c>
@@ -2442,28 +2532,28 @@
         <v>101200</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D28" s="20">
         <v>4020095</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G28" s="20">
         <v>2</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I28" s="3">
+        <v>64</v>
+      </c>
+      <c r="J28" s="3">
         <v>4</v>
       </c>
-      <c r="J28" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:10">
+      <c r="K28" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" spans="1:11">
       <c r="A29" s="3">
         <v>10120006</v>
       </c>
@@ -2471,25 +2561,25 @@
         <v>101200</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D29" s="20">
         <v>4020401</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G29" s="3">
         <v>2</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>5</v>
       </c>
-      <c r="J29" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" s="3" customFormat="1" spans="1:10">
+      <c r="K29" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" spans="1:11">
       <c r="A30" s="3">
         <v>10120007</v>
       </c>
@@ -2497,28 +2587,28 @@
         <v>101200</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30" s="20">
         <v>4020007</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G30" s="20">
         <v>2</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" s="3">
+        <v>67</v>
+      </c>
+      <c r="J30" s="3">
         <v>6</v>
       </c>
-      <c r="J30" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" s="4" customFormat="1" spans="1:10">
+      <c r="K30" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" s="4" customFormat="1" spans="1:11">
       <c r="A31" s="4">
         <v>10180001</v>
       </c>
@@ -2526,13 +2616,13 @@
         <v>101800</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D31" s="22">
         <v>4020002</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F31" s="4">
         <v>1</v>
@@ -2540,14 +2630,14 @@
       <c r="G31" s="4">
         <v>2</v>
       </c>
-      <c r="I31" s="4">
+      <c r="J31" s="4">
         <v>-1</v>
       </c>
-      <c r="J31" s="4">
+      <c r="K31" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="32" s="4" customFormat="1" spans="1:10">
+    <row r="32" s="4" customFormat="1" spans="1:11">
       <c r="A32" s="4">
         <v>10180002</v>
       </c>
@@ -2555,26 +2645,26 @@
         <v>101800</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D32" s="22">
         <v>4020003</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F32" s="23"/>
       <c r="G32" s="4">
         <v>2</v>
       </c>
-      <c r="I32" s="4">
+      <c r="J32" s="4">
         <v>1</v>
       </c>
-      <c r="J32" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" s="4" customFormat="1" spans="1:10">
+      <c r="K32" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" s="4" customFormat="1" spans="1:11">
       <c r="A33" s="4">
         <v>10180003</v>
       </c>
@@ -2582,28 +2672,28 @@
         <v>101800</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D33" s="22">
         <v>4020004</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G33" s="22">
         <v>2</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" s="4">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="J33" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" s="4" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K33" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" s="4" customFormat="1" spans="1:11">
       <c r="A34" s="4">
         <v>10180004</v>
       </c>
@@ -2611,28 +2701,28 @@
         <v>101800</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D34" s="22">
         <v>4020094</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G34" s="4">
         <v>2</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" s="4">
+        <v>69</v>
+      </c>
+      <c r="J34" s="4">
         <v>3</v>
       </c>
-      <c r="J34" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" s="4" customFormat="1" spans="1:10">
+      <c r="K34" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" s="4" customFormat="1" spans="1:11">
       <c r="A35" s="4">
         <v>10180005</v>
       </c>
@@ -2640,28 +2730,28 @@
         <v>101800</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D35" s="22">
         <v>4020345</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G35" s="22">
         <v>2</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="I35" s="4">
+        <v>70</v>
+      </c>
+      <c r="J35" s="4">
         <v>4</v>
       </c>
-      <c r="J35" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" s="4" customFormat="1" spans="1:10">
+      <c r="K35" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" spans="1:11">
       <c r="A36" s="4">
         <v>10180006</v>
       </c>
@@ -2669,28 +2759,28 @@
         <v>101800</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36" s="22">
         <v>4020346</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G36" s="4">
         <v>2</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I36" s="4">
+        <v>71</v>
+      </c>
+      <c r="J36" s="4">
         <v>5</v>
       </c>
-      <c r="J36" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" s="4" customFormat="1" spans="1:10">
+      <c r="K36" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="1" spans="1:11">
       <c r="A37" s="4">
         <v>10180007</v>
       </c>
@@ -2698,25 +2788,25 @@
         <v>101800</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D37" s="22">
         <v>4020347</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G37" s="22">
         <v>2</v>
       </c>
-      <c r="I37" s="4">
+      <c r="J37" s="4">
         <v>6</v>
       </c>
-      <c r="J37" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" s="4" customFormat="1" spans="1:10">
+      <c r="K37" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" spans="1:11">
       <c r="A38" s="4">
         <v>10180008</v>
       </c>
@@ -2724,28 +2814,28 @@
         <v>101800</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D38" s="22">
         <v>4020349</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G38" s="4">
         <v>2</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="I38" s="4">
+        <v>72</v>
+      </c>
+      <c r="J38" s="4">
         <v>7</v>
       </c>
-      <c r="J38" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" s="4" customFormat="1" spans="1:10">
+      <c r="K38" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" s="4" customFormat="1" spans="1:11">
       <c r="A39" s="4">
         <v>10180009</v>
       </c>
@@ -2753,28 +2843,28 @@
         <v>101800</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D39" s="22">
         <v>4020350</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G39" s="22">
         <v>2</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I39" s="4">
+        <v>73</v>
+      </c>
+      <c r="J39" s="4">
         <v>8</v>
       </c>
-      <c r="J39" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" s="4" customFormat="1" spans="1:10">
+      <c r="K39" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" s="4" customFormat="1" spans="1:11">
       <c r="A40" s="4">
         <v>10180010</v>
       </c>
@@ -2782,28 +2872,28 @@
         <v>101800</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D40" s="22">
         <v>4020007</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G40" s="4">
         <v>2</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40" s="4">
+        <v>74</v>
+      </c>
+      <c r="J40" s="4">
         <v>9</v>
       </c>
-      <c r="J40" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" s="5" customFormat="1" spans="1:10">
+      <c r="K40" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" s="5" customFormat="1" spans="1:11">
       <c r="A41" s="5">
         <v>10250001</v>
       </c>
@@ -2811,13 +2901,13 @@
         <v>102500</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D41" s="24">
         <v>4020002</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F41" s="5">
         <v>1</v>
@@ -2825,14 +2915,14 @@
       <c r="G41" s="5">
         <v>2</v>
       </c>
-      <c r="I41" s="5">
+      <c r="J41" s="5">
         <v>-1</v>
       </c>
-      <c r="J41" s="5">
+      <c r="K41" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="42" s="5" customFormat="1" spans="1:10">
+    <row r="42" s="5" customFormat="1" spans="1:11">
       <c r="A42" s="5">
         <v>10250002</v>
       </c>
@@ -2840,26 +2930,26 @@
         <v>102500</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D42" s="24">
         <v>4020003</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F42" s="25"/>
       <c r="G42" s="5">
         <v>2</v>
       </c>
-      <c r="I42" s="5">
+      <c r="J42" s="5">
         <v>1</v>
       </c>
-      <c r="J42" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" s="5" customFormat="1" spans="1:10">
+      <c r="K42" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" s="5" customFormat="1" spans="1:11">
       <c r="A43" s="5">
         <v>10250003</v>
       </c>
@@ -2867,28 +2957,28 @@
         <v>102500</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D43" s="24">
         <v>4020004</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G43" s="24">
         <v>2</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="I43" s="5">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="J43" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" s="5" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K43" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" s="5" customFormat="1" spans="1:11">
       <c r="A44" s="5">
         <v>10250004</v>
       </c>
@@ -2896,28 +2986,28 @@
         <v>102500</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D44" s="24">
         <v>4020094</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="I44" s="5">
+        <v>76</v>
+      </c>
+      <c r="J44" s="5">
         <v>3</v>
       </c>
-      <c r="J44" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" s="5" customFormat="1" spans="1:10">
+      <c r="K44" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" s="5" customFormat="1" spans="1:11">
       <c r="A45" s="5">
         <v>10250005</v>
       </c>
@@ -2925,28 +3015,28 @@
         <v>102500</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D45" s="24">
         <v>4020345</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G45" s="24">
         <v>2</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="I45" s="5">
+        <v>77</v>
+      </c>
+      <c r="J45" s="5">
         <v>4</v>
       </c>
-      <c r="J45" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" s="5" customFormat="1" spans="1:10">
+      <c r="K45" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" s="5" customFormat="1" spans="1:11">
       <c r="A46" s="5">
         <v>10250006</v>
       </c>
@@ -2954,28 +3044,28 @@
         <v>102500</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D46" s="24">
         <v>4020346</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="I46" s="5">
+        <v>78</v>
+      </c>
+      <c r="J46" s="5">
         <v>5</v>
       </c>
-      <c r="J46" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" s="5" customFormat="1" spans="1:10">
+      <c r="K46" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" s="5" customFormat="1" spans="1:11">
       <c r="A47" s="5">
         <v>10250007</v>
       </c>
@@ -2983,25 +3073,25 @@
         <v>102500</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="24">
         <v>4020347</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G47" s="24">
         <v>2</v>
       </c>
-      <c r="I47" s="5">
+      <c r="J47" s="5">
         <v>6</v>
       </c>
-      <c r="J47" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" s="5" customFormat="1" spans="1:10">
+      <c r="K47" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" s="5" customFormat="1" spans="1:11">
       <c r="A48" s="5">
         <v>10250008</v>
       </c>
@@ -3009,28 +3099,28 @@
         <v>102500</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D48" s="24">
         <v>4020349</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="I48" s="5">
+        <v>79</v>
+      </c>
+      <c r="J48" s="5">
         <v>7</v>
       </c>
-      <c r="J48" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" s="5" customFormat="1" spans="1:10">
+      <c r="K48" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" s="5" customFormat="1" spans="1:11">
       <c r="A49" s="5">
         <v>10250009</v>
       </c>
@@ -3038,28 +3128,28 @@
         <v>102500</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D49" s="24">
         <v>4020350</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G49" s="24">
         <v>2</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="I49" s="5">
+        <v>80</v>
+      </c>
+      <c r="J49" s="5">
         <v>8</v>
       </c>
-      <c r="J49" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" s="5" customFormat="1" spans="1:10">
+      <c r="K49" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" s="5" customFormat="1" spans="1:11">
       <c r="A50" s="5">
         <v>10250010</v>
       </c>
@@ -3067,28 +3157,28 @@
         <v>102500</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D50" s="24">
         <v>4020007</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="I50" s="5">
+        <v>81</v>
+      </c>
+      <c r="J50" s="5">
         <v>9</v>
       </c>
-      <c r="J50" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" s="6" customFormat="1" spans="1:10">
+      <c r="K50" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" s="6" customFormat="1" spans="1:11">
       <c r="A51" s="6">
         <v>10310001</v>
       </c>
@@ -3096,13 +3186,13 @@
         <v>103100</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D51" s="26">
         <v>4020002</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F51" s="6">
         <v>1</v>
@@ -3110,14 +3200,14 @@
       <c r="G51" s="6">
         <v>2</v>
       </c>
-      <c r="I51" s="6">
+      <c r="J51" s="6">
         <v>-1</v>
       </c>
-      <c r="J51" s="6">
+      <c r="K51" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="52" s="6" customFormat="1" spans="1:10">
+    <row r="52" s="6" customFormat="1" spans="1:11">
       <c r="A52" s="6">
         <v>10310002</v>
       </c>
@@ -3125,26 +3215,26 @@
         <v>103100</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D52" s="26">
         <v>4020003</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F52" s="27"/>
       <c r="G52" s="6">
         <v>2</v>
       </c>
-      <c r="I52" s="6">
+      <c r="J52" s="6">
         <v>1</v>
       </c>
-      <c r="J52" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" s="6" customFormat="1" spans="1:10">
+      <c r="K52" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" s="6" customFormat="1" spans="1:11">
       <c r="A53" s="6">
         <v>10310003</v>
       </c>
@@ -3152,29 +3242,29 @@
         <v>103100</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D53" s="26">
         <v>4020004</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F53" s="27"/>
       <c r="G53" s="27">
         <v>2</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="I53" s="6">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="J53" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" s="6" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K53" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" s="6" customFormat="1" spans="1:11">
       <c r="A54" s="6">
         <v>10310004</v>
       </c>
@@ -3182,28 +3272,28 @@
         <v>103100</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D54" s="26">
         <v>4020094</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G54" s="6">
         <v>2</v>
       </c>
       <c r="H54" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="I54" s="6">
+        <v>83</v>
+      </c>
+      <c r="J54" s="6">
         <v>3</v>
       </c>
-      <c r="J54" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" s="6" customFormat="1" spans="1:10">
+      <c r="K54" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" s="6" customFormat="1" spans="1:11">
       <c r="A55" s="6">
         <v>10310005</v>
       </c>
@@ -3211,28 +3301,28 @@
         <v>103100</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D55" s="26">
         <v>4020345</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G55" s="27">
         <v>2</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="I55" s="6">
+        <v>84</v>
+      </c>
+      <c r="J55" s="6">
         <v>4</v>
       </c>
-      <c r="J55" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="1:10">
+      <c r="K55" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" s="6" customFormat="1" spans="1:11">
       <c r="A56" s="6">
         <v>10310006</v>
       </c>
@@ -3240,28 +3330,28 @@
         <v>103100</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D56" s="26">
         <v>4020346</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G56" s="6">
         <v>2</v>
       </c>
       <c r="H56" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="I56" s="6">
+        <v>85</v>
+      </c>
+      <c r="J56" s="6">
         <v>5</v>
       </c>
-      <c r="J56" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" s="6" customFormat="1" spans="1:10">
+      <c r="K56" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" s="6" customFormat="1" spans="1:11">
       <c r="A57" s="6">
         <v>10310007</v>
       </c>
@@ -3269,25 +3359,25 @@
         <v>103100</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D57" s="26">
         <v>4020347</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G57" s="27">
         <v>2</v>
       </c>
-      <c r="I57" s="6">
+      <c r="J57" s="6">
         <v>6</v>
       </c>
-      <c r="J57" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" s="6" customFormat="1" spans="1:10">
+      <c r="K57" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" s="6" customFormat="1" spans="1:11">
       <c r="A58" s="6">
         <v>10310008</v>
       </c>
@@ -3295,28 +3385,28 @@
         <v>103100</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D58" s="26">
         <v>4020349</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G58" s="6">
         <v>2</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I58" s="6">
+        <v>86</v>
+      </c>
+      <c r="J58" s="6">
         <v>7</v>
       </c>
-      <c r="J58" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" s="6" customFormat="1" spans="1:10">
+      <c r="K58" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" s="6" customFormat="1" spans="1:11">
       <c r="A59" s="6">
         <v>10310009</v>
       </c>
@@ -3324,28 +3414,28 @@
         <v>103100</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D59" s="26">
         <v>4020350</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G59" s="27">
         <v>2</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="I59" s="6">
+        <v>87</v>
+      </c>
+      <c r="J59" s="6">
         <v>8</v>
       </c>
-      <c r="J59" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" s="6" customFormat="1" spans="1:10">
+      <c r="K59" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" s="6" customFormat="1" spans="1:11">
       <c r="A60" s="6">
         <v>10310010</v>
       </c>
@@ -3353,25 +3443,25 @@
         <v>103100</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D60" s="26">
         <v>4020412</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G60" s="6">
         <v>2</v>
       </c>
-      <c r="I60" s="6">
+      <c r="J60" s="6">
         <v>9</v>
       </c>
-      <c r="J60" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" s="6" customFormat="1" spans="1:10">
+      <c r="K60" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" s="6" customFormat="1" spans="1:11">
       <c r="A61" s="6">
         <v>10310011</v>
       </c>
@@ -3379,28 +3469,28 @@
         <v>103100</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D61" s="26">
         <v>4020413</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G61" s="27">
         <v>2</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="I61" s="6">
+        <v>91</v>
+      </c>
+      <c r="J61" s="6">
         <v>10</v>
       </c>
-      <c r="J61" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" s="6" customFormat="1" spans="1:10">
+      <c r="K61" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" s="6" customFormat="1" spans="1:11">
       <c r="A62" s="6">
         <v>10310012</v>
       </c>
@@ -3408,28 +3498,28 @@
         <v>103100</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D62" s="26">
         <v>4020414</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G62" s="6">
         <v>2</v>
       </c>
       <c r="H62" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="I62" s="6">
+        <v>93</v>
+      </c>
+      <c r="J62" s="6">
         <v>11</v>
       </c>
-      <c r="J62" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" s="6" customFormat="1" spans="1:10">
+      <c r="K62" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" s="6" customFormat="1" spans="1:11">
       <c r="A63" s="6">
         <v>10310013</v>
       </c>
@@ -3437,28 +3527,28 @@
         <v>103100</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D63" s="26">
         <v>4020007</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G63" s="27">
         <v>2</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="I63" s="6">
+        <v>94</v>
+      </c>
+      <c r="J63" s="6">
         <v>12</v>
       </c>
-      <c r="J63" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:10">
+      <c r="K63" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:11">
       <c r="A64" s="2">
         <v>10220001</v>
       </c>
@@ -3466,13 +3556,13 @@
         <v>102200</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D64" s="18">
         <v>4020002</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F64" s="2">
         <v>1</v>
@@ -3480,14 +3570,14 @@
       <c r="G64" s="2">
         <v>2</v>
       </c>
-      <c r="I64" s="2">
+      <c r="J64" s="2">
         <v>-1</v>
       </c>
-      <c r="J64" s="2">
+      <c r="K64" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" spans="1:10">
+    <row r="65" s="2" customFormat="1" spans="1:11">
       <c r="A65" s="2">
         <v>10220002</v>
       </c>
@@ -3495,26 +3585,26 @@
         <v>102200</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D65" s="18">
         <v>4020003</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F65" s="19"/>
       <c r="G65" s="2">
         <v>2</v>
       </c>
-      <c r="I65" s="2">
+      <c r="J65" s="2">
         <v>1</v>
       </c>
-      <c r="J65" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:10">
+      <c r="K65" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:11">
       <c r="A66" s="2">
         <v>10220003</v>
       </c>
@@ -3522,29 +3612,29 @@
         <v>102200</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D66" s="18">
         <v>4020004</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F66" s="19"/>
       <c r="G66" s="18">
         <v>2</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="I66" s="2">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="J66" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K66" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:11">
       <c r="A67" s="2">
         <v>10220004</v>
       </c>
@@ -3552,28 +3642,28 @@
         <v>102200</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D67" s="18">
         <v>4020094</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G67" s="2">
         <v>2</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I67" s="2">
+        <v>96</v>
+      </c>
+      <c r="J67" s="2">
         <v>3</v>
       </c>
-      <c r="J67" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:10">
+      <c r="K67" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:11">
       <c r="A68" s="2">
         <v>10220005</v>
       </c>
@@ -3581,28 +3671,28 @@
         <v>102200</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D68" s="18">
         <v>4020095</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G68" s="18">
         <v>2</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="I68" s="2">
+        <v>97</v>
+      </c>
+      <c r="J68" s="2">
         <v>4</v>
       </c>
-      <c r="J68" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:10">
+      <c r="K68" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:11">
       <c r="A69" s="2">
         <v>10220006</v>
       </c>
@@ -3610,25 +3700,25 @@
         <v>102200</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D69" s="18">
         <v>4020347</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G69" s="2">
         <v>2</v>
       </c>
-      <c r="I69" s="2">
+      <c r="J69" s="2">
         <v>5</v>
       </c>
-      <c r="J69" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:10">
+      <c r="K69" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:11">
       <c r="A70" s="2">
         <v>10220007</v>
       </c>
@@ -3636,28 +3726,28 @@
         <v>102200</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D70" s="18">
         <v>4020349</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G70" s="18">
         <v>2</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="I70" s="2">
+        <v>98</v>
+      </c>
+      <c r="J70" s="2">
         <v>6</v>
       </c>
-      <c r="J70" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:10">
+      <c r="K70" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="1:11">
       <c r="A71" s="2">
         <v>10220008</v>
       </c>
@@ -3665,28 +3755,28 @@
         <v>102200</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D71" s="18">
         <v>4020350</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G71" s="2">
         <v>2</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="I71" s="2">
+        <v>99</v>
+      </c>
+      <c r="J71" s="2">
         <v>7</v>
       </c>
-      <c r="J71" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:10">
+      <c r="K71" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:11">
       <c r="A72" s="2">
         <v>10220009</v>
       </c>
@@ -3694,28 +3784,28 @@
         <v>102200</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D72" s="18">
         <v>4020007</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G72" s="2">
         <v>2</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I72" s="2">
+        <v>100</v>
+      </c>
+      <c r="J72" s="2">
         <v>8</v>
       </c>
-      <c r="J72" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" s="7" customFormat="1" spans="1:10">
+      <c r="K72" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" s="7" customFormat="1" spans="1:11">
       <c r="A73" s="7">
         <v>10210001</v>
       </c>
@@ -3723,13 +3813,13 @@
         <v>102100</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D73" s="28">
         <v>4020002</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F73" s="7">
         <v>1</v>
@@ -3737,14 +3827,14 @@
       <c r="G73" s="7">
         <v>2</v>
       </c>
-      <c r="I73" s="7">
+      <c r="J73" s="7">
         <v>-1</v>
       </c>
-      <c r="J73" s="7">
+      <c r="K73" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="74" s="7" customFormat="1" spans="1:10">
+    <row r="74" s="7" customFormat="1" spans="1:11">
       <c r="A74" s="7">
         <v>10210002</v>
       </c>
@@ -3752,26 +3842,26 @@
         <v>102100</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D74" s="28">
         <v>4020003</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F74" s="29"/>
       <c r="G74" s="7">
         <v>2</v>
       </c>
-      <c r="I74" s="7">
+      <c r="J74" s="7">
         <v>1</v>
       </c>
-      <c r="J74" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" s="7" customFormat="1" spans="1:10">
+      <c r="K74" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" s="7" customFormat="1" spans="1:11">
       <c r="A75" s="7">
         <v>10210003</v>
       </c>
@@ -3779,28 +3869,28 @@
         <v>102100</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D75" s="28">
         <v>4020004</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G75" s="28">
         <v>2</v>
       </c>
       <c r="H75" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="I75" s="7">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="J75" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76" s="7" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K75" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" s="7" customFormat="1" spans="1:11">
       <c r="A76" s="7">
         <v>10210004</v>
       </c>
@@ -3808,28 +3898,28 @@
         <v>102100</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D76" s="28">
         <v>4020094</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G76" s="7">
         <v>2</v>
       </c>
       <c r="H76" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="I76" s="7">
+        <v>102</v>
+      </c>
+      <c r="J76" s="7">
         <v>3</v>
       </c>
-      <c r="J76" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" s="7" customFormat="1" spans="1:10">
+      <c r="K76" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" s="7" customFormat="1" spans="1:11">
       <c r="A77" s="7">
         <v>10210005</v>
       </c>
@@ -3837,28 +3927,28 @@
         <v>102100</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D77" s="28">
         <v>4020345</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G77" s="28">
         <v>2</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="I77" s="7">
+        <v>103</v>
+      </c>
+      <c r="J77" s="7">
         <v>4</v>
       </c>
-      <c r="J77" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" s="7" customFormat="1" spans="1:10">
+      <c r="K77" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" s="7" customFormat="1" spans="1:11">
       <c r="A78" s="7">
         <v>10210006</v>
       </c>
@@ -3866,28 +3956,28 @@
         <v>102100</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D78" s="28">
         <v>4020346</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G78" s="7">
         <v>2</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="I78" s="7">
+        <v>104</v>
+      </c>
+      <c r="J78" s="7">
         <v>5</v>
       </c>
-      <c r="J78" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" s="7" customFormat="1" spans="1:10">
+      <c r="K78" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" s="7" customFormat="1" spans="1:11">
       <c r="A79" s="7">
         <v>10210007</v>
       </c>
@@ -3895,25 +3985,25 @@
         <v>102100</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D79" s="28">
         <v>4020347</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G79" s="28">
         <v>2</v>
       </c>
-      <c r="I79" s="7">
+      <c r="J79" s="7">
         <v>6</v>
       </c>
-      <c r="J79" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" s="7" customFormat="1" spans="1:10">
+      <c r="K79" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" s="7" customFormat="1" spans="1:11">
       <c r="A80" s="7">
         <v>10210008</v>
       </c>
@@ -3921,28 +4011,28 @@
         <v>102100</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D80" s="28">
         <v>4020349</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G80" s="7">
         <v>2</v>
       </c>
       <c r="H80" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="I80" s="7">
+        <v>105</v>
+      </c>
+      <c r="J80" s="7">
         <v>7</v>
       </c>
-      <c r="J80" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" s="7" customFormat="1" spans="1:10">
+      <c r="K80" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" s="7" customFormat="1" spans="1:11">
       <c r="A81" s="7">
         <v>10210009</v>
       </c>
@@ -3950,28 +4040,28 @@
         <v>102100</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D81" s="28">
         <v>4020350</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G81" s="28">
         <v>2</v>
       </c>
       <c r="H81" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="I81" s="7">
+        <v>106</v>
+      </c>
+      <c r="J81" s="7">
         <v>8</v>
       </c>
-      <c r="J81" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" s="7" customFormat="1" spans="1:10">
+      <c r="K81" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" s="7" customFormat="1" spans="1:11">
       <c r="A82" s="7">
         <v>10210010</v>
       </c>
@@ -3979,25 +4069,25 @@
         <v>102100</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D82" s="28">
         <v>4020412</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G82" s="7">
         <v>2</v>
       </c>
-      <c r="I82" s="7">
+      <c r="J82" s="7">
         <v>9</v>
       </c>
-      <c r="J82" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" s="7" customFormat="1" spans="1:10">
+      <c r="K82" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" s="7" customFormat="1" spans="1:11">
       <c r="A83" s="7">
         <v>10210011</v>
       </c>
@@ -4005,28 +4095,28 @@
         <v>102100</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D83" s="28">
         <v>4020413</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G83" s="28">
         <v>2</v>
       </c>
       <c r="H83" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="I83" s="7">
+        <v>107</v>
+      </c>
+      <c r="J83" s="7">
         <v>10</v>
       </c>
-      <c r="J83" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" s="7" customFormat="1" spans="1:10">
+      <c r="K83" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" s="7" customFormat="1" spans="1:11">
       <c r="A84" s="7">
         <v>10210012</v>
       </c>
@@ -4034,28 +4124,28 @@
         <v>102100</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D84" s="28">
         <v>4020414</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G84" s="7">
         <v>2</v>
       </c>
       <c r="H84" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="I84" s="7">
+        <v>108</v>
+      </c>
+      <c r="J84" s="7">
         <v>11</v>
       </c>
-      <c r="J84" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" s="7" customFormat="1" spans="1:10">
+      <c r="K84" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" s="7" customFormat="1" spans="1:11">
       <c r="A85" s="7">
         <v>10210013</v>
       </c>
@@ -4063,28 +4153,28 @@
         <v>102100</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D85" s="28">
         <v>4020007</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G85" s="28">
         <v>2</v>
       </c>
       <c r="H85" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="I85" s="7">
+        <v>109</v>
+      </c>
+      <c r="J85" s="7">
         <v>12</v>
       </c>
-      <c r="J85" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" s="3" customFormat="1" spans="1:10">
+      <c r="K85" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" s="3" customFormat="1" spans="1:11">
       <c r="A86" s="3">
         <v>10390001</v>
       </c>
@@ -4092,28 +4182,26 @@
         <v>103900</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D86" s="20">
         <v>4020002</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E86" s="3"/>
       <c r="F86" s="3">
         <v>1</v>
       </c>
       <c r="G86" s="3">
         <v>2</v>
       </c>
-      <c r="I86" s="3">
+      <c r="J86" s="3">
         <v>-1</v>
       </c>
-      <c r="J86" s="3">
+      <c r="K86" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="87" s="3" customFormat="1" spans="1:10">
+    <row r="87" s="3" customFormat="1" spans="1:11">
       <c r="A87" s="3">
         <v>10390002</v>
       </c>
@@ -4121,29 +4209,27 @@
         <v>103900</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D87" s="20">
         <v>4020003</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="21"/>
       <c r="G87" s="3">
         <v>2</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="I87" s="3">
+        <v>110</v>
+      </c>
+      <c r="J87" s="3">
         <v>1</v>
       </c>
-      <c r="J87" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="88" s="3" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="K87" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A88" s="3">
         <v>10390003</v>
       </c>
@@ -4151,21 +4237,27 @@
         <v>103900</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D88" s="20"/>
-      <c r="E88" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D88" s="20">
+        <v>4020645</v>
+      </c>
+      <c r="E88" s="3"/>
       <c r="G88" s="20">
         <v>2</v>
       </c>
       <c r="H88" s="20"/>
-      <c r="I88" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" s="3" customFormat="1" spans="1:10">
+      <c r="I88" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J88" s="3">
+        <v>2</v>
+      </c>
+      <c r="K88" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" s="3" customFormat="1" spans="1:11">
       <c r="A89" s="3">
         <v>10390004</v>
       </c>
@@ -4173,28 +4265,26 @@
         <v>103900</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D89" s="20">
         <v>4020640</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="E89" s="3"/>
       <c r="G89" s="20">
         <v>2</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="I89" s="3">
+        <v>114</v>
+      </c>
+      <c r="J89" s="3">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" s="3" customFormat="1" spans="1:10">
+      <c r="K89" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" s="3" customFormat="1" spans="1:11">
       <c r="A90" s="3">
         <v>10390005</v>
       </c>
@@ -4202,23 +4292,29 @@
         <v>103900</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D90" s="20"/>
-      <c r="E90" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D90" s="20">
+        <v>4020646</v>
+      </c>
+      <c r="E90" s="3"/>
       <c r="G90" s="3">
         <v>2</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="I90" s="3">
+        <v>116</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J90" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="91" s="3" customFormat="1" spans="1:10">
+      <c r="K90" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" s="3" customFormat="1" spans="1:11">
       <c r="A91" s="3">
         <v>10390006</v>
       </c>
@@ -4226,28 +4322,26 @@
         <v>103900</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D91" s="20">
         <v>4020641</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="E91" s="3"/>
       <c r="G91" s="3">
         <v>2</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="I91" s="3">
+        <v>119</v>
+      </c>
+      <c r="J91" s="3">
         <v>5</v>
       </c>
-      <c r="J91" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" s="3" customFormat="1" spans="1:10">
+      <c r="K91" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" s="3" customFormat="1" spans="1:11">
       <c r="A92" s="3">
         <v>10390007</v>
       </c>
@@ -4255,23 +4349,29 @@
         <v>103900</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D92" s="20"/>
-      <c r="E92" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D92" s="20">
+        <v>4020647</v>
+      </c>
+      <c r="E92" s="3"/>
       <c r="G92" s="3">
         <v>2</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="I92" s="3">
+        <v>121</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J92" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="93" s="3" customFormat="1" spans="1:10">
+      <c r="K92" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" s="3" customFormat="1" spans="1:11">
       <c r="A93" s="3">
         <v>10390008</v>
       </c>
@@ -4279,28 +4379,26 @@
         <v>103900</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D93" s="20">
         <v>4020642</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="E93" s="3"/>
       <c r="G93" s="20">
         <v>2</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="I93" s="3">
+        <v>124</v>
+      </c>
+      <c r="J93" s="3">
         <v>7</v>
       </c>
-      <c r="J93" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" s="3" customFormat="1" spans="1:10">
+      <c r="K93" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" s="3" customFormat="1" spans="1:11">
       <c r="A94" s="3">
         <v>10390009</v>
       </c>
@@ -4308,23 +4406,29 @@
         <v>103900</v>
       </c>
       <c r="C94" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D94" s="20"/>
-      <c r="E94" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D94" s="20">
+        <v>4020648</v>
+      </c>
+      <c r="E94" s="3"/>
       <c r="G94" s="3">
         <v>2</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I94" s="3">
+        <v>126</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J94" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" s="3" customFormat="1" spans="1:10">
+      <c r="K94" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" s="3" customFormat="1" spans="1:11">
       <c r="A95" s="3">
         <v>10390010</v>
       </c>
@@ -4332,28 +4436,26 @@
         <v>103900</v>
       </c>
       <c r="C95" s="30" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D95" s="20">
         <v>4020643</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="E95" s="3"/>
       <c r="G95" s="3">
         <v>2</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="I95" s="3">
+        <v>129</v>
+      </c>
+      <c r="J95" s="3">
         <v>9</v>
       </c>
-      <c r="J95" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" s="3" customFormat="1" spans="1:10">
+      <c r="K95" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" s="3" customFormat="1" spans="1:11">
       <c r="A96" s="3">
         <v>10390011</v>
       </c>
@@ -4361,23 +4463,29 @@
         <v>103900</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="D96" s="20"/>
-      <c r="E96" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D96" s="20">
+        <v>4020649</v>
+      </c>
+      <c r="E96" s="3"/>
       <c r="G96" s="3">
         <v>2</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I96" s="3">
+        <v>131</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J96" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" s="3" customFormat="1" spans="1:10">
+      <c r="K96" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" s="3" customFormat="1" spans="1:11">
       <c r="A97" s="3">
         <v>10390012</v>
       </c>
@@ -4385,54 +4493,53 @@
         <v>103900</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D97" s="20">
         <v>4020644</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="E97" s="3"/>
       <c r="G97" s="20">
         <v>2</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="I97" s="3">
+        <v>134</v>
+      </c>
+      <c r="J97" s="3">
         <v>11</v>
       </c>
-      <c r="J97" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="98" s="3" customFormat="1" spans="1:10">
+      <c r="K97" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" s="3" customFormat="1" spans="1:11">
       <c r="A98" s="3">
         <v>10390013</v>
       </c>
       <c r="B98" s="3">
         <v>103900</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>52</v>
+      <c r="C98" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="D98" s="20">
-        <v>4020347</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>35</v>
-      </c>
+        <v>4020650</v>
+      </c>
+      <c r="E98" s="3"/>
       <c r="G98" s="20">
         <v>2</v>
       </c>
-      <c r="I98" s="3">
+      <c r="I98" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J98" s="3">
         <v>12</v>
       </c>
-      <c r="J98" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="99" s="3" customFormat="1" spans="1:10">
+      <c r="K98" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" s="3" customFormat="1" spans="1:11">
       <c r="A99" s="3">
         <v>10390014</v>
       </c>
@@ -4440,28 +4547,26 @@
         <v>103900</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D99" s="20">
         <v>4020349</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="E99" s="3"/>
       <c r="G99" s="3">
         <v>2</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I99" s="3">
+        <v>137</v>
+      </c>
+      <c r="J99" s="3">
         <v>13</v>
       </c>
-      <c r="J99" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" s="3" customFormat="1" spans="1:10">
+      <c r="K99" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" s="3" customFormat="1" spans="1:11">
       <c r="A100" s="3">
         <v>10390015</v>
       </c>
@@ -4469,57 +4574,56 @@
         <v>103900</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D100" s="20">
         <v>4020350</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="E100" s="3"/>
       <c r="G100" s="20">
         <v>2</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="I100" s="3">
+        <v>138</v>
+      </c>
+      <c r="J100" s="3">
         <v>14</v>
       </c>
-      <c r="J100" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" s="3" customFormat="1" spans="1:10">
+      <c r="K100" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" s="3" customFormat="1" spans="1:11">
       <c r="A101" s="3">
         <v>10390016</v>
       </c>
       <c r="B101" s="3">
         <v>103900</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>64</v>
+      <c r="C101" s="30" t="s">
+        <v>139</v>
       </c>
       <c r="D101" s="20">
-        <v>4020007</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>4020651</v>
+      </c>
+      <c r="E101" s="3"/>
       <c r="G101" s="3">
         <v>2</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I101" s="3">
+        <v>140</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J101" s="3">
         <v>15</v>
       </c>
-      <c r="J101" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" s="4" customFormat="1" spans="1:10">
+      <c r="K101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" s="4" customFormat="1" spans="1:11">
       <c r="A102" s="4">
         <v>10200001</v>
       </c>
@@ -4527,13 +4631,13 @@
         <v>102000</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D102" s="22">
         <v>4020002</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F102" s="4">
         <v>1</v>
@@ -4541,14 +4645,14 @@
       <c r="G102" s="4">
         <v>2</v>
       </c>
-      <c r="I102" s="4">
+      <c r="J102" s="4">
         <v>-1</v>
       </c>
-      <c r="J102" s="4">
+      <c r="K102" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="103" s="4" customFormat="1" spans="1:10">
+    <row r="103" s="4" customFormat="1" spans="1:11">
       <c r="A103" s="4">
         <v>10200002</v>
       </c>
@@ -4556,25 +4660,25 @@
         <v>102000</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D103" s="22">
         <v>4020003</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G103" s="4">
         <v>2</v>
       </c>
-      <c r="I103" s="4">
+      <c r="J103" s="4">
         <v>1</v>
       </c>
-      <c r="J103" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" s="4" customFormat="1" spans="1:10">
+      <c r="K103" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" s="4" customFormat="1" spans="1:11">
       <c r="A104" s="4">
         <v>10200003</v>
       </c>
@@ -4582,28 +4686,28 @@
         <v>102000</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D104" s="22">
         <v>4020004</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G104" s="22">
         <v>2</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="I104" s="4">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="J104" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" s="4" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K104" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" s="4" customFormat="1" spans="1:11">
       <c r="A105" s="4">
         <v>10200004</v>
       </c>
@@ -4611,28 +4715,28 @@
         <v>102000</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D105" s="22">
         <v>4020005</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G105" s="4">
         <v>2</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="I105" s="4">
+        <v>143</v>
+      </c>
+      <c r="J105" s="4">
         <v>3</v>
       </c>
-      <c r="J105" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="106" s="4" customFormat="1" spans="1:10">
+      <c r="K105" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" s="4" customFormat="1" spans="1:11">
       <c r="A106" s="4">
         <v>10200005</v>
       </c>
@@ -4640,28 +4744,28 @@
         <v>102000</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D106" s="22">
         <v>4020345</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G106" s="22">
         <v>2</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="I106" s="4">
+        <v>144</v>
+      </c>
+      <c r="J106" s="4">
         <v>4</v>
       </c>
-      <c r="J106" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" s="4" customFormat="1" spans="1:10">
+      <c r="K106" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" s="4" customFormat="1" spans="1:11">
       <c r="A107" s="4">
         <v>10200006</v>
       </c>
@@ -4669,28 +4773,28 @@
         <v>102000</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D107" s="22">
         <v>4020346</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G107" s="4">
         <v>2</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="I107" s="4">
+        <v>145</v>
+      </c>
+      <c r="J107" s="4">
         <v>5</v>
       </c>
-      <c r="J107" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" s="4" customFormat="1" spans="1:10">
+      <c r="K107" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" s="4" customFormat="1" spans="1:11">
       <c r="A108" s="4">
         <v>10200007</v>
       </c>
@@ -4698,25 +4802,25 @@
         <v>102000</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D108" s="22">
         <v>4020347</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G108" s="22">
         <v>2</v>
       </c>
-      <c r="I108" s="4">
+      <c r="J108" s="4">
         <v>6</v>
       </c>
-      <c r="J108" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="109" s="4" customFormat="1" spans="1:10">
+      <c r="K108" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" s="4" customFormat="1" spans="1:11">
       <c r="A109" s="4">
         <v>10200008</v>
       </c>
@@ -4724,28 +4828,28 @@
         <v>102000</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D109" s="22">
         <v>4020349</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G109" s="4">
         <v>2</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="I109" s="4">
+        <v>146</v>
+      </c>
+      <c r="J109" s="4">
         <v>7</v>
       </c>
-      <c r="J109" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" s="4" customFormat="1" spans="1:10">
+      <c r="K109" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" s="4" customFormat="1" spans="1:11">
       <c r="A110" s="4">
         <v>10200009</v>
       </c>
@@ -4753,28 +4857,28 @@
         <v>102000</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D110" s="22">
         <v>4020350</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G110" s="22">
         <v>2</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="I110" s="4">
+        <v>147</v>
+      </c>
+      <c r="J110" s="4">
         <v>8</v>
       </c>
-      <c r="J110" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="111" s="4" customFormat="1" spans="1:10">
+      <c r="K110" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" s="4" customFormat="1" spans="1:11">
       <c r="A111" s="4">
         <v>10200010</v>
       </c>
@@ -4782,28 +4886,28 @@
         <v>102000</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D111" s="22">
         <v>4020007</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G111" s="4">
         <v>2</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="I111" s="4">
+        <v>148</v>
+      </c>
+      <c r="J111" s="4">
         <v>9</v>
       </c>
-      <c r="J111" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="112" s="5" customFormat="1" spans="1:10">
+      <c r="K111" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" s="5" customFormat="1" spans="1:11">
       <c r="A112" s="5">
         <v>10270001</v>
       </c>
@@ -4811,28 +4915,26 @@
         <v>102700</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D112" s="24">
         <v>4020002</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="E112" s="5"/>
       <c r="F112" s="5">
         <v>1</v>
       </c>
       <c r="G112" s="5">
         <v>2</v>
       </c>
-      <c r="I112" s="5">
+      <c r="J112" s="5">
         <v>-1</v>
       </c>
-      <c r="J112" s="5">
+      <c r="K112" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="113" s="5" customFormat="1" spans="1:10">
+    <row r="113" s="5" customFormat="1" spans="1:11">
       <c r="A113" s="5">
         <v>10270002</v>
       </c>
@@ -4840,28 +4942,26 @@
         <v>102700</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D113" s="24">
         <v>4020003</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="E113" s="5"/>
       <c r="G113" s="5">
         <v>2</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I113" s="5">
+        <v>149</v>
+      </c>
+      <c r="J113" s="5">
         <v>1</v>
       </c>
-      <c r="J113" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="114" s="5" customFormat="1" spans="1:10">
+      <c r="K113" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" s="5" customFormat="1" spans="1:11">
       <c r="A114" s="5">
         <v>10270003</v>
       </c>
@@ -4869,26 +4969,25 @@
         <v>102700</v>
       </c>
       <c r="C114" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D114" s="24">
-        <v>4020640</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>25</v>
+        <v>4020645</v>
       </c>
       <c r="G114" s="5">
         <v>2</v>
       </c>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5">
-        <v>2</v>
+      <c r="I114" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="J114" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="115" s="5" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K114" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" s="5" customFormat="1" spans="1:11">
       <c r="A115" s="5">
         <v>10270004</v>
       </c>
@@ -4896,28 +4995,26 @@
         <v>102700</v>
       </c>
       <c r="C115" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D115" s="24">
-        <v>4020641</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>25</v>
-      </c>
+        <v>4020640</v>
+      </c>
+      <c r="E115" s="5"/>
       <c r="G115" s="5">
         <v>2</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I115" s="5">
+        <v>151</v>
+      </c>
+      <c r="J115" s="5">
         <v>3</v>
       </c>
-      <c r="J115" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" s="5" customFormat="1" spans="1:10">
+      <c r="K115" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" s="5" customFormat="1" spans="1:11">
       <c r="A116" s="5">
         <v>10270005</v>
       </c>
@@ -4925,28 +5022,28 @@
         <v>102700</v>
       </c>
       <c r="C116" s="31" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D116" s="24">
-        <v>4020642</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>25</v>
+        <v>4020646</v>
       </c>
       <c r="G116" s="5">
         <v>2</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I116" s="5">
+        <v>152</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J116" s="5">
         <v>4</v>
       </c>
-      <c r="J116" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="117" s="5" customFormat="1" spans="1:10">
+      <c r="K116" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" s="5" customFormat="1" spans="1:11">
       <c r="A117" s="5">
         <v>10270006</v>
       </c>
@@ -4954,28 +5051,26 @@
         <v>102700</v>
       </c>
       <c r="C117" s="31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D117" s="24">
-        <v>4020643</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>25</v>
-      </c>
+        <v>4020641</v>
+      </c>
+      <c r="E117" s="5"/>
       <c r="G117" s="5">
         <v>2</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I117" s="5">
+        <v>154</v>
+      </c>
+      <c r="J117" s="5">
         <v>5</v>
       </c>
-      <c r="J117" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" s="5" customFormat="1" spans="1:10">
+      <c r="K117" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" s="5" customFormat="1" spans="1:11">
       <c r="A118" s="5">
         <v>10270007</v>
       </c>
@@ -4983,563 +5078,700 @@
         <v>102700</v>
       </c>
       <c r="C118" s="31" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D118" s="24">
-        <v>4020644</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>25</v>
+        <v>4020647</v>
       </c>
       <c r="G118" s="5">
         <v>2</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I118" s="5">
+        <v>155</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J118" s="5">
         <v>6</v>
       </c>
-      <c r="J118" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="119" s="5" customFormat="1" spans="1:10">
+      <c r="K118" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" s="5" customFormat="1" spans="1:11">
       <c r="A119" s="5">
         <v>10270008</v>
       </c>
       <c r="B119" s="5">
         <v>102700</v>
       </c>
-      <c r="C119" s="5" t="s">
-        <v>52</v>
+      <c r="C119" s="31" t="s">
+        <v>123</v>
       </c>
       <c r="D119" s="24">
-        <v>4020347</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>4020642</v>
+      </c>
+      <c r="E119" s="5"/>
       <c r="G119" s="5">
         <v>2</v>
       </c>
-      <c r="I119" s="5">
+      <c r="H119" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J119" s="5">
         <v>7</v>
       </c>
-      <c r="J119" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" s="5" customFormat="1" spans="1:10">
+      <c r="K119" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" s="5" customFormat="1" spans="1:11">
       <c r="A120" s="5">
         <v>10270009</v>
       </c>
       <c r="B120" s="5">
         <v>102700</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>53</v>
+      <c r="C120" s="31" t="s">
+        <v>125</v>
       </c>
       <c r="D120" s="24">
-        <v>4020349</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>35</v>
+        <v>4020648</v>
       </c>
       <c r="G120" s="5">
         <v>2</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I120" s="5">
+        <v>158</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J120" s="5">
         <v>8</v>
       </c>
-      <c r="J120" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="121" s="5" customFormat="1" spans="1:10">
+      <c r="K120" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" s="5" customFormat="1" spans="1:11">
       <c r="A121" s="5">
         <v>10270010</v>
       </c>
       <c r="B121" s="5">
         <v>102700</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>55</v>
+      <c r="C121" s="31" t="s">
+        <v>128</v>
       </c>
       <c r="D121" s="24">
-        <v>4020350</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>4020643</v>
+      </c>
+      <c r="E121" s="5"/>
       <c r="G121" s="5">
         <v>2</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I121" s="5">
+        <v>160</v>
+      </c>
+      <c r="J121" s="5">
         <v>9</v>
       </c>
-      <c r="J121" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="122" s="5" customFormat="1" spans="1:10">
+      <c r="K121" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" s="5" customFormat="1" spans="1:11">
       <c r="A122" s="5">
         <v>10270011</v>
       </c>
       <c r="B122" s="5">
         <v>102700</v>
       </c>
-      <c r="C122" s="5" t="s">
-        <v>64</v>
+      <c r="C122" s="31" t="s">
+        <v>130</v>
       </c>
       <c r="D122" s="24">
-        <v>4020007</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>37</v>
+        <v>4020649</v>
       </c>
       <c r="G122" s="5">
         <v>2</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I122" s="5">
+        <v>161</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J122" s="5">
         <v>10</v>
       </c>
-      <c r="J122" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="123" s="1" customFormat="1" spans="1:10">
-      <c r="A123" s="1">
+      <c r="K122" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" s="5" customFormat="1" spans="1:11">
+      <c r="A123" s="5">
+        <v>10270012</v>
+      </c>
+      <c r="B123" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D123" s="24">
+        <v>4020644</v>
+      </c>
+      <c r="E123" s="5"/>
+      <c r="G123" s="5">
+        <v>2</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J123" s="5">
+        <v>11</v>
+      </c>
+      <c r="K123" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" s="5" customFormat="1" spans="1:11">
+      <c r="A124" s="5">
+        <v>10270013</v>
+      </c>
+      <c r="B124" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C124" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D124" s="24">
+        <v>4020650</v>
+      </c>
+      <c r="E124" s="5"/>
+      <c r="G124" s="5">
+        <v>2</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J124" s="5">
+        <v>12</v>
+      </c>
+      <c r="K124" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" s="5" customFormat="1" spans="1:11">
+      <c r="A125" s="5">
+        <v>10270014</v>
+      </c>
+      <c r="B125" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D125" s="24">
+        <v>4020349</v>
+      </c>
+      <c r="E125" s="5"/>
+      <c r="G125" s="5">
+        <v>2</v>
+      </c>
+      <c r="H125" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J125" s="5">
+        <v>13</v>
+      </c>
+      <c r="K125" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" s="5" customFormat="1" spans="1:11">
+      <c r="A126" s="5">
+        <v>10270015</v>
+      </c>
+      <c r="B126" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D126" s="24">
+        <v>4020350</v>
+      </c>
+      <c r="E126" s="5"/>
+      <c r="G126" s="5">
+        <v>2</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J126" s="5">
+        <v>14</v>
+      </c>
+      <c r="K126" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" s="5" customFormat="1" spans="1:11">
+      <c r="A127" s="5">
+        <v>10270016</v>
+      </c>
+      <c r="B127" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C127" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D127" s="24">
+        <v>4020651</v>
+      </c>
+      <c r="E127" s="5"/>
+      <c r="G127" s="5">
+        <v>2</v>
+      </c>
+      <c r="H127" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J127" s="5">
+        <v>15</v>
+      </c>
+      <c r="K127" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" s="1" customFormat="1" spans="1:11">
+      <c r="A128" s="1">
         <v>10150001</v>
-      </c>
-      <c r="B123" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D123" s="16">
-        <v>4020002</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F123" s="1">
-        <v>1</v>
-      </c>
-      <c r="G123" s="1">
-        <v>2</v>
-      </c>
-      <c r="I123" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" s="1" customFormat="1" spans="1:10">
-      <c r="A124" s="1">
-        <v>10150002</v>
-      </c>
-      <c r="B124" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D124" s="16">
-        <v>4020003</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G124" s="1">
-        <v>2</v>
-      </c>
-      <c r="I124" s="1">
-        <v>1</v>
-      </c>
-      <c r="J124" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="1" spans="1:10">
-      <c r="A125" s="1">
-        <v>10150003</v>
-      </c>
-      <c r="B125" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D125" s="16">
-        <v>4020004</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G125" s="1">
-        <v>2</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I125" s="1">
-        <v>2</v>
-      </c>
-      <c r="J125" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="126" s="1" customFormat="1" spans="1:10">
-      <c r="A126" s="1">
-        <v>10150004</v>
-      </c>
-      <c r="B126" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D126" s="16">
-        <v>4020094</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G126" s="1">
-        <v>2</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I126" s="1">
-        <v>3</v>
-      </c>
-      <c r="J126" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="127" s="1" customFormat="1" spans="1:10">
-      <c r="A127" s="1">
-        <v>10150005</v>
-      </c>
-      <c r="B127" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D127" s="16">
-        <v>4020345</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G127" s="1">
-        <v>2</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I127" s="1">
-        <v>4</v>
-      </c>
-      <c r="J127" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="128" s="1" customFormat="1" spans="1:10">
-      <c r="A128" s="1">
-        <v>10150006</v>
       </c>
       <c r="B128" s="1">
         <v>101500</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D128" s="16">
-        <v>4020346</v>
+        <v>4020002</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="F128" s="1">
+        <v>1</v>
+      </c>
       <c r="G128" s="1">
         <v>2</v>
       </c>
-      <c r="H128" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I128" s="1">
-        <v>5</v>
-      </c>
       <c r="J128" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="129" s="1" customFormat="1" spans="1:10">
+        <v>-1</v>
+      </c>
+      <c r="K128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" s="1" customFormat="1" spans="1:11">
       <c r="A129" s="1">
-        <v>10150007</v>
+        <v>10150002</v>
       </c>
       <c r="B129" s="1">
         <v>101500</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D129" s="16">
-        <v>4020347</v>
+        <v>4020003</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G129" s="1">
         <v>2</v>
       </c>
-      <c r="I129" s="1">
-        <v>7</v>
-      </c>
       <c r="J129" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="130" s="1" customFormat="1" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="K129" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="1" spans="1:11">
       <c r="A130" s="1">
-        <v>10150008</v>
+        <v>10150003</v>
       </c>
       <c r="B130" s="1">
         <v>101500</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D130" s="16">
-        <v>4020349</v>
+        <v>4020004</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G130" s="1">
         <v>2</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I130" s="1">
-        <v>8</v>
+        <v>169</v>
       </c>
       <c r="J130" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="131" s="1" customFormat="1" spans="1:10">
+        <v>2</v>
+      </c>
+      <c r="K130" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="1" spans="1:11">
       <c r="A131" s="1">
-        <v>10150009</v>
+        <v>10150004</v>
       </c>
       <c r="B131" s="1">
         <v>101500</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D131" s="16">
-        <v>4020350</v>
+        <v>4020094</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G131" s="1">
         <v>2</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I131" s="1">
-        <v>9</v>
+        <v>170</v>
       </c>
       <c r="J131" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="132" s="1" customFormat="1" spans="1:10">
+        <v>3</v>
+      </c>
+      <c r="K131" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" s="1" customFormat="1" spans="1:11">
       <c r="A132" s="1">
-        <v>10150010</v>
+        <v>10150005</v>
       </c>
       <c r="B132" s="1">
         <v>101500</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="D132" s="16">
-        <v>4020466</v>
+        <v>4020345</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="G132" s="1">
         <v>2</v>
       </c>
-      <c r="I132" s="1">
-        <v>10</v>
+      <c r="H132" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="J132" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="133" s="1" customFormat="1" spans="1:10">
+        <v>4</v>
+      </c>
+      <c r="K132" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" s="1" customFormat="1" spans="1:11">
       <c r="A133" s="1">
-        <v>10150011</v>
+        <v>10150006</v>
       </c>
       <c r="B133" s="1">
         <v>101500</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="D133" s="16">
-        <v>4020467</v>
+        <v>4020346</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="G133" s="1">
         <v>2</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I133" s="1">
-        <v>11</v>
+        <v>172</v>
       </c>
       <c r="J133" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="134" s="1" customFormat="1" spans="1:10">
+        <v>5</v>
+      </c>
+      <c r="K133" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" s="1" customFormat="1" spans="1:11">
       <c r="A134" s="1">
-        <v>10150012</v>
+        <v>10150007</v>
       </c>
       <c r="B134" s="1">
         <v>101500</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="D134" s="16">
-        <v>4020468</v>
+        <v>4020347</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G134" s="1">
         <v>2</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I134" s="1">
-        <v>12</v>
-      </c>
       <c r="J134" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="135" s="1" customFormat="1" spans="1:10">
+        <v>7</v>
+      </c>
+      <c r="K134" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" spans="1:11">
       <c r="A135" s="1">
-        <v>10150013</v>
+        <v>10150008</v>
       </c>
       <c r="B135" s="1">
         <v>101500</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="D135" s="16">
-        <v>4020469</v>
+        <v>4020349</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G135" s="1">
         <v>2</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I135" s="1">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="J135" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="1" spans="1:10">
+        <v>8</v>
+      </c>
+      <c r="K135" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="1" spans="1:11">
       <c r="A136" s="1">
-        <v>10150014</v>
+        <v>10150009</v>
       </c>
       <c r="B136" s="1">
         <v>101500</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="D136" s="16">
-        <v>4020470</v>
+        <v>4020350</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G136" s="1">
         <v>2</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I136" s="1">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="J136" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="137" s="1" customFormat="1" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K136" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="1" spans="1:11">
       <c r="A137" s="1">
-        <v>10150015</v>
+        <v>10150010</v>
       </c>
       <c r="B137" s="1">
         <v>101500</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>64</v>
+        <v>175</v>
       </c>
       <c r="D137" s="16">
+        <v>4020466</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G137" s="1">
+        <v>2</v>
+      </c>
+      <c r="J137" s="1">
+        <v>10</v>
+      </c>
+      <c r="K137" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="1" spans="1:11">
+      <c r="A138" s="1">
+        <v>10150011</v>
+      </c>
+      <c r="B138" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D138" s="16">
+        <v>4020467</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G138" s="1">
+        <v>2</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J138" s="1">
+        <v>11</v>
+      </c>
+      <c r="K138" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" s="1" customFormat="1" spans="1:11">
+      <c r="A139" s="1">
+        <v>10150012</v>
+      </c>
+      <c r="B139" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D139" s="16">
+        <v>4020468</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G139" s="1">
+        <v>2</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J139" s="1">
+        <v>12</v>
+      </c>
+      <c r="K139" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" s="1" customFormat="1" spans="1:11">
+      <c r="A140" s="1">
+        <v>10150013</v>
+      </c>
+      <c r="B140" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D140" s="16">
+        <v>4020469</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G140" s="1">
+        <v>2</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J140" s="1">
+        <v>13</v>
+      </c>
+      <c r="K140" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" s="1" customFormat="1" spans="1:11">
+      <c r="A141" s="1">
+        <v>10150014</v>
+      </c>
+      <c r="B141" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D141" s="16">
+        <v>4020470</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G141" s="1">
+        <v>2</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J141" s="1">
+        <v>14</v>
+      </c>
+      <c r="K141" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" s="1" customFormat="1" spans="1:11">
+      <c r="A142" s="1">
+        <v>10150015</v>
+      </c>
+      <c r="B142" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D142" s="16">
         <v>4020007</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G137" s="1">
-        <v>2</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I137" s="1">
+      <c r="E142" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" s="1">
+        <v>2</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J142" s="1">
         <v>15</v>
       </c>
-      <c r="J137" s="1">
+      <c r="K142" s="1">
         <v>100</v>
       </c>
     </row>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="196">
   <si>
     <t>属性id</t>
   </si>
@@ -240,12 +240,15 @@
     <t>中奖提成比例</t>
   </si>
   <si>
-    <t>yjy_jmtb_1.png</t>
+    <t>jntb_8</t>
   </si>
   <si>
     <t>提成人数上限</t>
   </si>
   <si>
+    <t>jntb_9</t>
+  </si>
+  <si>
     <t>下注金额增加</t>
   </si>
   <si>
@@ -450,6 +453,9 @@
     <t>解锁sweet win奖励</t>
   </si>
   <si>
+    <t>jntb_1_5.png</t>
+  </si>
+  <si>
     <t>PetSquadsweet</t>
   </si>
   <si>
@@ -462,6 +468,9 @@
     <t>解锁big win奖励</t>
   </si>
   <si>
+    <t>jntb_1_4</t>
+  </si>
+  <si>
     <t>10390004,10</t>
   </si>
   <si>
@@ -477,6 +486,9 @@
     <t>解锁mega win奖励</t>
   </si>
   <si>
+    <t>jntb_1_3</t>
+  </si>
+  <si>
     <t>10390002,10</t>
   </si>
   <si>
@@ -492,6 +504,9 @@
     <t>解锁epic win奖励</t>
   </si>
   <si>
+    <t>jntb_1_2</t>
+  </si>
+  <si>
     <t>10390008,10</t>
   </si>
   <si>
@@ -507,6 +522,9 @@
     <t>解锁legendary win奖励</t>
   </si>
   <si>
+    <t>jntb_1_1</t>
+  </si>
+  <si>
     <t>10390010,10</t>
   </si>
   <si>
@@ -522,18 +540,30 @@
     <t>解锁免费模式</t>
   </si>
   <si>
+    <t>jntb_2_3</t>
+  </si>
+  <si>
     <t>PetSquadFree</t>
   </si>
   <si>
+    <t>jntb_2_2</t>
+  </si>
+  <si>
     <t>10390013,1</t>
   </si>
   <si>
+    <t>jntb_2_1</t>
+  </si>
+  <si>
     <t>10390014,10</t>
   </si>
   <si>
     <t>解锁jackpot大奖</t>
   </si>
   <si>
+    <t>jntb_5</t>
+  </si>
+  <si>
     <t>10390015,10</t>
   </si>
   <si>
@@ -562,6 +592,9 @@
   </si>
   <si>
     <t>10270006,10</t>
+  </si>
+  <si>
+    <t>jntb_1_5</t>
   </si>
   <si>
     <t>ElephantFortunesweet</t>
@@ -2140,7 +2173,7 @@
         <v>4020608</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" s="16">
         <v>1</v>
@@ -2161,7 +2194,7 @@
         <v>100700</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="18">
         <v>4020002</v>
@@ -2190,7 +2223,7 @@
         <v>100700</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="18">
         <v>4020003</v>
@@ -2217,7 +2250,7 @@
         <v>100700</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="18">
         <v>4020004</v>
@@ -2229,7 +2262,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J17" s="2">
         <v>2</v>
@@ -2246,7 +2279,7 @@
         <v>100700</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="18">
         <v>4020094</v>
@@ -2258,7 +2291,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="2">
         <v>3</v>
@@ -2275,7 +2308,7 @@
         <v>100700</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="18">
         <v>4020345</v>
@@ -2287,7 +2320,7 @@
         <v>2</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J19" s="2">
         <v>4</v>
@@ -2304,7 +2337,7 @@
         <v>100700</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" s="18">
         <v>4020346</v>
@@ -2316,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J20" s="2">
         <v>5</v>
@@ -2333,7 +2366,7 @@
         <v>100700</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" s="18">
         <v>4020347</v>
@@ -2359,7 +2392,7 @@
         <v>100700</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="18">
         <v>4020349</v>
@@ -2371,7 +2404,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J22" s="2">
         <v>7</v>
@@ -2388,7 +2421,7 @@
         <v>100700</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="18">
         <v>4020350</v>
@@ -2400,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J23" s="2">
         <v>8</v>
@@ -2417,7 +2450,7 @@
         <v>101200</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" s="20">
         <v>4020002</v>
@@ -2446,7 +2479,7 @@
         <v>101200</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="20">
         <v>4020003</v>
@@ -2473,7 +2506,7 @@
         <v>101200</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D26" s="20">
         <v>4020004</v>
@@ -2486,7 +2519,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J26" s="3">
         <v>2</v>
@@ -2503,7 +2536,7 @@
         <v>101200</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D27" s="20">
         <v>4020094</v>
@@ -2515,7 +2548,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J27" s="3">
         <v>3</v>
@@ -2532,7 +2565,7 @@
         <v>101200</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D28" s="20">
         <v>4020095</v>
@@ -2544,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J28" s="3">
         <v>4</v>
@@ -2561,7 +2594,7 @@
         <v>101200</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D29" s="20">
         <v>4020401</v>
@@ -2587,7 +2620,7 @@
         <v>101200</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30" s="20">
         <v>4020007</v>
@@ -2599,7 +2632,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J30" s="3">
         <v>6</v>
@@ -2616,7 +2649,7 @@
         <v>101800</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D31" s="22">
         <v>4020002</v>
@@ -2645,7 +2678,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D32" s="22">
         <v>4020003</v>
@@ -2672,7 +2705,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" s="22">
         <v>4020004</v>
@@ -2684,7 +2717,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J33" s="4">
         <v>2</v>
@@ -2701,7 +2734,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D34" s="22">
         <v>4020094</v>
@@ -2713,7 +2746,7 @@
         <v>2</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J34" s="4">
         <v>3</v>
@@ -2730,7 +2763,7 @@
         <v>101800</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D35" s="22">
         <v>4020345</v>
@@ -2742,7 +2775,7 @@
         <v>2</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J35" s="4">
         <v>4</v>
@@ -2759,7 +2792,7 @@
         <v>101800</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D36" s="22">
         <v>4020346</v>
@@ -2771,7 +2804,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J36" s="4">
         <v>5</v>
@@ -2788,7 +2821,7 @@
         <v>101800</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D37" s="22">
         <v>4020347</v>
@@ -2814,7 +2847,7 @@
         <v>101800</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38" s="22">
         <v>4020349</v>
@@ -2826,7 +2859,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J38" s="4">
         <v>7</v>
@@ -2843,7 +2876,7 @@
         <v>101800</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D39" s="22">
         <v>4020350</v>
@@ -2855,7 +2888,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J39" s="4">
         <v>8</v>
@@ -2872,7 +2905,7 @@
         <v>101800</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D40" s="22">
         <v>4020007</v>
@@ -2884,7 +2917,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J40" s="4">
         <v>9</v>
@@ -2901,7 +2934,7 @@
         <v>102500</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" s="24">
         <v>4020002</v>
@@ -2930,7 +2963,7 @@
         <v>102500</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" s="24">
         <v>4020003</v>
@@ -2957,7 +2990,7 @@
         <v>102500</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D43" s="24">
         <v>4020004</v>
@@ -2969,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J43" s="5">
         <v>2</v>
@@ -2986,7 +3019,7 @@
         <v>102500</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D44" s="24">
         <v>4020094</v>
@@ -2998,7 +3031,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J44" s="5">
         <v>3</v>
@@ -3015,7 +3048,7 @@
         <v>102500</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D45" s="24">
         <v>4020345</v>
@@ -3027,7 +3060,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J45" s="5">
         <v>4</v>
@@ -3044,7 +3077,7 @@
         <v>102500</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D46" s="24">
         <v>4020346</v>
@@ -3056,7 +3089,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J46" s="5">
         <v>5</v>
@@ -3073,7 +3106,7 @@
         <v>102500</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D47" s="24">
         <v>4020347</v>
@@ -3099,7 +3132,7 @@
         <v>102500</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D48" s="24">
         <v>4020349</v>
@@ -3111,7 +3144,7 @@
         <v>2</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J48" s="5">
         <v>7</v>
@@ -3128,7 +3161,7 @@
         <v>102500</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D49" s="24">
         <v>4020350</v>
@@ -3140,7 +3173,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J49" s="5">
         <v>8</v>
@@ -3157,7 +3190,7 @@
         <v>102500</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D50" s="24">
         <v>4020007</v>
@@ -3169,7 +3202,7 @@
         <v>2</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J50" s="5">
         <v>9</v>
@@ -3186,7 +3219,7 @@
         <v>103100</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" s="26">
         <v>4020002</v>
@@ -3215,7 +3248,7 @@
         <v>103100</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D52" s="26">
         <v>4020003</v>
@@ -3255,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J53" s="6">
         <v>2</v>
@@ -3272,7 +3305,7 @@
         <v>103100</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D54" s="26">
         <v>4020094</v>
@@ -3284,7 +3317,7 @@
         <v>2</v>
       </c>
       <c r="H54" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J54" s="6">
         <v>3</v>
@@ -3301,7 +3334,7 @@
         <v>103100</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D55" s="26">
         <v>4020345</v>
@@ -3313,7 +3346,7 @@
         <v>2</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J55" s="6">
         <v>4</v>
@@ -3330,7 +3363,7 @@
         <v>103100</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D56" s="26">
         <v>4020346</v>
@@ -3342,7 +3375,7 @@
         <v>2</v>
       </c>
       <c r="H56" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J56" s="6">
         <v>5</v>
@@ -3359,7 +3392,7 @@
         <v>103100</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D57" s="26">
         <v>4020347</v>
@@ -3385,7 +3418,7 @@
         <v>103100</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D58" s="26">
         <v>4020349</v>
@@ -3397,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J58" s="6">
         <v>7</v>
@@ -3414,7 +3447,7 @@
         <v>103100</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D59" s="26">
         <v>4020350</v>
@@ -3426,7 +3459,7 @@
         <v>2</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J59" s="6">
         <v>8</v>
@@ -3443,13 +3476,13 @@
         <v>103100</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D60" s="26">
         <v>4020412</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G60" s="6">
         <v>2</v>
@@ -3469,19 +3502,19 @@
         <v>103100</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D61" s="26">
         <v>4020413</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G61" s="27">
         <v>2</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J61" s="6">
         <v>10</v>
@@ -3498,19 +3531,19 @@
         <v>103100</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D62" s="26">
         <v>4020414</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G62" s="6">
         <v>2</v>
       </c>
       <c r="H62" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J62" s="6">
         <v>11</v>
@@ -3527,7 +3560,7 @@
         <v>103100</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D63" s="26">
         <v>4020007</v>
@@ -3539,7 +3572,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J63" s="6">
         <v>12</v>
@@ -3556,7 +3589,7 @@
         <v>102200</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D64" s="18">
         <v>4020002</v>
@@ -3585,7 +3618,7 @@
         <v>102200</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D65" s="18">
         <v>4020003</v>
@@ -3612,7 +3645,7 @@
         <v>102200</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D66" s="18">
         <v>4020004</v>
@@ -3625,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J66" s="2">
         <v>2</v>
@@ -3642,7 +3675,7 @@
         <v>102200</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D67" s="18">
         <v>4020094</v>
@@ -3654,7 +3687,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J67" s="2">
         <v>3</v>
@@ -3671,7 +3704,7 @@
         <v>102200</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D68" s="18">
         <v>4020095</v>
@@ -3683,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J68" s="2">
         <v>4</v>
@@ -3700,7 +3733,7 @@
         <v>102200</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D69" s="18">
         <v>4020347</v>
@@ -3726,7 +3759,7 @@
         <v>102200</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D70" s="18">
         <v>4020349</v>
@@ -3738,7 +3771,7 @@
         <v>2</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J70" s="2">
         <v>6</v>
@@ -3755,7 +3788,7 @@
         <v>102200</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D71" s="18">
         <v>4020350</v>
@@ -3767,7 +3800,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J71" s="2">
         <v>7</v>
@@ -3784,7 +3817,7 @@
         <v>102200</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D72" s="18">
         <v>4020007</v>
@@ -3796,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J72" s="2">
         <v>8</v>
@@ -3813,7 +3846,7 @@
         <v>102100</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D73" s="28">
         <v>4020002</v>
@@ -3842,7 +3875,7 @@
         <v>102100</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D74" s="28">
         <v>4020003</v>
@@ -3869,7 +3902,7 @@
         <v>102100</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D75" s="28">
         <v>4020004</v>
@@ -3881,7 +3914,7 @@
         <v>2</v>
       </c>
       <c r="H75" s="28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J75" s="7">
         <v>2</v>
@@ -3898,7 +3931,7 @@
         <v>102100</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D76" s="28">
         <v>4020094</v>
@@ -3910,7 +3943,7 @@
         <v>2</v>
       </c>
       <c r="H76" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J76" s="7">
         <v>3</v>
@@ -3927,7 +3960,7 @@
         <v>102100</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D77" s="28">
         <v>4020345</v>
@@ -3939,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J77" s="7">
         <v>4</v>
@@ -3956,7 +3989,7 @@
         <v>102100</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D78" s="28">
         <v>4020346</v>
@@ -3968,7 +4001,7 @@
         <v>2</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J78" s="7">
         <v>5</v>
@@ -3985,7 +4018,7 @@
         <v>102100</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D79" s="28">
         <v>4020347</v>
@@ -4011,7 +4044,7 @@
         <v>102100</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D80" s="28">
         <v>4020349</v>
@@ -4023,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="H80" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J80" s="7">
         <v>7</v>
@@ -4040,7 +4073,7 @@
         <v>102100</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D81" s="28">
         <v>4020350</v>
@@ -4052,7 +4085,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J81" s="7">
         <v>8</v>
@@ -4069,13 +4102,13 @@
         <v>102100</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D82" s="28">
         <v>4020412</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G82" s="7">
         <v>2</v>
@@ -4095,19 +4128,19 @@
         <v>102100</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D83" s="28">
         <v>4020413</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G83" s="28">
         <v>2</v>
       </c>
       <c r="H83" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J83" s="7">
         <v>10</v>
@@ -4124,19 +4157,19 @@
         <v>102100</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D84" s="28">
         <v>4020414</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G84" s="7">
         <v>2</v>
       </c>
       <c r="H84" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J84" s="7">
         <v>11</v>
@@ -4153,7 +4186,7 @@
         <v>102100</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D85" s="28">
         <v>4020007</v>
@@ -4165,7 +4198,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J85" s="7">
         <v>12</v>
@@ -4182,12 +4215,14 @@
         <v>103900</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D86" s="20">
         <v>4020002</v>
       </c>
-      <c r="E86" s="3"/>
+      <c r="E86" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="F86" s="3">
         <v>1</v>
       </c>
@@ -4209,18 +4244,20 @@
         <v>103900</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D87" s="20">
         <v>4020003</v>
       </c>
-      <c r="E87" s="3"/>
+      <c r="E87" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="F87" s="21"/>
       <c r="G87" s="3">
         <v>2</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J87" s="3">
         <v>1</v>
@@ -4237,18 +4274,20 @@
         <v>103900</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D88" s="20">
         <v>4020645</v>
       </c>
-      <c r="E88" s="3"/>
+      <c r="E88" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="G88" s="20">
         <v>2</v>
       </c>
       <c r="H88" s="20"/>
       <c r="I88" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J88" s="3">
         <v>2</v>
@@ -4265,17 +4304,19 @@
         <v>103900</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D89" s="20">
         <v>4020640</v>
       </c>
-      <c r="E89" s="3"/>
+      <c r="E89" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="G89" s="20">
         <v>2</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J89" s="3">
         <v>3</v>
@@ -4292,20 +4333,22 @@
         <v>103900</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D90" s="20">
         <v>4020646</v>
       </c>
-      <c r="E90" s="3"/>
+      <c r="E90" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="G90" s="3">
         <v>2</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J90" s="3">
         <v>4</v>
@@ -4322,17 +4365,19 @@
         <v>103900</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D91" s="20">
         <v>4020641</v>
       </c>
-      <c r="E91" s="3"/>
+      <c r="E91" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="G91" s="3">
         <v>2</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J91" s="3">
         <v>5</v>
@@ -4349,20 +4394,22 @@
         <v>103900</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D92" s="20">
         <v>4020647</v>
       </c>
-      <c r="E92" s="3"/>
+      <c r="E92" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="G92" s="3">
         <v>2</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J92" s="3">
         <v>6</v>
@@ -4379,17 +4426,19 @@
         <v>103900</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D93" s="20">
         <v>4020642</v>
       </c>
-      <c r="E93" s="3"/>
+      <c r="E93" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="G93" s="20">
         <v>2</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J93" s="3">
         <v>7</v>
@@ -4406,20 +4455,22 @@
         <v>103900</v>
       </c>
       <c r="C94" s="30" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D94" s="20">
         <v>4020648</v>
       </c>
-      <c r="E94" s="3"/>
+      <c r="E94" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="G94" s="3">
         <v>2</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J94" s="3">
         <v>8</v>
@@ -4436,17 +4487,19 @@
         <v>103900</v>
       </c>
       <c r="C95" s="30" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D95" s="20">
         <v>4020643</v>
       </c>
-      <c r="E95" s="3"/>
+      <c r="E95" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="G95" s="3">
         <v>2</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J95" s="3">
         <v>9</v>
@@ -4463,20 +4516,22 @@
         <v>103900</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D96" s="20">
         <v>4020649</v>
       </c>
-      <c r="E96" s="3"/>
+      <c r="E96" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="G96" s="3">
         <v>2</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J96" s="3">
         <v>10</v>
@@ -4493,17 +4548,19 @@
         <v>103900</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D97" s="20">
         <v>4020644</v>
       </c>
-      <c r="E97" s="3"/>
+      <c r="E97" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="G97" s="20">
         <v>2</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J97" s="3">
         <v>11</v>
@@ -4520,17 +4577,19 @@
         <v>103900</v>
       </c>
       <c r="C98" s="30" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D98" s="20">
         <v>4020650</v>
       </c>
-      <c r="E98" s="3"/>
+      <c r="E98" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="G98" s="20">
         <v>2</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J98" s="3">
         <v>12</v>
@@ -4547,17 +4606,19 @@
         <v>103900</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D99" s="20">
         <v>4020349</v>
       </c>
-      <c r="E99" s="3"/>
+      <c r="E99" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="G99" s="3">
         <v>2</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J99" s="3">
         <v>13</v>
@@ -4574,17 +4635,19 @@
         <v>103900</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D100" s="20">
         <v>4020350</v>
       </c>
-      <c r="E100" s="3"/>
+      <c r="E100" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="G100" s="20">
         <v>2</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J100" s="3">
         <v>14</v>
@@ -4601,20 +4664,22 @@
         <v>103900</v>
       </c>
       <c r="C101" s="30" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D101" s="20">
         <v>4020651</v>
       </c>
-      <c r="E101" s="3"/>
+      <c r="E101" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="G101" s="3">
         <v>2</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="J101" s="3">
         <v>15</v>
@@ -4631,7 +4696,7 @@
         <v>102000</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D102" s="22">
         <v>4020002</v>
@@ -4660,7 +4725,7 @@
         <v>102000</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D103" s="22">
         <v>4020003</v>
@@ -4686,7 +4751,7 @@
         <v>102000</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D104" s="22">
         <v>4020004</v>
@@ -4698,7 +4763,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J104" s="4">
         <v>2</v>
@@ -4715,7 +4780,7 @@
         <v>102000</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D105" s="22">
         <v>4020005</v>
@@ -4727,7 +4792,7 @@
         <v>2</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="J105" s="4">
         <v>3</v>
@@ -4744,7 +4809,7 @@
         <v>102000</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D106" s="22">
         <v>4020345</v>
@@ -4756,7 +4821,7 @@
         <v>2</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J106" s="4">
         <v>4</v>
@@ -4773,7 +4838,7 @@
         <v>102000</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D107" s="22">
         <v>4020346</v>
@@ -4785,7 +4850,7 @@
         <v>2</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="J107" s="4">
         <v>5</v>
@@ -4802,7 +4867,7 @@
         <v>102000</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D108" s="22">
         <v>4020347</v>
@@ -4828,7 +4893,7 @@
         <v>102000</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D109" s="22">
         <v>4020349</v>
@@ -4840,7 +4905,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="J109" s="4">
         <v>7</v>
@@ -4857,7 +4922,7 @@
         <v>102000</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D110" s="22">
         <v>4020350</v>
@@ -4869,7 +4934,7 @@
         <v>2</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J110" s="4">
         <v>8</v>
@@ -4886,7 +4951,7 @@
         <v>102000</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D111" s="22">
         <v>4020007</v>
@@ -4898,7 +4963,7 @@
         <v>2</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="J111" s="4">
         <v>9</v>
@@ -4915,12 +4980,14 @@
         <v>102700</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D112" s="24">
         <v>4020002</v>
       </c>
-      <c r="E112" s="5"/>
+      <c r="E112" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="F112" s="5">
         <v>1</v>
       </c>
@@ -4942,17 +5009,19 @@
         <v>102700</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D113" s="24">
         <v>4020003</v>
       </c>
-      <c r="E113" s="5"/>
+      <c r="E113" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="G113" s="5">
         <v>2</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="J113" s="5">
         <v>1</v>
@@ -4969,16 +5038,19 @@
         <v>102700</v>
       </c>
       <c r="C114" s="31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D114" s="24">
         <v>4020645</v>
       </c>
+      <c r="E114" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="G114" s="5">
         <v>2</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J114" s="5">
         <v>2</v>
@@ -4995,17 +5067,19 @@
         <v>102700</v>
       </c>
       <c r="C115" s="31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D115" s="24">
         <v>4020640</v>
       </c>
-      <c r="E115" s="5"/>
+      <c r="E115" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="G115" s="5">
         <v>2</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="J115" s="5">
         <v>3</v>
@@ -5022,19 +5096,22 @@
         <v>102700</v>
       </c>
       <c r="C116" s="31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D116" s="24">
         <v>4020646</v>
       </c>
+      <c r="E116" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="G116" s="5">
         <v>2</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J116" s="5">
         <v>4</v>
@@ -5051,17 +5128,19 @@
         <v>102700</v>
       </c>
       <c r="C117" s="31" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D117" s="24">
         <v>4020641</v>
       </c>
-      <c r="E117" s="5"/>
+      <c r="E117" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="G117" s="5">
         <v>2</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J117" s="5">
         <v>5</v>
@@ -5078,19 +5157,22 @@
         <v>102700</v>
       </c>
       <c r="C118" s="31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D118" s="24">
         <v>4020647</v>
       </c>
+      <c r="E118" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="G118" s="5">
         <v>2</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J118" s="5">
         <v>6</v>
@@ -5107,17 +5189,19 @@
         <v>102700</v>
       </c>
       <c r="C119" s="31" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D119" s="24">
         <v>4020642</v>
       </c>
-      <c r="E119" s="5"/>
+      <c r="E119" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="G119" s="5">
         <v>2</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="J119" s="5">
         <v>7</v>
@@ -5134,19 +5218,22 @@
         <v>102700</v>
       </c>
       <c r="C120" s="31" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D120" s="24">
         <v>4020648</v>
       </c>
+      <c r="E120" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="G120" s="5">
         <v>2</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="J120" s="5">
         <v>8</v>
@@ -5163,17 +5250,19 @@
         <v>102700</v>
       </c>
       <c r="C121" s="31" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D121" s="24">
         <v>4020643</v>
       </c>
-      <c r="E121" s="5"/>
+      <c r="E121" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="G121" s="5">
         <v>2</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="J121" s="5">
         <v>9</v>
@@ -5190,19 +5279,22 @@
         <v>102700</v>
       </c>
       <c r="C122" s="31" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D122" s="24">
         <v>4020649</v>
       </c>
+      <c r="E122" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="G122" s="5">
         <v>2</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J122" s="5">
         <v>10</v>
@@ -5219,17 +5311,19 @@
         <v>102700</v>
       </c>
       <c r="C123" s="31" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D123" s="24">
         <v>4020644</v>
       </c>
-      <c r="E123" s="5"/>
+      <c r="E123" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="G123" s="5">
         <v>2</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J123" s="5">
         <v>11</v>
@@ -5246,17 +5340,19 @@
         <v>102700</v>
       </c>
       <c r="C124" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D124" s="24">
         <v>4020650</v>
       </c>
-      <c r="E124" s="5"/>
+      <c r="E124" s="5" t="s">
+        <v>142</v>
+      </c>
       <c r="G124" s="5">
         <v>2</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="J124" s="5">
         <v>12</v>
@@ -5273,17 +5369,19 @@
         <v>102700</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D125" s="24">
         <v>4020349</v>
       </c>
-      <c r="E125" s="5"/>
+      <c r="E125" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="G125" s="5">
         <v>2</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J125" s="5">
         <v>13</v>
@@ -5300,17 +5398,19 @@
         <v>102700</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D126" s="24">
         <v>4020350</v>
       </c>
-      <c r="E126" s="5"/>
+      <c r="E126" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="G126" s="5">
         <v>2</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="J126" s="5">
         <v>14</v>
@@ -5327,20 +5427,22 @@
         <v>102700</v>
       </c>
       <c r="C127" s="31" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D127" s="24">
         <v>4020651</v>
       </c>
-      <c r="E127" s="5"/>
+      <c r="E127" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="G127" s="5">
         <v>2</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J127" s="5">
         <v>15</v>
@@ -5357,7 +5459,7 @@
         <v>101500</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D128" s="16">
         <v>4020002</v>
@@ -5386,7 +5488,7 @@
         <v>101500</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D129" s="16">
         <v>4020003</v>
@@ -5412,7 +5514,7 @@
         <v>101500</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D130" s="16">
         <v>4020004</v>
@@ -5424,7 +5526,7 @@
         <v>2</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="J130" s="1">
         <v>2</v>
@@ -5441,7 +5543,7 @@
         <v>101500</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D131" s="16">
         <v>4020094</v>
@@ -5453,7 +5555,7 @@
         <v>2</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="J131" s="1">
         <v>3</v>
@@ -5470,7 +5572,7 @@
         <v>101500</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D132" s="16">
         <v>4020345</v>
@@ -5482,7 +5584,7 @@
         <v>2</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="J132" s="1">
         <v>4</v>
@@ -5499,7 +5601,7 @@
         <v>101500</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D133" s="16">
         <v>4020346</v>
@@ -5511,7 +5613,7 @@
         <v>2</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J133" s="1">
         <v>5</v>
@@ -5528,7 +5630,7 @@
         <v>101500</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D134" s="16">
         <v>4020347</v>
@@ -5554,7 +5656,7 @@
         <v>101500</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D135" s="16">
         <v>4020349</v>
@@ -5566,7 +5668,7 @@
         <v>2</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="J135" s="1">
         <v>8</v>
@@ -5583,7 +5685,7 @@
         <v>101500</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D136" s="16">
         <v>4020350</v>
@@ -5595,7 +5697,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J136" s="1">
         <v>9</v>
@@ -5612,13 +5714,13 @@
         <v>101500</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D137" s="16">
         <v>4020466</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G137" s="1">
         <v>2</v>
@@ -5638,19 +5740,19 @@
         <v>101500</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D138" s="16">
         <v>4020467</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G138" s="1">
         <v>2</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="J138" s="1">
         <v>11</v>
@@ -5667,19 +5769,19 @@
         <v>101500</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D139" s="16">
         <v>4020468</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G139" s="1">
         <v>2</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="J139" s="1">
         <v>12</v>
@@ -5696,19 +5798,19 @@
         <v>101500</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D140" s="16">
         <v>4020469</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G140" s="1">
         <v>2</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J140" s="1">
         <v>13</v>
@@ -5725,19 +5827,19 @@
         <v>101500</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D141" s="16">
         <v>4020470</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G141" s="1">
         <v>2</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="J141" s="1">
         <v>14</v>
@@ -5754,7 +5856,7 @@
         <v>101500</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D142" s="16">
         <v>4020007</v>
@@ -5766,7 +5868,7 @@
         <v>2</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J142" s="1">
         <v>15</v>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="prop" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="279">
   <si>
     <t>属性id</t>
   </si>
@@ -285,24 +285,21 @@
     <t>下注金额增加</t>
   </si>
   <si>
+    <t>10070003,1</t>
+  </si>
+  <si>
+    <t>10070004,10</t>
+  </si>
+  <si>
+    <t>10070005,1</t>
+  </si>
+  <si>
     <t>中奖概率增高</t>
   </si>
   <si>
     <t>10070006,10</t>
   </si>
   <si>
-    <t>10070003,1</t>
-  </si>
-  <si>
-    <t>10070004,10</t>
-  </si>
-  <si>
-    <t>10070005,1</t>
-  </si>
-  <si>
-    <t>10070002,10</t>
-  </si>
-  <si>
     <t>10070007,1</t>
   </si>
   <si>
@@ -696,27 +693,24 @@
     <t>10210019,10</t>
   </si>
   <si>
+    <t>PetSquadsweet</t>
+  </si>
+  <si>
+    <t>10390003,1</t>
+  </si>
+  <si>
+    <t>10390004,10</t>
+  </si>
+  <si>
+    <t>PetSquadbig</t>
+  </si>
+  <si>
+    <t>10390005,1</t>
+  </si>
+  <si>
     <t>10390006,10</t>
   </si>
   <si>
-    <t>PetSquadsweet</t>
-  </si>
-  <si>
-    <t>10390003,1</t>
-  </si>
-  <si>
-    <t>10390004,10</t>
-  </si>
-  <si>
-    <t>PetSquadbig</t>
-  </si>
-  <si>
-    <t>10390005,1</t>
-  </si>
-  <si>
-    <t>10390002,10</t>
-  </si>
-  <si>
     <t>PetSquadmega</t>
   </si>
   <si>
@@ -828,30 +822,27 @@
     <t>10200019,10</t>
   </si>
   <si>
+    <t>jntb_1_5</t>
+  </si>
+  <si>
+    <t>ElephantFortunesweet</t>
+  </si>
+  <si>
+    <t>10270003,1</t>
+  </si>
+  <si>
+    <t>10270004,10</t>
+  </si>
+  <si>
+    <t>ElephantFortunebig</t>
+  </si>
+  <si>
+    <t>10270005,1</t>
+  </si>
+  <si>
     <t>10270006,10</t>
   </si>
   <si>
-    <t>jntb_1_5</t>
-  </si>
-  <si>
-    <t>ElephantFortunesweet</t>
-  </si>
-  <si>
-    <t>10270003,1</t>
-  </si>
-  <si>
-    <t>10270004,10</t>
-  </si>
-  <si>
-    <t>ElephantFortunebig</t>
-  </si>
-  <si>
-    <t>10270005,1</t>
-  </si>
-  <si>
-    <t>10270002,10</t>
-  </si>
-  <si>
     <t>ElephantFortunemega</t>
   </si>
   <si>
@@ -912,19 +903,16 @@
     <t>ElephantFortunejackpot</t>
   </si>
   <si>
+    <t>10150003,1</t>
+  </si>
+  <si>
+    <t>10150004,10</t>
+  </si>
+  <si>
+    <t>10150005,1</t>
+  </si>
+  <si>
     <t>10150006,10</t>
-  </si>
-  <si>
-    <t>10150003,1</t>
-  </si>
-  <si>
-    <t>10150004,10</t>
-  </si>
-  <si>
-    <t>10150005,1</t>
-  </si>
-  <si>
-    <t>10150002,10</t>
   </si>
   <si>
     <t>10150007,1</t>
@@ -1149,7 +1137,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1195,6 +1183,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1517,7 +1511,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -1541,16 +1535,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
@@ -1559,89 +1553,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1702,10 +1696,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2634,7 +2631,7 @@
       <c r="G21" s="2">
         <v>2</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="20">
         <v>-1</v>
       </c>
       <c r="K21" s="2">
@@ -2643,29 +2640,26 @@
     </row>
     <row r="22" s="2" customFormat="1" spans="1:11">
       <c r="A22" s="2">
-        <v>10070002</v>
+        <v>10070003</v>
       </c>
       <c r="B22" s="2">
         <v>100700</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>57</v>
+      <c r="C22" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="D22" s="19">
-        <v>4020003</v>
+        <v>4020645</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="2">
-        <v>2</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="G22" s="19">
+        <v>2</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="J22" s="3">
+        <v>2</v>
       </c>
       <c r="K22" s="2">
         <v>100</v>
@@ -2673,26 +2667,28 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="1:11">
       <c r="A23" s="2">
-        <v>10070003</v>
+        <v>10070004</v>
       </c>
       <c r="B23" s="2">
         <v>100700</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D23" s="19">
-        <v>4020645</v>
+        <v>4020640</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="19">
-        <v>2</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="J23" s="2">
-        <v>2</v>
+      <c r="G23" s="2">
+        <v>2</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3</v>
       </c>
       <c r="K23" s="2">
         <v>100</v>
@@ -2700,28 +2696,28 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="1:11">
       <c r="A24" s="2">
-        <v>10070004</v>
+        <v>10070005</v>
       </c>
       <c r="B24" s="2">
         <v>100700</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D24" s="19">
-        <v>4020640</v>
+        <v>4020646</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24" s="2">
+        <v>34</v>
+      </c>
+      <c r="G24" s="19">
         <v>2</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="J24" s="2">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="J24" s="3">
+        <v>4</v>
       </c>
       <c r="K24" s="2">
         <v>100</v>
@@ -2729,28 +2725,28 @@
     </row>
     <row r="25" s="2" customFormat="1" spans="1:11">
       <c r="A25" s="2">
-        <v>10070005</v>
+        <v>10070006</v>
       </c>
       <c r="B25" s="2">
         <v>100700</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D25" s="19">
-        <v>4020646</v>
+        <v>4020641</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="2">
         <v>2</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="J25" s="2">
-        <v>4</v>
+        <v>59</v>
+      </c>
+      <c r="J25" s="3">
+        <v>5</v>
       </c>
       <c r="K25" s="2">
         <v>100</v>
@@ -2758,28 +2754,29 @@
     </row>
     <row r="26" s="2" customFormat="1" spans="1:11">
       <c r="A26" s="2">
-        <v>10070006</v>
+        <v>10070002</v>
       </c>
       <c r="B26" s="2">
         <v>100700</v>
       </c>
-      <c r="C26" s="21" t="s">
-        <v>36</v>
+      <c r="C26" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="D26" s="19">
-        <v>4020641</v>
+        <v>4020003</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F26" s="22"/>
       <c r="G26" s="2">
         <v>2</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J26" s="2">
-        <v>5</v>
+      <c r="J26" s="20">
+        <v>-1</v>
       </c>
       <c r="K26" s="2">
         <v>100</v>
@@ -2805,10 +2802,10 @@
         <v>2</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="2">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="J27" s="3">
+        <v>7</v>
       </c>
       <c r="K27" s="2">
         <v>100</v>
@@ -2834,10 +2831,10 @@
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J28" s="2">
-        <v>7</v>
+        <v>62</v>
+      </c>
+      <c r="J28" s="3">
+        <v>8</v>
       </c>
       <c r="K28" s="2">
         <v>100</v>
@@ -2863,10 +2860,10 @@
         <v>2</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J29" s="2">
-        <v>8</v>
+        <v>63</v>
+      </c>
+      <c r="J29" s="3">
+        <v>9</v>
       </c>
       <c r="K29" s="2">
         <v>100</v>
@@ -2892,10 +2889,10 @@
         <v>2</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J30" s="2">
-        <v>9</v>
+        <v>64</v>
+      </c>
+      <c r="J30" s="3">
+        <v>10</v>
       </c>
       <c r="K30" s="2">
         <v>100</v>
@@ -2921,10 +2918,10 @@
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J31" s="2">
-        <v>10</v>
+        <v>65</v>
+      </c>
+      <c r="J31" s="20">
+        <v>-1</v>
       </c>
       <c r="K31" s="2">
         <v>100</v>
@@ -2950,10 +2947,10 @@
         <v>2</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J32" s="2">
-        <v>11</v>
+        <v>66</v>
+      </c>
+      <c r="J32" s="20">
+        <v>-1</v>
       </c>
       <c r="K32" s="2">
         <v>100</v>
@@ -2967,18 +2964,18 @@
         <v>100700</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D33" s="19">
         <v>4020650</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G33" s="19">
         <v>2</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="3">
         <v>12</v>
       </c>
       <c r="K33" s="2">
@@ -2993,21 +2990,21 @@
         <v>100700</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D34" s="19">
         <v>4020653</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G34" s="2">
         <v>2</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="2">
+        <v>70</v>
+      </c>
+      <c r="J34" s="3">
         <v>13</v>
       </c>
       <c r="K34" s="2">
@@ -3022,21 +3019,21 @@
         <v>100700</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="19">
         <v>4020654</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" s="19">
         <v>2</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J35" s="2">
+        <v>72</v>
+      </c>
+      <c r="J35" s="3">
         <v>14</v>
       </c>
       <c r="K35" s="2">
@@ -3051,21 +3048,21 @@
         <v>100700</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" s="19">
         <v>4020655</v>
       </c>
       <c r="E36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="2">
+        <v>2</v>
+      </c>
+      <c r="H36" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="2">
-        <v>2</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="J36" s="3">
         <v>15</v>
       </c>
       <c r="K36" s="2">
@@ -3080,21 +3077,21 @@
         <v>100700</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="19">
         <v>4020656</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37" s="19">
         <v>2</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="J37" s="2">
+        <v>77</v>
+      </c>
+      <c r="J37" s="3">
         <v>16</v>
       </c>
       <c r="K37" s="2">
@@ -3109,22 +3106,22 @@
         <v>100700</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="19">
         <v>4020657</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="2">
+        <v>2</v>
+      </c>
+      <c r="H38" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="G38" s="2">
-        <v>2</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="J38" s="2">
-        <v>17</v>
+      <c r="J38" s="20">
+        <v>-1</v>
       </c>
       <c r="K38" s="2">
         <v>100</v>
@@ -3138,22 +3135,22 @@
         <v>100700</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="19">
         <v>4020658</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G39" s="19">
         <v>2</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="J39" s="2">
-        <v>18</v>
+        <v>82</v>
+      </c>
+      <c r="J39" s="20">
+        <v>-1</v>
       </c>
       <c r="K39" s="2">
         <v>100</v>
@@ -3169,7 +3166,7 @@
       <c r="C40" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="23">
         <v>4020002</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -3196,20 +3193,20 @@
         <v>101200</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="22">
+        <v>60</v>
+      </c>
+      <c r="D41" s="23">
         <v>4020003</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="23"/>
+      <c r="F41" s="24"/>
       <c r="G41" s="3">
         <v>2</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J41" s="3">
         <v>1</v>
@@ -3228,17 +3225,17 @@
       <c r="C42" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="23">
         <v>4020645</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F42" s="23"/>
-      <c r="G42" s="22">
-        <v>2</v>
-      </c>
-      <c r="H42" s="22"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="23">
+        <v>2</v>
+      </c>
+      <c r="H42" s="23"/>
       <c r="J42" s="3">
         <v>2</v>
       </c>
@@ -3256,7 +3253,7 @@
       <c r="C43" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="23">
         <v>4020640</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -3265,8 +3262,8 @@
       <c r="G43" s="3">
         <v>2</v>
       </c>
-      <c r="H43" s="22" t="s">
-        <v>85</v>
+      <c r="H43" s="23" t="s">
+        <v>84</v>
       </c>
       <c r="J43" s="3">
         <v>3</v>
@@ -3285,17 +3282,17 @@
       <c r="C44" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="23">
         <v>4020646</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G44" s="22">
-        <v>2</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>86</v>
+      <c r="G44" s="23">
+        <v>2</v>
+      </c>
+      <c r="H44" s="23" t="s">
+        <v>85</v>
       </c>
       <c r="J44" s="3">
         <v>4</v>
@@ -3314,7 +3311,7 @@
       <c r="C45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="23">
         <v>4020641</v>
       </c>
       <c r="E45" s="3" t="s">
@@ -3324,7 +3321,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J45" s="3">
         <v>5</v>
@@ -3343,17 +3340,17 @@
       <c r="C46" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="23">
         <v>4020647</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G46" s="22">
-        <v>2</v>
-      </c>
-      <c r="H46" s="22" t="s">
-        <v>88</v>
+      <c r="G46" s="23">
+        <v>2</v>
+      </c>
+      <c r="H46" s="23" t="s">
+        <v>87</v>
       </c>
       <c r="J46" s="3">
         <v>6</v>
@@ -3372,7 +3369,7 @@
       <c r="C47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="23">
         <v>4020642</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -3381,8 +3378,8 @@
       <c r="G47" s="3">
         <v>2</v>
       </c>
-      <c r="H47" s="22" t="s">
-        <v>89</v>
+      <c r="H47" s="23" t="s">
+        <v>88</v>
       </c>
       <c r="J47" s="3">
         <v>7</v>
@@ -3401,17 +3398,17 @@
       <c r="C48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="23">
         <v>4020648</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G48" s="22">
-        <v>2</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>90</v>
+      <c r="G48" s="23">
+        <v>2</v>
+      </c>
+      <c r="H48" s="23" t="s">
+        <v>89</v>
       </c>
       <c r="J48" s="3">
         <v>8</v>
@@ -3430,7 +3427,7 @@
       <c r="C49" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="23">
         <v>4020643</v>
       </c>
       <c r="E49" s="3" t="s">
@@ -3439,8 +3436,8 @@
       <c r="G49" s="3">
         <v>2</v>
       </c>
-      <c r="H49" s="22" t="s">
-        <v>91</v>
+      <c r="H49" s="23" t="s">
+        <v>90</v>
       </c>
       <c r="J49" s="3">
         <v>9</v>
@@ -3459,17 +3456,17 @@
       <c r="C50" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="23">
         <v>4020649</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G50" s="22">
-        <v>2</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>92</v>
+      <c r="G50" s="23">
+        <v>2</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>91</v>
       </c>
       <c r="J50" s="3">
         <v>10</v>
@@ -3488,7 +3485,7 @@
       <c r="C51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="23">
         <v>4020644</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -3497,8 +3494,8 @@
       <c r="G51" s="3">
         <v>2</v>
       </c>
-      <c r="H51" s="22" t="s">
-        <v>93</v>
+      <c r="H51" s="23" t="s">
+        <v>92</v>
       </c>
       <c r="J51" s="3">
         <v>11</v>
@@ -3515,18 +3512,18 @@
         <v>101200</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="23">
+        <v>4020659</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D52" s="22">
-        <v>4020659</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G52" s="22">
-        <v>2</v>
-      </c>
-      <c r="H52" s="22"/>
+      <c r="G52" s="23">
+        <v>2</v>
+      </c>
+      <c r="H52" s="23"/>
       <c r="J52" s="3">
         <v>12</v>
       </c>
@@ -3542,19 +3539,19 @@
         <v>101200</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="23">
+        <v>4020660</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2</v>
+      </c>
+      <c r="H53" s="23" t="s">
         <v>96</v>
-      </c>
-      <c r="D53" s="22">
-        <v>4020660</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G53" s="3">
-        <v>2</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>97</v>
       </c>
       <c r="J53" s="3">
         <v>13</v>
@@ -3571,19 +3568,19 @@
         <v>101200</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="23">
+        <v>4020661</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G54" s="23">
+        <v>2</v>
+      </c>
+      <c r="H54" s="23" t="s">
         <v>98</v>
-      </c>
-      <c r="D54" s="22">
-        <v>4020661</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G54" s="22">
-        <v>2</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="J54" s="3">
         <v>14</v>
@@ -3600,19 +3597,19 @@
         <v>101200</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" s="22">
+        <v>99</v>
+      </c>
+      <c r="D55" s="23">
         <v>4020662</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G55" s="3">
         <v>2</v>
       </c>
-      <c r="H55" s="22" t="s">
-        <v>101</v>
+      <c r="H55" s="23" t="s">
+        <v>100</v>
       </c>
       <c r="J55" s="3">
         <v>15</v>
@@ -3629,19 +3626,19 @@
         <v>101200</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="23">
+        <v>4020663</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G56" s="23">
+        <v>2</v>
+      </c>
+      <c r="H56" s="23" t="s">
         <v>102</v>
-      </c>
-      <c r="D56" s="22">
-        <v>4020663</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G56" s="22">
-        <v>2</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>103</v>
       </c>
       <c r="J56" s="3">
         <v>16</v>
@@ -3658,19 +3655,19 @@
         <v>101200</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="23">
+        <v>4020664</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2</v>
+      </c>
+      <c r="H57" s="23" t="s">
         <v>104</v>
-      </c>
-      <c r="D57" s="22">
-        <v>4020664</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2</v>
-      </c>
-      <c r="H57" s="22" t="s">
-        <v>105</v>
       </c>
       <c r="J57" s="3">
         <v>17</v>
@@ -3687,19 +3684,19 @@
         <v>101200</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="23">
+        <v>4020665</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G58" s="23">
+        <v>2</v>
+      </c>
+      <c r="H58" s="23" t="s">
         <v>106</v>
-      </c>
-      <c r="D58" s="22">
-        <v>4020665</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G58" s="22">
-        <v>2</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>107</v>
       </c>
       <c r="J58" s="3">
         <v>18</v>
@@ -3718,7 +3715,7 @@
       <c r="C59" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="23">
         <v>4020651</v>
       </c>
       <c r="E59" s="3" t="s">
@@ -3727,8 +3724,8 @@
       <c r="G59" s="3">
         <v>2</v>
       </c>
-      <c r="H59" s="22" t="s">
-        <v>108</v>
+      <c r="H59" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="J59" s="3">
         <v>19</v>
@@ -3747,7 +3744,7 @@
       <c r="C60" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D60" s="24">
+      <c r="D60" s="25">
         <v>4020002</v>
       </c>
       <c r="E60" s="4" t="s">
@@ -3774,20 +3771,20 @@
         <v>101800</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D61" s="24">
+        <v>60</v>
+      </c>
+      <c r="D61" s="25">
         <v>4020003</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F61" s="25"/>
+      <c r="F61" s="26"/>
       <c r="G61" s="4">
         <v>2</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J61" s="4">
         <v>1</v>
@@ -3803,19 +3800,19 @@
       <c r="B62" s="4">
         <v>101800</v>
       </c>
-      <c r="C62" s="26" t="s">
+      <c r="C62" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D62" s="24">
+      <c r="D62" s="25">
         <v>4020645</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G62" s="24">
-        <v>2</v>
-      </c>
-      <c r="H62" s="24"/>
+      <c r="G62" s="25">
+        <v>2</v>
+      </c>
+      <c r="H62" s="25"/>
       <c r="J62" s="4">
         <v>2</v>
       </c>
@@ -3830,10 +3827,10 @@
       <c r="B63" s="4">
         <v>101800</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="C63" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D63" s="24">
+      <c r="D63" s="25">
         <v>4020640</v>
       </c>
       <c r="E63" s="4" t="s">
@@ -3842,8 +3839,8 @@
       <c r="G63" s="4">
         <v>2</v>
       </c>
-      <c r="H63" s="24" t="s">
-        <v>110</v>
+      <c r="H63" s="25" t="s">
+        <v>109</v>
       </c>
       <c r="J63" s="4">
         <v>3</v>
@@ -3859,20 +3856,20 @@
       <c r="B64" s="4">
         <v>101800</v>
       </c>
-      <c r="C64" s="26" t="s">
+      <c r="C64" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D64" s="24">
+      <c r="D64" s="25">
         <v>4020646</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G64" s="24">
-        <v>2</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>111</v>
+      <c r="G64" s="25">
+        <v>2</v>
+      </c>
+      <c r="H64" s="25" t="s">
+        <v>110</v>
       </c>
       <c r="J64" s="4">
         <v>4</v>
@@ -3888,10 +3885,10 @@
       <c r="B65" s="4">
         <v>101800</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C65" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="24">
+      <c r="D65" s="25">
         <v>4020641</v>
       </c>
       <c r="E65" s="4" t="s">
@@ -3900,8 +3897,8 @@
       <c r="G65" s="4">
         <v>2</v>
       </c>
-      <c r="H65" s="24" t="s">
-        <v>112</v>
+      <c r="H65" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="J65" s="4">
         <v>5</v>
@@ -3917,20 +3914,20 @@
       <c r="B66" s="4">
         <v>101800</v>
       </c>
-      <c r="C66" s="26" t="s">
+      <c r="C66" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D66" s="24">
+      <c r="D66" s="25">
         <v>4020647</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G66" s="24">
+      <c r="G66" s="25">
         <v>2</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J66" s="4">
         <v>6</v>
@@ -3946,10 +3943,10 @@
       <c r="B67" s="4">
         <v>101800</v>
       </c>
-      <c r="C67" s="26" t="s">
+      <c r="C67" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D67" s="24">
+      <c r="D67" s="25">
         <v>4020642</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -3959,7 +3956,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J67" s="4">
         <v>7</v>
@@ -3975,20 +3972,20 @@
       <c r="B68" s="4">
         <v>101800</v>
       </c>
-      <c r="C68" s="26" t="s">
+      <c r="C68" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D68" s="24">
+      <c r="D68" s="25">
         <v>4020648</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G68" s="24">
+      <c r="G68" s="25">
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J68" s="4">
         <v>8</v>
@@ -4004,10 +4001,10 @@
       <c r="B69" s="4">
         <v>101800</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D69" s="24">
+      <c r="D69" s="25">
         <v>4020643</v>
       </c>
       <c r="E69" s="4" t="s">
@@ -4017,7 +4014,7 @@
         <v>2</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J69" s="4">
         <v>9</v>
@@ -4033,20 +4030,20 @@
       <c r="B70" s="4">
         <v>101800</v>
       </c>
-      <c r="C70" s="26" t="s">
+      <c r="C70" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D70" s="24">
+      <c r="D70" s="25">
         <v>4020649</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G70" s="24">
+      <c r="G70" s="25">
         <v>2</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J70" s="4">
         <v>10</v>
@@ -4062,10 +4059,10 @@
       <c r="B71" s="4">
         <v>101800</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D71" s="24">
+      <c r="D71" s="25">
         <v>4020644</v>
       </c>
       <c r="E71" s="4" t="s">
@@ -4075,7 +4072,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J71" s="4">
         <v>11</v>
@@ -4092,15 +4089,15 @@
         <v>101800</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" s="25">
+        <v>4020650</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D72" s="24">
-        <v>4020650</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G72" s="24">
+      <c r="G72" s="25">
         <v>2</v>
       </c>
       <c r="J72" s="4">
@@ -4118,19 +4115,19 @@
         <v>101800</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" s="24">
+        <v>69</v>
+      </c>
+      <c r="D73" s="25">
         <v>4020653</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G73" s="4">
         <v>2</v>
       </c>
-      <c r="H73" s="24" t="s">
-        <v>119</v>
+      <c r="H73" s="25" t="s">
+        <v>118</v>
       </c>
       <c r="J73" s="4">
         <v>13</v>
@@ -4147,19 +4144,19 @@
         <v>101800</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D74" s="24">
+        <v>71</v>
+      </c>
+      <c r="D74" s="25">
         <v>4020654</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G74" s="24">
-        <v>2</v>
-      </c>
-      <c r="H74" s="24" t="s">
-        <v>120</v>
+        <v>68</v>
+      </c>
+      <c r="G74" s="25">
+        <v>2</v>
+      </c>
+      <c r="H74" s="25" t="s">
+        <v>119</v>
       </c>
       <c r="J74" s="4">
         <v>14</v>
@@ -4176,19 +4173,19 @@
         <v>101800</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" s="25">
+        <v>4020655</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="24">
-        <v>4020655</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="G75" s="4">
         <v>2</v>
       </c>
-      <c r="H75" s="24" t="s">
-        <v>121</v>
+      <c r="H75" s="25" t="s">
+        <v>120</v>
       </c>
       <c r="J75" s="4">
         <v>15</v>
@@ -4205,19 +4202,19 @@
         <v>101800</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D76" s="24">
+        <v>76</v>
+      </c>
+      <c r="D76" s="25">
         <v>4020656</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G76" s="24">
-        <v>2</v>
-      </c>
-      <c r="H76" s="24" t="s">
-        <v>122</v>
+        <v>74</v>
+      </c>
+      <c r="G76" s="25">
+        <v>2</v>
+      </c>
+      <c r="H76" s="25" t="s">
+        <v>121</v>
       </c>
       <c r="J76" s="4">
         <v>16</v>
@@ -4234,19 +4231,19 @@
         <v>101800</v>
       </c>
       <c r="C77" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D77" s="25">
+        <v>4020657</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="24">
-        <v>4020657</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G77" s="4">
         <v>2</v>
       </c>
-      <c r="H77" s="24" t="s">
-        <v>123</v>
+      <c r="H77" s="25" t="s">
+        <v>122</v>
       </c>
       <c r="J77" s="4">
         <v>17</v>
@@ -4263,19 +4260,19 @@
         <v>101800</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="24">
+        <v>81</v>
+      </c>
+      <c r="D78" s="25">
         <v>4020658</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G78" s="24">
-        <v>2</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>124</v>
+        <v>79</v>
+      </c>
+      <c r="G78" s="25">
+        <v>2</v>
+      </c>
+      <c r="H78" s="25" t="s">
+        <v>123</v>
       </c>
       <c r="J78" s="4">
         <v>18</v>
@@ -4294,7 +4291,7 @@
       <c r="C79" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D79" s="24">
+      <c r="D79" s="25">
         <v>4020651</v>
       </c>
       <c r="E79" s="4" t="s">
@@ -4303,8 +4300,8 @@
       <c r="G79" s="4">
         <v>2</v>
       </c>
-      <c r="H79" s="24" t="s">
-        <v>125</v>
+      <c r="H79" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="J79" s="4">
         <v>19</v>
@@ -4323,7 +4320,7 @@
       <c r="C80" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D80" s="27">
+      <c r="D80" s="28">
         <v>4020002</v>
       </c>
       <c r="E80" s="5" t="s">
@@ -4350,20 +4347,20 @@
         <v>102500</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" s="27">
+        <v>60</v>
+      </c>
+      <c r="D81" s="28">
         <v>4020003</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F81" s="28"/>
+      <c r="F81" s="29"/>
       <c r="G81" s="5">
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J81" s="5">
         <v>1</v>
@@ -4382,16 +4379,16 @@
       <c r="C82" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="27">
+      <c r="D82" s="28">
         <v>4020645</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G82" s="27">
-        <v>2</v>
-      </c>
-      <c r="H82" s="27"/>
+      <c r="G82" s="28">
+        <v>2</v>
+      </c>
+      <c r="H82" s="28"/>
       <c r="J82" s="5">
         <v>2</v>
       </c>
@@ -4409,7 +4406,7 @@
       <c r="C83" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D83" s="27">
+      <c r="D83" s="28">
         <v>4020640</v>
       </c>
       <c r="E83" s="5" t="s">
@@ -4418,8 +4415,8 @@
       <c r="G83" s="5">
         <v>2</v>
       </c>
-      <c r="H83" s="27" t="s">
-        <v>127</v>
+      <c r="H83" s="28" t="s">
+        <v>126</v>
       </c>
       <c r="J83" s="5">
         <v>3</v>
@@ -4438,17 +4435,17 @@
       <c r="C84" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D84" s="27">
+      <c r="D84" s="28">
         <v>4020646</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G84" s="27">
-        <v>2</v>
-      </c>
-      <c r="H84" s="27" t="s">
-        <v>128</v>
+      <c r="G84" s="28">
+        <v>2</v>
+      </c>
+      <c r="H84" s="28" t="s">
+        <v>127</v>
       </c>
       <c r="J84" s="5">
         <v>4</v>
@@ -4467,7 +4464,7 @@
       <c r="C85" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D85" s="27">
+      <c r="D85" s="28">
         <v>4020641</v>
       </c>
       <c r="E85" s="5" t="s">
@@ -4476,8 +4473,8 @@
       <c r="G85" s="5">
         <v>2</v>
       </c>
-      <c r="H85" s="27" t="s">
-        <v>129</v>
+      <c r="H85" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="J85" s="5">
         <v>5</v>
@@ -4496,17 +4493,17 @@
       <c r="C86" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D86" s="27">
+      <c r="D86" s="28">
         <v>4020647</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G86" s="27">
+      <c r="G86" s="28">
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J86" s="5">
         <v>6</v>
@@ -4525,7 +4522,7 @@
       <c r="C87" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="28">
         <v>4020642</v>
       </c>
       <c r="E87" s="5" t="s">
@@ -4534,8 +4531,8 @@
       <c r="G87" s="5">
         <v>2</v>
       </c>
-      <c r="H87" s="27" t="s">
-        <v>131</v>
+      <c r="H87" s="28" t="s">
+        <v>130</v>
       </c>
       <c r="J87" s="5">
         <v>7</v>
@@ -4554,17 +4551,17 @@
       <c r="C88" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D88" s="27">
+      <c r="D88" s="28">
         <v>4020648</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G88" s="27">
-        <v>2</v>
-      </c>
-      <c r="H88" s="27" t="s">
-        <v>132</v>
+      <c r="G88" s="28">
+        <v>2</v>
+      </c>
+      <c r="H88" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J88" s="5">
         <v>8</v>
@@ -4583,17 +4580,17 @@
       <c r="C89" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D89" s="27">
+      <c r="D89" s="28">
         <v>4020643</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G89" s="27">
-        <v>2</v>
-      </c>
-      <c r="H89" s="27" t="s">
-        <v>133</v>
+      <c r="G89" s="28">
+        <v>2</v>
+      </c>
+      <c r="H89" s="28" t="s">
+        <v>132</v>
       </c>
       <c r="J89" s="5">
         <v>9</v>
@@ -4612,17 +4609,17 @@
       <c r="C90" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D90" s="27">
+      <c r="D90" s="28">
         <v>4020649</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G90" s="27">
-        <v>2</v>
-      </c>
-      <c r="H90" s="27" t="s">
-        <v>134</v>
+      <c r="G90" s="28">
+        <v>2</v>
+      </c>
+      <c r="H90" s="28" t="s">
+        <v>133</v>
       </c>
       <c r="J90" s="5">
         <v>10</v>
@@ -4641,17 +4638,17 @@
       <c r="C91" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D91" s="27">
+      <c r="D91" s="28">
         <v>4020644</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G91" s="27">
-        <v>2</v>
-      </c>
-      <c r="H91" s="27" t="s">
-        <v>135</v>
+      <c r="G91" s="28">
+        <v>2</v>
+      </c>
+      <c r="H91" s="28" t="s">
+        <v>134</v>
       </c>
       <c r="J91" s="5">
         <v>11</v>
@@ -4668,18 +4665,18 @@
         <v>102500</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D92" s="28">
+        <v>4020650</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="27">
-        <v>4020650</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G92" s="27">
-        <v>2</v>
-      </c>
-      <c r="H92" s="27"/>
+      <c r="G92" s="28">
+        <v>2</v>
+      </c>
+      <c r="H92" s="28"/>
       <c r="J92" s="5">
         <v>12</v>
       </c>
@@ -4695,19 +4692,19 @@
         <v>102500</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D93" s="27">
+        <v>69</v>
+      </c>
+      <c r="D93" s="28">
         <v>4020653</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G93" s="27">
-        <v>2</v>
-      </c>
-      <c r="H93" s="27" t="s">
-        <v>136</v>
+        <v>68</v>
+      </c>
+      <c r="G93" s="28">
+        <v>2</v>
+      </c>
+      <c r="H93" s="28" t="s">
+        <v>135</v>
       </c>
       <c r="J93" s="5">
         <v>13</v>
@@ -4724,19 +4721,19 @@
         <v>102500</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D94" s="27">
+        <v>71</v>
+      </c>
+      <c r="D94" s="28">
         <v>4020654</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G94" s="27">
-        <v>2</v>
-      </c>
-      <c r="H94" s="27" t="s">
-        <v>137</v>
+        <v>68</v>
+      </c>
+      <c r="G94" s="28">
+        <v>2</v>
+      </c>
+      <c r="H94" s="28" t="s">
+        <v>136</v>
       </c>
       <c r="J94" s="5">
         <v>14</v>
@@ -4753,19 +4750,19 @@
         <v>102500</v>
       </c>
       <c r="C95" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D95" s="28">
+        <v>4020655</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D95" s="27">
-        <v>4020655</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G95" s="27">
-        <v>2</v>
-      </c>
-      <c r="H95" s="27" t="s">
-        <v>138</v>
+      <c r="G95" s="28">
+        <v>2</v>
+      </c>
+      <c r="H95" s="28" t="s">
+        <v>137</v>
       </c>
       <c r="J95" s="5">
         <v>15</v>
@@ -4782,19 +4779,19 @@
         <v>102500</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D96" s="27">
+        <v>76</v>
+      </c>
+      <c r="D96" s="28">
         <v>4020656</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G96" s="27">
-        <v>2</v>
-      </c>
-      <c r="H96" s="27" t="s">
-        <v>139</v>
+        <v>74</v>
+      </c>
+      <c r="G96" s="28">
+        <v>2</v>
+      </c>
+      <c r="H96" s="28" t="s">
+        <v>138</v>
       </c>
       <c r="J96" s="5">
         <v>16</v>
@@ -4811,17 +4808,17 @@
         <v>102500</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97" s="28">
+        <v>4020657</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D97" s="27">
-        <v>4020657</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G97" s="27"/>
-      <c r="H97" s="27" t="s">
-        <v>140</v>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28" t="s">
+        <v>139</v>
       </c>
       <c r="J97" s="5">
         <v>17</v>
@@ -4838,19 +4835,19 @@
         <v>102500</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D98" s="27">
+        <v>81</v>
+      </c>
+      <c r="D98" s="28">
         <v>4020658</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G98" s="27">
-        <v>2</v>
-      </c>
-      <c r="H98" s="27" t="s">
-        <v>141</v>
+        <v>79</v>
+      </c>
+      <c r="G98" s="28">
+        <v>2</v>
+      </c>
+      <c r="H98" s="28" t="s">
+        <v>140</v>
       </c>
       <c r="J98" s="5">
         <v>18</v>
@@ -4869,7 +4866,7 @@
       <c r="C99" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D99" s="27">
+      <c r="D99" s="28">
         <v>4020651</v>
       </c>
       <c r="E99" s="5" t="s">
@@ -4878,8 +4875,8 @@
       <c r="G99" s="5">
         <v>2</v>
       </c>
-      <c r="H99" s="27" t="s">
-        <v>142</v>
+      <c r="H99" s="28" t="s">
+        <v>141</v>
       </c>
       <c r="J99" s="5">
         <v>19</v>
@@ -4898,7 +4895,7 @@
       <c r="C100" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D100" s="29">
+      <c r="D100" s="30">
         <v>4020002</v>
       </c>
       <c r="E100" s="6" t="s">
@@ -4925,20 +4922,20 @@
         <v>103100</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D101" s="29">
+        <v>60</v>
+      </c>
+      <c r="D101" s="30">
         <v>4020003</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F101" s="30"/>
+      <c r="F101" s="31"/>
       <c r="G101" s="6">
         <v>2</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J101" s="6">
         <v>1</v>
@@ -4957,17 +4954,17 @@
       <c r="C102" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D102" s="29">
+      <c r="D102" s="30">
         <v>4020645</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30">
-        <v>2</v>
-      </c>
-      <c r="H102" s="30"/>
+      <c r="F102" s="31"/>
+      <c r="G102" s="31">
+        <v>2</v>
+      </c>
+      <c r="H102" s="31"/>
       <c r="J102" s="6">
         <v>2</v>
       </c>
@@ -4985,7 +4982,7 @@
       <c r="C103" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D103" s="29">
+      <c r="D103" s="30">
         <v>4020640</v>
       </c>
       <c r="E103" s="6" t="s">
@@ -4994,8 +4991,8 @@
       <c r="G103" s="6">
         <v>2</v>
       </c>
-      <c r="H103" s="30" t="s">
-        <v>144</v>
+      <c r="H103" s="31" t="s">
+        <v>143</v>
       </c>
       <c r="J103" s="6">
         <v>3</v>
@@ -5014,17 +5011,17 @@
       <c r="C104" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D104" s="29">
+      <c r="D104" s="30">
         <v>4020646</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G104" s="30">
-        <v>2</v>
-      </c>
-      <c r="H104" s="30" t="s">
-        <v>145</v>
+      <c r="G104" s="31">
+        <v>2</v>
+      </c>
+      <c r="H104" s="31" t="s">
+        <v>144</v>
       </c>
       <c r="J104" s="6">
         <v>4</v>
@@ -5043,7 +5040,7 @@
       <c r="C105" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D105" s="29">
+      <c r="D105" s="30">
         <v>4020641</v>
       </c>
       <c r="E105" s="6" t="s">
@@ -5052,8 +5049,8 @@
       <c r="G105" s="6">
         <v>2</v>
       </c>
-      <c r="H105" s="30" t="s">
-        <v>146</v>
+      <c r="H105" s="31" t="s">
+        <v>145</v>
       </c>
       <c r="J105" s="6">
         <v>5</v>
@@ -5072,17 +5069,17 @@
       <c r="C106" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D106" s="29">
+      <c r="D106" s="30">
         <v>4020647</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G106" s="30">
+      <c r="G106" s="31">
         <v>2</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J106" s="6">
         <v>6</v>
@@ -5101,7 +5098,7 @@
       <c r="C107" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D107" s="29">
+      <c r="D107" s="30">
         <v>4020642</v>
       </c>
       <c r="E107" s="6" t="s">
@@ -5110,8 +5107,8 @@
       <c r="G107" s="6">
         <v>2</v>
       </c>
-      <c r="H107" s="30" t="s">
-        <v>148</v>
+      <c r="H107" s="31" t="s">
+        <v>147</v>
       </c>
       <c r="J107" s="6">
         <v>7</v>
@@ -5130,17 +5127,17 @@
       <c r="C108" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D108" s="29">
+      <c r="D108" s="30">
         <v>4020648</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G108" s="30">
-        <v>2</v>
-      </c>
-      <c r="H108" s="30" t="s">
-        <v>149</v>
+      <c r="G108" s="31">
+        <v>2</v>
+      </c>
+      <c r="H108" s="31" t="s">
+        <v>148</v>
       </c>
       <c r="J108" s="6">
         <v>8</v>
@@ -5159,7 +5156,7 @@
       <c r="C109" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D109" s="29">
+      <c r="D109" s="30">
         <v>4020643</v>
       </c>
       <c r="E109" s="6" t="s">
@@ -5169,7 +5166,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J109" s="6">
         <v>9</v>
@@ -5188,17 +5185,17 @@
       <c r="C110" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D110" s="29">
+      <c r="D110" s="30">
         <v>4020649</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G110" s="30">
-        <v>2</v>
-      </c>
-      <c r="H110" s="30" t="s">
-        <v>151</v>
+      <c r="G110" s="31">
+        <v>2</v>
+      </c>
+      <c r="H110" s="31" t="s">
+        <v>150</v>
       </c>
       <c r="J110" s="6">
         <v>10</v>
@@ -5217,7 +5214,7 @@
       <c r="C111" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D111" s="29">
+      <c r="D111" s="30">
         <v>4020644</v>
       </c>
       <c r="E111" s="6" t="s">
@@ -5226,8 +5223,8 @@
       <c r="G111" s="6">
         <v>2</v>
       </c>
-      <c r="H111" s="30" t="s">
-        <v>152</v>
+      <c r="H111" s="31" t="s">
+        <v>151</v>
       </c>
       <c r="J111" s="6">
         <v>11</v>
@@ -5244,18 +5241,18 @@
         <v>103100</v>
       </c>
       <c r="C112" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D112" s="30">
+        <v>4020650</v>
+      </c>
+      <c r="E112" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D112" s="29">
-        <v>4020650</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G112" s="30">
-        <v>2</v>
-      </c>
-      <c r="H112" s="30"/>
+      <c r="G112" s="31">
+        <v>2</v>
+      </c>
+      <c r="H112" s="31"/>
       <c r="J112" s="6">
         <v>12</v>
       </c>
@@ -5271,19 +5268,19 @@
         <v>103100</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D113" s="29">
+        <v>69</v>
+      </c>
+      <c r="D113" s="30">
         <v>4020653</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G113" s="6">
         <v>2</v>
       </c>
-      <c r="H113" s="30" t="s">
-        <v>153</v>
+      <c r="H113" s="31" t="s">
+        <v>152</v>
       </c>
       <c r="J113" s="6">
         <v>13</v>
@@ -5300,19 +5297,19 @@
         <v>103100</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D114" s="29">
+        <v>71</v>
+      </c>
+      <c r="D114" s="30">
         <v>4020654</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G114" s="30">
-        <v>2</v>
-      </c>
-      <c r="H114" s="30" t="s">
-        <v>154</v>
+        <v>68</v>
+      </c>
+      <c r="G114" s="31">
+        <v>2</v>
+      </c>
+      <c r="H114" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="J114" s="6">
         <v>14</v>
@@ -5329,19 +5326,19 @@
         <v>103100</v>
       </c>
       <c r="C115" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D115" s="30">
+        <v>4020655</v>
+      </c>
+      <c r="E115" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D115" s="29">
-        <v>4020655</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="G115" s="6">
         <v>2</v>
       </c>
-      <c r="H115" s="30" t="s">
-        <v>155</v>
+      <c r="H115" s="31" t="s">
+        <v>154</v>
       </c>
       <c r="J115" s="6">
         <v>15</v>
@@ -5358,19 +5355,19 @@
         <v>103100</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D116" s="29">
+        <v>76</v>
+      </c>
+      <c r="D116" s="30">
         <v>4020656</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G116" s="30">
-        <v>2</v>
-      </c>
-      <c r="H116" s="30" t="s">
-        <v>156</v>
+        <v>74</v>
+      </c>
+      <c r="G116" s="31">
+        <v>2</v>
+      </c>
+      <c r="H116" s="31" t="s">
+        <v>155</v>
       </c>
       <c r="J116" s="6">
         <v>16</v>
@@ -5387,19 +5384,19 @@
         <v>103100</v>
       </c>
       <c r="C117" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D117" s="30">
+        <v>4020657</v>
+      </c>
+      <c r="E117" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D117" s="29">
-        <v>4020657</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="G117" s="6">
         <v>2</v>
       </c>
-      <c r="H117" s="30" t="s">
-        <v>157</v>
+      <c r="H117" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="J117" s="6">
         <v>17</v>
@@ -5416,19 +5413,19 @@
         <v>103100</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D118" s="29">
+        <v>81</v>
+      </c>
+      <c r="D118" s="30">
         <v>4020658</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G118" s="30">
-        <v>2</v>
-      </c>
-      <c r="H118" s="30" t="s">
-        <v>158</v>
+        <v>79</v>
+      </c>
+      <c r="G118" s="31">
+        <v>2</v>
+      </c>
+      <c r="H118" s="31" t="s">
+        <v>157</v>
       </c>
       <c r="J118" s="6">
         <v>18</v>
@@ -5447,7 +5444,7 @@
       <c r="C119" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D119" s="29">
+      <c r="D119" s="30">
         <v>4020651</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -5456,8 +5453,8 @@
       <c r="G119" s="6">
         <v>2</v>
       </c>
-      <c r="H119" s="30" t="s">
-        <v>159</v>
+      <c r="H119" s="31" t="s">
+        <v>158</v>
       </c>
       <c r="J119" s="6">
         <v>19</v>
@@ -5503,7 +5500,7 @@
         <v>102200</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D121" s="19">
         <v>4020003</v>
@@ -5511,12 +5508,12 @@
       <c r="E121" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F121" s="20"/>
+      <c r="F121" s="22"/>
       <c r="G121" s="2">
         <v>2</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -5541,7 +5538,7 @@
       <c r="E122" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F122" s="20"/>
+      <c r="F122" s="22"/>
       <c r="G122" s="19">
         <v>2</v>
       </c>
@@ -5573,7 +5570,7 @@
         <v>2</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J123" s="2">
         <v>3</v>
@@ -5602,7 +5599,7 @@
         <v>2</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J124" s="2">
         <v>4</v>
@@ -5631,7 +5628,7 @@
         <v>2</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J125" s="2">
         <v>5</v>
@@ -5660,7 +5657,7 @@
         <v>2</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J126" s="2">
         <v>6</v>
@@ -5689,7 +5686,7 @@
         <v>2</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J127" s="2">
         <v>7</v>
@@ -5718,7 +5715,7 @@
         <v>2</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J128" s="2">
         <v>8</v>
@@ -5747,7 +5744,7 @@
         <v>2</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J129" s="2">
         <v>9</v>
@@ -5776,7 +5773,7 @@
         <v>2</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J130" s="2">
         <v>10</v>
@@ -5805,7 +5802,7 @@
         <v>2</v>
       </c>
       <c r="H131" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J131" s="2">
         <v>11</v>
@@ -5822,13 +5819,13 @@
         <v>102200</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D132" s="19">
         <v>4020650</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G132" s="2">
         <v>2</v>
@@ -5849,19 +5846,19 @@
         <v>102200</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D133" s="19">
         <v>4020653</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G133" s="2">
         <v>2</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J133" s="2">
         <v>13</v>
@@ -5878,19 +5875,19 @@
         <v>102200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D134" s="19">
         <v>4020654</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G134" s="2">
         <v>2</v>
       </c>
       <c r="H134" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J134" s="2">
         <v>14</v>
@@ -5907,19 +5904,19 @@
         <v>102200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D135" s="19">
         <v>4020655</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G135" s="2">
         <v>2</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J135" s="2">
         <v>15</v>
@@ -5936,19 +5933,19 @@
         <v>102200</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D136" s="19">
         <v>4020656</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G136" s="2">
         <v>2</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J136" s="2">
         <v>16</v>
@@ -5965,19 +5962,19 @@
         <v>102200</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D137" s="19">
         <v>4020657</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G137" s="2">
         <v>2</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J137" s="2">
         <v>17</v>
@@ -5994,19 +5991,19 @@
         <v>102200</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D138" s="19">
         <v>4020658</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G138" s="2">
         <v>2</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J138" s="2">
         <v>18</v>
@@ -6035,7 +6032,7 @@
         <v>2</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J139" s="2">
         <v>19</v>
@@ -6054,7 +6051,7 @@
       <c r="C140" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D140" s="31">
+      <c r="D140" s="32">
         <v>4020002</v>
       </c>
       <c r="E140" s="7" t="s">
@@ -6081,20 +6078,20 @@
         <v>102100</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D141" s="31">
+        <v>60</v>
+      </c>
+      <c r="D141" s="32">
         <v>4020003</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F141" s="32"/>
+      <c r="F141" s="33"/>
       <c r="G141" s="7">
         <v>2</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J141" s="7">
         <v>1</v>
@@ -6113,16 +6110,16 @@
       <c r="C142" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D142" s="31">
+      <c r="D142" s="32">
         <v>4020645</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G142" s="31">
-        <v>2</v>
-      </c>
-      <c r="H142" s="31"/>
+      <c r="G142" s="32">
+        <v>2</v>
+      </c>
+      <c r="H142" s="32"/>
       <c r="J142" s="7">
         <v>2</v>
       </c>
@@ -6140,7 +6137,7 @@
       <c r="C143" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D143" s="31">
+      <c r="D143" s="32">
         <v>4020640</v>
       </c>
       <c r="E143" s="7" t="s">
@@ -6149,8 +6146,8 @@
       <c r="G143" s="7">
         <v>2</v>
       </c>
-      <c r="H143" s="31" t="s">
-        <v>178</v>
+      <c r="H143" s="32" t="s">
+        <v>177</v>
       </c>
       <c r="J143" s="7">
         <v>3</v>
@@ -6169,17 +6166,17 @@
       <c r="C144" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D144" s="31">
+      <c r="D144" s="32">
         <v>4020646</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G144" s="31">
-        <v>2</v>
-      </c>
-      <c r="H144" s="31" t="s">
-        <v>179</v>
+      <c r="G144" s="32">
+        <v>2</v>
+      </c>
+      <c r="H144" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="J144" s="7">
         <v>4</v>
@@ -6198,7 +6195,7 @@
       <c r="C145" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D145" s="31">
+      <c r="D145" s="32">
         <v>4020641</v>
       </c>
       <c r="E145" s="7" t="s">
@@ -6207,8 +6204,8 @@
       <c r="G145" s="7">
         <v>2</v>
       </c>
-      <c r="H145" s="31" t="s">
-        <v>180</v>
+      <c r="H145" s="32" t="s">
+        <v>179</v>
       </c>
       <c r="J145" s="7">
         <v>5</v>
@@ -6227,17 +6224,17 @@
       <c r="C146" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D146" s="31">
+      <c r="D146" s="32">
         <v>4020647</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G146" s="31">
+      <c r="G146" s="32">
         <v>2</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J146" s="7">
         <v>6</v>
@@ -6256,7 +6253,7 @@
       <c r="C147" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D147" s="31">
+      <c r="D147" s="32">
         <v>4020642</v>
       </c>
       <c r="E147" s="7" t="s">
@@ -6265,8 +6262,8 @@
       <c r="G147" s="7">
         <v>2</v>
       </c>
-      <c r="H147" s="31" t="s">
-        <v>182</v>
+      <c r="H147" s="32" t="s">
+        <v>181</v>
       </c>
       <c r="J147" s="7">
         <v>7</v>
@@ -6285,17 +6282,17 @@
       <c r="C148" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D148" s="31">
+      <c r="D148" s="32">
         <v>4020648</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G148" s="31">
-        <v>2</v>
-      </c>
-      <c r="H148" s="31" t="s">
-        <v>183</v>
+      <c r="G148" s="32">
+        <v>2</v>
+      </c>
+      <c r="H148" s="32" t="s">
+        <v>182</v>
       </c>
       <c r="J148" s="7">
         <v>8</v>
@@ -6314,7 +6311,7 @@
       <c r="C149" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D149" s="31">
+      <c r="D149" s="32">
         <v>4020643</v>
       </c>
       <c r="E149" s="7" t="s">
@@ -6324,7 +6321,7 @@
         <v>2</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J149" s="7">
         <v>9</v>
@@ -6343,17 +6340,17 @@
       <c r="C150" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D150" s="31">
+      <c r="D150" s="32">
         <v>4020649</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G150" s="31">
-        <v>2</v>
-      </c>
-      <c r="H150" s="31" t="s">
-        <v>185</v>
+      <c r="G150" s="32">
+        <v>2</v>
+      </c>
+      <c r="H150" s="32" t="s">
+        <v>184</v>
       </c>
       <c r="J150" s="7">
         <v>10</v>
@@ -6372,7 +6369,7 @@
       <c r="C151" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D151" s="31">
+      <c r="D151" s="32">
         <v>4020644</v>
       </c>
       <c r="E151" s="7" t="s">
@@ -6381,8 +6378,8 @@
       <c r="G151" s="7">
         <v>2</v>
       </c>
-      <c r="H151" s="31" t="s">
-        <v>186</v>
+      <c r="H151" s="32" t="s">
+        <v>185</v>
       </c>
       <c r="J151" s="7">
         <v>11</v>
@@ -6399,18 +6396,18 @@
         <v>102100</v>
       </c>
       <c r="C152" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D152" s="32">
+        <v>4020650</v>
+      </c>
+      <c r="E152" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D152" s="31">
-        <v>4020650</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G152" s="31">
-        <v>2</v>
-      </c>
-      <c r="H152" s="31"/>
+      <c r="G152" s="32">
+        <v>2</v>
+      </c>
+      <c r="H152" s="32"/>
       <c r="J152" s="7">
         <v>12</v>
       </c>
@@ -6426,19 +6423,19 @@
         <v>102100</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D153" s="31">
+        <v>69</v>
+      </c>
+      <c r="D153" s="32">
         <v>4020653</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G153" s="31">
-        <v>2</v>
-      </c>
-      <c r="H153" s="31" t="s">
-        <v>187</v>
+        <v>68</v>
+      </c>
+      <c r="G153" s="32">
+        <v>2</v>
+      </c>
+      <c r="H153" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="J153" s="7">
         <v>13</v>
@@ -6455,19 +6452,19 @@
         <v>102100</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D154" s="31">
+        <v>71</v>
+      </c>
+      <c r="D154" s="32">
         <v>4020654</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G154" s="31">
-        <v>2</v>
-      </c>
-      <c r="H154" s="31" t="s">
-        <v>188</v>
+        <v>68</v>
+      </c>
+      <c r="G154" s="32">
+        <v>2</v>
+      </c>
+      <c r="H154" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="J154" s="7">
         <v>14</v>
@@ -6484,19 +6481,19 @@
         <v>102100</v>
       </c>
       <c r="C155" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D155" s="32">
+        <v>4020655</v>
+      </c>
+      <c r="E155" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D155" s="31">
-        <v>4020655</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G155" s="31">
-        <v>2</v>
-      </c>
-      <c r="H155" s="31" t="s">
-        <v>189</v>
+      <c r="G155" s="32">
+        <v>2</v>
+      </c>
+      <c r="H155" s="32" t="s">
+        <v>188</v>
       </c>
       <c r="J155" s="7">
         <v>15</v>
@@ -6513,19 +6510,19 @@
         <v>102100</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D156" s="31">
+        <v>76</v>
+      </c>
+      <c r="D156" s="32">
         <v>4020656</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G156" s="31">
-        <v>2</v>
-      </c>
-      <c r="H156" s="31" t="s">
-        <v>190</v>
+        <v>74</v>
+      </c>
+      <c r="G156" s="32">
+        <v>2</v>
+      </c>
+      <c r="H156" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="J156" s="7">
         <v>16</v>
@@ -6542,19 +6539,19 @@
         <v>102100</v>
       </c>
       <c r="C157" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D157" s="32">
+        <v>4020657</v>
+      </c>
+      <c r="E157" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D157" s="31">
-        <v>4020657</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G157" s="31">
-        <v>2</v>
-      </c>
-      <c r="H157" s="31" t="s">
-        <v>191</v>
+      <c r="G157" s="32">
+        <v>2</v>
+      </c>
+      <c r="H157" s="32" t="s">
+        <v>190</v>
       </c>
       <c r="J157" s="7">
         <v>17</v>
@@ -6571,19 +6568,19 @@
         <v>102100</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D158" s="31">
+        <v>81</v>
+      </c>
+      <c r="D158" s="32">
         <v>4020658</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G158" s="31">
-        <v>2</v>
-      </c>
-      <c r="H158" s="31" t="s">
-        <v>192</v>
+        <v>79</v>
+      </c>
+      <c r="G158" s="32">
+        <v>2</v>
+      </c>
+      <c r="H158" s="32" t="s">
+        <v>191</v>
       </c>
       <c r="J158" s="7">
         <v>18</v>
@@ -6602,17 +6599,17 @@
       <c r="C159" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D159" s="31">
+      <c r="D159" s="32">
         <v>4020651</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G159" s="31">
-        <v>2</v>
-      </c>
-      <c r="H159" s="31" t="s">
-        <v>193</v>
+      <c r="G159" s="32">
+        <v>2</v>
+      </c>
+      <c r="H159" s="32" t="s">
+        <v>192</v>
       </c>
       <c r="J159" s="7">
         <v>19</v>
@@ -6631,7 +6628,7 @@
       <c r="C160" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D160" s="22">
+      <c r="D160" s="23">
         <v>4020002</v>
       </c>
       <c r="E160" s="3" t="s">
@@ -6643,68 +6640,67 @@
       <c r="G160" s="3">
         <v>2</v>
       </c>
-      <c r="J160" s="3">
+      <c r="J160" s="20">
         <v>-1</v>
       </c>
       <c r="K160" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="161" s="3" customFormat="1" spans="1:11">
+    <row r="161" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A161" s="3">
-        <v>10390002</v>
+        <v>10390003</v>
       </c>
       <c r="B161" s="3">
         <v>103900</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D161" s="22">
-        <v>4020003</v>
+      <c r="C161" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D161" s="23">
+        <v>4020645</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F161" s="23"/>
-      <c r="G161" s="3">
-        <v>2</v>
-      </c>
-      <c r="H161" s="22" t="s">
-        <v>194</v>
+        <v>29</v>
+      </c>
+      <c r="G161" s="23">
+        <v>2</v>
+      </c>
+      <c r="H161" s="23"/>
+      <c r="I161" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="J161" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K161" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="162" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
+    <row r="162" s="3" customFormat="1" spans="1:11">
       <c r="A162" s="3">
-        <v>10390003</v>
+        <v>10390004</v>
       </c>
       <c r="B162" s="3">
         <v>103900</v>
       </c>
-      <c r="C162" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D162" s="22">
-        <v>4020645</v>
+      <c r="C162" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D162" s="23">
+        <v>4020640</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G162" s="22">
-        <v>2</v>
-      </c>
-      <c r="H162" s="22"/>
-      <c r="I162" s="3" t="s">
-        <v>195</v>
+      <c r="G162" s="23">
+        <v>2</v>
+      </c>
+      <c r="H162" s="23" t="s">
+        <v>194</v>
       </c>
       <c r="J162" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K162" s="3">
         <v>100</v>
@@ -6712,28 +6708,31 @@
     </row>
     <row r="163" s="3" customFormat="1" spans="1:11">
       <c r="A163" s="3">
-        <v>10390004</v>
+        <v>10390005</v>
       </c>
       <c r="B163" s="3">
         <v>103900</v>
       </c>
-      <c r="C163" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D163" s="22">
-        <v>4020640</v>
+      <c r="C163" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D163" s="23">
+        <v>4020646</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G163" s="22">
-        <v>2</v>
-      </c>
-      <c r="H163" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G163" s="3">
+        <v>2</v>
+      </c>
+      <c r="H163" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="I163" s="3" t="s">
         <v>196</v>
       </c>
       <c r="J163" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K163" s="3">
         <v>100</v>
@@ -6741,16 +6740,16 @@
     </row>
     <row r="164" s="3" customFormat="1" spans="1:11">
       <c r="A164" s="3">
-        <v>10390005</v>
+        <v>10390006</v>
       </c>
       <c r="B164" s="3">
         <v>103900</v>
       </c>
-      <c r="C164" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="D164" s="22">
-        <v>4020646</v>
+      <c r="C164" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D164" s="23">
+        <v>4020641</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>34</v>
@@ -6758,14 +6757,11 @@
       <c r="G164" s="3">
         <v>2</v>
       </c>
-      <c r="H164" s="22" t="s">
+      <c r="H164" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="I164" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J164" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K164" s="3">
         <v>100</v>
@@ -6773,28 +6769,29 @@
     </row>
     <row r="165" s="3" customFormat="1" spans="1:11">
       <c r="A165" s="3">
-        <v>10390006</v>
+        <v>10390002</v>
       </c>
       <c r="B165" s="3">
         <v>103900</v>
       </c>
-      <c r="C165" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D165" s="22">
-        <v>4020641</v>
+      <c r="C165" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D165" s="23">
+        <v>4020003</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F165" s="24"/>
       <c r="G165" s="3">
         <v>2</v>
       </c>
-      <c r="H165" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="J165" s="3">
-        <v>5</v>
+      <c r="H165" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="J165" s="20">
+        <v>-1</v>
       </c>
       <c r="K165" s="3">
         <v>100</v>
@@ -6807,10 +6804,10 @@
       <c r="B166" s="3">
         <v>103900</v>
       </c>
-      <c r="C166" s="33" t="s">
+      <c r="C166" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="D166" s="22">
+      <c r="D166" s="23">
         <v>4020647</v>
       </c>
       <c r="E166" s="3" t="s">
@@ -6819,14 +6816,14 @@
       <c r="G166" s="3">
         <v>2</v>
       </c>
-      <c r="H166" s="22" t="s">
-        <v>200</v>
+      <c r="H166" s="23" t="s">
+        <v>198</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J166" s="3">
-        <v>6</v>
+        <v>199</v>
+      </c>
+      <c r="J166" s="20">
+        <v>-1</v>
       </c>
       <c r="K166" s="3">
         <v>100</v>
@@ -6839,23 +6836,23 @@
       <c r="B167" s="3">
         <v>103900</v>
       </c>
-      <c r="C167" s="33" t="s">
+      <c r="C167" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D167" s="22">
+      <c r="D167" s="23">
         <v>4020642</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G167" s="22">
-        <v>2</v>
-      </c>
-      <c r="H167" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="J167" s="3">
-        <v>7</v>
+      <c r="G167" s="23">
+        <v>2</v>
+      </c>
+      <c r="H167" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="J167" s="20">
+        <v>-1</v>
       </c>
       <c r="K167" s="3">
         <v>100</v>
@@ -6868,10 +6865,10 @@
       <c r="B168" s="3">
         <v>103900</v>
       </c>
-      <c r="C168" s="33" t="s">
+      <c r="C168" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="D168" s="22">
+      <c r="D168" s="23">
         <v>4020648</v>
       </c>
       <c r="E168" s="3" t="s">
@@ -6880,14 +6877,14 @@
       <c r="G168" s="3">
         <v>2</v>
       </c>
-      <c r="H168" s="22" t="s">
-        <v>203</v>
+      <c r="H168" s="23" t="s">
+        <v>201</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J168" s="3">
-        <v>8</v>
+        <v>202</v>
+      </c>
+      <c r="J168" s="20">
+        <v>-1</v>
       </c>
       <c r="K168" s="3">
         <v>100</v>
@@ -6900,10 +6897,10 @@
       <c r="B169" s="3">
         <v>103900</v>
       </c>
-      <c r="C169" s="33" t="s">
+      <c r="C169" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="D169" s="22">
+      <c r="D169" s="23">
         <v>4020643</v>
       </c>
       <c r="E169" s="3" t="s">
@@ -6912,11 +6909,11 @@
       <c r="G169" s="3">
         <v>2</v>
       </c>
-      <c r="H169" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="J169" s="3">
-        <v>9</v>
+      <c r="H169" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="J169" s="20">
+        <v>-1</v>
       </c>
       <c r="K169" s="3">
         <v>100</v>
@@ -6929,10 +6926,10 @@
       <c r="B170" s="3">
         <v>103900</v>
       </c>
-      <c r="C170" s="33" t="s">
+      <c r="C170" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D170" s="22">
+      <c r="D170" s="23">
         <v>4020649</v>
       </c>
       <c r="E170" s="3" t="s">
@@ -6941,14 +6938,14 @@
       <c r="G170" s="3">
         <v>2</v>
       </c>
-      <c r="H170" s="22" t="s">
-        <v>206</v>
+      <c r="H170" s="23" t="s">
+        <v>204</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J170" s="3">
-        <v>10</v>
+        <v>205</v>
+      </c>
+      <c r="J170" s="20">
+        <v>-1</v>
       </c>
       <c r="K170" s="3">
         <v>100</v>
@@ -6961,23 +6958,23 @@
       <c r="B171" s="3">
         <v>103900</v>
       </c>
-      <c r="C171" s="33" t="s">
+      <c r="C171" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D171" s="22">
+      <c r="D171" s="23">
         <v>4020644</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G171" s="22">
-        <v>2</v>
-      </c>
-      <c r="H171" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="J171" s="3">
-        <v>11</v>
+      <c r="G171" s="23">
+        <v>2</v>
+      </c>
+      <c r="H171" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="J171" s="20">
+        <v>-1</v>
       </c>
       <c r="K171" s="3">
         <v>100</v>
@@ -6990,20 +6987,20 @@
       <c r="B172" s="3">
         <v>103900</v>
       </c>
-      <c r="C172" s="33" t="s">
+      <c r="C172" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D172" s="23">
+        <v>4020650</v>
+      </c>
+      <c r="E172" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D172" s="22">
-        <v>4020650</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G172" s="22">
+      <c r="G172" s="23">
         <v>2</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J172" s="3">
         <v>12</v>
@@ -7020,25 +7017,25 @@
         <v>103900</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D173" s="22">
+        <v>69</v>
+      </c>
+      <c r="D173" s="23">
         <v>4020653</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G173" s="22">
-        <v>2</v>
-      </c>
-      <c r="H173" s="22" t="s">
-        <v>210</v>
+        <v>68</v>
+      </c>
+      <c r="G173" s="23">
+        <v>2</v>
+      </c>
+      <c r="H173" s="23" t="s">
+        <v>208</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J173" s="3">
-        <v>13</v>
+        <v>209</v>
+      </c>
+      <c r="J173" s="20">
+        <v>-1</v>
       </c>
       <c r="K173" s="3">
         <v>100</v>
@@ -7052,22 +7049,22 @@
         <v>103900</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D174" s="22">
+        <v>71</v>
+      </c>
+      <c r="D174" s="23">
         <v>4020654</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G174" s="22">
-        <v>2</v>
-      </c>
-      <c r="H174" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="J174" s="3">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="G174" s="23">
+        <v>2</v>
+      </c>
+      <c r="H174" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="J174" s="20">
+        <v>-1</v>
       </c>
       <c r="K174" s="3">
         <v>100</v>
@@ -7081,25 +7078,25 @@
         <v>103900</v>
       </c>
       <c r="C175" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D175" s="23">
+        <v>4020655</v>
+      </c>
+      <c r="E175" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D175" s="22">
-        <v>4020655</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G175" s="22">
-        <v>2</v>
-      </c>
-      <c r="H175" s="22" t="s">
-        <v>213</v>
+      <c r="G175" s="23">
+        <v>2</v>
+      </c>
+      <c r="H175" s="23" t="s">
+        <v>211</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J175" s="3">
-        <v>15</v>
+        <v>212</v>
+      </c>
+      <c r="J175" s="20">
+        <v>-1</v>
       </c>
       <c r="K175" s="3">
         <v>100</v>
@@ -7113,22 +7110,22 @@
         <v>103900</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D176" s="22">
+        <v>76</v>
+      </c>
+      <c r="D176" s="23">
         <v>4020656</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G176" s="3">
         <v>2</v>
       </c>
-      <c r="H176" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="J176" s="3">
-        <v>16</v>
+      <c r="H176" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="J176" s="20">
+        <v>-1</v>
       </c>
       <c r="K176" s="3">
         <v>100</v>
@@ -7142,23 +7139,23 @@
         <v>103900</v>
       </c>
       <c r="C177" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D177" s="23">
+        <v>4020657</v>
+      </c>
+      <c r="E177" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D177" s="22">
-        <v>4020657</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G177" s="22"/>
-      <c r="H177" s="22" t="s">
-        <v>216</v>
+      <c r="G177" s="23"/>
+      <c r="H177" s="23" t="s">
+        <v>214</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J177" s="3">
-        <v>17</v>
+        <v>215</v>
+      </c>
+      <c r="J177" s="20">
+        <v>-1</v>
       </c>
       <c r="K177" s="3">
         <v>100</v>
@@ -7172,22 +7169,22 @@
         <v>103900</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D178" s="22">
+        <v>81</v>
+      </c>
+      <c r="D178" s="23">
         <v>4020658</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G178" s="22">
-        <v>2</v>
-      </c>
-      <c r="H178" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="J178" s="3">
-        <v>18</v>
+        <v>79</v>
+      </c>
+      <c r="G178" s="23">
+        <v>2</v>
+      </c>
+      <c r="H178" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="J178" s="20">
+        <v>-1</v>
       </c>
       <c r="K178" s="3">
         <v>100</v>
@@ -7200,10 +7197,10 @@
       <c r="B179" s="3">
         <v>103900</v>
       </c>
-      <c r="C179" s="33" t="s">
+      <c r="C179" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D179" s="22">
+      <c r="D179" s="23">
         <v>4020651</v>
       </c>
       <c r="E179" s="3" t="s">
@@ -7212,13 +7209,13 @@
       <c r="G179" s="3">
         <v>2</v>
       </c>
-      <c r="H179" s="22" t="s">
-        <v>219</v>
+      <c r="H179" s="23" t="s">
+        <v>217</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J179" s="3">
+        <v>218</v>
+      </c>
+      <c r="J179" s="4">
         <v>19</v>
       </c>
       <c r="K179" s="3">
@@ -7235,7 +7232,7 @@
       <c r="C180" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D180" s="24">
+      <c r="D180" s="25">
         <v>4020002</v>
       </c>
       <c r="E180" s="4" t="s">
@@ -7262,9 +7259,9 @@
         <v>102000</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D181" s="24">
+        <v>60</v>
+      </c>
+      <c r="D181" s="25">
         <v>4020003</v>
       </c>
       <c r="E181" s="4" t="s">
@@ -7274,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J181" s="4">
         <v>1</v>
@@ -7293,16 +7290,16 @@
       <c r="C182" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D182" s="24">
+      <c r="D182" s="25">
         <v>4020645</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G182" s="24">
-        <v>2</v>
-      </c>
-      <c r="H182" s="24"/>
+      <c r="G182" s="25">
+        <v>2</v>
+      </c>
+      <c r="H182" s="25"/>
       <c r="J182" s="4">
         <v>2</v>
       </c>
@@ -7320,7 +7317,7 @@
       <c r="C183" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D183" s="24">
+      <c r="D183" s="25">
         <v>4020640</v>
       </c>
       <c r="E183" s="4" t="s">
@@ -7329,8 +7326,8 @@
       <c r="G183" s="4">
         <v>2</v>
       </c>
-      <c r="H183" s="24" t="s">
-        <v>222</v>
+      <c r="H183" s="25" t="s">
+        <v>220</v>
       </c>
       <c r="J183" s="4">
         <v>3</v>
@@ -7349,17 +7346,17 @@
       <c r="C184" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D184" s="24">
+      <c r="D184" s="25">
         <v>4020646</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G184" s="24">
-        <v>2</v>
-      </c>
-      <c r="H184" s="24" t="s">
-        <v>223</v>
+      <c r="G184" s="25">
+        <v>2</v>
+      </c>
+      <c r="H184" s="25" t="s">
+        <v>221</v>
       </c>
       <c r="J184" s="4">
         <v>4</v>
@@ -7378,7 +7375,7 @@
       <c r="C185" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D185" s="24">
+      <c r="D185" s="25">
         <v>4020641</v>
       </c>
       <c r="E185" s="4" t="s">
@@ -7387,8 +7384,8 @@
       <c r="G185" s="4">
         <v>2</v>
       </c>
-      <c r="H185" s="24" t="s">
-        <v>224</v>
+      <c r="H185" s="25" t="s">
+        <v>222</v>
       </c>
       <c r="J185" s="4">
         <v>5</v>
@@ -7407,17 +7404,17 @@
       <c r="C186" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D186" s="24">
+      <c r="D186" s="25">
         <v>4020647</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G186" s="24">
+      <c r="G186" s="25">
         <v>2</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J186" s="4">
         <v>6</v>
@@ -7436,7 +7433,7 @@
       <c r="C187" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D187" s="24">
+      <c r="D187" s="25">
         <v>4020642</v>
       </c>
       <c r="E187" s="4" t="s">
@@ -7445,8 +7442,8 @@
       <c r="G187" s="4">
         <v>2</v>
       </c>
-      <c r="H187" s="24" t="s">
-        <v>226</v>
+      <c r="H187" s="25" t="s">
+        <v>224</v>
       </c>
       <c r="J187" s="4">
         <v>7</v>
@@ -7465,17 +7462,17 @@
       <c r="C188" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D188" s="24">
+      <c r="D188" s="25">
         <v>4020648</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G188" s="24">
-        <v>2</v>
-      </c>
-      <c r="H188" s="24" t="s">
-        <v>227</v>
+      <c r="G188" s="25">
+        <v>2</v>
+      </c>
+      <c r="H188" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="J188" s="4">
         <v>8</v>
@@ -7494,7 +7491,7 @@
       <c r="C189" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D189" s="24">
+      <c r="D189" s="25">
         <v>4020643</v>
       </c>
       <c r="E189" s="4" t="s">
@@ -7503,8 +7500,8 @@
       <c r="G189" s="4">
         <v>2</v>
       </c>
-      <c r="H189" s="24" t="s">
-        <v>228</v>
+      <c r="H189" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="J189" s="4">
         <v>9</v>
@@ -7523,7 +7520,7 @@
       <c r="C190" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D190" s="24">
+      <c r="D190" s="25">
         <v>4020649</v>
       </c>
       <c r="E190" s="4" t="s">
@@ -7532,8 +7529,8 @@
       <c r="G190" s="4">
         <v>2</v>
       </c>
-      <c r="H190" s="24" t="s">
-        <v>229</v>
+      <c r="H190" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="J190" s="4">
         <v>10</v>
@@ -7552,7 +7549,7 @@
       <c r="C191" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D191" s="24">
+      <c r="D191" s="25">
         <v>4020644</v>
       </c>
       <c r="E191" s="4" t="s">
@@ -7561,8 +7558,8 @@
       <c r="G191" s="4">
         <v>2</v>
       </c>
-      <c r="H191" s="24" t="s">
-        <v>230</v>
+      <c r="H191" s="25" t="s">
+        <v>228</v>
       </c>
       <c r="J191" s="4">
         <v>11</v>
@@ -7579,18 +7576,18 @@
         <v>102000</v>
       </c>
       <c r="C192" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D192" s="25">
+        <v>4020650</v>
+      </c>
+      <c r="E192" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D192" s="24">
-        <v>4020650</v>
-      </c>
-      <c r="E192" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="G192" s="4">
         <v>2</v>
       </c>
-      <c r="H192" s="24"/>
+      <c r="H192" s="25"/>
       <c r="J192" s="4">
         <v>12</v>
       </c>
@@ -7606,19 +7603,19 @@
         <v>102000</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D193" s="24">
+        <v>69</v>
+      </c>
+      <c r="D193" s="25">
         <v>4020653</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G193" s="4">
         <v>2</v>
       </c>
-      <c r="H193" s="24" t="s">
-        <v>231</v>
+      <c r="H193" s="25" t="s">
+        <v>229</v>
       </c>
       <c r="J193" s="4">
         <v>13</v>
@@ -7635,19 +7632,19 @@
         <v>102000</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D194" s="24">
+        <v>71</v>
+      </c>
+      <c r="D194" s="25">
         <v>4020654</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G194" s="4">
         <v>2</v>
       </c>
-      <c r="H194" s="24" t="s">
-        <v>232</v>
+      <c r="H194" s="25" t="s">
+        <v>230</v>
       </c>
       <c r="J194" s="4">
         <v>14</v>
@@ -7664,19 +7661,19 @@
         <v>102000</v>
       </c>
       <c r="C195" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D195" s="25">
+        <v>4020655</v>
+      </c>
+      <c r="E195" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D195" s="24">
-        <v>4020655</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="G195" s="4">
         <v>2</v>
       </c>
-      <c r="H195" s="24" t="s">
-        <v>233</v>
+      <c r="H195" s="25" t="s">
+        <v>231</v>
       </c>
       <c r="J195" s="4">
         <v>15</v>
@@ -7693,19 +7690,19 @@
         <v>102000</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D196" s="24">
+        <v>76</v>
+      </c>
+      <c r="D196" s="25">
         <v>4020656</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G196" s="4">
         <v>2</v>
       </c>
-      <c r="H196" s="24" t="s">
-        <v>234</v>
+      <c r="H196" s="25" t="s">
+        <v>232</v>
       </c>
       <c r="J196" s="4">
         <v>16</v>
@@ -7722,16 +7719,16 @@
         <v>102000</v>
       </c>
       <c r="C197" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D197" s="25">
+        <v>4020657</v>
+      </c>
+      <c r="E197" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D197" s="24">
-        <v>4020657</v>
-      </c>
-      <c r="E197" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H197" s="24" t="s">
-        <v>235</v>
+      <c r="H197" s="25" t="s">
+        <v>233</v>
       </c>
       <c r="J197" s="4">
         <v>17</v>
@@ -7748,19 +7745,19 @@
         <v>102000</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D198" s="24">
+        <v>81</v>
+      </c>
+      <c r="D198" s="25">
         <v>4020658</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G198" s="4">
         <v>2</v>
       </c>
-      <c r="H198" s="24" t="s">
-        <v>236</v>
+      <c r="H198" s="25" t="s">
+        <v>234</v>
       </c>
       <c r="J198" s="4">
         <v>18</v>
@@ -7779,7 +7776,7 @@
       <c r="C199" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D199" s="24">
+      <c r="D199" s="25">
         <v>4020651</v>
       </c>
       <c r="E199" s="4" t="s">
@@ -7788,8 +7785,8 @@
       <c r="G199" s="4">
         <v>2</v>
       </c>
-      <c r="H199" s="24" t="s">
-        <v>237</v>
+      <c r="H199" s="25" t="s">
+        <v>235</v>
       </c>
       <c r="J199" s="4">
         <v>19</v>
@@ -7808,7 +7805,7 @@
       <c r="C200" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D200" s="27">
+      <c r="D200" s="28">
         <v>4020002</v>
       </c>
       <c r="E200" s="5" t="s">
@@ -7820,7 +7817,7 @@
       <c r="G200" s="5">
         <v>2</v>
       </c>
-      <c r="J200" s="5">
+      <c r="J200" s="20">
         <v>-1</v>
       </c>
       <c r="K200" s="5">
@@ -7829,28 +7826,28 @@
     </row>
     <row r="201" s="5" customFormat="1" spans="1:11">
       <c r="A201" s="5">
-        <v>10270002</v>
+        <v>10270003</v>
       </c>
       <c r="B201" s="5">
         <v>102700</v>
       </c>
-      <c r="C201" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D201" s="27">
-        <v>4020003</v>
+      <c r="C201" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201" s="28">
+        <v>4020645</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>53</v>
+        <v>236</v>
       </c>
       <c r="G201" s="5">
         <v>2</v>
       </c>
-      <c r="H201" s="5" t="s">
-        <v>238</v>
+      <c r="I201" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="J201" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K201" s="5">
         <v>100</v>
@@ -7858,28 +7855,28 @@
     </row>
     <row r="202" s="5" customFormat="1" spans="1:11">
       <c r="A202" s="5">
-        <v>10270003</v>
+        <v>10270004</v>
       </c>
       <c r="B202" s="5">
         <v>102700</v>
       </c>
-      <c r="C202" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D202" s="27">
-        <v>4020645</v>
+      <c r="C202" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D202" s="28">
+        <v>4020640</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G202" s="5">
         <v>2</v>
       </c>
-      <c r="I202" s="5" t="s">
-        <v>240</v>
+      <c r="H202" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="J202" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K202" s="5">
         <v>100</v>
@@ -7887,28 +7884,31 @@
     </row>
     <row r="203" s="5" customFormat="1" spans="1:11">
       <c r="A203" s="5">
-        <v>10270004</v>
+        <v>10270005</v>
       </c>
       <c r="B203" s="5">
         <v>102700</v>
       </c>
-      <c r="C203" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D203" s="27">
-        <v>4020640</v>
+      <c r="C203" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D203" s="28">
+        <v>4020646</v>
       </c>
       <c r="E203" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G203" s="5">
+        <v>2</v>
+      </c>
+      <c r="H203" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G203" s="5">
-        <v>2</v>
-      </c>
-      <c r="H203" s="5" t="s">
-        <v>241</v>
+      <c r="I203" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="J203" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K203" s="5">
         <v>100</v>
@@ -7916,16 +7916,16 @@
     </row>
     <row r="204" s="5" customFormat="1" spans="1:11">
       <c r="A204" s="5">
-        <v>10270005</v>
+        <v>10270006</v>
       </c>
       <c r="B204" s="5">
         <v>102700</v>
       </c>
-      <c r="C204" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D204" s="27">
-        <v>4020646</v>
+      <c r="C204" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D204" s="28">
+        <v>4020641</v>
       </c>
       <c r="E204" s="5" t="s">
         <v>34</v>
@@ -7934,13 +7934,10 @@
         <v>2</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I204" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J204" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K204" s="5">
         <v>100</v>
@@ -7948,44 +7945,44 @@
     </row>
     <row r="205" s="5" customFormat="1" spans="1:11">
       <c r="A205" s="5">
-        <v>10270006</v>
+        <v>10270002</v>
       </c>
       <c r="B205" s="5">
         <v>102700</v>
       </c>
-      <c r="C205" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D205" s="27">
-        <v>4020641</v>
+      <c r="C205" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D205" s="28">
+        <v>4020003</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G205" s="5">
         <v>2</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="J205" s="5">
-        <v>5</v>
+        <v>242</v>
+      </c>
+      <c r="J205" s="20">
+        <v>-1</v>
       </c>
       <c r="K205" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="206" s="5" customFormat="1" spans="1:11">
+    <row r="206" s="5" customFormat="1" ht="20" customHeight="1" spans="1:11">
       <c r="A206" s="5">
         <v>10270007</v>
       </c>
       <c r="B206" s="5">
         <v>102700</v>
       </c>
-      <c r="C206" s="34" t="s">
+      <c r="C206" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D206" s="27">
+      <c r="D206" s="28">
         <v>4020647</v>
       </c>
       <c r="E206" s="5" t="s">
@@ -7995,10 +7992,10 @@
         <v>2</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J206" s="5">
         <v>6</v>
@@ -8014,10 +8011,10 @@
       <c r="B207" s="5">
         <v>102700</v>
       </c>
-      <c r="C207" s="34" t="s">
+      <c r="C207" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D207" s="27">
+      <c r="D207" s="28">
         <v>4020642</v>
       </c>
       <c r="E207" s="5" t="s">
@@ -8027,7 +8024,7 @@
         <v>2</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J207" s="5">
         <v>7</v>
@@ -8043,10 +8040,10 @@
       <c r="B208" s="5">
         <v>102700</v>
       </c>
-      <c r="C208" s="34" t="s">
+      <c r="C208" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D208" s="27">
+      <c r="D208" s="28">
         <v>4020648</v>
       </c>
       <c r="E208" s="5" t="s">
@@ -8056,13 +8053,13 @@
         <v>2</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="J208" s="5">
-        <v>8</v>
+        <v>246</v>
+      </c>
+      <c r="J208" s="20">
+        <v>-1</v>
       </c>
       <c r="K208" s="5">
         <v>100</v>
@@ -8075,10 +8072,10 @@
       <c r="B209" s="5">
         <v>102700</v>
       </c>
-      <c r="C209" s="34" t="s">
+      <c r="C209" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D209" s="27">
+      <c r="D209" s="28">
         <v>4020643</v>
       </c>
       <c r="E209" s="5" t="s">
@@ -8088,10 +8085,10 @@
         <v>2</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="J209" s="5">
-        <v>9</v>
+        <v>247</v>
+      </c>
+      <c r="J209" s="20">
+        <v>-1</v>
       </c>
       <c r="K209" s="5">
         <v>100</v>
@@ -8104,10 +8101,10 @@
       <c r="B210" s="5">
         <v>102700</v>
       </c>
-      <c r="C210" s="34" t="s">
+      <c r="C210" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D210" s="27">
+      <c r="D210" s="28">
         <v>4020649</v>
       </c>
       <c r="E210" s="5" t="s">
@@ -8117,13 +8114,13 @@
         <v>2</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J210" s="5">
-        <v>10</v>
+        <v>249</v>
+      </c>
+      <c r="J210" s="20">
+        <v>-1</v>
       </c>
       <c r="K210" s="5">
         <v>100</v>
@@ -8136,10 +8133,10 @@
       <c r="B211" s="5">
         <v>102700</v>
       </c>
-      <c r="C211" s="34" t="s">
+      <c r="C211" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="D211" s="27">
+      <c r="D211" s="28">
         <v>4020644</v>
       </c>
       <c r="E211" s="5" t="s">
@@ -8149,10 +8146,10 @@
         <v>2</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J211" s="5">
-        <v>11</v>
+        <v>250</v>
+      </c>
+      <c r="J211" s="20">
+        <v>-1</v>
       </c>
       <c r="K211" s="5">
         <v>100</v>
@@ -8165,20 +8162,20 @@
       <c r="B212" s="5">
         <v>102700</v>
       </c>
-      <c r="C212" s="34" t="s">
+      <c r="C212" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D212" s="28">
+        <v>4020650</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D212" s="27">
-        <v>4020650</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="G212" s="5">
         <v>2</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J212" s="5">
         <v>12</v>
@@ -8195,22 +8192,22 @@
         <v>102700</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D213" s="27">
+        <v>69</v>
+      </c>
+      <c r="D213" s="28">
         <v>4020653</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G213" s="5">
         <v>2</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J213" s="5">
         <v>13</v>
@@ -8227,19 +8224,19 @@
         <v>102700</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D214" s="27">
+        <v>71</v>
+      </c>
+      <c r="D214" s="28">
         <v>4020654</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G214" s="5">
         <v>2</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J214" s="5">
         <v>14</v>
@@ -8256,25 +8253,25 @@
         <v>102700</v>
       </c>
       <c r="C215" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D215" s="28">
+        <v>4020655</v>
+      </c>
+      <c r="E215" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D215" s="27">
-        <v>4020655</v>
-      </c>
-      <c r="E215" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="G215" s="5">
         <v>2</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="J215" s="5">
-        <v>15</v>
+        <v>256</v>
+      </c>
+      <c r="J215" s="20">
+        <v>-1</v>
       </c>
       <c r="K215" s="5">
         <v>100</v>
@@ -8288,22 +8285,22 @@
         <v>102700</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D216" s="27">
+        <v>76</v>
+      </c>
+      <c r="D216" s="28">
         <v>4020656</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G216" s="5">
         <v>2</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="J216" s="5">
-        <v>16</v>
+        <v>257</v>
+      </c>
+      <c r="J216" s="20">
+        <v>-1</v>
       </c>
       <c r="K216" s="5">
         <v>100</v>
@@ -8317,26 +8314,26 @@
         <v>102700</v>
       </c>
       <c r="C217" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D217" s="28">
+        <v>4020657</v>
+      </c>
+      <c r="E217" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D217" s="27">
-        <v>4020657</v>
-      </c>
-      <c r="E217" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F217" s="34"/>
+      <c r="F217" s="35"/>
       <c r="G217" s="5">
         <v>2</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="J217" s="5">
-        <v>17</v>
+        <v>259</v>
+      </c>
+      <c r="J217" s="20">
+        <v>-1</v>
       </c>
       <c r="K217" s="5">
         <v>100</v>
@@ -8350,22 +8347,22 @@
         <v>102700</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D218" s="27">
+        <v>81</v>
+      </c>
+      <c r="D218" s="28">
         <v>4020658</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G218" s="5">
         <v>2</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="J218" s="5">
-        <v>18</v>
+        <v>260</v>
+      </c>
+      <c r="J218" s="20">
+        <v>-1</v>
       </c>
       <c r="K218" s="5">
         <v>100</v>
@@ -8378,10 +8375,10 @@
       <c r="B219" s="5">
         <v>102700</v>
       </c>
-      <c r="C219" s="34" t="s">
+      <c r="C219" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D219" s="27">
+      <c r="D219" s="28">
         <v>4020651</v>
       </c>
       <c r="E219" s="5" t="s">
@@ -8391,10 +8388,10 @@
         <v>2</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J219" s="5">
         <v>19</v>
@@ -8425,7 +8422,7 @@
       <c r="G220" s="1">
         <v>2</v>
       </c>
-      <c r="J220" s="1">
+      <c r="J220" s="20">
         <v>-1</v>
       </c>
       <c r="K220" s="1">
@@ -8434,28 +8431,26 @@
     </row>
     <row r="221" s="1" customFormat="1" spans="1:11">
       <c r="A221" s="1">
-        <v>10150002</v>
+        <v>10150003</v>
       </c>
       <c r="B221" s="1">
         <v>101500</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D221" s="16">
-        <v>4020003</v>
+        <v>4020645</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>53</v>
+        <v>236</v>
       </c>
       <c r="G221" s="1">
         <v>2</v>
       </c>
-      <c r="H221" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J221" s="1">
-        <v>1</v>
+      <c r="H221" s="1"/>
+      <c r="J221" s="5">
+        <v>2</v>
       </c>
       <c r="K221" s="1">
         <v>100</v>
@@ -8463,26 +8458,28 @@
     </row>
     <row r="222" s="1" customFormat="1" spans="1:11">
       <c r="A222" s="1">
-        <v>10150003</v>
+        <v>10150004</v>
       </c>
       <c r="B222" s="1">
         <v>101500</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D222" s="16">
-        <v>4020645</v>
+        <v>4020640</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G222" s="1">
         <v>2</v>
       </c>
-      <c r="H222" s="1"/>
-      <c r="J222" s="1">
-        <v>2</v>
+      <c r="H222" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J222" s="5">
+        <v>3</v>
       </c>
       <c r="K222" s="1">
         <v>100</v>
@@ -8490,28 +8487,28 @@
     </row>
     <row r="223" s="1" customFormat="1" spans="1:11">
       <c r="A223" s="1">
-        <v>10150004</v>
+        <v>10150005</v>
       </c>
       <c r="B223" s="1">
         <v>101500</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D223" s="16">
-        <v>4020640</v>
+        <v>4020646</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>239</v>
+        <v>34</v>
       </c>
       <c r="G223" s="1">
         <v>2</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J223" s="1">
-        <v>3</v>
+        <v>264</v>
+      </c>
+      <c r="J223" s="5">
+        <v>4</v>
       </c>
       <c r="K223" s="1">
         <v>100</v>
@@ -8519,16 +8516,16 @@
     </row>
     <row r="224" s="1" customFormat="1" spans="1:11">
       <c r="A224" s="1">
-        <v>10150005</v>
+        <v>10150006</v>
       </c>
       <c r="B224" s="1">
         <v>101500</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D224" s="16">
-        <v>4020646</v>
+        <v>4020641</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>34</v>
@@ -8537,10 +8534,10 @@
         <v>2</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="J224" s="1">
-        <v>4</v>
+        <v>265</v>
+      </c>
+      <c r="J224" s="5">
+        <v>5</v>
       </c>
       <c r="K224" s="1">
         <v>100</v>
@@ -8548,28 +8545,28 @@
     </row>
     <row r="225" s="1" customFormat="1" spans="1:11">
       <c r="A225" s="1">
-        <v>10150006</v>
+        <v>10150002</v>
       </c>
       <c r="B225" s="1">
         <v>101500</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D225" s="16">
-        <v>4020641</v>
+        <v>4020003</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G225" s="1">
         <v>2</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="J225" s="1">
-        <v>5</v>
+        <v>266</v>
+      </c>
+      <c r="J225" s="20">
+        <v>-1</v>
       </c>
       <c r="K225" s="1">
         <v>100</v>
@@ -8595,9 +8592,9 @@
         <v>2</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="J226" s="1">
+        <v>266</v>
+      </c>
+      <c r="J226" s="5">
         <v>6</v>
       </c>
       <c r="K226" s="1">
@@ -8624,9 +8621,9 @@
         <v>2</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="J227" s="1">
+        <v>267</v>
+      </c>
+      <c r="J227" s="5">
         <v>7</v>
       </c>
       <c r="K227" s="1">
@@ -8653,10 +8650,10 @@
         <v>2</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J228" s="1">
-        <v>8</v>
+        <v>268</v>
+      </c>
+      <c r="J228" s="20">
+        <v>-1</v>
       </c>
       <c r="K228" s="1">
         <v>100</v>
@@ -8682,10 +8679,10 @@
         <v>2</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J229" s="1">
-        <v>9</v>
+        <v>269</v>
+      </c>
+      <c r="J229" s="20">
+        <v>-1</v>
       </c>
       <c r="K229" s="1">
         <v>100</v>
@@ -8711,10 +8708,10 @@
         <v>2</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J230" s="1">
-        <v>10</v>
+        <v>270</v>
+      </c>
+      <c r="J230" s="20">
+        <v>-1</v>
       </c>
       <c r="K230" s="1">
         <v>100</v>
@@ -8740,10 +8737,10 @@
         <v>2</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J231" s="1">
-        <v>11</v>
+        <v>271</v>
+      </c>
+      <c r="J231" s="20">
+        <v>-1</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>
@@ -8757,19 +8754,19 @@
         <v>101500</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D232" s="16">
         <v>4020650</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G232" s="1">
         <v>2</v>
       </c>
       <c r="H232" s="1"/>
-      <c r="J232" s="1">
+      <c r="J232" s="5">
         <v>12</v>
       </c>
       <c r="K232" s="1">
@@ -8784,21 +8781,21 @@
         <v>101500</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D233" s="16">
         <v>4020653</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G233" s="1">
         <v>2</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="J233" s="1">
+        <v>272</v>
+      </c>
+      <c r="J233" s="5">
         <v>13</v>
       </c>
       <c r="K233" s="1">
@@ -8813,21 +8810,21 @@
         <v>101500</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D234" s="16">
         <v>4020654</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G234" s="1">
         <v>2</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J234" s="1">
+        <v>273</v>
+      </c>
+      <c r="J234" s="5">
         <v>14</v>
       </c>
       <c r="K234" s="1">
@@ -8842,22 +8839,22 @@
         <v>101500</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D235" s="16">
         <v>4020655</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G235" s="1">
         <v>2</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="J235" s="1">
-        <v>15</v>
+        <v>274</v>
+      </c>
+      <c r="J235" s="20">
+        <v>-1</v>
       </c>
       <c r="K235" s="1">
         <v>100</v>
@@ -8871,22 +8868,22 @@
         <v>101500</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D236" s="16">
         <v>4020656</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G236" s="1">
         <v>2</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="J236" s="1">
-        <v>16</v>
+        <v>275</v>
+      </c>
+      <c r="J236" s="20">
+        <v>-1</v>
       </c>
       <c r="K236" s="1">
         <v>100</v>
@@ -8900,22 +8897,22 @@
         <v>101500</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D237" s="16">
         <v>4020657</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G237" s="1">
         <v>2</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="J237" s="1">
-        <v>17</v>
+        <v>276</v>
+      </c>
+      <c r="J237" s="20">
+        <v>-1</v>
       </c>
       <c r="K237" s="1">
         <v>100</v>
@@ -8929,22 +8926,22 @@
         <v>101500</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D238" s="16">
         <v>4020658</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G238" s="1">
         <v>2</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="J238" s="1">
-        <v>18</v>
+        <v>277</v>
+      </c>
+      <c r="J238" s="20">
+        <v>-1</v>
       </c>
       <c r="K238" s="1">
         <v>100</v>
@@ -8970,9 +8967,9 @@
         <v>2</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="J239" s="1">
+        <v>278</v>
+      </c>
+      <c r="J239" s="5">
         <v>19</v>
       </c>
       <c r="K239" s="1">

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="278">
   <si>
     <t>属性id</t>
   </si>
@@ -189,114 +189,126 @@
     <t>金额解锁</t>
   </si>
   <si>
-    <t>yjy_jmtb_4.png</t>
+    <t>jntb_8</t>
   </si>
   <si>
     <t>中奖概率提升</t>
   </si>
   <si>
+    <t>解锁sweet win奖励</t>
+  </si>
+  <si>
+    <t>jntb_1_5.png</t>
+  </si>
+  <si>
+    <t>10030002,10</t>
+  </si>
+  <si>
+    <t>PetSquadsweet</t>
+  </si>
+  <si>
+    <t>sweet win中奖概率提升</t>
+  </si>
+  <si>
+    <t>10030003,10</t>
+  </si>
+  <si>
+    <t>解锁big win奖励</t>
+  </si>
+  <si>
+    <t>jntb_1_4</t>
+  </si>
+  <si>
+    <t>10030004,10</t>
+  </si>
+  <si>
+    <t>PetSquadbig</t>
+  </si>
+  <si>
+    <t>big win中奖概率提升</t>
+  </si>
+  <si>
+    <t>10030005,10</t>
+  </si>
+  <si>
+    <t>解锁mega win奖励</t>
+  </si>
+  <si>
+    <t>jntb_1_3</t>
+  </si>
+  <si>
+    <t>PetSquadmega</t>
+  </si>
+  <si>
+    <t>mega win中奖概率提升</t>
+  </si>
+  <si>
+    <t>解锁epic win奖励</t>
+  </si>
+  <si>
+    <t>jntb_1_2</t>
+  </si>
+  <si>
+    <t>PetSquadepic</t>
+  </si>
+  <si>
+    <t>epic win中奖概率提升</t>
+  </si>
+  <si>
+    <t>解锁legendary win奖励</t>
+  </si>
+  <si>
+    <t>jntb_1_1</t>
+  </si>
+  <si>
+    <t>PetSquadlegendary</t>
+  </si>
+  <si>
+    <t>legendary win中奖概率提升</t>
+  </si>
+  <si>
+    <t>中樱桃符号概率提升</t>
+  </si>
+  <si>
+    <t>jntb_7</t>
+  </si>
+  <si>
+    <t>解锁jackpot大奖</t>
+  </si>
+  <si>
+    <t>jntb_5</t>
+  </si>
+  <si>
+    <t>10030007,10</t>
+  </si>
+  <si>
+    <t>中奖提成比例</t>
+  </si>
+  <si>
+    <t>提成人数上限</t>
+  </si>
+  <si>
+    <t>jntb_9</t>
+  </si>
+  <si>
+    <t>下注金额增加</t>
+  </si>
+  <si>
+    <t>10070003,1</t>
+  </si>
+  <si>
+    <t>10070004,10</t>
+  </si>
+  <si>
+    <t>10070005,1</t>
+  </si>
+  <si>
+    <t>中奖概率增高</t>
+  </si>
+  <si>
     <t>yjy_jmtb_5.png</t>
   </si>
   <si>
-    <t>解锁sweet win奖励</t>
-  </si>
-  <si>
-    <t>jntb_1_5.png</t>
-  </si>
-  <si>
-    <t>10030002,10</t>
-  </si>
-  <si>
-    <t>sweet win中奖概率提升</t>
-  </si>
-  <si>
-    <t>10030003,10</t>
-  </si>
-  <si>
-    <t>解锁big win奖励</t>
-  </si>
-  <si>
-    <t>jntb_1_4</t>
-  </si>
-  <si>
-    <t>10030004,10</t>
-  </si>
-  <si>
-    <t>big win中奖概率提升</t>
-  </si>
-  <si>
-    <t>10030005,10</t>
-  </si>
-  <si>
-    <t>解锁mega win奖励</t>
-  </si>
-  <si>
-    <t>jntb_1_3</t>
-  </si>
-  <si>
-    <t>mega win中奖概率提升</t>
-  </si>
-  <si>
-    <t>解锁epic win奖励</t>
-  </si>
-  <si>
-    <t>jntb_1_2</t>
-  </si>
-  <si>
-    <t>epic win中奖概率提升</t>
-  </si>
-  <si>
-    <t>解锁legendary win奖励</t>
-  </si>
-  <si>
-    <t>jntb_1_1</t>
-  </si>
-  <si>
-    <t>legendary win中奖概率提升</t>
-  </si>
-  <si>
-    <t>中樱桃符号概率提升</t>
-  </si>
-  <si>
-    <t>jntb_7</t>
-  </si>
-  <si>
-    <t>解锁jackpot大奖</t>
-  </si>
-  <si>
-    <t>jntb_5</t>
-  </si>
-  <si>
-    <t>10030007,10</t>
-  </si>
-  <si>
-    <t>中奖提成比例</t>
-  </si>
-  <si>
-    <t>jntb_8</t>
-  </si>
-  <si>
-    <t>提成人数上限</t>
-  </si>
-  <si>
-    <t>jntb_9</t>
-  </si>
-  <si>
-    <t>下注金额增加</t>
-  </si>
-  <si>
-    <t>10070003,1</t>
-  </si>
-  <si>
-    <t>10070004,10</t>
-  </si>
-  <si>
-    <t>10070005,1</t>
-  </si>
-  <si>
-    <t>中奖概率增高</t>
-  </si>
-  <si>
     <t>10070006,10</t>
   </si>
   <si>
@@ -321,12 +333,18 @@
     <t>jntb_2_3</t>
   </si>
   <si>
+    <t>PetSquadFree</t>
+  </si>
+  <si>
     <t>解锁免费模式20-50倍奖励</t>
   </si>
   <si>
     <t>10070013,1</t>
   </si>
   <si>
+    <t>PetSquadFree1</t>
+  </si>
+  <si>
     <t>免费模式20-50倍奖励提升</t>
   </si>
   <si>
@@ -342,6 +360,9 @@
     <t>10070015,10</t>
   </si>
   <si>
+    <t>PetSquadFree2</t>
+  </si>
+  <si>
     <t>免费模式50-100倍奖励提升</t>
   </si>
   <si>
@@ -357,6 +378,9 @@
     <t>10070017,10</t>
   </si>
   <si>
+    <t>PetSquadFree3</t>
+  </si>
+  <si>
     <t>免费模式100倍以上奖励提升</t>
   </si>
   <si>
@@ -438,6 +462,12 @@
     <t>10120019,10</t>
   </si>
   <si>
+    <t>PetSquadjackpot</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
     <t>10180006,10</t>
   </si>
   <si>
@@ -450,9 +480,6 @@
     <t>10180005,1</t>
   </si>
   <si>
-    <t>10180002,10</t>
-  </si>
-  <si>
     <t>10180007,1</t>
   </si>
   <si>
@@ -693,82 +720,52 @@
     <t>10210019,10</t>
   </si>
   <si>
-    <t>PetSquadsweet</t>
-  </si>
-  <si>
     <t>10390003,1</t>
   </si>
   <si>
     <t>10390004,10</t>
   </si>
   <si>
-    <t>PetSquadbig</t>
-  </si>
-  <si>
     <t>10390005,1</t>
   </si>
   <si>
     <t>10390006,10</t>
   </si>
   <si>
-    <t>PetSquadmega</t>
-  </si>
-  <si>
     <t>10390007,1</t>
   </si>
   <si>
     <t>10390008,10</t>
   </si>
   <si>
-    <t>PetSquadepic</t>
-  </si>
-  <si>
     <t>10390009,1</t>
   </si>
   <si>
     <t>10390010,10</t>
   </si>
   <si>
-    <t>PetSquadlegendary</t>
-  </si>
-  <si>
     <t>10390011,1</t>
   </si>
   <si>
-    <t>PetSquadFree</t>
-  </si>
-  <si>
     <t>10390013,1</t>
   </si>
   <si>
-    <t>PetSquadFree1</t>
-  </si>
-  <si>
     <t>10390014,1</t>
   </si>
   <si>
     <t>10390015,10</t>
   </si>
   <si>
-    <t>PetSquadFree2</t>
-  </si>
-  <si>
     <t>10390016,1</t>
   </si>
   <si>
     <t>10390017,10</t>
   </si>
   <si>
-    <t>PetSquadFree3</t>
-  </si>
-  <si>
     <t>10390018,1</t>
   </si>
   <si>
     <t>10390019,10</t>
-  </si>
-  <si>
-    <t>PetSquadjackpot</t>
   </si>
   <si>
     <t>10200006,10</t>
@@ -2055,7 +2052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K239"/>
+  <dimension ref="A1:L239"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="8" customWidth="1"/>
@@ -2214,7 +2211,7 @@
         <v>4020003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="1">
@@ -2235,19 +2232,22 @@
         <v>100300</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="16">
         <v>4020645</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17">
         <v>2</v>
       </c>
       <c r="H7" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J7" s="1">
@@ -2271,7 +2271,7 @@
         <v>4020640</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
@@ -2308,6 +2308,9 @@
       <c r="H9" s="17" t="s">
         <v>35</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
@@ -2323,7 +2326,7 @@
         <v>100300</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="16">
         <v>4020641</v>
@@ -2335,7 +2338,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
@@ -2352,16 +2355,19 @@
         <v>100300</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="16">
         <v>4020647</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" s="17">
         <v>2</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
@@ -2378,13 +2384,13 @@
         <v>100300</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="16">
         <v>4020642</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
@@ -2404,16 +2410,19 @@
         <v>100300</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" s="16">
         <v>4020648</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="17">
         <v>2</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="J13" s="1">
         <v>8</v>
@@ -2430,13 +2439,13 @@
         <v>100300</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" s="16">
         <v>4020643</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
@@ -2456,16 +2465,19 @@
         <v>100300</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D15" s="16">
         <v>4020649</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G15" s="17">
         <v>2</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="J15" s="1">
         <v>10</v>
@@ -2482,13 +2494,13 @@
         <v>100300</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D16" s="16">
         <v>4020644</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G16" s="1">
         <v>2</v>
@@ -2508,13 +2520,13 @@
         <v>100300</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D17" s="16">
         <v>4020006</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G17" s="17">
         <v>2</v>
@@ -2534,19 +2546,19 @@
         <v>100300</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D18" s="16">
         <v>4020651</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G18" s="1">
         <v>2</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J18" s="1">
         <v>13</v>
@@ -2563,13 +2575,13 @@
         <v>100300</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D19" s="16">
         <v>4020607</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G19" s="16">
         <v>1</v>
@@ -2590,13 +2602,13 @@
         <v>100300</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" s="16">
         <v>4020608</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G20" s="16">
         <v>1</v>
@@ -2617,7 +2629,7 @@
         <v>100700</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D21" s="19">
         <v>4020002</v>
@@ -2646,18 +2658,21 @@
         <v>100700</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="19">
         <v>4020645</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G22" s="19">
         <v>2</v>
       </c>
       <c r="H22" s="19"/>
+      <c r="I22" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="J22" s="3">
         <v>2</v>
       </c>
@@ -2679,13 +2694,13 @@
         <v>4020640</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J23" s="3">
         <v>3</v>
@@ -2714,7 +2729,10 @@
         <v>2</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="J24" s="3">
         <v>4</v>
@@ -2731,7 +2749,7 @@
         <v>100700</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="19">
         <v>4020641</v>
@@ -2743,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J25" s="3">
         <v>5</v>
@@ -2760,20 +2778,20 @@
         <v>100700</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D26" s="19">
         <v>4020003</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F26" s="22"/>
       <c r="G26" s="2">
         <v>2</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J26" s="20">
         <v>-1</v>
@@ -2790,19 +2808,22 @@
         <v>100700</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="19">
         <v>4020647</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" s="19">
         <v>2</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J27" s="3">
         <v>7</v>
@@ -2819,19 +2840,19 @@
         <v>100700</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D28" s="19">
         <v>4020642</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G28" s="2">
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J28" s="3">
         <v>8</v>
@@ -2848,19 +2869,22 @@
         <v>100700</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D29" s="19">
         <v>4020648</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G29" s="19">
         <v>2</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="J29" s="3">
         <v>9</v>
@@ -2877,19 +2901,19 @@
         <v>100700</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D30" s="19">
         <v>4020643</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G30" s="2">
         <v>2</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J30" s="3">
         <v>10</v>
@@ -2906,19 +2930,22 @@
         <v>100700</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D31" s="19">
         <v>4020649</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G31" s="19">
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J31" s="20">
         <v>-1</v>
@@ -2935,19 +2962,19 @@
         <v>100700</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D32" s="19">
         <v>4020644</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2">
         <v>2</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J32" s="20">
         <v>-1</v>
@@ -2964,16 +2991,19 @@
         <v>100700</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D33" s="19">
         <v>4020650</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G33" s="19">
         <v>2</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J33" s="3">
         <v>12</v>
@@ -2990,19 +3020,22 @@
         <v>100700</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D34" s="19">
         <v>4020653</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G34" s="2">
         <v>2</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>70</v>
+        <v>75</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="J34" s="3">
         <v>13</v>
@@ -3019,19 +3052,19 @@
         <v>100700</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D35" s="19">
         <v>4020654</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G35" s="19">
         <v>2</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J35" s="3">
         <v>14</v>
@@ -3048,19 +3081,22 @@
         <v>100700</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D36" s="19">
         <v>4020655</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G36" s="2">
         <v>2</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>75</v>
+        <v>81</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="J36" s="3">
         <v>15</v>
@@ -3077,19 +3113,19 @@
         <v>100700</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D37" s="19">
         <v>4020656</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G37" s="19">
         <v>2</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J37" s="3">
         <v>16</v>
@@ -3106,19 +3142,22 @@
         <v>100700</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D38" s="19">
         <v>4020657</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G38" s="2">
         <v>2</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="J38" s="20">
         <v>-1</v>
@@ -3135,19 +3174,19 @@
         <v>100700</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D39" s="19">
         <v>4020658</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G39" s="19">
         <v>2</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J39" s="20">
         <v>-1</v>
@@ -3164,13 +3203,13 @@
         <v>101200</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D40" s="23">
         <v>4020002</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
@@ -3193,20 +3232,20 @@
         <v>101200</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D41" s="23">
         <v>4020003</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F41" s="24"/>
       <c r="G41" s="3">
         <v>2</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J41" s="3">
         <v>1</v>
@@ -3223,19 +3262,22 @@
         <v>101200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" s="23">
         <v>4020645</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F42" s="24"/>
       <c r="G42" s="23">
         <v>2</v>
       </c>
       <c r="H42" s="23"/>
+      <c r="I42" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="J42" s="3">
         <v>2</v>
       </c>
@@ -3257,13 +3299,13 @@
         <v>4020640</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G43" s="3">
         <v>2</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J43" s="3">
         <v>3</v>
@@ -3292,7 +3334,10 @@
         <v>2</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>85</v>
+        <v>93</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="J44" s="3">
         <v>4</v>
@@ -3309,7 +3354,7 @@
         <v>101200</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" s="23">
         <v>4020641</v>
@@ -3321,7 +3366,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J45" s="3">
         <v>5</v>
@@ -3338,19 +3383,22 @@
         <v>101200</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D46" s="23">
         <v>4020647</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G46" s="23">
         <v>2</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="J46" s="3">
         <v>6</v>
@@ -3367,19 +3415,19 @@
         <v>101200</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D47" s="23">
         <v>4020642</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G47" s="3">
         <v>2</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J47" s="3">
         <v>7</v>
@@ -3396,19 +3444,22 @@
         <v>101200</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D48" s="23">
         <v>4020648</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G48" s="23">
         <v>2</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>89</v>
+        <v>97</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="J48" s="3">
         <v>8</v>
@@ -3417,7 +3468,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" s="3" customFormat="1" spans="1:11">
+    <row r="49" s="3" customFormat="1" spans="1:12">
       <c r="A49" s="3">
         <v>10120010</v>
       </c>
@@ -3425,19 +3476,19 @@
         <v>101200</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D49" s="23">
         <v>4020643</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G49" s="3">
         <v>2</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J49" s="3">
         <v>9</v>
@@ -3446,7 +3497,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" s="3" customFormat="1" spans="1:11">
+    <row r="50" s="3" customFormat="1" spans="1:12">
       <c r="A50" s="3">
         <v>10120011</v>
       </c>
@@ -3454,19 +3505,22 @@
         <v>101200</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D50" s="23">
         <v>4020649</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G50" s="23">
         <v>2</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>91</v>
+        <v>99</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J50" s="3">
         <v>10</v>
@@ -3475,7 +3529,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" s="3" customFormat="1" spans="1:11">
+    <row r="51" s="3" customFormat="1" spans="1:12">
       <c r="A51" s="3">
         <v>10120012</v>
       </c>
@@ -3483,19 +3537,19 @@
         <v>101200</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D51" s="23">
         <v>4020644</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G51" s="3">
         <v>2</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J51" s="3">
         <v>11</v>
@@ -3504,7 +3558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" s="3" customFormat="1" spans="1:11">
+    <row r="52" s="3" customFormat="1" spans="1:12">
       <c r="A52" s="3">
         <v>10120013</v>
       </c>
@@ -3512,18 +3566,21 @@
         <v>101200</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D52" s="23">
         <v>4020659</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G52" s="23">
         <v>2</v>
       </c>
       <c r="H52" s="23"/>
+      <c r="I52" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="J52" s="3">
         <v>12</v>
       </c>
@@ -3531,7 +3588,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" s="3" customFormat="1" spans="1:11">
+    <row r="53" s="3" customFormat="1" spans="1:12">
       <c r="A53" s="3">
         <v>10120014</v>
       </c>
@@ -3539,19 +3596,22 @@
         <v>101200</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D53" s="23">
         <v>4020660</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G53" s="3">
         <v>2</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>96</v>
+        <v>104</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="J53" s="3">
         <v>13</v>
@@ -3560,7 +3620,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" s="3" customFormat="1" spans="1:11">
+    <row r="54" s="3" customFormat="1" spans="1:12">
       <c r="A54" s="3">
         <v>10120015</v>
       </c>
@@ -3568,19 +3628,19 @@
         <v>101200</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D54" s="23">
         <v>4020661</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G54" s="23">
         <v>2</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J54" s="3">
         <v>14</v>
@@ -3589,7 +3649,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" s="3" customFormat="1" spans="1:11">
+    <row r="55" s="3" customFormat="1" spans="1:12">
       <c r="A55" s="3">
         <v>10120016</v>
       </c>
@@ -3597,19 +3657,22 @@
         <v>101200</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D55" s="23">
         <v>4020662</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G55" s="3">
         <v>2</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="J55" s="3">
         <v>15</v>
@@ -3618,7 +3681,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" s="3" customFormat="1" spans="1:11">
+    <row r="56" s="3" customFormat="1" spans="1:12">
       <c r="A56" s="3">
         <v>10120017</v>
       </c>
@@ -3626,19 +3689,19 @@
         <v>101200</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D56" s="23">
         <v>4020663</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G56" s="23">
         <v>2</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J56" s="3">
         <v>16</v>
@@ -3647,7 +3710,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" s="3" customFormat="1" spans="1:11">
+    <row r="57" s="3" customFormat="1" spans="1:12">
       <c r="A57" s="3">
         <v>10120018</v>
       </c>
@@ -3655,19 +3718,22 @@
         <v>101200</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D57" s="23">
         <v>4020664</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G57" s="3">
         <v>2</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>104</v>
+        <v>112</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="J57" s="3">
         <v>17</v>
@@ -3676,7 +3742,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" s="3" customFormat="1" spans="1:11">
+    <row r="58" s="3" customFormat="1" spans="1:12">
       <c r="A58" s="3">
         <v>10120019</v>
       </c>
@@ -3684,19 +3750,19 @@
         <v>101200</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D58" s="23">
         <v>4020665</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G58" s="23">
         <v>2</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J58" s="3">
         <v>18</v>
@@ -3705,7 +3771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" s="3" customFormat="1" spans="1:11">
+    <row r="59" s="3" customFormat="1" spans="1:12">
       <c r="A59" s="3">
         <v>10120020</v>
       </c>
@@ -3713,19 +3779,22 @@
         <v>101200</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D59" s="23">
         <v>4020651</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G59" s="3">
         <v>2</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>107</v>
+        <v>115</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="J59" s="3">
         <v>19</v>
@@ -3734,7 +3803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" s="4" customFormat="1" spans="1:11">
+    <row r="60" s="4" customFormat="1" spans="1:12">
       <c r="A60" s="4">
         <v>10180001</v>
       </c>
@@ -3742,13 +3811,13 @@
         <v>101800</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D60" s="25">
         <v>4020002</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F60" s="4">
         <v>1</v>
@@ -3756,14 +3825,17 @@
       <c r="G60" s="4">
         <v>2</v>
       </c>
-      <c r="J60" s="4">
+      <c r="J60" s="20">
         <v>-1</v>
       </c>
       <c r="K60" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" s="4" customFormat="1" spans="1:11">
+      <c r="L60" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" s="4" customFormat="1" spans="1:12">
       <c r="A61" s="4">
         <v>10180002</v>
       </c>
@@ -3771,29 +3843,29 @@
         <v>101800</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D61" s="25">
         <v>4020003</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F61" s="26"/>
       <c r="G61" s="4">
         <v>2</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J61" s="4">
-        <v>1</v>
+        <v>118</v>
+      </c>
+      <c r="J61" s="20">
+        <v>-1</v>
       </c>
       <c r="K61" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="62" s="4" customFormat="1" spans="1:11">
+    <row r="62" s="4" customFormat="1" spans="1:12">
       <c r="A62" s="4">
         <v>10180003</v>
       </c>
@@ -3801,26 +3873,29 @@
         <v>101800</v>
       </c>
       <c r="C62" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D62" s="25">
         <v>4020645</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G62" s="25">
         <v>2</v>
       </c>
       <c r="H62" s="25"/>
-      <c r="J62" s="4">
-        <v>2</v>
+      <c r="I62" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3</v>
       </c>
       <c r="K62" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="63" s="4" customFormat="1" spans="1:11">
+    <row r="63" s="4" customFormat="1" spans="1:12">
       <c r="A63" s="4">
         <v>10180004</v>
       </c>
@@ -3834,22 +3909,22 @@
         <v>4020640</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G63" s="4">
         <v>2</v>
       </c>
       <c r="H63" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="J63" s="4">
-        <v>3</v>
+        <v>119</v>
+      </c>
+      <c r="J63" s="3">
+        <v>4</v>
       </c>
       <c r="K63" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="64" s="4" customFormat="1" spans="1:11">
+    <row r="64" s="4" customFormat="1" spans="1:12">
       <c r="A64" s="4">
         <v>10180005</v>
       </c>
@@ -3869,10 +3944,13 @@
         <v>2</v>
       </c>
       <c r="H64" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="J64" s="4">
-        <v>4</v>
+        <v>120</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J64" s="3">
+        <v>5</v>
       </c>
       <c r="K64" s="4">
         <v>100</v>
@@ -3886,7 +3964,7 @@
         <v>101800</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D65" s="25">
         <v>4020641</v>
@@ -3898,10 +3976,10 @@
         <v>2</v>
       </c>
       <c r="H65" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="J65" s="4">
-        <v>5</v>
+        <v>121</v>
+      </c>
+      <c r="J65" s="3">
+        <v>6</v>
       </c>
       <c r="K65" s="4">
         <v>100</v>
@@ -3915,22 +3993,25 @@
         <v>101800</v>
       </c>
       <c r="C66" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D66" s="25">
         <v>4020647</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G66" s="25">
         <v>2</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="J66" s="4">
-        <v>6</v>
+        <v>118</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J66" s="3">
+        <v>7</v>
       </c>
       <c r="K66" s="4">
         <v>100</v>
@@ -3944,22 +4025,22 @@
         <v>101800</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D67" s="25">
         <v>4020642</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G67" s="4">
         <v>2</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="J67" s="4">
-        <v>7</v>
+        <v>122</v>
+      </c>
+      <c r="J67" s="3">
+        <v>8</v>
       </c>
       <c r="K67" s="4">
         <v>100</v>
@@ -3973,22 +4054,25 @@
         <v>101800</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D68" s="25">
         <v>4020648</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G68" s="25">
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J68" s="4">
-        <v>8</v>
+        <v>123</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J68" s="3">
+        <v>9</v>
       </c>
       <c r="K68" s="4">
         <v>100</v>
@@ -4002,22 +4086,22 @@
         <v>101800</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D69" s="25">
         <v>4020643</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G69" s="4">
         <v>2</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="J69" s="4">
-        <v>9</v>
+        <v>124</v>
+      </c>
+      <c r="J69" s="3">
+        <v>10</v>
       </c>
       <c r="K69" s="4">
         <v>100</v>
@@ -4031,22 +4115,25 @@
         <v>101800</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D70" s="25">
         <v>4020649</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G70" s="25">
         <v>2</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J70" s="4">
-        <v>10</v>
+        <v>125</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J70" s="20">
+        <v>-1</v>
       </c>
       <c r="K70" s="4">
         <v>100</v>
@@ -4060,22 +4147,22 @@
         <v>101800</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D71" s="25">
         <v>4020644</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G71" s="4">
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="J71" s="4">
-        <v>11</v>
+        <v>126</v>
+      </c>
+      <c r="J71" s="20">
+        <v>-1</v>
       </c>
       <c r="K71" s="4">
         <v>100</v>
@@ -4089,18 +4176,21 @@
         <v>101800</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D72" s="25">
         <v>4020650</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G72" s="25">
         <v>2</v>
       </c>
-      <c r="J72" s="4">
+      <c r="I72" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J72" s="3">
         <v>12</v>
       </c>
       <c r="K72" s="4">
@@ -4115,21 +4205,24 @@
         <v>101800</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D73" s="25">
         <v>4020653</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G73" s="4">
         <v>2</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="J73" s="4">
+        <v>127</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J73" s="3">
         <v>13</v>
       </c>
       <c r="K73" s="4">
@@ -4144,21 +4237,21 @@
         <v>101800</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D74" s="25">
         <v>4020654</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G74" s="25">
         <v>2</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="J74" s="4">
+        <v>128</v>
+      </c>
+      <c r="J74" s="3">
         <v>14</v>
       </c>
       <c r="K74" s="4">
@@ -4173,21 +4266,24 @@
         <v>101800</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D75" s="25">
         <v>4020655</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G75" s="4">
         <v>2</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="J75" s="4">
+        <v>129</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J75" s="3">
         <v>15</v>
       </c>
       <c r="K75" s="4">
@@ -4202,21 +4298,21 @@
         <v>101800</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D76" s="25">
         <v>4020656</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G76" s="25">
         <v>2</v>
       </c>
       <c r="H76" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="J76" s="4">
+        <v>130</v>
+      </c>
+      <c r="J76" s="3">
         <v>16</v>
       </c>
       <c r="K76" s="4">
@@ -4231,22 +4327,25 @@
         <v>101800</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D77" s="25">
         <v>4020657</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G77" s="4">
         <v>2</v>
       </c>
       <c r="H77" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="J77" s="4">
-        <v>17</v>
+        <v>131</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J77" s="20">
+        <v>-1</v>
       </c>
       <c r="K77" s="4">
         <v>100</v>
@@ -4260,22 +4359,22 @@
         <v>101800</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D78" s="25">
         <v>4020658</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G78" s="25">
         <v>2</v>
       </c>
       <c r="H78" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J78" s="4">
-        <v>18</v>
+        <v>132</v>
+      </c>
+      <c r="J78" s="20">
+        <v>-1</v>
       </c>
       <c r="K78" s="4">
         <v>100</v>
@@ -4289,19 +4388,22 @@
         <v>101800</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D79" s="25">
         <v>4020651</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G79" s="4">
         <v>2</v>
       </c>
       <c r="H79" s="25" t="s">
-        <v>124</v>
+        <v>133</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="J79" s="4">
         <v>19</v>
@@ -4318,13 +4420,13 @@
         <v>102500</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D80" s="28">
         <v>4020002</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F80" s="5">
         <v>1</v>
@@ -4347,20 +4449,20 @@
         <v>102500</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D81" s="28">
         <v>4020003</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F81" s="29"/>
       <c r="G81" s="5">
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J81" s="5">
         <v>1</v>
@@ -4377,18 +4479,21 @@
         <v>102500</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D82" s="28">
         <v>4020645</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G82" s="28">
         <v>2</v>
       </c>
       <c r="H82" s="28"/>
+      <c r="I82" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="J82" s="5">
         <v>2</v>
       </c>
@@ -4410,13 +4515,13 @@
         <v>4020640</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G83" s="5">
         <v>2</v>
       </c>
       <c r="H83" s="28" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J83" s="5">
         <v>3</v>
@@ -4445,7 +4550,10 @@
         <v>2</v>
       </c>
       <c r="H84" s="28" t="s">
-        <v>127</v>
+        <v>136</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="J84" s="5">
         <v>4</v>
@@ -4462,7 +4570,7 @@
         <v>102500</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D85" s="28">
         <v>4020641</v>
@@ -4474,7 +4582,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="28" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="J85" s="5">
         <v>5</v>
@@ -4491,19 +4599,22 @@
         <v>102500</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D86" s="28">
         <v>4020647</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G86" s="28">
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="J86" s="5">
         <v>6</v>
@@ -4520,19 +4631,19 @@
         <v>102500</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D87" s="28">
         <v>4020642</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G87" s="5">
         <v>2</v>
       </c>
       <c r="H87" s="28" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J87" s="5">
         <v>7</v>
@@ -4549,19 +4660,22 @@
         <v>102500</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D88" s="28">
         <v>4020648</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G88" s="28">
         <v>2</v>
       </c>
       <c r="H88" s="28" t="s">
-        <v>131</v>
+        <v>140</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="J88" s="5">
         <v>8</v>
@@ -4578,19 +4692,19 @@
         <v>102500</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D89" s="28">
         <v>4020643</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G89" s="28">
         <v>2</v>
       </c>
       <c r="H89" s="28" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J89" s="5">
         <v>9</v>
@@ -4607,19 +4721,22 @@
         <v>102500</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D90" s="28">
         <v>4020649</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G90" s="28">
         <v>2</v>
       </c>
       <c r="H90" s="28" t="s">
-        <v>133</v>
+        <v>142</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="J90" s="5">
         <v>10</v>
@@ -4636,19 +4753,19 @@
         <v>102500</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D91" s="28">
         <v>4020644</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G91" s="28">
         <v>2</v>
       </c>
       <c r="H91" s="28" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J91" s="5">
         <v>11</v>
@@ -4665,18 +4782,21 @@
         <v>102500</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D92" s="28">
         <v>4020650</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G92" s="28">
         <v>2</v>
       </c>
       <c r="H92" s="28"/>
+      <c r="I92" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="J92" s="5">
         <v>12</v>
       </c>
@@ -4692,19 +4812,22 @@
         <v>102500</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D93" s="28">
         <v>4020653</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G93" s="28">
         <v>2</v>
       </c>
       <c r="H93" s="28" t="s">
-        <v>135</v>
+        <v>144</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="J93" s="5">
         <v>13</v>
@@ -4721,19 +4844,19 @@
         <v>102500</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D94" s="28">
         <v>4020654</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G94" s="28">
         <v>2</v>
       </c>
       <c r="H94" s="28" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="J94" s="5">
         <v>14</v>
@@ -4750,19 +4873,22 @@
         <v>102500</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D95" s="28">
         <v>4020655</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G95" s="28">
         <v>2</v>
       </c>
       <c r="H95" s="28" t="s">
-        <v>137</v>
+        <v>146</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="J95" s="5">
         <v>15</v>
@@ -4779,19 +4905,19 @@
         <v>102500</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D96" s="28">
         <v>4020656</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G96" s="28">
         <v>2</v>
       </c>
       <c r="H96" s="28" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J96" s="5">
         <v>16</v>
@@ -4808,17 +4934,20 @@
         <v>102500</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D97" s="28">
         <v>4020657</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G97" s="28"/>
       <c r="H97" s="28" t="s">
-        <v>139</v>
+        <v>148</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="J97" s="5">
         <v>17</v>
@@ -4835,19 +4964,19 @@
         <v>102500</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D98" s="28">
         <v>4020658</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G98" s="28">
         <v>2</v>
       </c>
       <c r="H98" s="28" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J98" s="5">
         <v>18</v>
@@ -4864,19 +4993,22 @@
         <v>102500</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D99" s="28">
         <v>4020651</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G99" s="5">
         <v>2</v>
       </c>
       <c r="H99" s="28" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="J99" s="5">
         <v>19</v>
@@ -4893,13 +5025,13 @@
         <v>103100</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D100" s="30">
         <v>4020002</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F100" s="6">
         <v>1</v>
@@ -4922,20 +5054,20 @@
         <v>103100</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D101" s="30">
         <v>4020003</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F101" s="31"/>
       <c r="G101" s="6">
         <v>2</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J101" s="6">
         <v>1</v>
@@ -4952,19 +5084,22 @@
         <v>103100</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D102" s="30">
         <v>4020645</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F102" s="31"/>
       <c r="G102" s="31">
         <v>2</v>
       </c>
       <c r="H102" s="31"/>
+      <c r="I102" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="J102" s="6">
         <v>2</v>
       </c>
@@ -4986,13 +5121,13 @@
         <v>4020640</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G103" s="6">
         <v>2</v>
       </c>
       <c r="H103" s="31" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J103" s="6">
         <v>3</v>
@@ -5021,7 +5156,10 @@
         <v>2</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>144</v>
+        <v>153</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="J104" s="6">
         <v>4</v>
@@ -5038,7 +5176,7 @@
         <v>103100</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D105" s="30">
         <v>4020641</v>
@@ -5050,7 +5188,7 @@
         <v>2</v>
       </c>
       <c r="H105" s="31" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J105" s="6">
         <v>5</v>
@@ -5067,19 +5205,22 @@
         <v>103100</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D106" s="30">
         <v>4020647</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G106" s="31">
         <v>2</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>146</v>
+        <v>155</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="J106" s="6">
         <v>6</v>
@@ -5096,19 +5237,19 @@
         <v>103100</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D107" s="30">
         <v>4020642</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G107" s="6">
         <v>2</v>
       </c>
       <c r="H107" s="31" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="J107" s="6">
         <v>7</v>
@@ -5125,19 +5266,22 @@
         <v>103100</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D108" s="30">
         <v>4020648</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G108" s="31">
         <v>2</v>
       </c>
       <c r="H108" s="31" t="s">
-        <v>148</v>
+        <v>157</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J108" s="6">
         <v>8</v>
@@ -5154,19 +5298,19 @@
         <v>103100</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D109" s="30">
         <v>4020643</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G109" s="6">
         <v>2</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="J109" s="6">
         <v>9</v>
@@ -5183,19 +5327,22 @@
         <v>103100</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D110" s="30">
         <v>4020649</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G110" s="31">
         <v>2</v>
       </c>
       <c r="H110" s="31" t="s">
-        <v>150</v>
+        <v>159</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="J110" s="6">
         <v>10</v>
@@ -5212,19 +5359,19 @@
         <v>103100</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D111" s="30">
         <v>4020644</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G111" s="6">
         <v>2</v>
       </c>
       <c r="H111" s="31" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J111" s="6">
         <v>11</v>
@@ -5241,18 +5388,21 @@
         <v>103100</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D112" s="30">
         <v>4020650</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G112" s="31">
         <v>2</v>
       </c>
       <c r="H112" s="31"/>
+      <c r="I112" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="J112" s="6">
         <v>12</v>
       </c>
@@ -5268,19 +5418,22 @@
         <v>103100</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D113" s="30">
         <v>4020653</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G113" s="6">
         <v>2</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>152</v>
+        <v>161</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="J113" s="6">
         <v>13</v>
@@ -5297,19 +5450,19 @@
         <v>103100</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D114" s="30">
         <v>4020654</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G114" s="31">
         <v>2</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J114" s="6">
         <v>14</v>
@@ -5326,19 +5479,22 @@
         <v>103100</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D115" s="30">
         <v>4020655</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G115" s="6">
         <v>2</v>
       </c>
       <c r="H115" s="31" t="s">
-        <v>154</v>
+        <v>163</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="J115" s="6">
         <v>15</v>
@@ -5355,19 +5511,19 @@
         <v>103100</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D116" s="30">
         <v>4020656</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G116" s="31">
         <v>2</v>
       </c>
       <c r="H116" s="31" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J116" s="6">
         <v>16</v>
@@ -5384,19 +5540,22 @@
         <v>103100</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D117" s="30">
         <v>4020657</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G117" s="6">
         <v>2</v>
       </c>
       <c r="H117" s="31" t="s">
-        <v>156</v>
+        <v>165</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="J117" s="6">
         <v>17</v>
@@ -5413,19 +5572,19 @@
         <v>103100</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D118" s="30">
         <v>4020658</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G118" s="31">
         <v>2</v>
       </c>
       <c r="H118" s="31" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J118" s="6">
         <v>18</v>
@@ -5442,19 +5601,22 @@
         <v>103100</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D119" s="30">
         <v>4020651</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G119" s="6">
         <v>2</v>
       </c>
       <c r="H119" s="31" t="s">
-        <v>158</v>
+        <v>167</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="J119" s="6">
         <v>19</v>
@@ -5471,13 +5633,13 @@
         <v>102200</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D120" s="19">
         <v>4020002</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -5500,20 +5662,20 @@
         <v>102200</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D121" s="19">
         <v>4020003</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F121" s="22"/>
       <c r="G121" s="2">
         <v>2</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -5530,19 +5692,22 @@
         <v>102200</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D122" s="19">
         <v>4020645</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F122" s="22"/>
       <c r="G122" s="19">
         <v>2</v>
       </c>
       <c r="H122" s="19"/>
+      <c r="I122" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="J122" s="2">
         <v>2</v>
       </c>
@@ -5564,13 +5729,13 @@
         <v>4020640</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G123" s="2">
         <v>2</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J123" s="2">
         <v>3</v>
@@ -5599,7 +5764,10 @@
         <v>2</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>161</v>
+        <v>170</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="J124" s="2">
         <v>4</v>
@@ -5616,7 +5784,7 @@
         <v>102200</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D125" s="19">
         <v>4020641</v>
@@ -5628,7 +5796,7 @@
         <v>2</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J125" s="2">
         <v>5</v>
@@ -5645,19 +5813,22 @@
         <v>102200</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D126" s="19">
         <v>4020647</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G126" s="19">
         <v>2</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>163</v>
+        <v>172</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J126" s="2">
         <v>6</v>
@@ -5674,19 +5845,19 @@
         <v>102200</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D127" s="19">
         <v>4020642</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G127" s="2">
         <v>2</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J127" s="2">
         <v>7</v>
@@ -5703,19 +5874,22 @@
         <v>102200</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D128" s="19">
         <v>4020648</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G128" s="2">
         <v>2</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>165</v>
+        <v>174</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="J128" s="2">
         <v>8</v>
@@ -5732,19 +5906,19 @@
         <v>102200</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D129" s="19">
         <v>4020643</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G129" s="2">
         <v>2</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J129" s="2">
         <v>9</v>
@@ -5761,19 +5935,22 @@
         <v>102200</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D130" s="19">
         <v>4020649</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G130" s="2">
         <v>2</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>167</v>
+        <v>176</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J130" s="2">
         <v>10</v>
@@ -5790,19 +5967,19 @@
         <v>102200</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D131" s="19">
         <v>4020644</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G131" s="2">
         <v>2</v>
       </c>
       <c r="H131" s="19" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J131" s="2">
         <v>11</v>
@@ -5819,18 +5996,21 @@
         <v>102200</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D132" s="19">
         <v>4020650</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G132" s="2">
         <v>2</v>
       </c>
       <c r="H132" s="19"/>
+      <c r="I132" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="J132" s="2">
         <v>12</v>
       </c>
@@ -5846,19 +6026,22 @@
         <v>102200</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D133" s="19">
         <v>4020653</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G133" s="2">
         <v>2</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>169</v>
+        <v>178</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="J133" s="2">
         <v>13</v>
@@ -5875,19 +6058,19 @@
         <v>102200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D134" s="19">
         <v>4020654</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G134" s="2">
         <v>2</v>
       </c>
       <c r="H134" s="19" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J134" s="2">
         <v>14</v>
@@ -5904,19 +6087,22 @@
         <v>102200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D135" s="19">
         <v>4020655</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G135" s="2">
         <v>2</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>171</v>
+        <v>180</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="J135" s="2">
         <v>15</v>
@@ -5933,19 +6119,19 @@
         <v>102200</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D136" s="19">
         <v>4020656</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G136" s="2">
         <v>2</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J136" s="2">
         <v>16</v>
@@ -5962,19 +6148,22 @@
         <v>102200</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D137" s="19">
         <v>4020657</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G137" s="2">
         <v>2</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>173</v>
+        <v>182</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="J137" s="2">
         <v>17</v>
@@ -5991,19 +6180,19 @@
         <v>102200</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D138" s="19">
         <v>4020658</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G138" s="2">
         <v>2</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J138" s="2">
         <v>18</v>
@@ -6020,19 +6209,22 @@
         <v>102200</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D139" s="19">
         <v>4020651</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G139" s="2">
         <v>2</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>175</v>
+        <v>184</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="J139" s="2">
         <v>19</v>
@@ -6049,13 +6241,13 @@
         <v>102100</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D140" s="32">
         <v>4020002</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F140" s="7">
         <v>1</v>
@@ -6078,20 +6270,20 @@
         <v>102100</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D141" s="32">
         <v>4020003</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F141" s="33"/>
       <c r="G141" s="7">
         <v>2</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J141" s="7">
         <v>1</v>
@@ -6108,18 +6300,21 @@
         <v>102100</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D142" s="32">
         <v>4020645</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G142" s="32">
         <v>2</v>
       </c>
       <c r="H142" s="32"/>
+      <c r="I142" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="J142" s="7">
         <v>2</v>
       </c>
@@ -6141,13 +6336,13 @@
         <v>4020640</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G143" s="7">
         <v>2</v>
       </c>
       <c r="H143" s="32" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J143" s="7">
         <v>3</v>
@@ -6176,7 +6371,10 @@
         <v>2</v>
       </c>
       <c r="H144" s="32" t="s">
-        <v>178</v>
+        <v>187</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="J144" s="7">
         <v>4</v>
@@ -6193,7 +6391,7 @@
         <v>102100</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D145" s="32">
         <v>4020641</v>
@@ -6205,7 +6403,7 @@
         <v>2</v>
       </c>
       <c r="H145" s="32" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="J145" s="7">
         <v>5</v>
@@ -6222,19 +6420,22 @@
         <v>102100</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D146" s="32">
         <v>4020647</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G146" s="32">
         <v>2</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>180</v>
+        <v>189</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="J146" s="7">
         <v>6</v>
@@ -6251,19 +6452,19 @@
         <v>102100</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D147" s="32">
         <v>4020642</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G147" s="7">
         <v>2</v>
       </c>
       <c r="H147" s="32" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J147" s="7">
         <v>7</v>
@@ -6280,19 +6481,22 @@
         <v>102100</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D148" s="32">
         <v>4020648</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G148" s="32">
         <v>2</v>
       </c>
       <c r="H148" s="32" t="s">
-        <v>182</v>
+        <v>191</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="J148" s="7">
         <v>8</v>
@@ -6309,19 +6513,19 @@
         <v>102100</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D149" s="32">
         <v>4020643</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G149" s="7">
         <v>2</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J149" s="7">
         <v>9</v>
@@ -6338,19 +6542,22 @@
         <v>102100</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D150" s="32">
         <v>4020649</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G150" s="32">
         <v>2</v>
       </c>
       <c r="H150" s="32" t="s">
-        <v>184</v>
+        <v>193</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="J150" s="7">
         <v>10</v>
@@ -6367,19 +6574,19 @@
         <v>102100</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D151" s="32">
         <v>4020644</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G151" s="7">
         <v>2</v>
       </c>
       <c r="H151" s="32" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="J151" s="7">
         <v>11</v>
@@ -6396,18 +6603,21 @@
         <v>102100</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D152" s="32">
         <v>4020650</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G152" s="32">
         <v>2</v>
       </c>
       <c r="H152" s="32"/>
+      <c r="I152" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="J152" s="7">
         <v>12</v>
       </c>
@@ -6423,19 +6633,22 @@
         <v>102100</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D153" s="32">
         <v>4020653</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G153" s="32">
         <v>2</v>
       </c>
       <c r="H153" s="32" t="s">
-        <v>186</v>
+        <v>195</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="J153" s="7">
         <v>13</v>
@@ -6452,19 +6665,19 @@
         <v>102100</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D154" s="32">
         <v>4020654</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G154" s="32">
         <v>2</v>
       </c>
       <c r="H154" s="32" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J154" s="7">
         <v>14</v>
@@ -6481,19 +6694,22 @@
         <v>102100</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D155" s="32">
         <v>4020655</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G155" s="32">
         <v>2</v>
       </c>
       <c r="H155" s="32" t="s">
-        <v>188</v>
+        <v>197</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="J155" s="7">
         <v>15</v>
@@ -6510,19 +6726,19 @@
         <v>102100</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D156" s="32">
         <v>4020656</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G156" s="32">
         <v>2</v>
       </c>
       <c r="H156" s="32" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="J156" s="7">
         <v>16</v>
@@ -6539,19 +6755,22 @@
         <v>102100</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D157" s="32">
         <v>4020657</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G157" s="32">
         <v>2</v>
       </c>
       <c r="H157" s="32" t="s">
-        <v>190</v>
+        <v>199</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="J157" s="7">
         <v>17</v>
@@ -6568,19 +6787,19 @@
         <v>102100</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D158" s="32">
         <v>4020658</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G158" s="32">
         <v>2</v>
       </c>
       <c r="H158" s="32" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="J158" s="7">
         <v>18</v>
@@ -6597,19 +6816,22 @@
         <v>102100</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D159" s="32">
         <v>4020651</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G159" s="32">
         <v>2</v>
       </c>
       <c r="H159" s="32" t="s">
-        <v>192</v>
+        <v>201</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="J159" s="7">
         <v>19</v>
@@ -6626,13 +6848,13 @@
         <v>103900</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D160" s="23">
         <v>4020002</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F160" s="3">
         <v>1</v>
@@ -6655,20 +6877,20 @@
         <v>103900</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D161" s="23">
         <v>4020645</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G161" s="23">
         <v>2</v>
       </c>
       <c r="H161" s="23"/>
       <c r="I161" s="3" t="s">
-        <v>193</v>
+        <v>30</v>
       </c>
       <c r="J161" s="3">
         <v>2</v>
@@ -6691,13 +6913,13 @@
         <v>4020640</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G162" s="23">
         <v>2</v>
       </c>
       <c r="H162" s="23" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J162" s="3">
         <v>3</v>
@@ -6726,10 +6948,10 @@
         <v>2</v>
       </c>
       <c r="H163" s="23" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="J163" s="3">
         <v>4</v>
@@ -6746,7 +6968,7 @@
         <v>103900</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D164" s="23">
         <v>4020641</v>
@@ -6758,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="H164" s="23" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J164" s="3">
         <v>5</v>
@@ -6775,20 +6997,20 @@
         <v>103900</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D165" s="23">
         <v>4020003</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F165" s="24"/>
       <c r="G165" s="3">
         <v>2</v>
       </c>
       <c r="H165" s="23" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J165" s="20">
         <v>-1</v>
@@ -6805,22 +7027,22 @@
         <v>103900</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D166" s="23">
         <v>4020647</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G166" s="3">
         <v>2</v>
       </c>
       <c r="H166" s="23" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="J166" s="20">
         <v>-1</v>
@@ -6837,19 +7059,19 @@
         <v>103900</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D167" s="23">
         <v>4020642</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G167" s="23">
         <v>2</v>
       </c>
       <c r="H167" s="23" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J167" s="20">
         <v>-1</v>
@@ -6866,22 +7088,22 @@
         <v>103900</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D168" s="23">
         <v>4020648</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G168" s="3">
         <v>2</v>
       </c>
       <c r="H168" s="23" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="J168" s="20">
         <v>-1</v>
@@ -6898,19 +7120,19 @@
         <v>103900</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D169" s="23">
         <v>4020643</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G169" s="3">
         <v>2</v>
       </c>
       <c r="H169" s="23" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J169" s="20">
         <v>-1</v>
@@ -6927,22 +7149,22 @@
         <v>103900</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D170" s="23">
         <v>4020649</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G170" s="3">
         <v>2</v>
       </c>
       <c r="H170" s="23" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>205</v>
+        <v>49</v>
       </c>
       <c r="J170" s="20">
         <v>-1</v>
@@ -6959,19 +7181,19 @@
         <v>103900</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D171" s="23">
         <v>4020644</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G171" s="23">
         <v>2</v>
       </c>
       <c r="H171" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J171" s="20">
         <v>-1</v>
@@ -6988,19 +7210,19 @@
         <v>103900</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D172" s="23">
         <v>4020650</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G172" s="23">
         <v>2</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="J172" s="3">
         <v>12</v>
@@ -7017,22 +7239,22 @@
         <v>103900</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D173" s="23">
         <v>4020653</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G173" s="23">
         <v>2</v>
       </c>
       <c r="H173" s="23" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="J173" s="20">
         <v>-1</v>
@@ -7049,19 +7271,19 @@
         <v>103900</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D174" s="23">
         <v>4020654</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G174" s="23">
         <v>2</v>
       </c>
       <c r="H174" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J174" s="20">
         <v>-1</v>
@@ -7078,22 +7300,22 @@
         <v>103900</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D175" s="23">
         <v>4020655</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G175" s="23">
         <v>2</v>
       </c>
       <c r="H175" s="23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="J175" s="20">
         <v>-1</v>
@@ -7110,19 +7332,19 @@
         <v>103900</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D176" s="23">
         <v>4020656</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G176" s="3">
         <v>2</v>
       </c>
       <c r="H176" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J176" s="20">
         <v>-1</v>
@@ -7139,20 +7361,20 @@
         <v>103900</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D177" s="23">
         <v>4020657</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G177" s="23"/>
       <c r="H177" s="23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>215</v>
+        <v>88</v>
       </c>
       <c r="J177" s="20">
         <v>-1</v>
@@ -7169,13 +7391,13 @@
         <v>103900</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D178" s="23">
         <v>4020658</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G178" s="23">
         <v>2</v>
@@ -7198,13 +7420,13 @@
         <v>103900</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D179" s="23">
         <v>4020651</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G179" s="3">
         <v>2</v>
@@ -7213,7 +7435,7 @@
         <v>217</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="J179" s="4">
         <v>19</v>
@@ -7230,13 +7452,13 @@
         <v>102000</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D180" s="25">
         <v>4020002</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F180" s="4">
         <v>1</v>
@@ -7259,19 +7481,19 @@
         <v>102000</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D181" s="25">
         <v>4020003</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G181" s="4">
         <v>2</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J181" s="4">
         <v>1</v>
@@ -7288,18 +7510,21 @@
         <v>102000</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D182" s="25">
         <v>4020645</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G182" s="25">
         <v>2</v>
       </c>
       <c r="H182" s="25"/>
+      <c r="I182" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="J182" s="4">
         <v>2</v>
       </c>
@@ -7321,13 +7546,13 @@
         <v>4020640</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G183" s="4">
         <v>2</v>
       </c>
       <c r="H183" s="25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J183" s="4">
         <v>3</v>
@@ -7356,7 +7581,10 @@
         <v>2</v>
       </c>
       <c r="H184" s="25" t="s">
-        <v>221</v>
+        <v>220</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="J184" s="4">
         <v>4</v>
@@ -7373,7 +7601,7 @@
         <v>102000</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D185" s="25">
         <v>4020641</v>
@@ -7385,7 +7613,7 @@
         <v>2</v>
       </c>
       <c r="H185" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J185" s="4">
         <v>5</v>
@@ -7402,19 +7630,22 @@
         <v>102000</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D186" s="25">
         <v>4020647</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G186" s="25">
         <v>2</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="J186" s="4">
         <v>6</v>
@@ -7431,19 +7662,19 @@
         <v>102000</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D187" s="25">
         <v>4020642</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G187" s="4">
         <v>2</v>
       </c>
       <c r="H187" s="25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J187" s="4">
         <v>7</v>
@@ -7460,19 +7691,22 @@
         <v>102000</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D188" s="25">
         <v>4020648</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G188" s="25">
         <v>2</v>
       </c>
       <c r="H188" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="J188" s="4">
         <v>8</v>
@@ -7489,19 +7723,19 @@
         <v>102000</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D189" s="25">
         <v>4020643</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G189" s="4">
         <v>2</v>
       </c>
       <c r="H189" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J189" s="4">
         <v>9</v>
@@ -7518,19 +7752,22 @@
         <v>102000</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D190" s="25">
         <v>4020649</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G190" s="4">
         <v>2</v>
       </c>
       <c r="H190" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="J190" s="4">
         <v>10</v>
@@ -7547,19 +7784,19 @@
         <v>102000</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D191" s="25">
         <v>4020644</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G191" s="4">
         <v>2</v>
       </c>
       <c r="H191" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J191" s="4">
         <v>11</v>
@@ -7576,18 +7813,21 @@
         <v>102000</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D192" s="25">
         <v>4020650</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G192" s="4">
         <v>2</v>
       </c>
       <c r="H192" s="25"/>
+      <c r="I192" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="J192" s="4">
         <v>12</v>
       </c>
@@ -7603,19 +7843,22 @@
         <v>102000</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D193" s="25">
         <v>4020653</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G193" s="4">
         <v>2</v>
       </c>
       <c r="H193" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="J193" s="4">
         <v>13</v>
@@ -7632,19 +7875,19 @@
         <v>102000</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D194" s="25">
         <v>4020654</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G194" s="4">
         <v>2</v>
       </c>
       <c r="H194" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J194" s="4">
         <v>14</v>
@@ -7661,19 +7904,22 @@
         <v>102000</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D195" s="25">
         <v>4020655</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G195" s="4">
         <v>2</v>
       </c>
       <c r="H195" s="25" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="J195" s="4">
         <v>15</v>
@@ -7690,19 +7936,19 @@
         <v>102000</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D196" s="25">
         <v>4020656</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G196" s="4">
         <v>2</v>
       </c>
       <c r="H196" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J196" s="4">
         <v>16</v>
@@ -7719,16 +7965,19 @@
         <v>102000</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D197" s="25">
         <v>4020657</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H197" s="25" t="s">
-        <v>233</v>
+        <v>232</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="J197" s="4">
         <v>17</v>
@@ -7745,19 +7994,19 @@
         <v>102000</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D198" s="25">
         <v>4020658</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G198" s="4">
         <v>2</v>
       </c>
       <c r="H198" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J198" s="4">
         <v>18</v>
@@ -7774,19 +8023,22 @@
         <v>102000</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D199" s="25">
         <v>4020651</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G199" s="4">
         <v>2</v>
       </c>
       <c r="H199" s="25" t="s">
-        <v>235</v>
+        <v>234</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="J199" s="4">
         <v>19</v>
@@ -7803,13 +8055,13 @@
         <v>102700</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D200" s="28">
         <v>4020002</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F200" s="5">
         <v>1</v>
@@ -7832,19 +8084,19 @@
         <v>102700</v>
       </c>
       <c r="C201" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D201" s="28">
         <v>4020645</v>
       </c>
       <c r="E201" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G201" s="5">
+        <v>2</v>
+      </c>
+      <c r="I201" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="G201" s="5">
-        <v>2</v>
-      </c>
-      <c r="I201" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="J201" s="5">
         <v>2</v>
@@ -7867,13 +8119,13 @@
         <v>4020640</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G202" s="5">
         <v>2</v>
       </c>
       <c r="H202" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J202" s="5">
         <v>3</v>
@@ -7902,10 +8154,10 @@
         <v>2</v>
       </c>
       <c r="H203" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I203" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="I203" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="J203" s="5">
         <v>4</v>
@@ -7922,7 +8174,7 @@
         <v>102700</v>
       </c>
       <c r="C204" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D204" s="28">
         <v>4020641</v>
@@ -7934,7 +8186,7 @@
         <v>2</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J204" s="5">
         <v>5</v>
@@ -7951,19 +8203,19 @@
         <v>102700</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D205" s="28">
         <v>4020003</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G205" s="5">
         <v>2</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J205" s="20">
         <v>-1</v>
@@ -7980,22 +8232,22 @@
         <v>102700</v>
       </c>
       <c r="C206" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D206" s="28">
         <v>4020647</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G206" s="5">
         <v>2</v>
       </c>
       <c r="H206" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I206" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="I206" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="J206" s="5">
         <v>6</v>
@@ -8012,19 +8264,19 @@
         <v>102700</v>
       </c>
       <c r="C207" s="35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D207" s="28">
         <v>4020642</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G207" s="5">
         <v>2</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J207" s="5">
         <v>7</v>
@@ -8041,22 +8293,22 @@
         <v>102700</v>
       </c>
       <c r="C208" s="35" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D208" s="28">
         <v>4020648</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G208" s="5">
         <v>2</v>
       </c>
       <c r="H208" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I208" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="I208" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="J208" s="20">
         <v>-1</v>
@@ -8073,19 +8325,19 @@
         <v>102700</v>
       </c>
       <c r="C209" s="35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D209" s="28">
         <v>4020643</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G209" s="5">
         <v>2</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J209" s="20">
         <v>-1</v>
@@ -8102,22 +8354,22 @@
         <v>102700</v>
       </c>
       <c r="C210" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D210" s="28">
         <v>4020649</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G210" s="5">
         <v>2</v>
       </c>
       <c r="H210" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="I210" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="I210" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="J210" s="20">
         <v>-1</v>
@@ -8134,19 +8386,19 @@
         <v>102700</v>
       </c>
       <c r="C211" s="35" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D211" s="28">
         <v>4020644</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G211" s="5">
         <v>2</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J211" s="20">
         <v>-1</v>
@@ -8163,19 +8415,19 @@
         <v>102700</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D212" s="28">
         <v>4020650</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G212" s="5">
         <v>2</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J212" s="5">
         <v>12</v>
@@ -8192,22 +8444,22 @@
         <v>102700</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D213" s="28">
         <v>4020653</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G213" s="5">
         <v>2</v>
       </c>
       <c r="H213" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="I213" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="I213" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="J213" s="5">
         <v>13</v>
@@ -8224,22 +8476,22 @@
         <v>102700</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D214" s="28">
         <v>4020654</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G214" s="5">
         <v>2</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="J214" s="5">
-        <v>14</v>
+        <v>253</v>
+      </c>
+      <c r="J214" s="20">
+        <v>-1</v>
       </c>
       <c r="K214" s="5">
         <v>100</v>
@@ -8253,22 +8505,22 @@
         <v>102700</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D215" s="28">
         <v>4020655</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G215" s="5">
         <v>2</v>
       </c>
       <c r="H215" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="I215" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="I215" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="J215" s="20">
         <v>-1</v>
@@ -8285,19 +8537,19 @@
         <v>102700</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D216" s="28">
         <v>4020656</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G216" s="5">
         <v>2</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J216" s="20">
         <v>-1</v>
@@ -8314,23 +8566,23 @@
         <v>102700</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D217" s="28">
         <v>4020657</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F217" s="35"/>
       <c r="G217" s="5">
         <v>2</v>
       </c>
       <c r="H217" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I217" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="I217" s="5" t="s">
-        <v>259</v>
       </c>
       <c r="J217" s="20">
         <v>-1</v>
@@ -8347,19 +8599,19 @@
         <v>102700</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D218" s="28">
         <v>4020658</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G218" s="5">
         <v>2</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J218" s="20">
         <v>-1</v>
@@ -8376,22 +8628,22 @@
         <v>102700</v>
       </c>
       <c r="C219" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D219" s="28">
         <v>4020651</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G219" s="5">
         <v>2</v>
       </c>
       <c r="H219" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I219" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="I219" s="5" t="s">
-        <v>262</v>
       </c>
       <c r="J219" s="5">
         <v>19</v>
@@ -8408,13 +8660,13 @@
         <v>101500</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D220" s="16">
         <v>4020002</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F220" s="1">
         <v>1</v>
@@ -8437,18 +8689,21 @@
         <v>101500</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D221" s="16">
         <v>4020645</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G221" s="1">
         <v>2</v>
       </c>
       <c r="H221" s="1"/>
+      <c r="I221" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="J221" s="5">
         <v>2</v>
       </c>
@@ -8470,13 +8725,13 @@
         <v>4020640</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G222" s="1">
         <v>2</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J222" s="5">
         <v>3</v>
@@ -8505,7 +8760,10 @@
         <v>2</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="J223" s="5">
         <v>4</v>
@@ -8522,7 +8780,7 @@
         <v>101500</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D224" s="16">
         <v>4020641</v>
@@ -8534,7 +8792,7 @@
         <v>2</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J224" s="5">
         <v>5</v>
@@ -8551,19 +8809,19 @@
         <v>101500</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D225" s="16">
         <v>4020003</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G225" s="1">
         <v>2</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J225" s="20">
         <v>-1</v>
@@ -8580,19 +8838,22 @@
         <v>101500</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D226" s="16">
         <v>4020647</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G226" s="1">
         <v>2</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J226" s="5">
         <v>6</v>
@@ -8609,19 +8870,19 @@
         <v>101500</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D227" s="16">
         <v>4020642</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G227" s="1">
         <v>2</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J227" s="5">
         <v>7</v>
@@ -8638,19 +8899,22 @@
         <v>101500</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D228" s="16">
         <v>4020648</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G228" s="1">
         <v>2</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="J228" s="20">
         <v>-1</v>
@@ -8667,19 +8931,19 @@
         <v>101500</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D229" s="16">
         <v>4020643</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G229" s="1">
         <v>2</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J229" s="20">
         <v>-1</v>
@@ -8696,19 +8960,22 @@
         <v>101500</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D230" s="16">
         <v>4020649</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G230" s="1">
         <v>2</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="J230" s="20">
         <v>-1</v>
@@ -8725,19 +8992,19 @@
         <v>101500</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D231" s="16">
         <v>4020644</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G231" s="1">
         <v>2</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J231" s="20">
         <v>-1</v>
@@ -8754,18 +9021,21 @@
         <v>101500</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D232" s="16">
         <v>4020650</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G232" s="1">
         <v>2</v>
       </c>
       <c r="H232" s="1"/>
+      <c r="I232" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J232" s="5">
         <v>12</v>
       </c>
@@ -8781,19 +9051,22 @@
         <v>101500</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D233" s="16">
         <v>4020653</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G233" s="1">
         <v>2</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="J233" s="5">
         <v>13</v>
@@ -8810,19 +9083,19 @@
         <v>101500</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D234" s="16">
         <v>4020654</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G234" s="1">
         <v>2</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J234" s="5">
         <v>14</v>
@@ -8839,19 +9112,22 @@
         <v>101500</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D235" s="16">
         <v>4020655</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G235" s="1">
         <v>2</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="J235" s="20">
         <v>-1</v>
@@ -8868,19 +9144,19 @@
         <v>101500</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D236" s="16">
         <v>4020656</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G236" s="1">
         <v>2</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J236" s="20">
         <v>-1</v>
@@ -8897,19 +9173,22 @@
         <v>101500</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D237" s="16">
         <v>4020657</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G237" s="1">
         <v>2</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="J237" s="20">
         <v>-1</v>
@@ -8926,19 +9205,19 @@
         <v>101500</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D238" s="16">
         <v>4020658</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G238" s="1">
         <v>2</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J238" s="20">
         <v>-1</v>
@@ -8955,19 +9234,22 @@
         <v>101500</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D239" s="16">
         <v>4020651</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G239" s="1">
         <v>2</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="J239" s="5">
         <v>19</v>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="prop" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="279">
   <si>
     <t>属性id</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>10070018,1</t>
+  </si>
+  <si>
+    <t>初始化</t>
   </si>
   <si>
     <t>10120006,10</t>
@@ -958,7 +961,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -975,6 +978,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1502,16 +1511,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -1520,119 +1526,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1702,6 +1711,9 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1715,6 +1727,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1738,7 +1753,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2052,7 +2073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:L243"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="8" customWidth="1"/>
@@ -3195,91 +3216,82 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" s="3" customFormat="1" spans="1:11">
-      <c r="A40" s="3">
-        <v>10120001</v>
-      </c>
-      <c r="B40" s="3">
-        <v>101200</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="23">
-        <v>4020002</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3">
-        <v>2</v>
-      </c>
-      <c r="J40" s="3">
+    <row r="40" s="2" customFormat="1" spans="1:11">
+      <c r="A40" s="2">
+        <v>10070020</v>
+      </c>
+      <c r="B40" s="2">
+        <v>100700</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="G40" s="19">
+        <v>2</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="J40" s="20">
         <v>-1</v>
       </c>
-      <c r="K40" s="3">
+      <c r="K40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:11">
       <c r="A41" s="3">
-        <v>10120002</v>
+        <v>10120001</v>
       </c>
       <c r="B41" s="3">
         <v>101200</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" s="23">
-        <v>4020003</v>
+        <v>59</v>
+      </c>
+      <c r="D41" s="24">
+        <v>4020002</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F41" s="24"/>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
       <c r="G41" s="3">
         <v>2</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:11">
       <c r="A42" s="3">
-        <v>10120003</v>
+        <v>10120002</v>
       </c>
       <c r="B42" s="3">
         <v>101200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="23">
-        <v>4020645</v>
+        <v>63</v>
+      </c>
+      <c r="D42" s="24">
+        <v>4020003</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="23">
-        <v>2</v>
-      </c>
-      <c r="H42" s="23"/>
-      <c r="I42" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="F42" s="25"/>
+      <c r="G42" s="3">
+        <v>2</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -3287,28 +3299,30 @@
     </row>
     <row r="43" s="3" customFormat="1" spans="1:11">
       <c r="A43" s="3">
-        <v>10120004</v>
+        <v>10120003</v>
       </c>
       <c r="B43" s="3">
         <v>101200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43" s="23">
-        <v>4020640</v>
+        <v>27</v>
+      </c>
+      <c r="D43" s="24">
+        <v>4020645</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G43" s="3">
-        <v>2</v>
-      </c>
-      <c r="H43" s="23" t="s">
-        <v>92</v>
+      <c r="F43" s="25"/>
+      <c r="G43" s="24">
+        <v>2</v>
+      </c>
+      <c r="H43" s="24"/>
+      <c r="I43" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -3316,31 +3330,28 @@
     </row>
     <row r="44" s="3" customFormat="1" spans="1:11">
       <c r="A44" s="3">
-        <v>10120005</v>
+        <v>10120004</v>
       </c>
       <c r="B44" s="3">
         <v>101200</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" s="23">
-        <v>4020646</v>
+        <v>31</v>
+      </c>
+      <c r="D44" s="24">
+        <v>4020640</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="23">
-        <v>2</v>
-      </c>
-      <c r="H44" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2</v>
+      </c>
+      <c r="H44" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
@@ -3348,28 +3359,31 @@
     </row>
     <row r="45" s="3" customFormat="1" spans="1:11">
       <c r="A45" s="3">
-        <v>10120006</v>
+        <v>10120005</v>
       </c>
       <c r="B45" s="3">
         <v>101200</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="23">
-        <v>4020641</v>
+        <v>33</v>
+      </c>
+      <c r="D45" s="24">
+        <v>4020646</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G45" s="3">
-        <v>2</v>
-      </c>
-      <c r="H45" s="3" t="s">
+      <c r="G45" s="24">
+        <v>2</v>
+      </c>
+      <c r="H45" s="24" t="s">
         <v>94</v>
       </c>
+      <c r="I45" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -3377,31 +3391,28 @@
     </row>
     <row r="46" s="3" customFormat="1" spans="1:11">
       <c r="A46" s="3">
-        <v>10120007</v>
+        <v>10120006</v>
       </c>
       <c r="B46" s="3">
         <v>101200</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="23">
-        <v>4020647</v>
+        <v>37</v>
+      </c>
+      <c r="D46" s="24">
+        <v>4020641</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" s="23">
-        <v>2</v>
-      </c>
-      <c r="H46" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46" s="3">
         <v>100</v>
@@ -3409,28 +3420,31 @@
     </row>
     <row r="47" s="3" customFormat="1" spans="1:11">
       <c r="A47" s="3">
-        <v>10120008</v>
+        <v>10120007</v>
       </c>
       <c r="B47" s="3">
         <v>101200</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="23">
-        <v>4020642</v>
+        <v>39</v>
+      </c>
+      <c r="D47" s="24">
+        <v>4020647</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G47" s="3">
-        <v>2</v>
-      </c>
-      <c r="H47" s="23" t="s">
+      <c r="G47" s="24">
+        <v>2</v>
+      </c>
+      <c r="H47" s="24" t="s">
         <v>96</v>
       </c>
+      <c r="I47" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="J47" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -3438,31 +3452,28 @@
     </row>
     <row r="48" s="3" customFormat="1" spans="1:11">
       <c r="A48" s="3">
-        <v>10120009</v>
+        <v>10120008</v>
       </c>
       <c r="B48" s="3">
         <v>101200</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" s="23">
-        <v>4020648</v>
+        <v>42</v>
+      </c>
+      <c r="D48" s="24">
+        <v>4020642</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G48" s="23">
-        <v>2</v>
-      </c>
-      <c r="H48" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2</v>
+      </c>
+      <c r="H48" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="J48" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -3470,28 +3481,31 @@
     </row>
     <row r="49" s="3" customFormat="1" spans="1:12">
       <c r="A49" s="3">
-        <v>10120010</v>
+        <v>10120009</v>
       </c>
       <c r="B49" s="3">
         <v>101200</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D49" s="23">
-        <v>4020643</v>
+        <v>43</v>
+      </c>
+      <c r="D49" s="24">
+        <v>4020648</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G49" s="3">
-        <v>2</v>
-      </c>
-      <c r="H49" s="23" t="s">
+      <c r="G49" s="24">
+        <v>2</v>
+      </c>
+      <c r="H49" s="24" t="s">
         <v>98</v>
       </c>
+      <c r="I49" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="J49" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -3499,31 +3513,28 @@
     </row>
     <row r="50" s="3" customFormat="1" spans="1:12">
       <c r="A50" s="3">
-        <v>10120011</v>
+        <v>10120010</v>
       </c>
       <c r="B50" s="3">
         <v>101200</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D50" s="23">
-        <v>4020649</v>
+        <v>46</v>
+      </c>
+      <c r="D50" s="24">
+        <v>4020643</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G50" s="23">
-        <v>2</v>
-      </c>
-      <c r="H50" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2</v>
+      </c>
+      <c r="H50" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="J50" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K50" s="3">
         <v>100</v>
@@ -3531,28 +3542,31 @@
     </row>
     <row r="51" s="3" customFormat="1" spans="1:12">
       <c r="A51" s="3">
-        <v>10120012</v>
+        <v>10120011</v>
       </c>
       <c r="B51" s="3">
         <v>101200</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="23">
-        <v>4020644</v>
+        <v>47</v>
+      </c>
+      <c r="D51" s="24">
+        <v>4020649</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G51" s="3">
-        <v>2</v>
-      </c>
-      <c r="H51" s="23" t="s">
-        <v>100</v>
+      <c r="G51" s="24">
+        <v>2</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J51" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K51" s="3">
         <v>100</v>
@@ -3560,29 +3574,28 @@
     </row>
     <row r="52" s="3" customFormat="1" spans="1:12">
       <c r="A52" s="3">
-        <v>10120013</v>
+        <v>10120012</v>
       </c>
       <c r="B52" s="3">
         <v>101200</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="24">
+        <v>4020644</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2</v>
+      </c>
+      <c r="H52" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D52" s="23">
-        <v>4020659</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G52" s="23">
-        <v>2</v>
-      </c>
-      <c r="H52" s="23"/>
-      <c r="I52" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="J52" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -3590,31 +3603,29 @@
     </row>
     <row r="53" s="3" customFormat="1" spans="1:12">
       <c r="A53" s="3">
-        <v>10120014</v>
+        <v>10120013</v>
       </c>
       <c r="B53" s="3">
         <v>101200</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" s="24">
+        <v>4020659</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="23">
-        <v>4020660</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G53" s="3">
-        <v>2</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>104</v>
-      </c>
+      <c r="G53" s="24">
+        <v>2</v>
+      </c>
+      <c r="H53" s="24"/>
       <c r="I53" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J53" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K53" s="3">
         <v>100</v>
@@ -3622,28 +3633,31 @@
     </row>
     <row r="54" s="3" customFormat="1" spans="1:12">
       <c r="A54" s="3">
-        <v>10120015</v>
+        <v>10120014</v>
       </c>
       <c r="B54" s="3">
         <v>101200</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="24">
+        <v>4020660</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="3">
+        <v>2</v>
+      </c>
+      <c r="H54" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="23">
-        <v>4020661</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G54" s="23">
-        <v>2</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>106</v>
+      <c r="I54" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="J54" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K54" s="3">
         <v>100</v>
@@ -3651,31 +3665,28 @@
     </row>
     <row r="55" s="3" customFormat="1" spans="1:12">
       <c r="A55" s="3">
-        <v>10120016</v>
+        <v>10120015</v>
       </c>
       <c r="B55" s="3">
         <v>101200</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="24">
+        <v>4020661</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G55" s="24">
+        <v>2</v>
+      </c>
+      <c r="H55" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="23">
-        <v>4020662</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G55" s="3">
-        <v>2</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J55" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K55" s="3">
         <v>100</v>
@@ -3683,28 +3694,31 @@
     </row>
     <row r="56" s="3" customFormat="1" spans="1:12">
       <c r="A56" s="3">
-        <v>10120017</v>
+        <v>10120016</v>
       </c>
       <c r="B56" s="3">
         <v>101200</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D56" s="24">
+        <v>4020662</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G56" s="3">
+        <v>2</v>
+      </c>
+      <c r="H56" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="23">
-        <v>4020663</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G56" s="23">
-        <v>2</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>110</v>
+      <c r="I56" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="J56" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K56" s="3">
         <v>100</v>
@@ -3712,31 +3726,28 @@
     </row>
     <row r="57" s="3" customFormat="1" spans="1:12">
       <c r="A57" s="3">
-        <v>10120018</v>
+        <v>10120017</v>
       </c>
       <c r="B57" s="3">
         <v>101200</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="24">
+        <v>4020663</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G57" s="24">
+        <v>2</v>
+      </c>
+      <c r="H57" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="23">
-        <v>4020664</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="J57" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3744,28 +3755,31 @@
     </row>
     <row r="58" s="3" customFormat="1" spans="1:12">
       <c r="A58" s="3">
-        <v>10120019</v>
+        <v>10120018</v>
       </c>
       <c r="B58" s="3">
         <v>101200</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" s="24">
+        <v>4020664</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2</v>
+      </c>
+      <c r="H58" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="23">
-        <v>4020665</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G58" s="23">
-        <v>2</v>
-      </c>
-      <c r="H58" s="23" t="s">
-        <v>114</v>
+      <c r="I58" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="J58" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -3773,123 +3787,122 @@
     </row>
     <row r="59" s="3" customFormat="1" spans="1:12">
       <c r="A59" s="3">
-        <v>10120020</v>
+        <v>10120019</v>
       </c>
       <c r="B59" s="3">
         <v>101200</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="24">
+        <v>4020665</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" s="24">
+        <v>2</v>
+      </c>
+      <c r="H59" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="J59" s="3">
+        <v>18</v>
+      </c>
+      <c r="K59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:12">
+      <c r="A60" s="3">
+        <v>10120020</v>
+      </c>
+      <c r="B60" s="3">
+        <v>101200</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D59" s="23">
+      <c r="D60" s="24">
         <v>4020651</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G59" s="3">
-        <v>2</v>
-      </c>
-      <c r="H59" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="I59" s="3" t="s">
+      <c r="G60" s="3">
+        <v>2</v>
+      </c>
+      <c r="H60" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="J59" s="3">
+      <c r="I60" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J60" s="3">
         <v>19</v>
       </c>
-      <c r="K59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" s="4" customFormat="1" spans="1:12">
-      <c r="A60" s="4">
-        <v>10180001</v>
-      </c>
-      <c r="B60" s="4">
-        <v>101800</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" s="25">
-        <v>4020002</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="4">
-        <v>1</v>
-      </c>
-      <c r="G60" s="4">
-        <v>2</v>
-      </c>
-      <c r="J60" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K60" s="4">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>117</v>
+      <c r="K60" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="61" s="4" customFormat="1" spans="1:12">
       <c r="A61" s="4">
-        <v>10180002</v>
+        <v>10180001</v>
       </c>
       <c r="B61" s="4">
         <v>101800</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="25">
-        <v>4020003</v>
+        <v>59</v>
+      </c>
+      <c r="D61" s="26">
+        <v>4020002</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F61" s="26"/>
+      <c r="F61" s="4">
+        <v>1</v>
+      </c>
       <c r="G61" s="4">
         <v>2</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="J61" s="20">
         <v>-1</v>
       </c>
       <c r="K61" s="4">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="62" s="4" customFormat="1" spans="1:12">
       <c r="A62" s="4">
-        <v>10180003</v>
+        <v>10180002</v>
       </c>
       <c r="B62" s="4">
         <v>101800</v>
       </c>
-      <c r="C62" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="25">
-        <v>4020645</v>
+      <c r="C62" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" s="26">
+        <v>4020003</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G62" s="25">
-        <v>2</v>
-      </c>
-      <c r="H62" s="25"/>
-      <c r="I62" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3</v>
+        <v>25</v>
+      </c>
+      <c r="F62" s="27"/>
+      <c r="G62" s="4">
+        <v>2</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J62" s="20">
+        <v>-1</v>
       </c>
       <c r="K62" s="4">
         <v>100</v>
@@ -3897,28 +3910,29 @@
     </row>
     <row r="63" s="4" customFormat="1" spans="1:12">
       <c r="A63" s="4">
-        <v>10180004</v>
+        <v>10180003</v>
       </c>
       <c r="B63" s="4">
         <v>101800</v>
       </c>
-      <c r="C63" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D63" s="25">
-        <v>4020640</v>
+      <c r="C63" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="26">
+        <v>4020645</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G63" s="4">
-        <v>2</v>
-      </c>
-      <c r="H63" s="25" t="s">
-        <v>119</v>
+      <c r="G63" s="26">
+        <v>2</v>
+      </c>
+      <c r="H63" s="26"/>
+      <c r="I63" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" s="4">
         <v>100</v>
@@ -3926,31 +3940,28 @@
     </row>
     <row r="64" s="4" customFormat="1" spans="1:12">
       <c r="A64" s="4">
-        <v>10180005</v>
+        <v>10180004</v>
       </c>
       <c r="B64" s="4">
         <v>101800</v>
       </c>
-      <c r="C64" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="25">
-        <v>4020646</v>
+      <c r="C64" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" s="26">
+        <v>4020640</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G64" s="25">
-        <v>2</v>
-      </c>
-      <c r="H64" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="4">
+        <v>2</v>
+      </c>
+      <c r="H64" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="J64" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" s="4">
         <v>100</v>
@@ -3958,28 +3969,31 @@
     </row>
     <row r="65" s="4" customFormat="1" spans="1:11">
       <c r="A65" s="4">
-        <v>10180006</v>
+        <v>10180005</v>
       </c>
       <c r="B65" s="4">
         <v>101800</v>
       </c>
-      <c r="C65" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" s="25">
-        <v>4020641</v>
+      <c r="C65" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="26">
+        <v>4020646</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G65" s="4">
-        <v>2</v>
-      </c>
-      <c r="H65" s="25" t="s">
+      <c r="G65" s="26">
+        <v>2</v>
+      </c>
+      <c r="H65" s="26" t="s">
         <v>121</v>
       </c>
+      <c r="I65" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" s="4">
         <v>100</v>
@@ -3987,31 +4001,28 @@
     </row>
     <row r="66" s="4" customFormat="1" spans="1:11">
       <c r="A66" s="4">
-        <v>10180007</v>
+        <v>10180006</v>
       </c>
       <c r="B66" s="4">
         <v>101800</v>
       </c>
-      <c r="C66" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D66" s="25">
-        <v>4020647</v>
+      <c r="C66" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="26">
+        <v>4020641</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G66" s="25">
-        <v>2</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="G66" s="4">
+        <v>2</v>
+      </c>
+      <c r="H66" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="J66" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="4">
         <v>100</v>
@@ -4019,28 +4030,31 @@
     </row>
     <row r="67" s="4" customFormat="1" spans="1:11">
       <c r="A67" s="4">
-        <v>10180008</v>
+        <v>10180007</v>
       </c>
       <c r="B67" s="4">
         <v>101800</v>
       </c>
-      <c r="C67" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D67" s="25">
-        <v>4020642</v>
+      <c r="C67" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" s="26">
+        <v>4020647</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G67" s="26">
         <v>2</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="J67" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K67" s="4">
         <v>100</v>
@@ -4048,31 +4062,28 @@
     </row>
     <row r="68" s="4" customFormat="1" spans="1:11">
       <c r="A68" s="4">
-        <v>10180009</v>
+        <v>10180008</v>
       </c>
       <c r="B68" s="4">
         <v>101800</v>
       </c>
-      <c r="C68" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" s="25">
-        <v>4020648</v>
+      <c r="C68" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68" s="26">
+        <v>4020642</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="25">
+        <v>40</v>
+      </c>
+      <c r="G68" s="4">
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="J68" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K68" s="4">
         <v>100</v>
@@ -4080,28 +4091,31 @@
     </row>
     <row r="69" s="4" customFormat="1" spans="1:11">
       <c r="A69" s="4">
-        <v>10180010</v>
+        <v>10180009</v>
       </c>
       <c r="B69" s="4">
         <v>101800</v>
       </c>
-      <c r="C69" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D69" s="25">
-        <v>4020643</v>
+      <c r="C69" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D69" s="26">
+        <v>4020648</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G69" s="4">
+      <c r="G69" s="26">
         <v>2</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="I69" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="J69" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K69" s="4">
         <v>100</v>
@@ -4109,31 +4123,28 @@
     </row>
     <row r="70" s="4" customFormat="1" spans="1:11">
       <c r="A70" s="4">
-        <v>10180011</v>
+        <v>10180010</v>
       </c>
       <c r="B70" s="4">
         <v>101800</v>
       </c>
-      <c r="C70" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D70" s="25">
-        <v>4020649</v>
+      <c r="C70" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="26">
+        <v>4020643</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G70" s="25">
+        <v>44</v>
+      </c>
+      <c r="G70" s="4">
         <v>2</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J70" s="20">
-        <v>-1</v>
+      <c r="J70" s="3">
+        <v>10</v>
       </c>
       <c r="K70" s="4">
         <v>100</v>
@@ -4141,26 +4152,29 @@
     </row>
     <row r="71" s="4" customFormat="1" spans="1:11">
       <c r="A71" s="4">
-        <v>10180012</v>
+        <v>10180011</v>
       </c>
       <c r="B71" s="4">
         <v>101800</v>
       </c>
-      <c r="C71" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="D71" s="25">
-        <v>4020644</v>
+      <c r="C71" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D71" s="26">
+        <v>4020649</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G71" s="4">
+      <c r="G71" s="26">
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="I71" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="J71" s="20">
         <v>-1</v>
       </c>
@@ -4170,28 +4184,28 @@
     </row>
     <row r="72" s="4" customFormat="1" spans="1:11">
       <c r="A72" s="4">
-        <v>10180013</v>
+        <v>10180012</v>
       </c>
       <c r="B72" s="4">
         <v>101800</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D72" s="25">
-        <v>4020650</v>
+      <c r="C72" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D72" s="26">
+        <v>4020644</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G72" s="25">
-        <v>2</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="J72" s="3">
-        <v>12</v>
+        <v>48</v>
+      </c>
+      <c r="G72" s="4">
+        <v>2</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J72" s="20">
+        <v>-1</v>
       </c>
       <c r="K72" s="4">
         <v>100</v>
@@ -4199,31 +4213,28 @@
     </row>
     <row r="73" s="4" customFormat="1" spans="1:11">
       <c r="A73" s="4">
-        <v>10180014</v>
+        <v>10180013</v>
       </c>
       <c r="B73" s="4">
         <v>101800</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D73" s="25">
-        <v>4020653</v>
+        <v>71</v>
+      </c>
+      <c r="D73" s="26">
+        <v>4020650</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G73" s="4">
-        <v>2</v>
-      </c>
-      <c r="H73" s="25" t="s">
-        <v>127</v>
+      <c r="G73" s="26">
+        <v>2</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J73" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K73" s="4">
         <v>100</v>
@@ -4231,28 +4242,31 @@
     </row>
     <row r="74" s="4" customFormat="1" spans="1:11">
       <c r="A74" s="4">
-        <v>10180015</v>
+        <v>10180014</v>
       </c>
       <c r="B74" s="4">
         <v>101800</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D74" s="25">
-        <v>4020654</v>
+        <v>74</v>
+      </c>
+      <c r="D74" s="26">
+        <v>4020653</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G74" s="25">
-        <v>2</v>
-      </c>
-      <c r="H74" s="25" t="s">
+      <c r="G74" s="4">
+        <v>2</v>
+      </c>
+      <c r="H74" s="26" t="s">
         <v>128</v>
       </c>
+      <c r="I74" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="J74" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K74" s="4">
         <v>100</v>
@@ -4260,31 +4274,28 @@
     </row>
     <row r="75" s="4" customFormat="1" spans="1:11">
       <c r="A75" s="4">
-        <v>10180016</v>
+        <v>10180015</v>
       </c>
       <c r="B75" s="4">
         <v>101800</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D75" s="25">
-        <v>4020655</v>
+        <v>77</v>
+      </c>
+      <c r="D75" s="26">
+        <v>4020654</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G75" s="4">
-        <v>2</v>
-      </c>
-      <c r="H75" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G75" s="26">
+        <v>2</v>
+      </c>
+      <c r="H75" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="J75" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K75" s="4">
         <v>100</v>
@@ -4292,28 +4303,31 @@
     </row>
     <row r="76" s="4" customFormat="1" spans="1:11">
       <c r="A76" s="4">
-        <v>10180017</v>
+        <v>10180016</v>
       </c>
       <c r="B76" s="4">
         <v>101800</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D76" s="25">
-        <v>4020656</v>
+        <v>79</v>
+      </c>
+      <c r="D76" s="26">
+        <v>4020655</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G76" s="25">
-        <v>2</v>
-      </c>
-      <c r="H76" s="25" t="s">
+      <c r="G76" s="4">
+        <v>2</v>
+      </c>
+      <c r="H76" s="26" t="s">
         <v>130</v>
       </c>
+      <c r="I76" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="J76" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K76" s="4">
         <v>100</v>
@@ -4321,31 +4335,28 @@
     </row>
     <row r="77" s="4" customFormat="1" spans="1:11">
       <c r="A77" s="4">
-        <v>10180018</v>
+        <v>10180017</v>
       </c>
       <c r="B77" s="4">
         <v>101800</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D77" s="25">
-        <v>4020657</v>
+        <v>83</v>
+      </c>
+      <c r="D77" s="26">
+        <v>4020656</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G77" s="4">
-        <v>2</v>
-      </c>
-      <c r="H77" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="G77" s="26">
+        <v>2</v>
+      </c>
+      <c r="H77" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J77" s="20">
-        <v>-1</v>
+      <c r="J77" s="3">
+        <v>16</v>
       </c>
       <c r="K77" s="4">
         <v>100</v>
@@ -4353,25 +4364,28 @@
     </row>
     <row r="78" s="4" customFormat="1" spans="1:11">
       <c r="A78" s="4">
-        <v>10180019</v>
+        <v>10180018</v>
       </c>
       <c r="B78" s="4">
         <v>101800</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" s="25">
-        <v>4020658</v>
+        <v>85</v>
+      </c>
+      <c r="D78" s="26">
+        <v>4020657</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G78" s="25">
-        <v>2</v>
-      </c>
-      <c r="H78" s="25" t="s">
+      <c r="G78" s="4">
+        <v>2</v>
+      </c>
+      <c r="H78" s="26" t="s">
         <v>132</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="J78" s="20">
         <v>-1</v>
@@ -4382,149 +4396,141 @@
     </row>
     <row r="79" s="4" customFormat="1" spans="1:11">
       <c r="A79" s="4">
-        <v>10180020</v>
+        <v>10180019</v>
       </c>
       <c r="B79" s="4">
         <v>101800</v>
       </c>
       <c r="C79" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="26">
+        <v>4020658</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G79" s="26">
+        <v>2</v>
+      </c>
+      <c r="H79" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="J79" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K79" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" s="4" customFormat="1" spans="1:11">
+      <c r="A80" s="4">
+        <v>10180020</v>
+      </c>
+      <c r="B80" s="4">
+        <v>101800</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D79" s="25">
+      <c r="D80" s="26">
         <v>4020651</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G79" s="4">
-        <v>2</v>
-      </c>
-      <c r="H79" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J79" s="4">
+      <c r="G80" s="4">
+        <v>2</v>
+      </c>
+      <c r="H80" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J80" s="4">
         <v>19</v>
       </c>
-      <c r="K79" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" s="5" customFormat="1" spans="1:11">
-      <c r="A80" s="5">
-        <v>10250001</v>
-      </c>
-      <c r="B80" s="5">
-        <v>102500</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D80" s="28">
-        <v>4020002</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" s="5">
-        <v>1</v>
-      </c>
-      <c r="G80" s="5">
-        <v>2</v>
-      </c>
-      <c r="J80" s="5">
+      <c r="K80" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" s="4" customFormat="1" spans="1:11">
+      <c r="A81" s="4">
+        <v>10180021</v>
+      </c>
+      <c r="B81" s="4">
+        <v>101800</v>
+      </c>
+      <c r="C81" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="26"/>
+      <c r="G81" s="4">
+        <v>2</v>
+      </c>
+      <c r="H81" s="26"/>
+      <c r="J81" s="20">
         <v>-1</v>
       </c>
-      <c r="K80" s="5">
+      <c r="K81" s="4">
         <v>0</v>
-      </c>
-    </row>
-    <row r="81" s="5" customFormat="1" spans="1:11">
-      <c r="A81" s="5">
-        <v>10250002</v>
-      </c>
-      <c r="B81" s="5">
-        <v>102500</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D81" s="28">
-        <v>4020003</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" s="29"/>
-      <c r="G81" s="5">
-        <v>2</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J81" s="5">
-        <v>1</v>
-      </c>
-      <c r="K81" s="5">
-        <v>100</v>
       </c>
     </row>
     <row r="82" s="5" customFormat="1" spans="1:11">
       <c r="A82" s="5">
-        <v>10250003</v>
+        <v>10250001</v>
       </c>
       <c r="B82" s="5">
         <v>102500</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D82" s="28">
-        <v>4020645</v>
+        <v>59</v>
+      </c>
+      <c r="D82" s="30">
+        <v>4020002</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G82" s="28">
-        <v>2</v>
-      </c>
-      <c r="H82" s="28"/>
-      <c r="I82" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1</v>
+      </c>
+      <c r="G82" s="5">
+        <v>2</v>
       </c>
       <c r="J82" s="5">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K82" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" s="5" customFormat="1" spans="1:11">
       <c r="A83" s="5">
-        <v>10250004</v>
+        <v>10250002</v>
       </c>
       <c r="B83" s="5">
         <v>102500</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D83" s="28">
-        <v>4020640</v>
+        <v>63</v>
+      </c>
+      <c r="D83" s="30">
+        <v>4020003</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>28</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F83" s="31"/>
       <c r="G83" s="5">
         <v>2</v>
       </c>
-      <c r="H83" s="28" t="s">
+      <c r="H83" s="5" t="s">
         <v>135</v>
       </c>
       <c r="J83" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K83" s="5">
         <v>100</v>
@@ -4532,31 +4538,29 @@
     </row>
     <row r="84" s="5" customFormat="1" spans="1:11">
       <c r="A84" s="5">
-        <v>10250005</v>
+        <v>10250003</v>
       </c>
       <c r="B84" s="5">
         <v>102500</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D84" s="28">
-        <v>4020646</v>
+        <v>27</v>
+      </c>
+      <c r="D84" s="30">
+        <v>4020645</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G84" s="28">
-        <v>2</v>
-      </c>
-      <c r="H84" s="28" t="s">
-        <v>136</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G84" s="30">
+        <v>2</v>
+      </c>
+      <c r="H84" s="30"/>
       <c r="I84" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J84" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K84" s="5">
         <v>100</v>
@@ -4564,28 +4568,28 @@
     </row>
     <row r="85" s="5" customFormat="1" spans="1:11">
       <c r="A85" s="5">
-        <v>10250006</v>
+        <v>10250004</v>
       </c>
       <c r="B85" s="5">
         <v>102500</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D85" s="28">
-        <v>4020641</v>
+        <v>31</v>
+      </c>
+      <c r="D85" s="30">
+        <v>4020640</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G85" s="5">
         <v>2</v>
       </c>
-      <c r="H85" s="28" t="s">
-        <v>137</v>
+      <c r="H85" s="30" t="s">
+        <v>136</v>
       </c>
       <c r="J85" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K85" s="5">
         <v>100</v>
@@ -4593,31 +4597,31 @@
     </row>
     <row r="86" s="5" customFormat="1" spans="1:11">
       <c r="A86" s="5">
-        <v>10250007</v>
+        <v>10250005</v>
       </c>
       <c r="B86" s="5">
         <v>102500</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D86" s="28">
-        <v>4020647</v>
+        <v>33</v>
+      </c>
+      <c r="D86" s="30">
+        <v>4020646</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G86" s="28">
-        <v>2</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>138</v>
+        <v>34</v>
+      </c>
+      <c r="G86" s="30">
+        <v>2</v>
+      </c>
+      <c r="H86" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J86" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K86" s="5">
         <v>100</v>
@@ -4625,28 +4629,28 @@
     </row>
     <row r="87" s="5" customFormat="1" spans="1:11">
       <c r="A87" s="5">
-        <v>10250008</v>
+        <v>10250006</v>
       </c>
       <c r="B87" s="5">
         <v>102500</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D87" s="28">
-        <v>4020642</v>
+        <v>37</v>
+      </c>
+      <c r="D87" s="30">
+        <v>4020641</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G87" s="5">
         <v>2</v>
       </c>
-      <c r="H87" s="28" t="s">
-        <v>139</v>
+      <c r="H87" s="30" t="s">
+        <v>138</v>
       </c>
       <c r="J87" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K87" s="5">
         <v>100</v>
@@ -4654,31 +4658,31 @@
     </row>
     <row r="88" s="5" customFormat="1" spans="1:11">
       <c r="A88" s="5">
-        <v>10250009</v>
+        <v>10250007</v>
       </c>
       <c r="B88" s="5">
         <v>102500</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" s="28">
-        <v>4020648</v>
+        <v>39</v>
+      </c>
+      <c r="D88" s="30">
+        <v>4020647</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="28">
-        <v>2</v>
-      </c>
-      <c r="H88" s="28" t="s">
-        <v>140</v>
+        <v>40</v>
+      </c>
+      <c r="G88" s="30">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J88" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K88" s="5">
         <v>100</v>
@@ -4686,28 +4690,28 @@
     </row>
     <row r="89" s="5" customFormat="1" spans="1:11">
       <c r="A89" s="5">
-        <v>10250010</v>
+        <v>10250008</v>
       </c>
       <c r="B89" s="5">
         <v>102500</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D89" s="28">
-        <v>4020643</v>
+        <v>42</v>
+      </c>
+      <c r="D89" s="30">
+        <v>4020642</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G89" s="28">
-        <v>2</v>
-      </c>
-      <c r="H89" s="28" t="s">
-        <v>141</v>
+        <v>40</v>
+      </c>
+      <c r="G89" s="5">
+        <v>2</v>
+      </c>
+      <c r="H89" s="30" t="s">
+        <v>140</v>
       </c>
       <c r="J89" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K89" s="5">
         <v>100</v>
@@ -4715,31 +4719,31 @@
     </row>
     <row r="90" s="5" customFormat="1" spans="1:11">
       <c r="A90" s="5">
-        <v>10250011</v>
+        <v>10250009</v>
       </c>
       <c r="B90" s="5">
         <v>102500</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D90" s="28">
-        <v>4020649</v>
+        <v>43</v>
+      </c>
+      <c r="D90" s="30">
+        <v>4020648</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G90" s="28">
-        <v>2</v>
-      </c>
-      <c r="H90" s="28" t="s">
-        <v>142</v>
+        <v>44</v>
+      </c>
+      <c r="G90" s="30">
+        <v>2</v>
+      </c>
+      <c r="H90" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J90" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K90" s="5">
         <v>100</v>
@@ -4747,28 +4751,28 @@
     </row>
     <row r="91" s="5" customFormat="1" spans="1:11">
       <c r="A91" s="5">
-        <v>10250012</v>
+        <v>10250010</v>
       </c>
       <c r="B91" s="5">
         <v>102500</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D91" s="28">
-        <v>4020644</v>
+        <v>46</v>
+      </c>
+      <c r="D91" s="30">
+        <v>4020643</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G91" s="28">
-        <v>2</v>
-      </c>
-      <c r="H91" s="28" t="s">
-        <v>143</v>
+        <v>44</v>
+      </c>
+      <c r="G91" s="30">
+        <v>2</v>
+      </c>
+      <c r="H91" s="30" t="s">
+        <v>142</v>
       </c>
       <c r="J91" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K91" s="5">
         <v>100</v>
@@ -4776,29 +4780,31 @@
     </row>
     <row r="92" s="5" customFormat="1" spans="1:11">
       <c r="A92" s="5">
-        <v>10250013</v>
+        <v>10250011</v>
       </c>
       <c r="B92" s="5">
         <v>102500</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D92" s="28">
-        <v>4020650</v>
+        <v>47</v>
+      </c>
+      <c r="D92" s="30">
+        <v>4020649</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G92" s="28">
-        <v>2</v>
-      </c>
-      <c r="H92" s="28"/>
+        <v>48</v>
+      </c>
+      <c r="G92" s="30">
+        <v>2</v>
+      </c>
+      <c r="H92" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="I92" s="5" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="J92" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K92" s="5">
         <v>100</v>
@@ -4806,31 +4812,28 @@
     </row>
     <row r="93" s="5" customFormat="1" spans="1:11">
       <c r="A93" s="5">
-        <v>10250014</v>
+        <v>10250012</v>
       </c>
       <c r="B93" s="5">
         <v>102500</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D93" s="28">
-        <v>4020653</v>
+        <v>50</v>
+      </c>
+      <c r="D93" s="30">
+        <v>4020644</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G93" s="28">
-        <v>2</v>
-      </c>
-      <c r="H93" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G93" s="30">
+        <v>2</v>
+      </c>
+      <c r="H93" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="I93" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="J93" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K93" s="5">
         <v>100</v>
@@ -4838,28 +4841,29 @@
     </row>
     <row r="94" s="5" customFormat="1" spans="1:11">
       <c r="A94" s="5">
-        <v>10250015</v>
+        <v>10250013</v>
       </c>
       <c r="B94" s="5">
         <v>102500</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D94" s="28">
-        <v>4020654</v>
+        <v>71</v>
+      </c>
+      <c r="D94" s="30">
+        <v>4020650</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G94" s="28">
-        <v>2</v>
-      </c>
-      <c r="H94" s="28" t="s">
-        <v>145</v>
+      <c r="G94" s="30">
+        <v>2</v>
+      </c>
+      <c r="H94" s="30"/>
+      <c r="I94" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="J94" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K94" s="5">
         <v>100</v>
@@ -4867,31 +4871,31 @@
     </row>
     <row r="95" s="5" customFormat="1" spans="1:11">
       <c r="A95" s="5">
-        <v>10250016</v>
+        <v>10250014</v>
       </c>
       <c r="B95" s="5">
         <v>102500</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D95" s="28">
-        <v>4020655</v>
+        <v>74</v>
+      </c>
+      <c r="D95" s="30">
+        <v>4020653</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G95" s="28">
-        <v>2</v>
-      </c>
-      <c r="H95" s="28" t="s">
-        <v>146</v>
+        <v>72</v>
+      </c>
+      <c r="G95" s="30">
+        <v>2</v>
+      </c>
+      <c r="H95" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J95" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K95" s="5">
         <v>100</v>
@@ -4899,28 +4903,28 @@
     </row>
     <row r="96" s="5" customFormat="1" spans="1:11">
       <c r="A96" s="5">
-        <v>10250017</v>
+        <v>10250015</v>
       </c>
       <c r="B96" s="5">
         <v>102500</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D96" s="28">
-        <v>4020656</v>
+        <v>77</v>
+      </c>
+      <c r="D96" s="30">
+        <v>4020654</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G96" s="28">
-        <v>2</v>
-      </c>
-      <c r="H96" s="28" t="s">
-        <v>147</v>
+        <v>72</v>
+      </c>
+      <c r="G96" s="30">
+        <v>2</v>
+      </c>
+      <c r="H96" s="30" t="s">
+        <v>146</v>
       </c>
       <c r="J96" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K96" s="5">
         <v>100</v>
@@ -4928,29 +4932,31 @@
     </row>
     <row r="97" s="5" customFormat="1" spans="1:11">
       <c r="A97" s="5">
-        <v>10250018</v>
+        <v>10250016</v>
       </c>
       <c r="B97" s="5">
         <v>102500</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D97" s="28">
-        <v>4020657</v>
+        <v>79</v>
+      </c>
+      <c r="D97" s="30">
+        <v>4020655</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28" t="s">
-        <v>148</v>
+        <v>80</v>
+      </c>
+      <c r="G97" s="30">
+        <v>2</v>
+      </c>
+      <c r="H97" s="30" t="s">
+        <v>147</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J97" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K97" s="5">
         <v>100</v>
@@ -4958,28 +4964,28 @@
     </row>
     <row r="98" s="5" customFormat="1" spans="1:11">
       <c r="A98" s="5">
-        <v>10250019</v>
+        <v>10250017</v>
       </c>
       <c r="B98" s="5">
         <v>102500</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="28">
-        <v>4020658</v>
+        <v>83</v>
+      </c>
+      <c r="D98" s="30">
+        <v>4020656</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G98" s="28">
-        <v>2</v>
-      </c>
-      <c r="H98" s="28" t="s">
-        <v>149</v>
+        <v>80</v>
+      </c>
+      <c r="G98" s="30">
+        <v>2</v>
+      </c>
+      <c r="H98" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="J98" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K98" s="5">
         <v>100</v>
@@ -4987,150 +4993,149 @@
     </row>
     <row r="99" s="5" customFormat="1" spans="1:11">
       <c r="A99" s="5">
-        <v>10250020</v>
+        <v>10250018</v>
       </c>
       <c r="B99" s="5">
         <v>102500</v>
       </c>
       <c r="C99" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D99" s="30">
+        <v>4020657</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J99" s="5">
+        <v>17</v>
+      </c>
+      <c r="K99" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" s="5" customFormat="1" spans="1:11">
+      <c r="A100" s="5">
+        <v>10250019</v>
+      </c>
+      <c r="B100" s="5">
+        <v>102500</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="30">
+        <v>4020658</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G100" s="30">
+        <v>2</v>
+      </c>
+      <c r="H100" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="J100" s="5">
+        <v>18</v>
+      </c>
+      <c r="K100" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" s="5" customFormat="1" spans="1:11">
+      <c r="A101" s="5">
+        <v>10250020</v>
+      </c>
+      <c r="B101" s="5">
+        <v>102500</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D99" s="28">
+      <c r="D101" s="30">
         <v>4020651</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E101" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G99" s="5">
-        <v>2</v>
-      </c>
-      <c r="H99" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="J99" s="5">
+      <c r="G101" s="5">
+        <v>2</v>
+      </c>
+      <c r="H101" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J101" s="5">
         <v>19</v>
       </c>
-      <c r="K99" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" s="6" customFormat="1" spans="1:11">
-      <c r="A100" s="6">
-        <v>10310001</v>
-      </c>
-      <c r="B100" s="6">
-        <v>103100</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D100" s="30">
-        <v>4020002</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100" s="6">
-        <v>1</v>
-      </c>
-      <c r="G100" s="6">
-        <v>2</v>
-      </c>
-      <c r="J100" s="6">
-        <v>-1</v>
-      </c>
-      <c r="K100" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" s="6" customFormat="1" spans="1:11">
-      <c r="A101" s="6">
-        <v>10310002</v>
-      </c>
-      <c r="B101" s="6">
-        <v>103100</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D101" s="30">
-        <v>4020003</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F101" s="31"/>
-      <c r="G101" s="6">
-        <v>2</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J101" s="6">
-        <v>1</v>
-      </c>
-      <c r="K101" s="6">
+      <c r="K101" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="102" s="6" customFormat="1" spans="1:11">
       <c r="A102" s="6">
-        <v>10310003</v>
+        <v>10310001</v>
       </c>
       <c r="B102" s="6">
         <v>103100</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D102" s="30">
-        <v>4020645</v>
+        <v>59</v>
+      </c>
+      <c r="D102" s="32">
+        <v>4020002</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F102" s="31"/>
-      <c r="G102" s="31">
-        <v>2</v>
-      </c>
-      <c r="H102" s="31"/>
-      <c r="I102" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="F102" s="6">
+        <v>1</v>
+      </c>
+      <c r="G102" s="6">
+        <v>2</v>
       </c>
       <c r="J102" s="6">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K102" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" s="6" customFormat="1" spans="1:11">
       <c r="A103" s="6">
-        <v>10310004</v>
+        <v>10310002</v>
       </c>
       <c r="B103" s="6">
         <v>103100</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D103" s="30">
-        <v>4020640</v>
+        <v>63</v>
+      </c>
+      <c r="D103" s="32">
+        <v>4020003</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F103" s="33"/>
       <c r="G103" s="6">
         <v>2</v>
       </c>
-      <c r="H103" s="31" t="s">
+      <c r="H103" s="6" t="s">
         <v>152</v>
       </c>
       <c r="J103" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K103" s="6">
         <v>100</v>
@@ -5138,31 +5143,30 @@
     </row>
     <row r="104" s="6" customFormat="1" spans="1:11">
       <c r="A104" s="6">
-        <v>10310005</v>
+        <v>10310003</v>
       </c>
       <c r="B104" s="6">
         <v>103100</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D104" s="30">
-        <v>4020646</v>
+        <v>27</v>
+      </c>
+      <c r="D104" s="32">
+        <v>4020645</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G104" s="31">
-        <v>2</v>
-      </c>
-      <c r="H104" s="31" t="s">
-        <v>153</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F104" s="33"/>
+      <c r="G104" s="33">
+        <v>2</v>
+      </c>
+      <c r="H104" s="33"/>
       <c r="I104" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J104" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K104" s="6">
         <v>100</v>
@@ -5170,28 +5174,28 @@
     </row>
     <row r="105" s="6" customFormat="1" spans="1:11">
       <c r="A105" s="6">
-        <v>10310006</v>
+        <v>10310004</v>
       </c>
       <c r="B105" s="6">
         <v>103100</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D105" s="30">
-        <v>4020641</v>
+        <v>31</v>
+      </c>
+      <c r="D105" s="32">
+        <v>4020640</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G105" s="6">
         <v>2</v>
       </c>
-      <c r="H105" s="31" t="s">
-        <v>154</v>
+      <c r="H105" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="J105" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K105" s="6">
         <v>100</v>
@@ -5199,31 +5203,31 @@
     </row>
     <row r="106" s="6" customFormat="1" spans="1:11">
       <c r="A106" s="6">
-        <v>10310007</v>
+        <v>10310005</v>
       </c>
       <c r="B106" s="6">
         <v>103100</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D106" s="30">
-        <v>4020647</v>
+        <v>33</v>
+      </c>
+      <c r="D106" s="32">
+        <v>4020646</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G106" s="31">
-        <v>2</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>155</v>
+        <v>34</v>
+      </c>
+      <c r="G106" s="33">
+        <v>2</v>
+      </c>
+      <c r="H106" s="33" t="s">
+        <v>154</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J106" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K106" s="6">
         <v>100</v>
@@ -5231,28 +5235,28 @@
     </row>
     <row r="107" s="6" customFormat="1" spans="1:11">
       <c r="A107" s="6">
-        <v>10310008</v>
+        <v>10310006</v>
       </c>
       <c r="B107" s="6">
         <v>103100</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D107" s="30">
-        <v>4020642</v>
+        <v>37</v>
+      </c>
+      <c r="D107" s="32">
+        <v>4020641</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G107" s="6">
         <v>2</v>
       </c>
-      <c r="H107" s="31" t="s">
-        <v>156</v>
+      <c r="H107" s="33" t="s">
+        <v>155</v>
       </c>
       <c r="J107" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K107" s="6">
         <v>100</v>
@@ -5260,31 +5264,31 @@
     </row>
     <row r="108" s="6" customFormat="1" spans="1:11">
       <c r="A108" s="6">
-        <v>10310009</v>
+        <v>10310007</v>
       </c>
       <c r="B108" s="6">
         <v>103100</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D108" s="30">
-        <v>4020648</v>
+        <v>39</v>
+      </c>
+      <c r="D108" s="32">
+        <v>4020647</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G108" s="31">
-        <v>2</v>
-      </c>
-      <c r="H108" s="31" t="s">
-        <v>157</v>
+        <v>40</v>
+      </c>
+      <c r="G108" s="33">
+        <v>2</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J108" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K108" s="6">
         <v>100</v>
@@ -5292,28 +5296,28 @@
     </row>
     <row r="109" s="6" customFormat="1" spans="1:11">
       <c r="A109" s="6">
-        <v>10310010</v>
+        <v>10310008</v>
       </c>
       <c r="B109" s="6">
         <v>103100</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D109" s="30">
-        <v>4020643</v>
+        <v>42</v>
+      </c>
+      <c r="D109" s="32">
+        <v>4020642</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G109" s="6">
         <v>2</v>
       </c>
-      <c r="H109" s="6" t="s">
-        <v>158</v>
+      <c r="H109" s="33" t="s">
+        <v>157</v>
       </c>
       <c r="J109" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K109" s="6">
         <v>100</v>
@@ -5321,31 +5325,31 @@
     </row>
     <row r="110" s="6" customFormat="1" spans="1:11">
       <c r="A110" s="6">
-        <v>10310011</v>
+        <v>10310009</v>
       </c>
       <c r="B110" s="6">
         <v>103100</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D110" s="30">
-        <v>4020649</v>
+        <v>43</v>
+      </c>
+      <c r="D110" s="32">
+        <v>4020648</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G110" s="31">
-        <v>2</v>
-      </c>
-      <c r="H110" s="31" t="s">
-        <v>159</v>
+        <v>44</v>
+      </c>
+      <c r="G110" s="33">
+        <v>2</v>
+      </c>
+      <c r="H110" s="33" t="s">
+        <v>158</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J110" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K110" s="6">
         <v>100</v>
@@ -5353,28 +5357,28 @@
     </row>
     <row r="111" s="6" customFormat="1" spans="1:11">
       <c r="A111" s="6">
-        <v>10310012</v>
+        <v>10310010</v>
       </c>
       <c r="B111" s="6">
         <v>103100</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D111" s="30">
-        <v>4020644</v>
+        <v>46</v>
+      </c>
+      <c r="D111" s="32">
+        <v>4020643</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G111" s="6">
         <v>2</v>
       </c>
-      <c r="H111" s="31" t="s">
-        <v>160</v>
+      <c r="H111" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="J111" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K111" s="6">
         <v>100</v>
@@ -5382,29 +5386,31 @@
     </row>
     <row r="112" s="6" customFormat="1" spans="1:11">
       <c r="A112" s="6">
-        <v>10310013</v>
+        <v>10310011</v>
       </c>
       <c r="B112" s="6">
         <v>103100</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D112" s="30">
-        <v>4020650</v>
+        <v>47</v>
+      </c>
+      <c r="D112" s="32">
+        <v>4020649</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G112" s="31">
-        <v>2</v>
-      </c>
-      <c r="H112" s="31"/>
+        <v>48</v>
+      </c>
+      <c r="G112" s="33">
+        <v>2</v>
+      </c>
+      <c r="H112" s="33" t="s">
+        <v>160</v>
+      </c>
       <c r="I112" s="6" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="J112" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K112" s="6">
         <v>100</v>
@@ -5412,31 +5418,28 @@
     </row>
     <row r="113" s="6" customFormat="1" spans="1:11">
       <c r="A113" s="6">
-        <v>10310014</v>
+        <v>10310012</v>
       </c>
       <c r="B113" s="6">
         <v>103100</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D113" s="30">
-        <v>4020653</v>
+        <v>50</v>
+      </c>
+      <c r="D113" s="32">
+        <v>4020644</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G113" s="6">
         <v>2</v>
       </c>
-      <c r="H113" s="31" t="s">
+      <c r="H113" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="I113" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="J113" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K113" s="6">
         <v>100</v>
@@ -5444,28 +5447,29 @@
     </row>
     <row r="114" s="6" customFormat="1" spans="1:11">
       <c r="A114" s="6">
-        <v>10310015</v>
+        <v>10310013</v>
       </c>
       <c r="B114" s="6">
         <v>103100</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D114" s="30">
-        <v>4020654</v>
+        <v>71</v>
+      </c>
+      <c r="D114" s="32">
+        <v>4020650</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G114" s="31">
-        <v>2</v>
-      </c>
-      <c r="H114" s="31" t="s">
-        <v>162</v>
+      <c r="G114" s="33">
+        <v>2</v>
+      </c>
+      <c r="H114" s="33"/>
+      <c r="I114" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="J114" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K114" s="6">
         <v>100</v>
@@ -5473,31 +5477,31 @@
     </row>
     <row r="115" s="6" customFormat="1" spans="1:11">
       <c r="A115" s="6">
-        <v>10310016</v>
+        <v>10310014</v>
       </c>
       <c r="B115" s="6">
         <v>103100</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D115" s="30">
-        <v>4020655</v>
+        <v>74</v>
+      </c>
+      <c r="D115" s="32">
+        <v>4020653</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G115" s="6">
         <v>2</v>
       </c>
-      <c r="H115" s="31" t="s">
-        <v>163</v>
+      <c r="H115" s="33" t="s">
+        <v>162</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J115" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K115" s="6">
         <v>100</v>
@@ -5505,28 +5509,28 @@
     </row>
     <row r="116" s="6" customFormat="1" spans="1:11">
       <c r="A116" s="6">
-        <v>10310017</v>
+        <v>10310015</v>
       </c>
       <c r="B116" s="6">
         <v>103100</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D116" s="30">
-        <v>4020656</v>
+        <v>77</v>
+      </c>
+      <c r="D116" s="32">
+        <v>4020654</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G116" s="31">
-        <v>2</v>
-      </c>
-      <c r="H116" s="31" t="s">
-        <v>164</v>
+        <v>72</v>
+      </c>
+      <c r="G116" s="33">
+        <v>2</v>
+      </c>
+      <c r="H116" s="33" t="s">
+        <v>163</v>
       </c>
       <c r="J116" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K116" s="6">
         <v>100</v>
@@ -5534,31 +5538,31 @@
     </row>
     <row r="117" s="6" customFormat="1" spans="1:11">
       <c r="A117" s="6">
-        <v>10310018</v>
+        <v>10310016</v>
       </c>
       <c r="B117" s="6">
         <v>103100</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D117" s="30">
-        <v>4020657</v>
+        <v>79</v>
+      </c>
+      <c r="D117" s="32">
+        <v>4020655</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G117" s="6">
         <v>2</v>
       </c>
-      <c r="H117" s="31" t="s">
-        <v>165</v>
+      <c r="H117" s="33" t="s">
+        <v>164</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J117" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K117" s="6">
         <v>100</v>
@@ -5566,28 +5570,28 @@
     </row>
     <row r="118" s="6" customFormat="1" spans="1:11">
       <c r="A118" s="6">
-        <v>10310019</v>
+        <v>10310017</v>
       </c>
       <c r="B118" s="6">
         <v>103100</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D118" s="30">
-        <v>4020658</v>
+        <v>83</v>
+      </c>
+      <c r="D118" s="32">
+        <v>4020656</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G118" s="31">
-        <v>2</v>
-      </c>
-      <c r="H118" s="31" t="s">
-        <v>166</v>
+        <v>80</v>
+      </c>
+      <c r="G118" s="33">
+        <v>2</v>
+      </c>
+      <c r="H118" s="33" t="s">
+        <v>165</v>
       </c>
       <c r="J118" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K118" s="6">
         <v>100</v>
@@ -5595,150 +5599,151 @@
     </row>
     <row r="119" s="6" customFormat="1" spans="1:11">
       <c r="A119" s="6">
-        <v>10310020</v>
+        <v>10310018</v>
       </c>
       <c r="B119" s="6">
         <v>103100</v>
       </c>
       <c r="C119" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D119" s="32">
+        <v>4020657</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G119" s="6">
+        <v>2</v>
+      </c>
+      <c r="H119" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J119" s="6">
+        <v>17</v>
+      </c>
+      <c r="K119" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" s="6" customFormat="1" spans="1:11">
+      <c r="A120" s="6">
+        <v>10310019</v>
+      </c>
+      <c r="B120" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D120" s="32">
+        <v>4020658</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G120" s="33">
+        <v>2</v>
+      </c>
+      <c r="H120" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="J120" s="6">
+        <v>18</v>
+      </c>
+      <c r="K120" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" s="6" customFormat="1" spans="1:11">
+      <c r="A121" s="6">
+        <v>10310020</v>
+      </c>
+      <c r="B121" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D119" s="30">
+      <c r="D121" s="32">
         <v>4020651</v>
       </c>
-      <c r="E119" s="6" t="s">
+      <c r="E121" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G119" s="6">
-        <v>2</v>
-      </c>
-      <c r="H119" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="J119" s="6">
+      <c r="G121" s="6">
+        <v>2</v>
+      </c>
+      <c r="H121" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="J121" s="6">
         <v>19</v>
       </c>
-      <c r="K119" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" s="2" customFormat="1" spans="1:11">
-      <c r="A120" s="2">
-        <v>10220001</v>
-      </c>
-      <c r="B120" s="2">
-        <v>102200</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D120" s="19">
-        <v>4020002</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="2">
-        <v>1</v>
-      </c>
-      <c r="G120" s="2">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K120" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="1:11">
-      <c r="A121" s="2">
-        <v>10220002</v>
-      </c>
-      <c r="B121" s="2">
-        <v>102200</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D121" s="19">
-        <v>4020003</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="22"/>
-      <c r="G121" s="2">
-        <v>2</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="J121" s="2">
-        <v>1</v>
-      </c>
-      <c r="K121" s="2">
+      <c r="K121" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="122" s="2" customFormat="1" spans="1:11">
       <c r="A122" s="2">
-        <v>10220003</v>
+        <v>10220001</v>
       </c>
       <c r="B122" s="2">
         <v>102200</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D122" s="19">
-        <v>4020645</v>
+        <v>4020002</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F122" s="22"/>
-      <c r="G122" s="19">
-        <v>2</v>
-      </c>
-      <c r="H122" s="19"/>
-      <c r="I122" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="F122" s="2">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2">
+        <v>2</v>
       </c>
       <c r="J122" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K122" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" s="2" customFormat="1" spans="1:11">
       <c r="A123" s="2">
-        <v>10220004</v>
+        <v>10220002</v>
       </c>
       <c r="B123" s="2">
         <v>102200</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D123" s="19">
-        <v>4020640</v>
+        <v>4020003</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F123" s="22"/>
       <c r="G123" s="2">
         <v>2</v>
       </c>
-      <c r="H123" s="19" t="s">
+      <c r="H123" s="2" t="s">
         <v>169</v>
       </c>
       <c r="J123" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K123" s="2">
         <v>100</v>
@@ -5746,31 +5751,30 @@
     </row>
     <row r="124" s="2" customFormat="1" spans="1:11">
       <c r="A124" s="2">
-        <v>10220005</v>
+        <v>10220003</v>
       </c>
       <c r="B124" s="2">
         <v>102200</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D124" s="19">
-        <v>4020646</v>
+        <v>4020645</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F124" s="22"/>
       <c r="G124" s="19">
         <v>2</v>
       </c>
-      <c r="H124" s="19" t="s">
-        <v>170</v>
-      </c>
+      <c r="H124" s="19"/>
       <c r="I124" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J124" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K124" s="2">
         <v>100</v>
@@ -5778,28 +5782,28 @@
     </row>
     <row r="125" s="2" customFormat="1" spans="1:11">
       <c r="A125" s="2">
-        <v>10220006</v>
+        <v>10220004</v>
       </c>
       <c r="B125" s="2">
         <v>102200</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D125" s="19">
-        <v>4020641</v>
+        <v>4020640</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G125" s="2">
         <v>2</v>
       </c>
-      <c r="H125" s="2" t="s">
-        <v>171</v>
+      <c r="H125" s="19" t="s">
+        <v>170</v>
       </c>
       <c r="J125" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K125" s="2">
         <v>100</v>
@@ -5807,31 +5811,31 @@
     </row>
     <row r="126" s="2" customFormat="1" spans="1:11">
       <c r="A126" s="2">
-        <v>10220007</v>
+        <v>10220005</v>
       </c>
       <c r="B126" s="2">
         <v>102200</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D126" s="19">
-        <v>4020647</v>
+        <v>4020646</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G126" s="19">
         <v>2</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J126" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K126" s="2">
         <v>100</v>
@@ -5839,28 +5843,28 @@
     </row>
     <row r="127" s="2" customFormat="1" spans="1:11">
       <c r="A127" s="2">
-        <v>10220008</v>
+        <v>10220006</v>
       </c>
       <c r="B127" s="2">
         <v>102200</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D127" s="19">
-        <v>4020642</v>
+        <v>4020641</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G127" s="2">
         <v>2</v>
       </c>
-      <c r="H127" s="19" t="s">
-        <v>173</v>
+      <c r="H127" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="J127" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K127" s="2">
         <v>100</v>
@@ -5868,31 +5872,31 @@
     </row>
     <row r="128" s="2" customFormat="1" spans="1:11">
       <c r="A128" s="2">
-        <v>10220009</v>
+        <v>10220007</v>
       </c>
       <c r="B128" s="2">
         <v>102200</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D128" s="19">
-        <v>4020648</v>
+        <v>4020647</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="2">
+        <v>40</v>
+      </c>
+      <c r="G128" s="19">
         <v>2</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J128" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K128" s="2">
         <v>100</v>
@@ -5900,28 +5904,28 @@
     </row>
     <row r="129" s="2" customFormat="1" spans="1:11">
       <c r="A129" s="2">
-        <v>10220010</v>
+        <v>10220008</v>
       </c>
       <c r="B129" s="2">
         <v>102200</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D129" s="19">
-        <v>4020643</v>
+        <v>4020642</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G129" s="2">
         <v>2</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J129" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K129" s="2">
         <v>100</v>
@@ -5929,31 +5933,31 @@
     </row>
     <row r="130" s="2" customFormat="1" spans="1:11">
       <c r="A130" s="2">
-        <v>10220011</v>
+        <v>10220009</v>
       </c>
       <c r="B130" s="2">
         <v>102200</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D130" s="19">
-        <v>4020649</v>
+        <v>4020648</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G130" s="2">
         <v>2</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J130" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K130" s="2">
         <v>100</v>
@@ -5961,28 +5965,28 @@
     </row>
     <row r="131" s="2" customFormat="1" spans="1:11">
       <c r="A131" s="2">
-        <v>10220012</v>
+        <v>10220010</v>
       </c>
       <c r="B131" s="2">
         <v>102200</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D131" s="19">
-        <v>4020644</v>
+        <v>4020643</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G131" s="2">
         <v>2</v>
       </c>
       <c r="H131" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J131" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K131" s="2">
         <v>100</v>
@@ -5990,29 +5994,31 @@
     </row>
     <row r="132" s="2" customFormat="1" spans="1:11">
       <c r="A132" s="2">
-        <v>10220013</v>
+        <v>10220011</v>
       </c>
       <c r="B132" s="2">
         <v>102200</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D132" s="19">
-        <v>4020650</v>
+        <v>4020649</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G132" s="2">
         <v>2</v>
       </c>
-      <c r="H132" s="19"/>
+      <c r="H132" s="19" t="s">
+        <v>177</v>
+      </c>
       <c r="I132" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="J132" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K132" s="2">
         <v>100</v>
@@ -6020,19 +6026,19 @@
     </row>
     <row r="133" s="2" customFormat="1" spans="1:11">
       <c r="A133" s="2">
-        <v>10220014</v>
+        <v>10220012</v>
       </c>
       <c r="B133" s="2">
         <v>102200</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D133" s="19">
-        <v>4020653</v>
+        <v>4020644</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G133" s="2">
         <v>2</v>
@@ -6040,11 +6046,8 @@
       <c r="H133" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="I133" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="J133" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K133" s="2">
         <v>100</v>
@@ -6052,16 +6055,16 @@
     </row>
     <row r="134" s="2" customFormat="1" spans="1:11">
       <c r="A134" s="2">
-        <v>10220015</v>
+        <v>10220013</v>
       </c>
       <c r="B134" s="2">
         <v>102200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D134" s="19">
-        <v>4020654</v>
+        <v>4020650</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>72</v>
@@ -6069,11 +6072,12 @@
       <c r="G134" s="2">
         <v>2</v>
       </c>
-      <c r="H134" s="19" t="s">
-        <v>179</v>
+      <c r="H134" s="19"/>
+      <c r="I134" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J134" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K134" s="2">
         <v>100</v>
@@ -6081,31 +6085,31 @@
     </row>
     <row r="135" s="2" customFormat="1" spans="1:11">
       <c r="A135" s="2">
-        <v>10220016</v>
+        <v>10220014</v>
       </c>
       <c r="B135" s="2">
         <v>102200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D135" s="19">
-        <v>4020655</v>
+        <v>4020653</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G135" s="2">
         <v>2</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J135" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K135" s="2">
         <v>100</v>
@@ -6113,28 +6117,28 @@
     </row>
     <row r="136" s="2" customFormat="1" spans="1:11">
       <c r="A136" s="2">
-        <v>10220017</v>
+        <v>10220015</v>
       </c>
       <c r="B136" s="2">
         <v>102200</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D136" s="19">
-        <v>4020656</v>
+        <v>4020654</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G136" s="2">
         <v>2</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J136" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K136" s="2">
         <v>100</v>
@@ -6142,31 +6146,31 @@
     </row>
     <row r="137" s="2" customFormat="1" spans="1:11">
       <c r="A137" s="2">
-        <v>10220018</v>
+        <v>10220016</v>
       </c>
       <c r="B137" s="2">
         <v>102200</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D137" s="19">
-        <v>4020657</v>
+        <v>4020655</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G137" s="2">
         <v>2</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J137" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K137" s="2">
         <v>100</v>
@@ -6174,28 +6178,28 @@
     </row>
     <row r="138" s="2" customFormat="1" spans="1:11">
       <c r="A138" s="2">
-        <v>10220019</v>
+        <v>10220017</v>
       </c>
       <c r="B138" s="2">
         <v>102200</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D138" s="19">
-        <v>4020658</v>
+        <v>4020656</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G138" s="2">
         <v>2</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J138" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K138" s="2">
         <v>100</v>
@@ -6203,149 +6207,151 @@
     </row>
     <row r="139" s="2" customFormat="1" spans="1:11">
       <c r="A139" s="2">
-        <v>10220020</v>
+        <v>10220018</v>
       </c>
       <c r="B139" s="2">
         <v>102200</v>
       </c>
       <c r="C139" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D139" s="19">
+        <v>4020657</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G139" s="2">
+        <v>2</v>
+      </c>
+      <c r="H139" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J139" s="2">
+        <v>17</v>
+      </c>
+      <c r="K139" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" s="2" customFormat="1" spans="1:11">
+      <c r="A140" s="2">
+        <v>10220019</v>
+      </c>
+      <c r="B140" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D140" s="19">
+        <v>4020658</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G140" s="2">
+        <v>2</v>
+      </c>
+      <c r="H140" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="J140" s="2">
+        <v>18</v>
+      </c>
+      <c r="K140" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" s="2" customFormat="1" spans="1:11">
+      <c r="A141" s="2">
+        <v>10220020</v>
+      </c>
+      <c r="B141" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D139" s="19">
+      <c r="D141" s="19">
         <v>4020651</v>
       </c>
-      <c r="E139" s="2" t="s">
+      <c r="E141" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G139" s="2">
-        <v>2</v>
-      </c>
-      <c r="H139" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J139" s="2">
+      <c r="G141" s="2">
+        <v>2</v>
+      </c>
+      <c r="H141" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J141" s="2">
         <v>19</v>
       </c>
-      <c r="K139" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" s="7" customFormat="1" spans="1:11">
-      <c r="A140" s="7">
-        <v>10210001</v>
-      </c>
-      <c r="B140" s="7">
-        <v>102100</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D140" s="32">
-        <v>4020002</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" s="7">
-        <v>1</v>
-      </c>
-      <c r="G140" s="7">
-        <v>2</v>
-      </c>
-      <c r="J140" s="7">
-        <v>-1</v>
-      </c>
-      <c r="K140" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" s="7" customFormat="1" spans="1:11">
-      <c r="A141" s="7">
-        <v>10210002</v>
-      </c>
-      <c r="B141" s="7">
-        <v>102100</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D141" s="32">
-        <v>4020003</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" s="33"/>
-      <c r="G141" s="7">
-        <v>2</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="J141" s="7">
-        <v>1</v>
-      </c>
-      <c r="K141" s="7">
+      <c r="K141" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="142" s="7" customFormat="1" spans="1:11">
       <c r="A142" s="7">
-        <v>10210003</v>
+        <v>10210001</v>
       </c>
       <c r="B142" s="7">
         <v>102100</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D142" s="32">
-        <v>4020645</v>
+        <v>59</v>
+      </c>
+      <c r="D142" s="34">
+        <v>4020002</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G142" s="32">
-        <v>2</v>
-      </c>
-      <c r="H142" s="32"/>
-      <c r="I142" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="F142" s="7">
+        <v>1</v>
+      </c>
+      <c r="G142" s="7">
+        <v>2</v>
       </c>
       <c r="J142" s="7">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K142" s="7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" s="7" customFormat="1" spans="1:11">
       <c r="A143" s="7">
-        <v>10210004</v>
+        <v>10210002</v>
       </c>
       <c r="B143" s="7">
         <v>102100</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D143" s="32">
-        <v>4020640</v>
+        <v>63</v>
+      </c>
+      <c r="D143" s="34">
+        <v>4020003</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>28</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F143" s="35"/>
       <c r="G143" s="7">
         <v>2</v>
       </c>
-      <c r="H143" s="32" t="s">
+      <c r="H143" s="7" t="s">
         <v>186</v>
       </c>
       <c r="J143" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K143" s="7">
         <v>100</v>
@@ -6353,31 +6359,29 @@
     </row>
     <row r="144" s="7" customFormat="1" spans="1:11">
       <c r="A144" s="7">
-        <v>10210005</v>
+        <v>10210003</v>
       </c>
       <c r="B144" s="7">
         <v>102100</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D144" s="32">
-        <v>4020646</v>
+        <v>27</v>
+      </c>
+      <c r="D144" s="34">
+        <v>4020645</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G144" s="32">
-        <v>2</v>
-      </c>
-      <c r="H144" s="32" t="s">
-        <v>187</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G144" s="34">
+        <v>2</v>
+      </c>
+      <c r="H144" s="34"/>
       <c r="I144" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J144" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K144" s="7">
         <v>100</v>
@@ -6385,28 +6389,28 @@
     </row>
     <row r="145" s="7" customFormat="1" spans="1:11">
       <c r="A145" s="7">
-        <v>10210006</v>
+        <v>10210004</v>
       </c>
       <c r="B145" s="7">
         <v>102100</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D145" s="32">
-        <v>4020641</v>
+        <v>31</v>
+      </c>
+      <c r="D145" s="34">
+        <v>4020640</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G145" s="7">
         <v>2</v>
       </c>
-      <c r="H145" s="32" t="s">
-        <v>188</v>
+      <c r="H145" s="34" t="s">
+        <v>187</v>
       </c>
       <c r="J145" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K145" s="7">
         <v>100</v>
@@ -6414,31 +6418,31 @@
     </row>
     <row r="146" s="7" customFormat="1" spans="1:11">
       <c r="A146" s="7">
-        <v>10210007</v>
+        <v>10210005</v>
       </c>
       <c r="B146" s="7">
         <v>102100</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D146" s="32">
-        <v>4020647</v>
+        <v>33</v>
+      </c>
+      <c r="D146" s="34">
+        <v>4020646</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G146" s="32">
-        <v>2</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>189</v>
+        <v>34</v>
+      </c>
+      <c r="G146" s="34">
+        <v>2</v>
+      </c>
+      <c r="H146" s="34" t="s">
+        <v>188</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J146" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K146" s="7">
         <v>100</v>
@@ -6446,28 +6450,28 @@
     </row>
     <row r="147" s="7" customFormat="1" spans="1:11">
       <c r="A147" s="7">
-        <v>10210008</v>
+        <v>10210006</v>
       </c>
       <c r="B147" s="7">
         <v>102100</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D147" s="32">
-        <v>4020642</v>
+        <v>37</v>
+      </c>
+      <c r="D147" s="34">
+        <v>4020641</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G147" s="7">
         <v>2</v>
       </c>
-      <c r="H147" s="32" t="s">
-        <v>190</v>
+      <c r="H147" s="34" t="s">
+        <v>189</v>
       </c>
       <c r="J147" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K147" s="7">
         <v>100</v>
@@ -6475,31 +6479,31 @@
     </row>
     <row r="148" s="7" customFormat="1" spans="1:11">
       <c r="A148" s="7">
-        <v>10210009</v>
+        <v>10210007</v>
       </c>
       <c r="B148" s="7">
         <v>102100</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D148" s="32">
-        <v>4020648</v>
+        <v>39</v>
+      </c>
+      <c r="D148" s="34">
+        <v>4020647</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G148" s="32">
-        <v>2</v>
-      </c>
-      <c r="H148" s="32" t="s">
-        <v>191</v>
+        <v>40</v>
+      </c>
+      <c r="G148" s="34">
+        <v>2</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J148" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K148" s="7">
         <v>100</v>
@@ -6507,28 +6511,28 @@
     </row>
     <row r="149" s="7" customFormat="1" spans="1:11">
       <c r="A149" s="7">
-        <v>10210010</v>
+        <v>10210008</v>
       </c>
       <c r="B149" s="7">
         <v>102100</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D149" s="32">
-        <v>4020643</v>
+        <v>42</v>
+      </c>
+      <c r="D149" s="34">
+        <v>4020642</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G149" s="7">
         <v>2</v>
       </c>
-      <c r="H149" s="7" t="s">
-        <v>192</v>
+      <c r="H149" s="34" t="s">
+        <v>191</v>
       </c>
       <c r="J149" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K149" s="7">
         <v>100</v>
@@ -6536,31 +6540,31 @@
     </row>
     <row r="150" s="7" customFormat="1" spans="1:11">
       <c r="A150" s="7">
-        <v>10210011</v>
+        <v>10210009</v>
       </c>
       <c r="B150" s="7">
         <v>102100</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D150" s="32">
-        <v>4020649</v>
+        <v>43</v>
+      </c>
+      <c r="D150" s="34">
+        <v>4020648</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G150" s="32">
-        <v>2</v>
-      </c>
-      <c r="H150" s="32" t="s">
-        <v>193</v>
+        <v>44</v>
+      </c>
+      <c r="G150" s="34">
+        <v>2</v>
+      </c>
+      <c r="H150" s="34" t="s">
+        <v>192</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J150" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K150" s="7">
         <v>100</v>
@@ -6568,28 +6572,28 @@
     </row>
     <row r="151" s="7" customFormat="1" spans="1:11">
       <c r="A151" s="7">
-        <v>10210012</v>
+        <v>10210010</v>
       </c>
       <c r="B151" s="7">
         <v>102100</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D151" s="32">
-        <v>4020644</v>
+        <v>46</v>
+      </c>
+      <c r="D151" s="34">
+        <v>4020643</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G151" s="7">
         <v>2</v>
       </c>
-      <c r="H151" s="32" t="s">
-        <v>194</v>
+      <c r="H151" s="7" t="s">
+        <v>193</v>
       </c>
       <c r="J151" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K151" s="7">
         <v>100</v>
@@ -6597,29 +6601,31 @@
     </row>
     <row r="152" s="7" customFormat="1" spans="1:11">
       <c r="A152" s="7">
-        <v>10210013</v>
+        <v>10210011</v>
       </c>
       <c r="B152" s="7">
         <v>102100</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D152" s="32">
-        <v>4020650</v>
+        <v>47</v>
+      </c>
+      <c r="D152" s="34">
+        <v>4020649</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G152" s="32">
-        <v>2</v>
-      </c>
-      <c r="H152" s="32"/>
+        <v>48</v>
+      </c>
+      <c r="G152" s="34">
+        <v>2</v>
+      </c>
+      <c r="H152" s="34" t="s">
+        <v>194</v>
+      </c>
       <c r="I152" s="7" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="J152" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K152" s="7">
         <v>100</v>
@@ -6627,31 +6633,28 @@
     </row>
     <row r="153" s="7" customFormat="1" spans="1:11">
       <c r="A153" s="7">
-        <v>10210014</v>
+        <v>10210012</v>
       </c>
       <c r="B153" s="7">
         <v>102100</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D153" s="32">
-        <v>4020653</v>
+        <v>50</v>
+      </c>
+      <c r="D153" s="34">
+        <v>4020644</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G153" s="32">
-        <v>2</v>
-      </c>
-      <c r="H153" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="G153" s="7">
+        <v>2</v>
+      </c>
+      <c r="H153" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="I153" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="J153" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K153" s="7">
         <v>100</v>
@@ -6659,28 +6662,29 @@
     </row>
     <row r="154" s="7" customFormat="1" spans="1:11">
       <c r="A154" s="7">
-        <v>10210015</v>
+        <v>10210013</v>
       </c>
       <c r="B154" s="7">
         <v>102100</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D154" s="32">
-        <v>4020654</v>
+        <v>71</v>
+      </c>
+      <c r="D154" s="34">
+        <v>4020650</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G154" s="32">
-        <v>2</v>
-      </c>
-      <c r="H154" s="32" t="s">
-        <v>196</v>
+      <c r="G154" s="34">
+        <v>2</v>
+      </c>
+      <c r="H154" s="34"/>
+      <c r="I154" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="J154" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K154" s="7">
         <v>100</v>
@@ -6688,31 +6692,31 @@
     </row>
     <row r="155" s="7" customFormat="1" spans="1:11">
       <c r="A155" s="7">
-        <v>10210016</v>
+        <v>10210014</v>
       </c>
       <c r="B155" s="7">
         <v>102100</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D155" s="32">
-        <v>4020655</v>
+        <v>74</v>
+      </c>
+      <c r="D155" s="34">
+        <v>4020653</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G155" s="32">
-        <v>2</v>
-      </c>
-      <c r="H155" s="32" t="s">
-        <v>197</v>
+        <v>72</v>
+      </c>
+      <c r="G155" s="34">
+        <v>2</v>
+      </c>
+      <c r="H155" s="34" t="s">
+        <v>196</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J155" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K155" s="7">
         <v>100</v>
@@ -6720,28 +6724,28 @@
     </row>
     <row r="156" s="7" customFormat="1" spans="1:11">
       <c r="A156" s="7">
-        <v>10210017</v>
+        <v>10210015</v>
       </c>
       <c r="B156" s="7">
         <v>102100</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D156" s="32">
-        <v>4020656</v>
+        <v>77</v>
+      </c>
+      <c r="D156" s="34">
+        <v>4020654</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G156" s="32">
-        <v>2</v>
-      </c>
-      <c r="H156" s="32" t="s">
-        <v>198</v>
+        <v>72</v>
+      </c>
+      <c r="G156" s="34">
+        <v>2</v>
+      </c>
+      <c r="H156" s="34" t="s">
+        <v>197</v>
       </c>
       <c r="J156" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K156" s="7">
         <v>100</v>
@@ -6749,31 +6753,31 @@
     </row>
     <row r="157" s="7" customFormat="1" spans="1:11">
       <c r="A157" s="7">
-        <v>10210018</v>
+        <v>10210016</v>
       </c>
       <c r="B157" s="7">
         <v>102100</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D157" s="32">
-        <v>4020657</v>
+        <v>79</v>
+      </c>
+      <c r="D157" s="34">
+        <v>4020655</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G157" s="32">
-        <v>2</v>
-      </c>
-      <c r="H157" s="32" t="s">
-        <v>199</v>
+        <v>80</v>
+      </c>
+      <c r="G157" s="34">
+        <v>2</v>
+      </c>
+      <c r="H157" s="34" t="s">
+        <v>198</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J157" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K157" s="7">
         <v>100</v>
@@ -6781,28 +6785,28 @@
     </row>
     <row r="158" s="7" customFormat="1" spans="1:11">
       <c r="A158" s="7">
-        <v>10210019</v>
+        <v>10210017</v>
       </c>
       <c r="B158" s="7">
         <v>102100</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D158" s="32">
-        <v>4020658</v>
+        <v>83</v>
+      </c>
+      <c r="D158" s="34">
+        <v>4020656</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G158" s="32">
-        <v>2</v>
-      </c>
-      <c r="H158" s="32" t="s">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="G158" s="34">
+        <v>2</v>
+      </c>
+      <c r="H158" s="34" t="s">
+        <v>199</v>
       </c>
       <c r="J158" s="7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K158" s="7">
         <v>100</v>
@@ -6810,151 +6814,151 @@
     </row>
     <row r="159" s="7" customFormat="1" spans="1:11">
       <c r="A159" s="7">
-        <v>10210020</v>
+        <v>10210018</v>
       </c>
       <c r="B159" s="7">
         <v>102100</v>
       </c>
       <c r="C159" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D159" s="34">
+        <v>4020657</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G159" s="34">
+        <v>2</v>
+      </c>
+      <c r="H159" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J159" s="7">
+        <v>17</v>
+      </c>
+      <c r="K159" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160" s="7" customFormat="1" spans="1:11">
+      <c r="A160" s="7">
+        <v>10210019</v>
+      </c>
+      <c r="B160" s="7">
+        <v>102100</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="34">
+        <v>4020658</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G160" s="34">
+        <v>2</v>
+      </c>
+      <c r="H160" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="J160" s="7">
+        <v>18</v>
+      </c>
+      <c r="K160" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161" s="7" customFormat="1" spans="1:11">
+      <c r="A161" s="7">
+        <v>10210020</v>
+      </c>
+      <c r="B161" s="7">
+        <v>102100</v>
+      </c>
+      <c r="C161" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D159" s="32">
+      <c r="D161" s="34">
         <v>4020651</v>
       </c>
-      <c r="E159" s="7" t="s">
+      <c r="E161" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G159" s="32">
-        <v>2</v>
-      </c>
-      <c r="H159" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="I159" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="J159" s="7">
+      <c r="G161" s="34">
+        <v>2</v>
+      </c>
+      <c r="H161" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J161" s="7">
         <v>19</v>
       </c>
-      <c r="K159" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="160" s="3" customFormat="1" spans="1:11">
-      <c r="A160" s="3">
-        <v>10390001</v>
-      </c>
-      <c r="B160" s="3">
-        <v>103900</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D160" s="23">
-        <v>4020002</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F160" s="3">
-        <v>1</v>
-      </c>
-      <c r="G160" s="3">
-        <v>2</v>
-      </c>
-      <c r="J160" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K160" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
-      <c r="A161" s="3">
-        <v>10390003</v>
-      </c>
-      <c r="B161" s="3">
-        <v>103900</v>
-      </c>
-      <c r="C161" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D161" s="23">
-        <v>4020645</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G161" s="23">
-        <v>2</v>
-      </c>
-      <c r="H161" s="23"/>
-      <c r="I161" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J161" s="3">
-        <v>2</v>
-      </c>
-      <c r="K161" s="3">
+      <c r="K161" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="162" s="3" customFormat="1" spans="1:11">
       <c r="A162" s="3">
-        <v>10390004</v>
+        <v>10390001</v>
       </c>
       <c r="B162" s="3">
         <v>103900</v>
       </c>
-      <c r="C162" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D162" s="23">
-        <v>4020640</v>
+      <c r="C162" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D162" s="24">
+        <v>4020002</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G162" s="23">
-        <v>2</v>
-      </c>
-      <c r="H162" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="J162" s="3">
-        <v>3</v>
+        <v>25</v>
+      </c>
+      <c r="F162" s="3">
+        <v>1</v>
+      </c>
+      <c r="G162" s="3">
+        <v>2</v>
+      </c>
+      <c r="J162" s="20">
+        <v>-1</v>
       </c>
       <c r="K162" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="163" s="3" customFormat="1" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A163" s="3">
-        <v>10390005</v>
+        <v>10390003</v>
       </c>
       <c r="B163" s="3">
         <v>103900</v>
       </c>
-      <c r="C163" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D163" s="23">
-        <v>4020646</v>
+      <c r="C163" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163" s="24">
+        <v>4020645</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G163" s="3">
-        <v>2</v>
-      </c>
-      <c r="H163" s="23" t="s">
-        <v>203</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G163" s="24">
+        <v>2</v>
+      </c>
+      <c r="H163" s="24"/>
       <c r="I163" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J163" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K163" s="3">
         <v>100</v>
@@ -6962,28 +6966,28 @@
     </row>
     <row r="164" s="3" customFormat="1" spans="1:11">
       <c r="A164" s="3">
-        <v>10390006</v>
+        <v>10390004</v>
       </c>
       <c r="B164" s="3">
         <v>103900</v>
       </c>
-      <c r="C164" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D164" s="23">
-        <v>4020641</v>
+      <c r="C164" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D164" s="24">
+        <v>4020640</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G164" s="3">
-        <v>2</v>
-      </c>
-      <c r="H164" s="23" t="s">
-        <v>204</v>
+        <v>28</v>
+      </c>
+      <c r="G164" s="24">
+        <v>2</v>
+      </c>
+      <c r="H164" s="24" t="s">
+        <v>203</v>
       </c>
       <c r="J164" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K164" s="3">
         <v>100</v>
@@ -6991,29 +6995,31 @@
     </row>
     <row r="165" s="3" customFormat="1" spans="1:11">
       <c r="A165" s="3">
-        <v>10390002</v>
+        <v>10390005</v>
       </c>
       <c r="B165" s="3">
         <v>103900</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D165" s="23">
-        <v>4020003</v>
+      <c r="C165" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D165" s="24">
+        <v>4020646</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F165" s="24"/>
+        <v>34</v>
+      </c>
       <c r="G165" s="3">
         <v>2</v>
       </c>
-      <c r="H165" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="J165" s="20">
-        <v>-1</v>
+      <c r="H165" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J165" s="3">
+        <v>4</v>
       </c>
       <c r="K165" s="3">
         <v>100</v>
@@ -7021,31 +7027,28 @@
     </row>
     <row r="166" s="3" customFormat="1" spans="1:11">
       <c r="A166" s="3">
-        <v>10390007</v>
+        <v>10390006</v>
       </c>
       <c r="B166" s="3">
         <v>103900</v>
       </c>
-      <c r="C166" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D166" s="23">
-        <v>4020647</v>
+      <c r="C166" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="D166" s="24">
+        <v>4020641</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G166" s="3">
         <v>2</v>
       </c>
-      <c r="H166" s="23" t="s">
+      <c r="H166" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="I166" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J166" s="20">
-        <v>-1</v>
+      <c r="J166" s="3">
+        <v>5</v>
       </c>
       <c r="K166" s="3">
         <v>100</v>
@@ -7053,24 +7056,25 @@
     </row>
     <row r="167" s="3" customFormat="1" spans="1:11">
       <c r="A167" s="3">
-        <v>10390008</v>
+        <v>10390002</v>
       </c>
       <c r="B167" s="3">
         <v>103900</v>
       </c>
-      <c r="C167" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D167" s="23">
-        <v>4020642</v>
+      <c r="C167" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D167" s="24">
+        <v>4020003</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G167" s="23">
-        <v>2</v>
-      </c>
-      <c r="H167" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F167" s="25"/>
+      <c r="G167" s="3">
+        <v>2</v>
+      </c>
+      <c r="H167" s="24" t="s">
         <v>206</v>
       </c>
       <c r="J167" s="20">
@@ -7082,28 +7086,28 @@
     </row>
     <row r="168" s="3" customFormat="1" spans="1:11">
       <c r="A168" s="3">
-        <v>10390009</v>
+        <v>10390007</v>
       </c>
       <c r="B168" s="3">
         <v>103900</v>
       </c>
-      <c r="C168" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D168" s="23">
-        <v>4020648</v>
+      <c r="C168" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D168" s="24">
+        <v>4020647</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G168" s="3">
         <v>2</v>
       </c>
-      <c r="H168" s="23" t="s">
-        <v>207</v>
+      <c r="H168" s="24" t="s">
+        <v>206</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J168" s="20">
         <v>-1</v>
@@ -7114,25 +7118,25 @@
     </row>
     <row r="169" s="3" customFormat="1" spans="1:11">
       <c r="A169" s="3">
-        <v>10390010</v>
+        <v>10390008</v>
       </c>
       <c r="B169" s="3">
         <v>103900</v>
       </c>
-      <c r="C169" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="D169" s="23">
-        <v>4020643</v>
+      <c r="C169" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D169" s="24">
+        <v>4020642</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G169" s="3">
-        <v>2</v>
-      </c>
-      <c r="H169" s="23" t="s">
-        <v>208</v>
+        <v>40</v>
+      </c>
+      <c r="G169" s="24">
+        <v>2</v>
+      </c>
+      <c r="H169" s="24" t="s">
+        <v>207</v>
       </c>
       <c r="J169" s="20">
         <v>-1</v>
@@ -7143,28 +7147,28 @@
     </row>
     <row r="170" s="3" customFormat="1" spans="1:11">
       <c r="A170" s="3">
-        <v>10390011</v>
+        <v>10390009</v>
       </c>
       <c r="B170" s="3">
         <v>103900</v>
       </c>
-      <c r="C170" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D170" s="23">
-        <v>4020649</v>
+      <c r="C170" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D170" s="24">
+        <v>4020648</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G170" s="3">
         <v>2</v>
       </c>
-      <c r="H170" s="23" t="s">
-        <v>209</v>
+      <c r="H170" s="24" t="s">
+        <v>208</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J170" s="20">
         <v>-1</v>
@@ -7175,25 +7179,25 @@
     </row>
     <row r="171" s="3" customFormat="1" spans="1:11">
       <c r="A171" s="3">
-        <v>10390012</v>
+        <v>10390010</v>
       </c>
       <c r="B171" s="3">
         <v>103900</v>
       </c>
-      <c r="C171" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="D171" s="23">
-        <v>4020644</v>
+      <c r="C171" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D171" s="24">
+        <v>4020643</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G171" s="23">
-        <v>2</v>
-      </c>
-      <c r="H171" s="23" t="s">
-        <v>210</v>
+        <v>44</v>
+      </c>
+      <c r="G171" s="3">
+        <v>2</v>
+      </c>
+      <c r="H171" s="24" t="s">
+        <v>209</v>
       </c>
       <c r="J171" s="20">
         <v>-1</v>
@@ -7204,28 +7208,31 @@
     </row>
     <row r="172" s="3" customFormat="1" spans="1:11">
       <c r="A172" s="3">
-        <v>10390013</v>
+        <v>10390011</v>
       </c>
       <c r="B172" s="3">
         <v>103900</v>
       </c>
-      <c r="C172" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="D172" s="23">
-        <v>4020650</v>
+      <c r="C172" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D172" s="24">
+        <v>4020649</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G172" s="23">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="G172" s="3">
+        <v>2</v>
+      </c>
+      <c r="H172" s="24" t="s">
+        <v>210</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J172" s="3">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="J172" s="20">
+        <v>-1</v>
       </c>
       <c r="K172" s="3">
         <v>100</v>
@@ -7233,28 +7240,25 @@
     </row>
     <row r="173" s="3" customFormat="1" spans="1:11">
       <c r="A173" s="3">
-        <v>10390014</v>
+        <v>10390012</v>
       </c>
       <c r="B173" s="3">
         <v>103900</v>
       </c>
-      <c r="C173" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D173" s="23">
-        <v>4020653</v>
+      <c r="C173" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D173" s="24">
+        <v>4020644</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G173" s="23">
-        <v>2</v>
-      </c>
-      <c r="H173" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G173" s="24">
+        <v>2</v>
+      </c>
+      <c r="H173" s="24" t="s">
         <v>211</v>
-      </c>
-      <c r="I173" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="J173" s="20">
         <v>-1</v>
@@ -7265,28 +7269,28 @@
     </row>
     <row r="174" s="3" customFormat="1" spans="1:11">
       <c r="A174" s="3">
-        <v>10390015</v>
+        <v>10390013</v>
       </c>
       <c r="B174" s="3">
         <v>103900</v>
       </c>
-      <c r="C174" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D174" s="23">
-        <v>4020654</v>
+      <c r="C174" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D174" s="24">
+        <v>4020650</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G174" s="23">
-        <v>2</v>
-      </c>
-      <c r="H174" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J174" s="20">
-        <v>-1</v>
+      <c r="G174" s="24">
+        <v>2</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J174" s="3">
+        <v>12</v>
       </c>
       <c r="K174" s="3">
         <v>100</v>
@@ -7294,28 +7298,28 @@
     </row>
     <row r="175" s="3" customFormat="1" spans="1:11">
       <c r="A175" s="3">
-        <v>10390016</v>
+        <v>10390014</v>
       </c>
       <c r="B175" s="3">
         <v>103900</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D175" s="23">
-        <v>4020655</v>
+        <v>74</v>
+      </c>
+      <c r="D175" s="24">
+        <v>4020653</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G175" s="23">
-        <v>2</v>
-      </c>
-      <c r="H175" s="23" t="s">
-        <v>213</v>
+        <v>72</v>
+      </c>
+      <c r="G175" s="24">
+        <v>2</v>
+      </c>
+      <c r="H175" s="24" t="s">
+        <v>212</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J175" s="20">
         <v>-1</v>
@@ -7326,25 +7330,25 @@
     </row>
     <row r="176" s="3" customFormat="1" spans="1:11">
       <c r="A176" s="3">
-        <v>10390017</v>
+        <v>10390015</v>
       </c>
       <c r="B176" s="3">
         <v>103900</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D176" s="23">
-        <v>4020656</v>
+        <v>77</v>
+      </c>
+      <c r="D176" s="24">
+        <v>4020654</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G176" s="3">
-        <v>2</v>
-      </c>
-      <c r="H176" s="23" t="s">
-        <v>214</v>
+        <v>72</v>
+      </c>
+      <c r="G176" s="24">
+        <v>2</v>
+      </c>
+      <c r="H176" s="24" t="s">
+        <v>213</v>
       </c>
       <c r="J176" s="20">
         <v>-1</v>
@@ -7355,26 +7359,28 @@
     </row>
     <row r="177" s="3" customFormat="1" spans="1:11">
       <c r="A177" s="3">
-        <v>10390018</v>
+        <v>10390016</v>
       </c>
       <c r="B177" s="3">
         <v>103900</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D177" s="23">
-        <v>4020657</v>
+        <v>79</v>
+      </c>
+      <c r="D177" s="24">
+        <v>4020655</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G177" s="23"/>
-      <c r="H177" s="23" t="s">
-        <v>215</v>
+        <v>80</v>
+      </c>
+      <c r="G177" s="24">
+        <v>2</v>
+      </c>
+      <c r="H177" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J177" s="20">
         <v>-1</v>
@@ -7385,25 +7391,25 @@
     </row>
     <row r="178" s="3" customFormat="1" spans="1:11">
       <c r="A178" s="3">
-        <v>10390019</v>
+        <v>10390017</v>
       </c>
       <c r="B178" s="3">
         <v>103900</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D178" s="23">
-        <v>4020658</v>
+        <v>83</v>
+      </c>
+      <c r="D178" s="24">
+        <v>4020656</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G178" s="23">
-        <v>2</v>
-      </c>
-      <c r="H178" s="23" t="s">
-        <v>216</v>
+        <v>80</v>
+      </c>
+      <c r="G178" s="3">
+        <v>2</v>
+      </c>
+      <c r="H178" s="24" t="s">
+        <v>215</v>
       </c>
       <c r="J178" s="20">
         <v>-1</v>
@@ -7414,180 +7420,170 @@
     </row>
     <row r="179" s="3" customFormat="1" spans="1:11">
       <c r="A179" s="3">
-        <v>10390020</v>
+        <v>10390018</v>
       </c>
       <c r="B179" s="3">
         <v>103900</v>
       </c>
-      <c r="C179" s="34" t="s">
+      <c r="C179" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D179" s="24">
+        <v>4020657</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G179" s="24"/>
+      <c r="H179" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J179" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K179" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180" s="3" customFormat="1" spans="1:11">
+      <c r="A180" s="3">
+        <v>10390019</v>
+      </c>
+      <c r="B180" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D180" s="24">
+        <v>4020658</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G180" s="24">
+        <v>2</v>
+      </c>
+      <c r="H180" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="J180" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K180" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="181" s="3" customFormat="1" spans="1:11">
+      <c r="A181" s="3">
+        <v>10390020</v>
+      </c>
+      <c r="B181" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C181" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D179" s="23">
+      <c r="D181" s="24">
         <v>4020651</v>
       </c>
-      <c r="E179" s="3" t="s">
+      <c r="E181" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G179" s="3">
-        <v>2</v>
-      </c>
-      <c r="H179" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="I179" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J179" s="4">
+      <c r="G181" s="3">
+        <v>2</v>
+      </c>
+      <c r="H181" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J181" s="4">
         <v>19</v>
       </c>
-      <c r="K179" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="180" s="4" customFormat="1" spans="1:11">
-      <c r="A180" s="4">
-        <v>10200001</v>
-      </c>
-      <c r="B180" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D180" s="25">
-        <v>4020002</v>
-      </c>
-      <c r="E180" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F180" s="4">
-        <v>1</v>
-      </c>
-      <c r="G180" s="4">
-        <v>2</v>
-      </c>
-      <c r="J180" s="4">
+      <c r="K181" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" s="3" customFormat="1" spans="1:11">
+      <c r="A182" s="3">
+        <v>10390021</v>
+      </c>
+      <c r="B182" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C182" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D182" s="24"/>
+      <c r="G182" s="3">
+        <v>2</v>
+      </c>
+      <c r="H182" s="24"/>
+      <c r="J182" s="20">
         <v>-1</v>
       </c>
-      <c r="K180" s="4">
+      <c r="K182" s="3">
         <v>0</v>
-      </c>
-    </row>
-    <row r="181" s="4" customFormat="1" spans="1:11">
-      <c r="A181" s="4">
-        <v>10200002</v>
-      </c>
-      <c r="B181" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D181" s="25">
-        <v>4020003</v>
-      </c>
-      <c r="E181" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G181" s="4">
-        <v>2</v>
-      </c>
-      <c r="H181" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="J181" s="4">
-        <v>1</v>
-      </c>
-      <c r="K181" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="182" s="4" customFormat="1" spans="1:11">
-      <c r="A182" s="4">
-        <v>10200003</v>
-      </c>
-      <c r="B182" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D182" s="25">
-        <v>4020645</v>
-      </c>
-      <c r="E182" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G182" s="25">
-        <v>2</v>
-      </c>
-      <c r="H182" s="25"/>
-      <c r="I182" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J182" s="4">
-        <v>2</v>
-      </c>
-      <c r="K182" s="4">
-        <v>100</v>
       </c>
     </row>
     <row r="183" s="4" customFormat="1" spans="1:11">
       <c r="A183" s="4">
-        <v>10200004</v>
+        <v>10200001</v>
       </c>
       <c r="B183" s="4">
         <v>102000</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D183" s="25">
-        <v>4020640</v>
+        <v>59</v>
+      </c>
+      <c r="D183" s="26">
+        <v>4020002</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="F183" s="4">
+        <v>1</v>
       </c>
       <c r="G183" s="4">
         <v>2</v>
       </c>
-      <c r="H183" s="25" t="s">
-        <v>219</v>
-      </c>
       <c r="J183" s="4">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K183" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" s="4" customFormat="1" spans="1:11">
       <c r="A184" s="4">
-        <v>10200005</v>
+        <v>10200002</v>
       </c>
       <c r="B184" s="4">
         <v>102000</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D184" s="25">
-        <v>4020646</v>
+        <v>63</v>
+      </c>
+      <c r="D184" s="26">
+        <v>4020003</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G184" s="25">
-        <v>2</v>
-      </c>
-      <c r="H184" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="I184" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="G184" s="4">
+        <v>2</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>219</v>
       </c>
       <c r="J184" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K184" s="4">
         <v>100</v>
@@ -7595,28 +7591,29 @@
     </row>
     <row r="185" s="4" customFormat="1" spans="1:11">
       <c r="A185" s="4">
-        <v>10200006</v>
+        <v>10200003</v>
       </c>
       <c r="B185" s="4">
         <v>102000</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D185" s="25">
-        <v>4020641</v>
+        <v>27</v>
+      </c>
+      <c r="D185" s="26">
+        <v>4020645</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G185" s="4">
-        <v>2</v>
-      </c>
-      <c r="H185" s="25" t="s">
-        <v>221</v>
+        <v>28</v>
+      </c>
+      <c r="G185" s="26">
+        <v>2</v>
+      </c>
+      <c r="H185" s="26"/>
+      <c r="I185" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="J185" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K185" s="4">
         <v>100</v>
@@ -7624,31 +7621,28 @@
     </row>
     <row r="186" s="4" customFormat="1" spans="1:11">
       <c r="A186" s="4">
-        <v>10200007</v>
+        <v>10200004</v>
       </c>
       <c r="B186" s="4">
         <v>102000</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D186" s="25">
-        <v>4020647</v>
+        <v>31</v>
+      </c>
+      <c r="D186" s="26">
+        <v>4020640</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G186" s="25">
-        <v>2</v>
-      </c>
-      <c r="H186" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="I186" s="4" t="s">
-        <v>41</v>
+        <v>28</v>
+      </c>
+      <c r="G186" s="4">
+        <v>2</v>
+      </c>
+      <c r="H186" s="26" t="s">
+        <v>220</v>
       </c>
       <c r="J186" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K186" s="4">
         <v>100</v>
@@ -7656,28 +7650,31 @@
     </row>
     <row r="187" s="4" customFormat="1" spans="1:11">
       <c r="A187" s="4">
-        <v>10200008</v>
+        <v>10200005</v>
       </c>
       <c r="B187" s="4">
         <v>102000</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D187" s="25">
-        <v>4020642</v>
+        <v>33</v>
+      </c>
+      <c r="D187" s="26">
+        <v>4020646</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G187" s="4">
-        <v>2</v>
-      </c>
-      <c r="H187" s="25" t="s">
-        <v>223</v>
+        <v>34</v>
+      </c>
+      <c r="G187" s="26">
+        <v>2</v>
+      </c>
+      <c r="H187" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="J187" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K187" s="4">
         <v>100</v>
@@ -7685,31 +7682,28 @@
     </row>
     <row r="188" s="4" customFormat="1" spans="1:11">
       <c r="A188" s="4">
-        <v>10200009</v>
+        <v>10200006</v>
       </c>
       <c r="B188" s="4">
         <v>102000</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D188" s="25">
-        <v>4020648</v>
+        <v>37</v>
+      </c>
+      <c r="D188" s="26">
+        <v>4020641</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G188" s="25">
-        <v>2</v>
-      </c>
-      <c r="H188" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="I188" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="G188" s="4">
+        <v>2</v>
+      </c>
+      <c r="H188" s="26" t="s">
+        <v>222</v>
       </c>
       <c r="J188" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K188" s="4">
         <v>100</v>
@@ -7717,28 +7711,31 @@
     </row>
     <row r="189" s="4" customFormat="1" spans="1:11">
       <c r="A189" s="4">
-        <v>10200010</v>
+        <v>10200007</v>
       </c>
       <c r="B189" s="4">
         <v>102000</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D189" s="25">
-        <v>4020643</v>
+        <v>39</v>
+      </c>
+      <c r="D189" s="26">
+        <v>4020647</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G189" s="4">
-        <v>2</v>
-      </c>
-      <c r="H189" s="25" t="s">
-        <v>225</v>
+        <v>40</v>
+      </c>
+      <c r="G189" s="26">
+        <v>2</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="J189" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K189" s="4">
         <v>100</v>
@@ -7746,31 +7743,28 @@
     </row>
     <row r="190" s="4" customFormat="1" spans="1:11">
       <c r="A190" s="4">
-        <v>10200011</v>
+        <v>10200008</v>
       </c>
       <c r="B190" s="4">
         <v>102000</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D190" s="25">
-        <v>4020649</v>
+        <v>42</v>
+      </c>
+      <c r="D190" s="26">
+        <v>4020642</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G190" s="4">
         <v>2</v>
       </c>
-      <c r="H190" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="I190" s="4" t="s">
-        <v>49</v>
+      <c r="H190" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="J190" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K190" s="4">
         <v>100</v>
@@ -7778,28 +7772,31 @@
     </row>
     <row r="191" s="4" customFormat="1" spans="1:11">
       <c r="A191" s="4">
-        <v>10200012</v>
+        <v>10200009</v>
       </c>
       <c r="B191" s="4">
         <v>102000</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D191" s="25">
-        <v>4020644</v>
+        <v>43</v>
+      </c>
+      <c r="D191" s="26">
+        <v>4020648</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G191" s="4">
-        <v>2</v>
-      </c>
-      <c r="H191" s="25" t="s">
-        <v>227</v>
+        <v>44</v>
+      </c>
+      <c r="G191" s="26">
+        <v>2</v>
+      </c>
+      <c r="H191" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="J191" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K191" s="4">
         <v>100</v>
@@ -7807,29 +7804,28 @@
     </row>
     <row r="192" s="4" customFormat="1" spans="1:11">
       <c r="A192" s="4">
-        <v>10200013</v>
+        <v>10200010</v>
       </c>
       <c r="B192" s="4">
         <v>102000</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D192" s="25">
-        <v>4020650</v>
+        <v>46</v>
+      </c>
+      <c r="D192" s="26">
+        <v>4020643</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G192" s="4">
         <v>2</v>
       </c>
-      <c r="H192" s="25"/>
-      <c r="I192" s="4" t="s">
-        <v>73</v>
+      <c r="H192" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="J192" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K192" s="4">
         <v>100</v>
@@ -7837,31 +7833,31 @@
     </row>
     <row r="193" s="4" customFormat="1" spans="1:11">
       <c r="A193" s="4">
-        <v>10200014</v>
+        <v>10200011</v>
       </c>
       <c r="B193" s="4">
         <v>102000</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D193" s="25">
-        <v>4020653</v>
+        <v>47</v>
+      </c>
+      <c r="D193" s="26">
+        <v>4020649</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G193" s="4">
         <v>2</v>
       </c>
-      <c r="H193" s="25" t="s">
-        <v>228</v>
+      <c r="H193" s="26" t="s">
+        <v>227</v>
       </c>
       <c r="I193" s="4" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="J193" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K193" s="4">
         <v>100</v>
@@ -7869,28 +7865,28 @@
     </row>
     <row r="194" s="4" customFormat="1" spans="1:11">
       <c r="A194" s="4">
-        <v>10200015</v>
+        <v>10200012</v>
       </c>
       <c r="B194" s="4">
         <v>102000</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D194" s="25">
-        <v>4020654</v>
+        <v>50</v>
+      </c>
+      <c r="D194" s="26">
+        <v>4020644</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G194" s="4">
         <v>2</v>
       </c>
-      <c r="H194" s="25" t="s">
-        <v>229</v>
+      <c r="H194" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="J194" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K194" s="4">
         <v>100</v>
@@ -7898,31 +7894,29 @@
     </row>
     <row r="195" s="4" customFormat="1" spans="1:11">
       <c r="A195" s="4">
-        <v>10200016</v>
+        <v>10200013</v>
       </c>
       <c r="B195" s="4">
         <v>102000</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D195" s="25">
-        <v>4020655</v>
+        <v>71</v>
+      </c>
+      <c r="D195" s="26">
+        <v>4020650</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G195" s="4">
         <v>2</v>
       </c>
-      <c r="H195" s="25" t="s">
-        <v>230</v>
-      </c>
+      <c r="H195" s="26"/>
       <c r="I195" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J195" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K195" s="4">
         <v>100</v>
@@ -7930,28 +7924,31 @@
     </row>
     <row r="196" s="4" customFormat="1" spans="1:11">
       <c r="A196" s="4">
-        <v>10200017</v>
+        <v>10200014</v>
       </c>
       <c r="B196" s="4">
         <v>102000</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D196" s="25">
-        <v>4020656</v>
+        <v>74</v>
+      </c>
+      <c r="D196" s="26">
+        <v>4020653</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G196" s="4">
         <v>2</v>
       </c>
-      <c r="H196" s="25" t="s">
-        <v>231</v>
+      <c r="H196" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="J196" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K196" s="4">
         <v>100</v>
@@ -7959,28 +7956,28 @@
     </row>
     <row r="197" s="4" customFormat="1" spans="1:11">
       <c r="A197" s="4">
-        <v>10200018</v>
+        <v>10200015</v>
       </c>
       <c r="B197" s="4">
         <v>102000</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D197" s="25">
-        <v>4020657</v>
+        <v>77</v>
+      </c>
+      <c r="D197" s="26">
+        <v>4020654</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H197" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="I197" s="4" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G197" s="4">
+        <v>2</v>
+      </c>
+      <c r="H197" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="J197" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K197" s="4">
         <v>100</v>
@@ -7988,28 +7985,31 @@
     </row>
     <row r="198" s="4" customFormat="1" spans="1:11">
       <c r="A198" s="4">
-        <v>10200019</v>
+        <v>10200016</v>
       </c>
       <c r="B198" s="4">
         <v>102000</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D198" s="25">
-        <v>4020658</v>
+        <v>79</v>
+      </c>
+      <c r="D198" s="26">
+        <v>4020655</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G198" s="4">
         <v>2</v>
       </c>
-      <c r="H198" s="25" t="s">
-        <v>233</v>
+      <c r="H198" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="J198" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K198" s="4">
         <v>100</v>
@@ -8017,179 +8017,176 @@
     </row>
     <row r="199" s="4" customFormat="1" spans="1:11">
       <c r="A199" s="4">
-        <v>10200020</v>
+        <v>10200017</v>
       </c>
       <c r="B199" s="4">
         <v>102000</v>
       </c>
       <c r="C199" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D199" s="26">
+        <v>4020656</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G199" s="4">
+        <v>2</v>
+      </c>
+      <c r="H199" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="J199" s="4">
+        <v>16</v>
+      </c>
+      <c r="K199" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="200" s="4" customFormat="1" spans="1:11">
+      <c r="A200" s="4">
+        <v>10200018</v>
+      </c>
+      <c r="B200" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D200" s="26">
+        <v>4020657</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H200" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J200" s="4">
+        <v>17</v>
+      </c>
+      <c r="K200" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="201" s="4" customFormat="1" spans="1:11">
+      <c r="A201" s="4">
+        <v>10200019</v>
+      </c>
+      <c r="B201" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D201" s="26">
+        <v>4020658</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G201" s="4">
+        <v>2</v>
+      </c>
+      <c r="H201" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="J201" s="4">
+        <v>18</v>
+      </c>
+      <c r="K201" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="202" s="4" customFormat="1" spans="1:11">
+      <c r="A202" s="4">
+        <v>10200020</v>
+      </c>
+      <c r="B202" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D199" s="25">
+      <c r="D202" s="26">
         <v>4020651</v>
       </c>
-      <c r="E199" s="4" t="s">
+      <c r="E202" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G199" s="4">
-        <v>2</v>
-      </c>
-      <c r="H199" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="I199" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J199" s="4">
+      <c r="G202" s="4">
+        <v>2</v>
+      </c>
+      <c r="H202" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J202" s="4">
         <v>19</v>
       </c>
-      <c r="K199" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="200" s="5" customFormat="1" spans="1:11">
-      <c r="A200" s="5">
-        <v>10270001</v>
-      </c>
-      <c r="B200" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D200" s="28">
-        <v>4020002</v>
-      </c>
-      <c r="E200" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F200" s="5">
-        <v>1</v>
-      </c>
-      <c r="G200" s="5">
-        <v>2</v>
-      </c>
-      <c r="J200" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K200" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" s="5" customFormat="1" spans="1:11">
-      <c r="A201" s="5">
-        <v>10270003</v>
-      </c>
-      <c r="B201" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C201" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D201" s="28">
-        <v>4020645</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="G201" s="5">
-        <v>2</v>
-      </c>
-      <c r="I201" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J201" s="5">
-        <v>2</v>
-      </c>
-      <c r="K201" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="202" s="5" customFormat="1" spans="1:11">
-      <c r="A202" s="5">
-        <v>10270004</v>
-      </c>
-      <c r="B202" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C202" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D202" s="28">
-        <v>4020640</v>
-      </c>
-      <c r="E202" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="G202" s="5">
-        <v>2</v>
-      </c>
-      <c r="H202" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="J202" s="5">
-        <v>3</v>
-      </c>
-      <c r="K202" s="5">
+      <c r="K202" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="203" s="5" customFormat="1" spans="1:11">
       <c r="A203" s="5">
-        <v>10270005</v>
+        <v>10270001</v>
       </c>
       <c r="B203" s="5">
         <v>102700</v>
       </c>
-      <c r="C203" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D203" s="28">
-        <v>4020646</v>
+      <c r="C203" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D203" s="30">
+        <v>4020002</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="F203" s="5">
+        <v>1</v>
       </c>
       <c r="G203" s="5">
         <v>2</v>
       </c>
-      <c r="H203" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="I203" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="J203" s="5">
-        <v>4</v>
+      <c r="J203" s="20">
+        <v>-1</v>
       </c>
       <c r="K203" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" s="5" customFormat="1" spans="1:11">
       <c r="A204" s="5">
-        <v>10270006</v>
+        <v>10270003</v>
       </c>
       <c r="B204" s="5">
         <v>102700</v>
       </c>
-      <c r="C204" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D204" s="28">
-        <v>4020641</v>
+      <c r="C204" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="30">
+        <v>4020645</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>34</v>
+        <v>236</v>
       </c>
       <c r="G204" s="5">
         <v>2</v>
       </c>
-      <c r="H204" s="5" t="s">
-        <v>240</v>
+      <c r="I204" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="J204" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K204" s="5">
         <v>100</v>
@@ -8197,60 +8194,60 @@
     </row>
     <row r="205" s="5" customFormat="1" spans="1:11">
       <c r="A205" s="5">
-        <v>10270002</v>
+        <v>10270004</v>
       </c>
       <c r="B205" s="5">
         <v>102700</v>
       </c>
-      <c r="C205" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D205" s="28">
-        <v>4020003</v>
+      <c r="C205" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D205" s="30">
+        <v>4020640</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>25</v>
+        <v>236</v>
       </c>
       <c r="G205" s="5">
         <v>2</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="J205" s="20">
-        <v>-1</v>
+        <v>238</v>
+      </c>
+      <c r="J205" s="5">
+        <v>3</v>
       </c>
       <c r="K205" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="206" s="5" customFormat="1" ht="20" customHeight="1" spans="1:11">
+    <row r="206" s="5" customFormat="1" spans="1:11">
       <c r="A206" s="5">
-        <v>10270007</v>
+        <v>10270005</v>
       </c>
       <c r="B206" s="5">
         <v>102700</v>
       </c>
-      <c r="C206" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="D206" s="28">
-        <v>4020647</v>
+      <c r="C206" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D206" s="30">
+        <v>4020646</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G206" s="5">
         <v>2</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J206" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K206" s="5">
         <v>100</v>
@@ -8258,28 +8255,28 @@
     </row>
     <row r="207" s="5" customFormat="1" spans="1:11">
       <c r="A207" s="5">
-        <v>10270008</v>
+        <v>10270006</v>
       </c>
       <c r="B207" s="5">
         <v>102700</v>
       </c>
-      <c r="C207" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D207" s="28">
-        <v>4020642</v>
+      <c r="C207" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D207" s="30">
+        <v>4020641</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G207" s="5">
         <v>2</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J207" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K207" s="5">
         <v>100</v>
@@ -8287,28 +8284,25 @@
     </row>
     <row r="208" s="5" customFormat="1" spans="1:11">
       <c r="A208" s="5">
-        <v>10270009</v>
+        <v>10270002</v>
       </c>
       <c r="B208" s="5">
         <v>102700</v>
       </c>
-      <c r="C208" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D208" s="28">
-        <v>4020648</v>
+      <c r="C208" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D208" s="30">
+        <v>4020003</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G208" s="5">
         <v>2</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="I208" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J208" s="20">
         <v>-1</v>
@@ -8317,30 +8311,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="209" s="5" customFormat="1" spans="1:11">
+    <row r="209" s="5" customFormat="1" ht="20" customHeight="1" spans="1:11">
       <c r="A209" s="5">
-        <v>10270010</v>
+        <v>10270007</v>
       </c>
       <c r="B209" s="5">
         <v>102700</v>
       </c>
-      <c r="C209" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D209" s="28">
-        <v>4020643</v>
+      <c r="C209" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D209" s="30">
+        <v>4020647</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G209" s="5">
         <v>2</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="J209" s="20">
-        <v>-1</v>
+        <v>242</v>
+      </c>
+      <c r="I209" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J209" s="5">
+        <v>6</v>
       </c>
       <c r="K209" s="5">
         <v>100</v>
@@ -8348,31 +8345,28 @@
     </row>
     <row r="210" s="5" customFormat="1" spans="1:11">
       <c r="A210" s="5">
-        <v>10270011</v>
+        <v>10270008</v>
       </c>
       <c r="B210" s="5">
         <v>102700</v>
       </c>
-      <c r="C210" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D210" s="28">
-        <v>4020649</v>
+      <c r="C210" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D210" s="30">
+        <v>4020642</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G210" s="5">
         <v>2</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="I210" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="J210" s="20">
-        <v>-1</v>
+        <v>244</v>
+      </c>
+      <c r="J210" s="5">
+        <v>7</v>
       </c>
       <c r="K210" s="5">
         <v>100</v>
@@ -8380,25 +8374,28 @@
     </row>
     <row r="211" s="5" customFormat="1" spans="1:11">
       <c r="A211" s="5">
-        <v>10270012</v>
+        <v>10270009</v>
       </c>
       <c r="B211" s="5">
         <v>102700</v>
       </c>
-      <c r="C211" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="D211" s="28">
-        <v>4020644</v>
+      <c r="C211" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D211" s="30">
+        <v>4020648</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G211" s="5">
         <v>2</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
+      </c>
+      <c r="I211" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="J211" s="20">
         <v>-1</v>
@@ -8409,28 +8406,28 @@
     </row>
     <row r="212" s="5" customFormat="1" spans="1:11">
       <c r="A212" s="5">
-        <v>10270013</v>
+        <v>10270010</v>
       </c>
       <c r="B212" s="5">
         <v>102700</v>
       </c>
-      <c r="C212" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D212" s="28">
-        <v>4020650</v>
+      <c r="C212" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D212" s="30">
+        <v>4020643</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G212" s="5">
         <v>2</v>
       </c>
-      <c r="I212" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="J212" s="5">
-        <v>12</v>
+      <c r="H212" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="J212" s="20">
+        <v>-1</v>
       </c>
       <c r="K212" s="5">
         <v>100</v>
@@ -8438,31 +8435,31 @@
     </row>
     <row r="213" s="5" customFormat="1" spans="1:11">
       <c r="A213" s="5">
-        <v>10270014</v>
+        <v>10270011</v>
       </c>
       <c r="B213" s="5">
         <v>102700</v>
       </c>
-      <c r="C213" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D213" s="28">
-        <v>4020653</v>
+      <c r="C213" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D213" s="30">
+        <v>4020649</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G213" s="5">
         <v>2</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J213" s="5">
-        <v>13</v>
+        <v>249</v>
+      </c>
+      <c r="J213" s="20">
+        <v>-1</v>
       </c>
       <c r="K213" s="5">
         <v>100</v>
@@ -8470,25 +8467,25 @@
     </row>
     <row r="214" s="5" customFormat="1" spans="1:11">
       <c r="A214" s="5">
-        <v>10270015</v>
+        <v>10270012</v>
       </c>
       <c r="B214" s="5">
         <v>102700</v>
       </c>
-      <c r="C214" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D214" s="28">
-        <v>4020654</v>
+      <c r="C214" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D214" s="30">
+        <v>4020644</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G214" s="5">
         <v>2</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J214" s="20">
         <v>-1</v>
@@ -8499,31 +8496,28 @@
     </row>
     <row r="215" s="5" customFormat="1" spans="1:11">
       <c r="A215" s="5">
-        <v>10270016</v>
+        <v>10270013</v>
       </c>
       <c r="B215" s="5">
         <v>102700</v>
       </c>
-      <c r="C215" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D215" s="28">
-        <v>4020655</v>
+      <c r="C215" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D215" s="30">
+        <v>4020650</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G215" s="5">
         <v>2</v>
       </c>
-      <c r="H215" s="5" t="s">
-        <v>254</v>
-      </c>
       <c r="I215" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="J215" s="20">
-        <v>-1</v>
+        <v>251</v>
+      </c>
+      <c r="J215" s="5">
+        <v>12</v>
       </c>
       <c r="K215" s="5">
         <v>100</v>
@@ -8531,28 +8525,31 @@
     </row>
     <row r="216" s="5" customFormat="1" spans="1:11">
       <c r="A216" s="5">
-        <v>10270017</v>
+        <v>10270014</v>
       </c>
       <c r="B216" s="5">
         <v>102700</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D216" s="28">
-        <v>4020656</v>
+        <v>74</v>
+      </c>
+      <c r="D216" s="30">
+        <v>4020653</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G216" s="5">
         <v>2</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="J216" s="20">
-        <v>-1</v>
+        <v>252</v>
+      </c>
+      <c r="I216" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J216" s="5">
+        <v>13</v>
       </c>
       <c r="K216" s="5">
         <v>100</v>
@@ -8560,29 +8557,25 @@
     </row>
     <row r="217" s="5" customFormat="1" spans="1:11">
       <c r="A217" s="5">
-        <v>10270018</v>
+        <v>10270015</v>
       </c>
       <c r="B217" s="5">
         <v>102700</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D217" s="28">
-        <v>4020657</v>
+        <v>77</v>
+      </c>
+      <c r="D217" s="30">
+        <v>4020654</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F217" s="35"/>
+        <v>72</v>
+      </c>
       <c r="G217" s="5">
         <v>2</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="I217" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J217" s="20">
         <v>-1</v>
@@ -8593,25 +8586,28 @@
     </row>
     <row r="218" s="5" customFormat="1" spans="1:11">
       <c r="A218" s="5">
-        <v>10270019</v>
+        <v>10270016</v>
       </c>
       <c r="B218" s="5">
         <v>102700</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D218" s="28">
-        <v>4020658</v>
+        <v>79</v>
+      </c>
+      <c r="D218" s="30">
+        <v>4020655</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G218" s="5">
         <v>2</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
+      </c>
+      <c r="I218" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="J218" s="20">
         <v>-1</v>
@@ -8622,209 +8618,202 @@
     </row>
     <row r="219" s="5" customFormat="1" spans="1:11">
       <c r="A219" s="5">
-        <v>10270020</v>
+        <v>10270017</v>
       </c>
       <c r="B219" s="5">
         <v>102700</v>
       </c>
-      <c r="C219" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D219" s="28">
-        <v>4020651</v>
+      <c r="C219" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D219" s="30">
+        <v>4020656</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G219" s="5">
         <v>2</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="I219" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="J219" s="5">
-        <v>19</v>
+        <v>257</v>
+      </c>
+      <c r="J219" s="20">
+        <v>-1</v>
       </c>
       <c r="K219" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="220" s="1" customFormat="1" spans="1:11">
-      <c r="A220" s="1">
-        <v>10150001</v>
-      </c>
-      <c r="B220" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D220" s="16">
-        <v>4020002</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F220" s="1">
-        <v>1</v>
-      </c>
-      <c r="G220" s="1">
-        <v>2</v>
+    <row r="220" s="5" customFormat="1" spans="1:11">
+      <c r="A220" s="5">
+        <v>10270018</v>
+      </c>
+      <c r="B220" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D220" s="30">
+        <v>4020657</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F220" s="38"/>
+      <c r="G220" s="5">
+        <v>2</v>
+      </c>
+      <c r="H220" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I220" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="J220" s="20">
         <v>-1</v>
       </c>
-      <c r="K220" s="1">
+      <c r="K220" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="221" s="5" customFormat="1" spans="1:11">
+      <c r="A221" s="5">
+        <v>10270019</v>
+      </c>
+      <c r="B221" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D221" s="30">
+        <v>4020658</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G221" s="5">
+        <v>2</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J221" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K221" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" s="5" customFormat="1" spans="1:11">
+      <c r="A222" s="5">
+        <v>10270020</v>
+      </c>
+      <c r="B222" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C222" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D222" s="30">
+        <v>4020651</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G222" s="5">
+        <v>2</v>
+      </c>
+      <c r="H222" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="I222" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="J222" s="5">
+        <v>19</v>
+      </c>
+      <c r="K222" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="223" s="5" customFormat="1" spans="1:11">
+      <c r="A223" s="5">
+        <v>10270021</v>
+      </c>
+      <c r="B223" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C223" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D223" s="30"/>
+      <c r="G223" s="5">
+        <v>2</v>
+      </c>
+      <c r="J223" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K223" s="5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="221" s="1" customFormat="1" spans="1:11">
-      <c r="A221" s="1">
-        <v>10150003</v>
-      </c>
-      <c r="B221" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D221" s="16">
-        <v>4020645</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G221" s="1">
-        <v>2</v>
-      </c>
-      <c r="H221" s="1"/>
-      <c r="I221" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J221" s="5">
-        <v>2</v>
-      </c>
-      <c r="K221" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="222" s="1" customFormat="1" spans="1:11">
-      <c r="A222" s="1">
-        <v>10150004</v>
-      </c>
-      <c r="B222" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D222" s="16">
-        <v>4020640</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G222" s="1">
-        <v>2</v>
-      </c>
-      <c r="H222" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="J222" s="5">
-        <v>3</v>
-      </c>
-      <c r="K222" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="223" s="1" customFormat="1" spans="1:11">
-      <c r="A223" s="1">
-        <v>10150005</v>
-      </c>
-      <c r="B223" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D223" s="16">
-        <v>4020646</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G223" s="1">
-        <v>2</v>
-      </c>
-      <c r="H223" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I223" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J223" s="5">
-        <v>4</v>
-      </c>
-      <c r="K223" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" spans="1:11">
       <c r="A224" s="1">
-        <v>10150006</v>
+        <v>10150001</v>
       </c>
       <c r="B224" s="1">
         <v>101500</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D224" s="16">
-        <v>4020641</v>
+        <v>4020002</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="F224" s="1">
+        <v>1</v>
       </c>
       <c r="G224" s="1">
         <v>2</v>
       </c>
-      <c r="H224" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J224" s="5">
-        <v>5</v>
+      <c r="J224" s="20">
+        <v>-1</v>
       </c>
       <c r="K224" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" spans="1:11">
       <c r="A225" s="1">
-        <v>10150002</v>
+        <v>10150003</v>
       </c>
       <c r="B225" s="1">
         <v>101500</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D225" s="16">
-        <v>4020003</v>
+        <v>4020645</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>25</v>
+        <v>236</v>
       </c>
       <c r="G225" s="1">
         <v>2</v>
       </c>
-      <c r="H225" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="J225" s="20">
-        <v>-1</v>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J225" s="5">
+        <v>2</v>
       </c>
       <c r="K225" s="1">
         <v>100</v>
@@ -8832,31 +8821,28 @@
     </row>
     <row r="226" s="1" customFormat="1" spans="1:11">
       <c r="A226" s="1">
-        <v>10150007</v>
+        <v>10150004</v>
       </c>
       <c r="B226" s="1">
         <v>101500</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D226" s="16">
-        <v>4020647</v>
+        <v>4020640</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>40</v>
+        <v>236</v>
       </c>
       <c r="G226" s="1">
         <v>2</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="I226" s="1" t="s">
-        <v>41</v>
+        <v>263</v>
       </c>
       <c r="J226" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K226" s="1">
         <v>100</v>
@@ -8864,28 +8850,31 @@
     </row>
     <row r="227" s="1" customFormat="1" spans="1:11">
       <c r="A227" s="1">
-        <v>10150008</v>
+        <v>10150005</v>
       </c>
       <c r="B227" s="1">
         <v>101500</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D227" s="16">
-        <v>4020642</v>
+        <v>4020646</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G227" s="1">
         <v>2</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="J227" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K227" s="1">
         <v>100</v>
@@ -8893,31 +8882,28 @@
     </row>
     <row r="228" s="1" customFormat="1" spans="1:11">
       <c r="A228" s="1">
-        <v>10150009</v>
+        <v>10150006</v>
       </c>
       <c r="B228" s="1">
         <v>101500</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D228" s="16">
-        <v>4020648</v>
+        <v>4020641</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G228" s="1">
         <v>2</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="I228" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J228" s="20">
-        <v>-1</v>
+        <v>265</v>
+      </c>
+      <c r="J228" s="5">
+        <v>5</v>
       </c>
       <c r="K228" s="1">
         <v>100</v>
@@ -8925,25 +8911,25 @@
     </row>
     <row r="229" s="1" customFormat="1" spans="1:11">
       <c r="A229" s="1">
-        <v>10150010</v>
+        <v>10150002</v>
       </c>
       <c r="B229" s="1">
         <v>101500</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D229" s="16">
-        <v>4020643</v>
+        <v>4020003</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G229" s="1">
         <v>2</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J229" s="20">
         <v>-1</v>
@@ -8954,31 +8940,31 @@
     </row>
     <row r="230" s="1" customFormat="1" spans="1:11">
       <c r="A230" s="1">
-        <v>10150011</v>
+        <v>10150007</v>
       </c>
       <c r="B230" s="1">
         <v>101500</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D230" s="16">
-        <v>4020649</v>
+        <v>4020647</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G230" s="1">
         <v>2</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J230" s="20">
-        <v>-1</v>
+        <v>41</v>
+      </c>
+      <c r="J230" s="5">
+        <v>6</v>
       </c>
       <c r="K230" s="1">
         <v>100</v>
@@ -8986,28 +8972,28 @@
     </row>
     <row r="231" s="1" customFormat="1" spans="1:11">
       <c r="A231" s="1">
-        <v>10150012</v>
+        <v>10150008</v>
       </c>
       <c r="B231" s="1">
         <v>101500</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D231" s="16">
-        <v>4020644</v>
+        <v>4020642</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G231" s="1">
         <v>2</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="J231" s="20">
-        <v>-1</v>
+        <v>267</v>
+      </c>
+      <c r="J231" s="5">
+        <v>7</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>
@@ -9015,29 +9001,31 @@
     </row>
     <row r="232" s="1" customFormat="1" spans="1:11">
       <c r="A232" s="1">
-        <v>10150013</v>
+        <v>10150009</v>
       </c>
       <c r="B232" s="1">
         <v>101500</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D232" s="16">
-        <v>4020650</v>
+        <v>4020648</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G232" s="1">
         <v>2</v>
       </c>
-      <c r="H232" s="1"/>
+      <c r="H232" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I232" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J232" s="5">
-        <v>12</v>
+        <v>45</v>
+      </c>
+      <c r="J232" s="20">
+        <v>-1</v>
       </c>
       <c r="K232" s="1">
         <v>100</v>
@@ -9045,31 +9033,28 @@
     </row>
     <row r="233" s="1" customFormat="1" spans="1:11">
       <c r="A233" s="1">
-        <v>10150014</v>
+        <v>10150010</v>
       </c>
       <c r="B233" s="1">
         <v>101500</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D233" s="16">
-        <v>4020653</v>
+        <v>4020643</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G233" s="1">
         <v>2</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I233" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J233" s="5">
-        <v>13</v>
+        <v>269</v>
+      </c>
+      <c r="J233" s="20">
+        <v>-1</v>
       </c>
       <c r="K233" s="1">
         <v>100</v>
@@ -9077,28 +9062,31 @@
     </row>
     <row r="234" s="1" customFormat="1" spans="1:11">
       <c r="A234" s="1">
-        <v>10150015</v>
+        <v>10150011</v>
       </c>
       <c r="B234" s="1">
         <v>101500</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D234" s="16">
-        <v>4020654</v>
+        <v>4020649</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G234" s="1">
         <v>2</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J234" s="5">
-        <v>14</v>
+        <v>270</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J234" s="20">
+        <v>-1</v>
       </c>
       <c r="K234" s="1">
         <v>100</v>
@@ -9106,28 +9094,25 @@
     </row>
     <row r="235" s="1" customFormat="1" spans="1:11">
       <c r="A235" s="1">
-        <v>10150016</v>
+        <v>10150012</v>
       </c>
       <c r="B235" s="1">
         <v>101500</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D235" s="16">
-        <v>4020655</v>
+        <v>4020644</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G235" s="1">
         <v>2</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="I235" s="1" t="s">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="J235" s="20">
         <v>-1</v>
@@ -9138,28 +9123,29 @@
     </row>
     <row r="236" s="1" customFormat="1" spans="1:11">
       <c r="A236" s="1">
-        <v>10150017</v>
+        <v>10150013</v>
       </c>
       <c r="B236" s="1">
         <v>101500</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D236" s="16">
-        <v>4020656</v>
+        <v>4020650</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G236" s="1">
         <v>2</v>
       </c>
-      <c r="H236" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J236" s="20">
-        <v>-1</v>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J236" s="5">
+        <v>12</v>
       </c>
       <c r="K236" s="1">
         <v>100</v>
@@ -9167,31 +9153,31 @@
     </row>
     <row r="237" s="1" customFormat="1" spans="1:11">
       <c r="A237" s="1">
-        <v>10150018</v>
+        <v>10150014</v>
       </c>
       <c r="B237" s="1">
         <v>101500</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D237" s="16">
-        <v>4020657</v>
+        <v>4020653</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G237" s="1">
         <v>2</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J237" s="20">
-        <v>-1</v>
+        <v>76</v>
+      </c>
+      <c r="J237" s="5">
+        <v>13</v>
       </c>
       <c r="K237" s="1">
         <v>100</v>
@@ -9199,28 +9185,28 @@
     </row>
     <row r="238" s="1" customFormat="1" spans="1:11">
       <c r="A238" s="1">
-        <v>10150019</v>
+        <v>10150015</v>
       </c>
       <c r="B238" s="1">
         <v>101500</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D238" s="16">
-        <v>4020658</v>
+        <v>4020654</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G238" s="1">
         <v>2</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="J238" s="20">
-        <v>-1</v>
+        <v>273</v>
+      </c>
+      <c r="J238" s="5">
+        <v>14</v>
       </c>
       <c r="K238" s="1">
         <v>100</v>
@@ -9228,33 +9214,155 @@
     </row>
     <row r="239" s="1" customFormat="1" spans="1:11">
       <c r="A239" s="1">
-        <v>10150020</v>
+        <v>10150016</v>
       </c>
       <c r="B239" s="1">
         <v>101500</v>
       </c>
       <c r="C239" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D239" s="16">
+        <v>4020655</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G239" s="1">
+        <v>2</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J239" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K239" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="240" s="1" customFormat="1" spans="1:11">
+      <c r="A240" s="1">
+        <v>10150017</v>
+      </c>
+      <c r="B240" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D240" s="16">
+        <v>4020656</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G240" s="1">
+        <v>2</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J240" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K240" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="241" s="1" customFormat="1" spans="1:11">
+      <c r="A241" s="1">
+        <v>10150018</v>
+      </c>
+      <c r="B241" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D241" s="16">
+        <v>4020657</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G241" s="1">
+        <v>2</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J241" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K241" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="242" s="1" customFormat="1" spans="1:11">
+      <c r="A242" s="1">
+        <v>10150019</v>
+      </c>
+      <c r="B242" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D242" s="16">
+        <v>4020658</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G242" s="1">
+        <v>2</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J242" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K242" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="243" s="1" customFormat="1" spans="1:11">
+      <c r="A243" s="1">
+        <v>10150020</v>
+      </c>
+      <c r="B243" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C243" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D239" s="16">
+      <c r="D243" s="16">
         <v>4020651</v>
       </c>
-      <c r="E239" s="1" t="s">
+      <c r="E243" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G239" s="1">
-        <v>2</v>
-      </c>
-      <c r="H239" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I239" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J239" s="5">
+      <c r="G243" s="1">
+        <v>2</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J243" s="5">
         <v>19</v>
       </c>
-      <c r="K239" s="1">
+      <c r="K243" s="1">
         <v>100</v>
       </c>
     </row>

--- a/hall/resources/sample/prop.xlsx
+++ b/hall/resources/sample/prop.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="278">
   <si>
     <t>属性id</t>
   </si>
@@ -580,9 +580,6 @@
   </si>
   <si>
     <t>10310005,1</t>
-  </si>
-  <si>
-    <t>10310002,10</t>
   </si>
   <si>
     <t>10310007,1</t>
@@ -2073,7 +2070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L243"/>
+  <dimension ref="A1:L244"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="8" customWidth="1"/>
@@ -5104,7 +5101,7 @@
       <c r="G102" s="6">
         <v>2</v>
       </c>
-      <c r="J102" s="6">
+      <c r="J102" s="20">
         <v>-1</v>
       </c>
       <c r="K102" s="6">
@@ -5134,8 +5131,8 @@
       <c r="H103" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="J103" s="6">
-        <v>1</v>
+      <c r="J103" s="20">
+        <v>-1</v>
       </c>
       <c r="K103" s="6">
         <v>100</v>
@@ -5282,7 +5279,7 @@
         <v>2</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I108" s="6" t="s">
         <v>41</v>
@@ -5314,7 +5311,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J109" s="6">
         <v>7</v>
@@ -5343,7 +5340,7 @@
         <v>2</v>
       </c>
       <c r="H110" s="33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>45</v>
@@ -5375,7 +5372,7 @@
         <v>2</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J111" s="6">
         <v>9</v>
@@ -5404,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="H112" s="33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I112" s="6" t="s">
         <v>49</v>
@@ -5436,7 +5433,7 @@
         <v>2</v>
       </c>
       <c r="H113" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J113" s="6">
         <v>11</v>
@@ -5495,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="H115" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I115" s="6" t="s">
         <v>76</v>
@@ -5527,7 +5524,7 @@
         <v>2</v>
       </c>
       <c r="H116" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J116" s="6">
         <v>14</v>
@@ -5556,7 +5553,7 @@
         <v>2</v>
       </c>
       <c r="H117" s="33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I117" s="6" t="s">
         <v>82</v>
@@ -5588,7 +5585,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J118" s="6">
         <v>16</v>
@@ -5617,13 +5614,13 @@
         <v>2</v>
       </c>
       <c r="H119" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I119" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="J119" s="6">
-        <v>17</v>
+      <c r="J119" s="20">
+        <v>-1</v>
       </c>
       <c r="K119" s="6">
         <v>100</v>
@@ -5649,10 +5646,10 @@
         <v>2</v>
       </c>
       <c r="H120" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="J120" s="6">
-        <v>18</v>
+        <v>166</v>
+      </c>
+      <c r="J120" s="20">
+        <v>-1</v>
       </c>
       <c r="K120" s="6">
         <v>100</v>
@@ -5678,7 +5675,7 @@
         <v>2</v>
       </c>
       <c r="H121" s="33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I121" s="6" t="s">
         <v>117</v>
@@ -5690,91 +5687,82 @@
         <v>100</v>
       </c>
     </row>
-    <row r="122" s="2" customFormat="1" spans="1:11">
-      <c r="A122" s="2">
-        <v>10220001</v>
-      </c>
-      <c r="B122" s="2">
-        <v>102200</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D122" s="19">
-        <v>4020002</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" s="2">
-        <v>1</v>
-      </c>
-      <c r="G122" s="2">
-        <v>2</v>
-      </c>
-      <c r="J122" s="2">
+    <row r="122" s="6" customFormat="1" spans="1:11">
+      <c r="A122" s="6">
+        <v>10310021</v>
+      </c>
+      <c r="B122" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D122" s="32"/>
+      <c r="G122" s="6">
+        <v>2</v>
+      </c>
+      <c r="H122" s="33"/>
+      <c r="J122" s="20">
         <v>-1</v>
       </c>
-      <c r="K122" s="2">
+      <c r="K122" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="123" s="2" customFormat="1" spans="1:11">
       <c r="A123" s="2">
-        <v>10220002</v>
+        <v>10220001</v>
       </c>
       <c r="B123" s="2">
         <v>102200</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D123" s="19">
-        <v>4020003</v>
+        <v>4020002</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F123" s="22"/>
+      <c r="F123" s="2">
+        <v>1</v>
+      </c>
       <c r="G123" s="2">
         <v>2</v>
       </c>
-      <c r="H123" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="J123" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K123" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" s="2" customFormat="1" spans="1:11">
       <c r="A124" s="2">
-        <v>10220003</v>
+        <v>10220002</v>
       </c>
       <c r="B124" s="2">
         <v>102200</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D124" s="19">
-        <v>4020645</v>
+        <v>4020003</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F124" s="22"/>
-      <c r="G124" s="19">
-        <v>2</v>
-      </c>
-      <c r="H124" s="19"/>
-      <c r="I124" s="2" t="s">
-        <v>30</v>
+      <c r="G124" s="2">
+        <v>2</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="J124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K124" s="2">
         <v>100</v>
@@ -5782,28 +5770,30 @@
     </row>
     <row r="125" s="2" customFormat="1" spans="1:11">
       <c r="A125" s="2">
-        <v>10220004</v>
+        <v>10220003</v>
       </c>
       <c r="B125" s="2">
         <v>102200</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D125" s="19">
-        <v>4020640</v>
+        <v>4020645</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G125" s="2">
-        <v>2</v>
-      </c>
-      <c r="H125" s="19" t="s">
-        <v>170</v>
+      <c r="F125" s="22"/>
+      <c r="G125" s="19">
+        <v>2</v>
+      </c>
+      <c r="H125" s="19"/>
+      <c r="I125" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="J125" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K125" s="2">
         <v>100</v>
@@ -5811,31 +5801,28 @@
     </row>
     <row r="126" s="2" customFormat="1" spans="1:11">
       <c r="A126" s="2">
-        <v>10220005</v>
+        <v>10220004</v>
       </c>
       <c r="B126" s="2">
         <v>102200</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D126" s="19">
-        <v>4020646</v>
+        <v>4020640</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G126" s="19">
+        <v>28</v>
+      </c>
+      <c r="G126" s="2">
         <v>2</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>36</v>
+        <v>169</v>
       </c>
       <c r="J126" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K126" s="2">
         <v>100</v>
@@ -5843,28 +5830,31 @@
     </row>
     <row r="127" s="2" customFormat="1" spans="1:11">
       <c r="A127" s="2">
-        <v>10220006</v>
+        <v>10220005</v>
       </c>
       <c r="B127" s="2">
         <v>102200</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D127" s="19">
-        <v>4020641</v>
+        <v>4020646</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G127" s="2">
-        <v>2</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>172</v>
+      <c r="G127" s="19">
+        <v>2</v>
+      </c>
+      <c r="H127" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="J127" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K127" s="2">
         <v>100</v>
@@ -5872,31 +5862,28 @@
     </row>
     <row r="128" s="2" customFormat="1" spans="1:11">
       <c r="A128" s="2">
-        <v>10220007</v>
+        <v>10220006</v>
       </c>
       <c r="B128" s="2">
         <v>102200</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D128" s="19">
-        <v>4020647</v>
+        <v>4020641</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G128" s="19">
-        <v>2</v>
-      </c>
-      <c r="H128" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="G128" s="2">
+        <v>2</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="J128" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K128" s="2">
         <v>100</v>
@@ -5904,28 +5891,31 @@
     </row>
     <row r="129" s="2" customFormat="1" spans="1:11">
       <c r="A129" s="2">
-        <v>10220008</v>
+        <v>10220007</v>
       </c>
       <c r="B129" s="2">
         <v>102200</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D129" s="19">
-        <v>4020642</v>
+        <v>4020647</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G129" s="2">
+      <c r="G129" s="19">
         <v>2</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J129" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K129" s="2">
         <v>100</v>
@@ -5933,31 +5923,28 @@
     </row>
     <row r="130" s="2" customFormat="1" spans="1:11">
       <c r="A130" s="2">
-        <v>10220009</v>
+        <v>10220008</v>
       </c>
       <c r="B130" s="2">
         <v>102200</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D130" s="19">
-        <v>4020648</v>
+        <v>4020642</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G130" s="2">
         <v>2</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="J130" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K130" s="2">
         <v>100</v>
@@ -5965,16 +5952,16 @@
     </row>
     <row r="131" s="2" customFormat="1" spans="1:11">
       <c r="A131" s="2">
-        <v>10220010</v>
+        <v>10220009</v>
       </c>
       <c r="B131" s="2">
         <v>102200</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D131" s="19">
-        <v>4020643</v>
+        <v>4020648</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>44</v>
@@ -5983,10 +5970,13 @@
         <v>2</v>
       </c>
       <c r="H131" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="J131" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K131" s="2">
         <v>100</v>
@@ -5994,31 +5984,28 @@
     </row>
     <row r="132" s="2" customFormat="1" spans="1:11">
       <c r="A132" s="2">
-        <v>10220011</v>
+        <v>10220010</v>
       </c>
       <c r="B132" s="2">
         <v>102200</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D132" s="19">
-        <v>4020649</v>
+        <v>4020643</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G132" s="2">
         <v>2</v>
       </c>
       <c r="H132" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="J132" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K132" s="2">
         <v>100</v>
@@ -6026,16 +6013,16 @@
     </row>
     <row r="133" s="2" customFormat="1" spans="1:11">
       <c r="A133" s="2">
-        <v>10220012</v>
+        <v>10220011</v>
       </c>
       <c r="B133" s="2">
         <v>102200</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D133" s="19">
-        <v>4020644</v>
+        <v>4020649</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>48</v>
@@ -6044,10 +6031,13 @@
         <v>2</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>178</v>
+        <v>176</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J133" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K133" s="2">
         <v>100</v>
@@ -6055,29 +6045,28 @@
     </row>
     <row r="134" s="2" customFormat="1" spans="1:11">
       <c r="A134" s="2">
-        <v>10220013</v>
+        <v>10220012</v>
       </c>
       <c r="B134" s="2">
         <v>102200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D134" s="19">
-        <v>4020650</v>
+        <v>4020644</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G134" s="2">
         <v>2</v>
       </c>
-      <c r="H134" s="19"/>
-      <c r="I134" s="2" t="s">
-        <v>73</v>
+      <c r="H134" s="19" t="s">
+        <v>177</v>
       </c>
       <c r="J134" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K134" s="2">
         <v>100</v>
@@ -6085,16 +6074,16 @@
     </row>
     <row r="135" s="2" customFormat="1" spans="1:11">
       <c r="A135" s="2">
-        <v>10220014</v>
+        <v>10220013</v>
       </c>
       <c r="B135" s="2">
         <v>102200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D135" s="19">
-        <v>4020653</v>
+        <v>4020650</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>72</v>
@@ -6102,14 +6091,12 @@
       <c r="G135" s="2">
         <v>2</v>
       </c>
-      <c r="H135" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="H135" s="19"/>
       <c r="I135" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J135" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K135" s="2">
         <v>100</v>
@@ -6117,16 +6104,16 @@
     </row>
     <row r="136" s="2" customFormat="1" spans="1:11">
       <c r="A136" s="2">
-        <v>10220015</v>
+        <v>10220014</v>
       </c>
       <c r="B136" s="2">
         <v>102200</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D136" s="19">
-        <v>4020654</v>
+        <v>4020653</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>72</v>
@@ -6135,10 +6122,13 @@
         <v>2</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>180</v>
+        <v>178</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="J136" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K136" s="2">
         <v>100</v>
@@ -6146,31 +6136,28 @@
     </row>
     <row r="137" s="2" customFormat="1" spans="1:11">
       <c r="A137" s="2">
-        <v>10220016</v>
+        <v>10220015</v>
       </c>
       <c r="B137" s="2">
         <v>102200</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D137" s="19">
-        <v>4020655</v>
+        <v>4020654</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G137" s="2">
         <v>2</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="J137" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K137" s="2">
         <v>100</v>
@@ -6178,16 +6165,16 @@
     </row>
     <row r="138" s="2" customFormat="1" spans="1:11">
       <c r="A138" s="2">
-        <v>10220017</v>
+        <v>10220016</v>
       </c>
       <c r="B138" s="2">
         <v>102200</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D138" s="19">
-        <v>4020656</v>
+        <v>4020655</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>80</v>
@@ -6196,10 +6183,13 @@
         <v>2</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="J138" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K138" s="2">
         <v>100</v>
@@ -6207,31 +6197,28 @@
     </row>
     <row r="139" s="2" customFormat="1" spans="1:11">
       <c r="A139" s="2">
-        <v>10220018</v>
+        <v>10220017</v>
       </c>
       <c r="B139" s="2">
         <v>102200</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D139" s="19">
-        <v>4020657</v>
+        <v>4020656</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G139" s="2">
         <v>2</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="J139" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K139" s="2">
         <v>100</v>
@@ -6239,16 +6226,16 @@
     </row>
     <row r="140" s="2" customFormat="1" spans="1:11">
       <c r="A140" s="2">
-        <v>10220019</v>
+        <v>10220018</v>
       </c>
       <c r="B140" s="2">
         <v>102200</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D140" s="19">
-        <v>4020658</v>
+        <v>4020657</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>86</v>
@@ -6257,10 +6244,13 @@
         <v>2</v>
       </c>
       <c r="H140" s="19" t="s">
-        <v>184</v>
+        <v>182</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="J140" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K140" s="2">
         <v>100</v>
@@ -6268,120 +6258,119 @@
     </row>
     <row r="141" s="2" customFormat="1" spans="1:11">
       <c r="A141" s="2">
-        <v>10220020</v>
+        <v>10220019</v>
       </c>
       <c r="B141" s="2">
         <v>102200</v>
       </c>
       <c r="C141" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D141" s="19">
+        <v>4020658</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G141" s="2">
+        <v>2</v>
+      </c>
+      <c r="H141" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="J141" s="2">
+        <v>18</v>
+      </c>
+      <c r="K141" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" s="2" customFormat="1" spans="1:11">
+      <c r="A142" s="2">
+        <v>10220020</v>
+      </c>
+      <c r="B142" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D141" s="19">
+      <c r="D142" s="19">
         <v>4020651</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="E142" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G141" s="2">
-        <v>2</v>
-      </c>
-      <c r="H141" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="I141" s="2" t="s">
+      <c r="G142" s="2">
+        <v>2</v>
+      </c>
+      <c r="H142" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="I142" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J141" s="2">
+      <c r="J142" s="2">
         <v>19</v>
       </c>
-      <c r="K141" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="142" s="7" customFormat="1" spans="1:11">
-      <c r="A142" s="7">
-        <v>10210001</v>
-      </c>
-      <c r="B142" s="7">
-        <v>102100</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D142" s="34">
-        <v>4020002</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" s="7">
-        <v>1</v>
-      </c>
-      <c r="G142" s="7">
-        <v>2</v>
-      </c>
-      <c r="J142" s="7">
-        <v>-1</v>
-      </c>
-      <c r="K142" s="7">
-        <v>0</v>
+      <c r="K142" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="143" s="7" customFormat="1" spans="1:11">
       <c r="A143" s="7">
-        <v>10210002</v>
+        <v>10210001</v>
       </c>
       <c r="B143" s="7">
         <v>102100</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D143" s="34">
-        <v>4020003</v>
+        <v>4020002</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F143" s="35"/>
+      <c r="F143" s="7">
+        <v>1</v>
+      </c>
       <c r="G143" s="7">
         <v>2</v>
       </c>
-      <c r="H143" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="J143" s="7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K143" s="7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" s="7" customFormat="1" spans="1:11">
       <c r="A144" s="7">
-        <v>10210003</v>
+        <v>10210002</v>
       </c>
       <c r="B144" s="7">
         <v>102100</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D144" s="34">
-        <v>4020645</v>
+        <v>4020003</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G144" s="34">
-        <v>2</v>
-      </c>
-      <c r="H144" s="34"/>
-      <c r="I144" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="F144" s="35"/>
+      <c r="G144" s="7">
+        <v>2</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="J144" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K144" s="7">
         <v>100</v>
@@ -6389,28 +6378,29 @@
     </row>
     <row r="145" s="7" customFormat="1" spans="1:11">
       <c r="A145" s="7">
-        <v>10210004</v>
+        <v>10210003</v>
       </c>
       <c r="B145" s="7">
         <v>102100</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D145" s="34">
-        <v>4020640</v>
+        <v>4020645</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G145" s="7">
-        <v>2</v>
-      </c>
-      <c r="H145" s="34" t="s">
-        <v>187</v>
+      <c r="G145" s="34">
+        <v>2</v>
+      </c>
+      <c r="H145" s="34"/>
+      <c r="I145" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="J145" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K145" s="7">
         <v>100</v>
@@ -6418,31 +6408,28 @@
     </row>
     <row r="146" s="7" customFormat="1" spans="1:11">
       <c r="A146" s="7">
-        <v>10210005</v>
+        <v>10210004</v>
       </c>
       <c r="B146" s="7">
         <v>102100</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D146" s="34">
-        <v>4020646</v>
+        <v>4020640</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G146" s="34">
+        <v>28</v>
+      </c>
+      <c r="G146" s="7">
         <v>2</v>
       </c>
       <c r="H146" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="I146" s="7" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="J146" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K146" s="7">
         <v>100</v>
@@ -6450,28 +6437,31 @@
     </row>
     <row r="147" s="7" customFormat="1" spans="1:11">
       <c r="A147" s="7">
-        <v>10210006</v>
+        <v>10210005</v>
       </c>
       <c r="B147" s="7">
         <v>102100</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D147" s="34">
-        <v>4020641</v>
+        <v>4020646</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G147" s="34">
         <v>2</v>
       </c>
       <c r="H147" s="34" t="s">
-        <v>189</v>
+        <v>187</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="J147" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K147" s="7">
         <v>100</v>
@@ -6479,31 +6469,28 @@
     </row>
     <row r="148" s="7" customFormat="1" spans="1:11">
       <c r="A148" s="7">
-        <v>10210007</v>
+        <v>10210006</v>
       </c>
       <c r="B148" s="7">
         <v>102100</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D148" s="34">
-        <v>4020647</v>
+        <v>4020641</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G148" s="34">
-        <v>2</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="I148" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="G148" s="7">
+        <v>2</v>
+      </c>
+      <c r="H148" s="34" t="s">
+        <v>188</v>
       </c>
       <c r="J148" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K148" s="7">
         <v>100</v>
@@ -6511,28 +6498,31 @@
     </row>
     <row r="149" s="7" customFormat="1" spans="1:11">
       <c r="A149" s="7">
-        <v>10210008</v>
+        <v>10210007</v>
       </c>
       <c r="B149" s="7">
         <v>102100</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D149" s="34">
-        <v>4020642</v>
+        <v>4020647</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G149" s="7">
-        <v>2</v>
-      </c>
-      <c r="H149" s="34" t="s">
-        <v>191</v>
+      <c r="G149" s="34">
+        <v>2</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="J149" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K149" s="7">
         <v>100</v>
@@ -6540,31 +6530,28 @@
     </row>
     <row r="150" s="7" customFormat="1" spans="1:11">
       <c r="A150" s="7">
-        <v>10210009</v>
+        <v>10210008</v>
       </c>
       <c r="B150" s="7">
         <v>102100</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D150" s="34">
-        <v>4020648</v>
+        <v>4020642</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G150" s="34">
+        <v>40</v>
+      </c>
+      <c r="G150" s="7">
         <v>2</v>
       </c>
       <c r="H150" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="I150" s="7" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="J150" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K150" s="7">
         <v>100</v>
@@ -6572,28 +6559,31 @@
     </row>
     <row r="151" s="7" customFormat="1" spans="1:11">
       <c r="A151" s="7">
-        <v>10210010</v>
+        <v>10210009</v>
       </c>
       <c r="B151" s="7">
         <v>102100</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D151" s="34">
-        <v>4020643</v>
+        <v>4020648</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G151" s="7">
-        <v>2</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>193</v>
+      <c r="G151" s="34">
+        <v>2</v>
+      </c>
+      <c r="H151" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="J151" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K151" s="7">
         <v>100</v>
@@ -6601,31 +6591,28 @@
     </row>
     <row r="152" s="7" customFormat="1" spans="1:11">
       <c r="A152" s="7">
-        <v>10210011</v>
+        <v>10210010</v>
       </c>
       <c r="B152" s="7">
         <v>102100</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D152" s="34">
-        <v>4020649</v>
+        <v>4020643</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G152" s="34">
-        <v>2</v>
-      </c>
-      <c r="H152" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="I152" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="G152" s="7">
+        <v>2</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="J152" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K152" s="7">
         <v>100</v>
@@ -6633,28 +6620,31 @@
     </row>
     <row r="153" s="7" customFormat="1" spans="1:11">
       <c r="A153" s="7">
-        <v>10210012</v>
+        <v>10210011</v>
       </c>
       <c r="B153" s="7">
         <v>102100</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D153" s="34">
-        <v>4020644</v>
+        <v>4020649</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="34">
         <v>2</v>
       </c>
       <c r="H153" s="34" t="s">
-        <v>195</v>
+        <v>193</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="J153" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K153" s="7">
         <v>100</v>
@@ -6662,29 +6652,28 @@
     </row>
     <row r="154" s="7" customFormat="1" spans="1:11">
       <c r="A154" s="7">
-        <v>10210013</v>
+        <v>10210012</v>
       </c>
       <c r="B154" s="7">
         <v>102100</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D154" s="34">
-        <v>4020650</v>
+        <v>4020644</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G154" s="34">
-        <v>2</v>
-      </c>
-      <c r="H154" s="34"/>
-      <c r="I154" s="7" t="s">
-        <v>73</v>
+        <v>48</v>
+      </c>
+      <c r="G154" s="7">
+        <v>2</v>
+      </c>
+      <c r="H154" s="34" t="s">
+        <v>194</v>
       </c>
       <c r="J154" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K154" s="7">
         <v>100</v>
@@ -6692,16 +6681,16 @@
     </row>
     <row r="155" s="7" customFormat="1" spans="1:11">
       <c r="A155" s="7">
-        <v>10210014</v>
+        <v>10210013</v>
       </c>
       <c r="B155" s="7">
         <v>102100</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D155" s="34">
-        <v>4020653</v>
+        <v>4020650</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>72</v>
@@ -6709,14 +6698,12 @@
       <c r="G155" s="34">
         <v>2</v>
       </c>
-      <c r="H155" s="34" t="s">
-        <v>196</v>
-      </c>
+      <c r="H155" s="34"/>
       <c r="I155" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J155" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K155" s="7">
         <v>100</v>
@@ -6724,16 +6711,16 @@
     </row>
     <row r="156" s="7" customFormat="1" spans="1:11">
       <c r="A156" s="7">
-        <v>10210015</v>
+        <v>10210014</v>
       </c>
       <c r="B156" s="7">
         <v>102100</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D156" s="34">
-        <v>4020654</v>
+        <v>4020653</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>72</v>
@@ -6742,10 +6729,13 @@
         <v>2</v>
       </c>
       <c r="H156" s="34" t="s">
-        <v>197</v>
+        <v>195</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="J156" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K156" s="7">
         <v>100</v>
@@ -6753,31 +6743,28 @@
     </row>
     <row r="157" s="7" customFormat="1" spans="1:11">
       <c r="A157" s="7">
-        <v>10210016</v>
+        <v>10210015</v>
       </c>
       <c r="B157" s="7">
         <v>102100</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D157" s="34">
-        <v>4020655</v>
+        <v>4020654</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G157" s="34">
         <v>2</v>
       </c>
       <c r="H157" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="I157" s="7" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="J157" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K157" s="7">
         <v>100</v>
@@ -6785,16 +6772,16 @@
     </row>
     <row r="158" s="7" customFormat="1" spans="1:11">
       <c r="A158" s="7">
-        <v>10210017</v>
+        <v>10210016</v>
       </c>
       <c r="B158" s="7">
         <v>102100</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D158" s="34">
-        <v>4020656</v>
+        <v>4020655</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>80</v>
@@ -6803,10 +6790,13 @@
         <v>2</v>
       </c>
       <c r="H158" s="34" t="s">
-        <v>199</v>
+        <v>197</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="J158" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K158" s="7">
         <v>100</v>
@@ -6814,31 +6804,28 @@
     </row>
     <row r="159" s="7" customFormat="1" spans="1:11">
       <c r="A159" s="7">
-        <v>10210018</v>
+        <v>10210017</v>
       </c>
       <c r="B159" s="7">
         <v>102100</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D159" s="34">
-        <v>4020657</v>
+        <v>4020656</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G159" s="34">
         <v>2</v>
       </c>
       <c r="H159" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="I159" s="7" t="s">
-        <v>88</v>
+        <v>198</v>
       </c>
       <c r="J159" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K159" s="7">
         <v>100</v>
@@ -6846,16 +6833,16 @@
     </row>
     <row r="160" s="7" customFormat="1" spans="1:11">
       <c r="A160" s="7">
-        <v>10210019</v>
+        <v>10210018</v>
       </c>
       <c r="B160" s="7">
         <v>102100</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D160" s="34">
-        <v>4020658</v>
+        <v>4020657</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>86</v>
@@ -6864,10 +6851,13 @@
         <v>2</v>
       </c>
       <c r="H160" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="J160" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K160" s="7">
         <v>100</v>
@@ -6875,107 +6865,106 @@
     </row>
     <row r="161" s="7" customFormat="1" spans="1:11">
       <c r="A161" s="7">
-        <v>10210020</v>
+        <v>10210019</v>
       </c>
       <c r="B161" s="7">
         <v>102100</v>
       </c>
       <c r="C161" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D161" s="34">
+        <v>4020658</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G161" s="34">
+        <v>2</v>
+      </c>
+      <c r="H161" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="J161" s="7">
+        <v>18</v>
+      </c>
+      <c r="K161" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="162" s="7" customFormat="1" spans="1:11">
+      <c r="A162" s="7">
+        <v>10210020</v>
+      </c>
+      <c r="B162" s="7">
+        <v>102100</v>
+      </c>
+      <c r="C162" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D161" s="34">
+      <c r="D162" s="34">
         <v>4020651</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="E162" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G161" s="34">
-        <v>2</v>
-      </c>
-      <c r="H161" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="I161" s="7" t="s">
+      <c r="G162" s="34">
+        <v>2</v>
+      </c>
+      <c r="H162" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="I162" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J161" s="7">
+      <c r="J162" s="7">
         <v>19</v>
       </c>
-      <c r="K161" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="162" s="3" customFormat="1" spans="1:11">
-      <c r="A162" s="3">
+      <c r="K162" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" s="3" customFormat="1" spans="1:11">
+      <c r="A163" s="3">
         <v>10390001</v>
-      </c>
-      <c r="B162" s="3">
-        <v>103900</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D162" s="24">
-        <v>4020002</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F162" s="3">
-        <v>1</v>
-      </c>
-      <c r="G162" s="3">
-        <v>2</v>
-      </c>
-      <c r="J162" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K162" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
-      <c r="A163" s="3">
-        <v>10390003</v>
       </c>
       <c r="B163" s="3">
         <v>103900</v>
       </c>
-      <c r="C163" s="36" t="s">
-        <v>27</v>
+      <c r="C163" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D163" s="24">
-        <v>4020645</v>
+        <v>4020002</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G163" s="24">
-        <v>2</v>
-      </c>
-      <c r="H163" s="24"/>
-      <c r="I163" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J163" s="3">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="F163" s="3">
+        <v>1</v>
+      </c>
+      <c r="G163" s="3">
+        <v>2</v>
+      </c>
+      <c r="J163" s="20">
+        <v>-1</v>
       </c>
       <c r="K163" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="164" s="3" customFormat="1" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" s="3" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A164" s="3">
-        <v>10390004</v>
+        <v>10390003</v>
       </c>
       <c r="B164" s="3">
         <v>103900</v>
       </c>
       <c r="C164" s="36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D164" s="24">
-        <v>4020640</v>
+        <v>4020645</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>28</v>
@@ -6983,11 +6972,12 @@
       <c r="G164" s="24">
         <v>2</v>
       </c>
-      <c r="H164" s="24" t="s">
-        <v>203</v>
+      <c r="H164" s="24"/>
+      <c r="I164" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="J164" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K164" s="3">
         <v>100</v>
@@ -6995,31 +6985,28 @@
     </row>
     <row r="165" s="3" customFormat="1" spans="1:11">
       <c r="A165" s="3">
-        <v>10390005</v>
+        <v>10390004</v>
       </c>
       <c r="B165" s="3">
         <v>103900</v>
       </c>
       <c r="C165" s="36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D165" s="24">
-        <v>4020646</v>
+        <v>4020640</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G165" s="3">
+        <v>28</v>
+      </c>
+      <c r="G165" s="24">
         <v>2</v>
       </c>
       <c r="H165" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="I165" s="3" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="J165" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K165" s="3">
         <v>100</v>
@@ -7027,16 +7014,16 @@
     </row>
     <row r="166" s="3" customFormat="1" spans="1:11">
       <c r="A166" s="3">
-        <v>10390006</v>
+        <v>10390005</v>
       </c>
       <c r="B166" s="3">
         <v>103900</v>
       </c>
       <c r="C166" s="36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D166" s="24">
-        <v>4020641</v>
+        <v>4020646</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>34</v>
@@ -7045,10 +7032,13 @@
         <v>2</v>
       </c>
       <c r="H166" s="24" t="s">
-        <v>205</v>
+        <v>203</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="J166" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K166" s="3">
         <v>100</v>
@@ -7056,29 +7046,28 @@
     </row>
     <row r="167" s="3" customFormat="1" spans="1:11">
       <c r="A167" s="3">
-        <v>10390002</v>
+        <v>10390006</v>
       </c>
       <c r="B167" s="3">
         <v>103900</v>
       </c>
-      <c r="C167" s="3" t="s">
-        <v>63</v>
+      <c r="C167" s="36" t="s">
+        <v>37</v>
       </c>
       <c r="D167" s="24">
-        <v>4020003</v>
+        <v>4020641</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F167" s="25"/>
+        <v>34</v>
+      </c>
       <c r="G167" s="3">
         <v>2</v>
       </c>
       <c r="H167" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="J167" s="20">
-        <v>-1</v>
+        <v>204</v>
+      </c>
+      <c r="J167" s="3">
+        <v>5</v>
       </c>
       <c r="K167" s="3">
         <v>100</v>
@@ -7086,28 +7075,26 @@
     </row>
     <row r="168" s="3" customFormat="1" spans="1:11">
       <c r="A168" s="3">
-        <v>10390007</v>
+        <v>10390002</v>
       </c>
       <c r="B168" s="3">
         <v>103900</v>
       </c>
-      <c r="C168" s="36" t="s">
-        <v>39</v>
+      <c r="C168" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D168" s="24">
-        <v>4020647</v>
+        <v>4020003</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F168" s="25"/>
       <c r="G168" s="3">
         <v>2</v>
       </c>
       <c r="H168" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="I168" s="3" t="s">
-        <v>41</v>
+        <v>205</v>
       </c>
       <c r="J168" s="20">
         <v>-1</v>
@@ -7118,25 +7105,28 @@
     </row>
     <row r="169" s="3" customFormat="1" spans="1:11">
       <c r="A169" s="3">
-        <v>10390008</v>
+        <v>10390007</v>
       </c>
       <c r="B169" s="3">
         <v>103900</v>
       </c>
       <c r="C169" s="36" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D169" s="24">
-        <v>4020642</v>
+        <v>4020647</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G169" s="24">
+      <c r="G169" s="3">
         <v>2</v>
       </c>
       <c r="H169" s="24" t="s">
-        <v>207</v>
+        <v>205</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="J169" s="20">
         <v>-1</v>
@@ -7147,28 +7137,25 @@
     </row>
     <row r="170" s="3" customFormat="1" spans="1:11">
       <c r="A170" s="3">
-        <v>10390009</v>
+        <v>10390008</v>
       </c>
       <c r="B170" s="3">
         <v>103900</v>
       </c>
       <c r="C170" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D170" s="24">
-        <v>4020648</v>
+        <v>4020642</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G170" s="3">
+        <v>40</v>
+      </c>
+      <c r="G170" s="24">
         <v>2</v>
       </c>
       <c r="H170" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="I170" s="3" t="s">
-        <v>45</v>
+        <v>206</v>
       </c>
       <c r="J170" s="20">
         <v>-1</v>
@@ -7179,16 +7166,16 @@
     </row>
     <row r="171" s="3" customFormat="1" spans="1:11">
       <c r="A171" s="3">
-        <v>10390010</v>
+        <v>10390009</v>
       </c>
       <c r="B171" s="3">
         <v>103900</v>
       </c>
       <c r="C171" s="36" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D171" s="24">
-        <v>4020643</v>
+        <v>4020648</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>44</v>
@@ -7197,7 +7184,10 @@
         <v>2</v>
       </c>
       <c r="H171" s="24" t="s">
-        <v>209</v>
+        <v>207</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="J171" s="20">
         <v>-1</v>
@@ -7208,28 +7198,25 @@
     </row>
     <row r="172" s="3" customFormat="1" spans="1:11">
       <c r="A172" s="3">
-        <v>10390011</v>
+        <v>10390010</v>
       </c>
       <c r="B172" s="3">
         <v>103900</v>
       </c>
       <c r="C172" s="36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D172" s="24">
-        <v>4020649</v>
+        <v>4020643</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G172" s="3">
         <v>2</v>
       </c>
       <c r="H172" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="I172" s="3" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="J172" s="20">
         <v>-1</v>
@@ -7240,25 +7227,28 @@
     </row>
     <row r="173" s="3" customFormat="1" spans="1:11">
       <c r="A173" s="3">
-        <v>10390012</v>
+        <v>10390011</v>
       </c>
       <c r="B173" s="3">
         <v>103900</v>
       </c>
       <c r="C173" s="36" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D173" s="24">
-        <v>4020644</v>
+        <v>4020649</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G173" s="24">
+      <c r="G173" s="3">
         <v>2</v>
       </c>
       <c r="H173" s="24" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J173" s="20">
         <v>-1</v>
@@ -7269,28 +7259,28 @@
     </row>
     <row r="174" s="3" customFormat="1" spans="1:11">
       <c r="A174" s="3">
-        <v>10390013</v>
+        <v>10390012</v>
       </c>
       <c r="B174" s="3">
         <v>103900</v>
       </c>
       <c r="C174" s="36" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D174" s="24">
-        <v>4020650</v>
+        <v>4020644</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G174" s="24">
         <v>2</v>
       </c>
-      <c r="I174" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J174" s="3">
-        <v>12</v>
+      <c r="H174" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="J174" s="20">
+        <v>-1</v>
       </c>
       <c r="K174" s="3">
         <v>100</v>
@@ -7298,16 +7288,16 @@
     </row>
     <row r="175" s="3" customFormat="1" spans="1:11">
       <c r="A175" s="3">
-        <v>10390014</v>
+        <v>10390013</v>
       </c>
       <c r="B175" s="3">
         <v>103900</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>74</v>
+      <c r="C175" s="36" t="s">
+        <v>71</v>
       </c>
       <c r="D175" s="24">
-        <v>4020653</v>
+        <v>4020650</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>72</v>
@@ -7315,14 +7305,11 @@
       <c r="G175" s="24">
         <v>2</v>
       </c>
-      <c r="H175" s="24" t="s">
-        <v>212</v>
-      </c>
       <c r="I175" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J175" s="20">
-        <v>-1</v>
+        <v>73</v>
+      </c>
+      <c r="J175" s="3">
+        <v>12</v>
       </c>
       <c r="K175" s="3">
         <v>100</v>
@@ -7330,16 +7317,16 @@
     </row>
     <row r="176" s="3" customFormat="1" spans="1:11">
       <c r="A176" s="3">
-        <v>10390015</v>
+        <v>10390014</v>
       </c>
       <c r="B176" s="3">
         <v>103900</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D176" s="24">
-        <v>4020654</v>
+        <v>4020653</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>72</v>
@@ -7348,7 +7335,10 @@
         <v>2</v>
       </c>
       <c r="H176" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="J176" s="20">
         <v>-1</v>
@@ -7359,28 +7349,25 @@
     </row>
     <row r="177" s="3" customFormat="1" spans="1:11">
       <c r="A177" s="3">
-        <v>10390016</v>
+        <v>10390015</v>
       </c>
       <c r="B177" s="3">
         <v>103900</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D177" s="24">
-        <v>4020655</v>
+        <v>4020654</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G177" s="24">
         <v>2</v>
       </c>
       <c r="H177" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="I177" s="3" t="s">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="J177" s="20">
         <v>-1</v>
@@ -7391,25 +7378,28 @@
     </row>
     <row r="178" s="3" customFormat="1" spans="1:11">
       <c r="A178" s="3">
-        <v>10390017</v>
+        <v>10390016</v>
       </c>
       <c r="B178" s="3">
         <v>103900</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D178" s="24">
-        <v>4020656</v>
+        <v>4020655</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G178" s="3">
+      <c r="G178" s="24">
         <v>2</v>
       </c>
       <c r="H178" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="J178" s="20">
         <v>-1</v>
@@ -7420,26 +7410,25 @@
     </row>
     <row r="179" s="3" customFormat="1" spans="1:11">
       <c r="A179" s="3">
-        <v>10390018</v>
+        <v>10390017</v>
       </c>
       <c r="B179" s="3">
         <v>103900</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D179" s="24">
-        <v>4020657</v>
+        <v>4020656</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G179" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="G179" s="3">
+        <v>2</v>
+      </c>
       <c r="H179" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="I179" s="3" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="J179" s="20">
         <v>-1</v>
@@ -7450,25 +7439,26 @@
     </row>
     <row r="180" s="3" customFormat="1" spans="1:11">
       <c r="A180" s="3">
-        <v>10390019</v>
+        <v>10390018</v>
       </c>
       <c r="B180" s="3">
         <v>103900</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D180" s="24">
-        <v>4020658</v>
+        <v>4020657</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G180" s="24">
-        <v>2</v>
-      </c>
+      <c r="G180" s="24"/>
       <c r="H180" s="24" t="s">
-        <v>217</v>
+        <v>215</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="J180" s="20">
         <v>-1</v>
@@ -7479,31 +7469,28 @@
     </row>
     <row r="181" s="3" customFormat="1" spans="1:11">
       <c r="A181" s="3">
-        <v>10390020</v>
+        <v>10390019</v>
       </c>
       <c r="B181" s="3">
         <v>103900</v>
       </c>
-      <c r="C181" s="36" t="s">
-        <v>53</v>
+      <c r="C181" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="D181" s="24">
-        <v>4020651</v>
+        <v>4020658</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G181" s="3">
+        <v>86</v>
+      </c>
+      <c r="G181" s="24">
         <v>2</v>
       </c>
       <c r="H181" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="I181" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J181" s="4">
-        <v>19</v>
+        <v>216</v>
+      </c>
+      <c r="J181" s="20">
+        <v>-1</v>
       </c>
       <c r="K181" s="3">
         <v>100</v>
@@ -7511,109 +7498,111 @@
     </row>
     <row r="182" s="3" customFormat="1" spans="1:11">
       <c r="A182" s="3">
-        <v>10390021</v>
+        <v>10390020</v>
       </c>
       <c r="B182" s="3">
         <v>103900</v>
       </c>
-      <c r="C182" s="37" t="s">
+      <c r="C182" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D182" s="24">
+        <v>4020651</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G182" s="3">
+        <v>2</v>
+      </c>
+      <c r="H182" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J182" s="4">
+        <v>19</v>
+      </c>
+      <c r="K182" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="183" s="3" customFormat="1" spans="1:11">
+      <c r="A183" s="3">
+        <v>10390021</v>
+      </c>
+      <c r="B183" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C183" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="D182" s="24"/>
-      <c r="G182" s="3">
-        <v>2</v>
-      </c>
-      <c r="H182" s="24"/>
-      <c r="J182" s="20">
+      <c r="D183" s="24"/>
+      <c r="G183" s="3">
+        <v>2</v>
+      </c>
+      <c r="H183" s="24"/>
+      <c r="J183" s="20">
         <v>-1</v>
       </c>
-      <c r="K182" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" s="4" customFormat="1" spans="1:11">
-      <c r="A183" s="4">
-        <v>10200001</v>
-      </c>
-      <c r="B183" s="4">
-        <v>102000</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D183" s="26">
-        <v>4020002</v>
-      </c>
-      <c r="E183" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F183" s="4">
-        <v>1</v>
-      </c>
-      <c r="G183" s="4">
-        <v>2</v>
-      </c>
-      <c r="J183" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K183" s="4">
+      <c r="K183" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="184" s="4" customFormat="1" spans="1:11">
       <c r="A184" s="4">
-        <v>10200002</v>
+        <v>10200001</v>
       </c>
       <c r="B184" s="4">
         <v>102000</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D184" s="26">
-        <v>4020003</v>
+        <v>4020002</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="F184" s="4">
+        <v>1</v>
+      </c>
       <c r="G184" s="4">
         <v>2</v>
       </c>
-      <c r="H184" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="J184" s="4">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K184" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" s="4" customFormat="1" spans="1:11">
       <c r="A185" s="4">
-        <v>10200003</v>
+        <v>10200002</v>
       </c>
       <c r="B185" s="4">
         <v>102000</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D185" s="26">
-        <v>4020645</v>
+        <v>4020003</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G185" s="26">
-        <v>2</v>
-      </c>
-      <c r="H185" s="26"/>
-      <c r="I185" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G185" s="4">
+        <v>2</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="J185" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K185" s="4">
         <v>100</v>
@@ -7621,28 +7610,29 @@
     </row>
     <row r="186" s="4" customFormat="1" spans="1:11">
       <c r="A186" s="4">
-        <v>10200004</v>
+        <v>10200003</v>
       </c>
       <c r="B186" s="4">
         <v>102000</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D186" s="26">
-        <v>4020640</v>
+        <v>4020645</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G186" s="4">
-        <v>2</v>
-      </c>
-      <c r="H186" s="26" t="s">
-        <v>220</v>
+      <c r="G186" s="26">
+        <v>2</v>
+      </c>
+      <c r="H186" s="26"/>
+      <c r="I186" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="J186" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K186" s="4">
         <v>100</v>
@@ -7650,31 +7640,28 @@
     </row>
     <row r="187" s="4" customFormat="1" spans="1:11">
       <c r="A187" s="4">
-        <v>10200005</v>
+        <v>10200004</v>
       </c>
       <c r="B187" s="4">
         <v>102000</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D187" s="26">
-        <v>4020646</v>
+        <v>4020640</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G187" s="26">
+        <v>28</v>
+      </c>
+      <c r="G187" s="4">
         <v>2</v>
       </c>
       <c r="H187" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="I187" s="4" t="s">
-        <v>36</v>
+        <v>219</v>
       </c>
       <c r="J187" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K187" s="4">
         <v>100</v>
@@ -7682,28 +7669,31 @@
     </row>
     <row r="188" s="4" customFormat="1" spans="1:11">
       <c r="A188" s="4">
-        <v>10200006</v>
+        <v>10200005</v>
       </c>
       <c r="B188" s="4">
         <v>102000</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D188" s="26">
-        <v>4020641</v>
+        <v>4020646</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G188" s="4">
+      <c r="G188" s="26">
         <v>2</v>
       </c>
       <c r="H188" s="26" t="s">
-        <v>222</v>
+        <v>220</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="J188" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K188" s="4">
         <v>100</v>
@@ -7711,31 +7701,28 @@
     </row>
     <row r="189" s="4" customFormat="1" spans="1:11">
       <c r="A189" s="4">
-        <v>10200007</v>
+        <v>10200006</v>
       </c>
       <c r="B189" s="4">
         <v>102000</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D189" s="26">
-        <v>4020647</v>
+        <v>4020641</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G189" s="26">
-        <v>2</v>
-      </c>
-      <c r="H189" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="I189" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="G189" s="4">
+        <v>2</v>
+      </c>
+      <c r="H189" s="26" t="s">
+        <v>221</v>
       </c>
       <c r="J189" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K189" s="4">
         <v>100</v>
@@ -7743,28 +7730,31 @@
     </row>
     <row r="190" s="4" customFormat="1" spans="1:11">
       <c r="A190" s="4">
-        <v>10200008</v>
+        <v>10200007</v>
       </c>
       <c r="B190" s="4">
         <v>102000</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D190" s="26">
-        <v>4020642</v>
+        <v>4020647</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G190" s="4">
-        <v>2</v>
-      </c>
-      <c r="H190" s="26" t="s">
-        <v>224</v>
+      <c r="G190" s="26">
+        <v>2</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="J190" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K190" s="4">
         <v>100</v>
@@ -7772,31 +7762,28 @@
     </row>
     <row r="191" s="4" customFormat="1" spans="1:11">
       <c r="A191" s="4">
-        <v>10200009</v>
+        <v>10200008</v>
       </c>
       <c r="B191" s="4">
         <v>102000</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D191" s="26">
-        <v>4020648</v>
+        <v>4020642</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G191" s="26">
+        <v>40</v>
+      </c>
+      <c r="G191" s="4">
         <v>2</v>
       </c>
       <c r="H191" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="I191" s="4" t="s">
-        <v>45</v>
+        <v>223</v>
       </c>
       <c r="J191" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K191" s="4">
         <v>100</v>
@@ -7804,28 +7791,31 @@
     </row>
     <row r="192" s="4" customFormat="1" spans="1:11">
       <c r="A192" s="4">
-        <v>10200010</v>
+        <v>10200009</v>
       </c>
       <c r="B192" s="4">
         <v>102000</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D192" s="26">
-        <v>4020643</v>
+        <v>4020648</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G192" s="4">
+      <c r="G192" s="26">
         <v>2</v>
       </c>
       <c r="H192" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="J192" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K192" s="4">
         <v>100</v>
@@ -7833,31 +7823,28 @@
     </row>
     <row r="193" s="4" customFormat="1" spans="1:11">
       <c r="A193" s="4">
-        <v>10200011</v>
+        <v>10200010</v>
       </c>
       <c r="B193" s="4">
         <v>102000</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D193" s="26">
-        <v>4020649</v>
+        <v>4020643</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G193" s="4">
         <v>2</v>
       </c>
       <c r="H193" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="I193" s="4" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="J193" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K193" s="4">
         <v>100</v>
@@ -7865,16 +7852,16 @@
     </row>
     <row r="194" s="4" customFormat="1" spans="1:11">
       <c r="A194" s="4">
-        <v>10200012</v>
+        <v>10200011</v>
       </c>
       <c r="B194" s="4">
         <v>102000</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D194" s="26">
-        <v>4020644</v>
+        <v>4020649</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>48</v>
@@ -7883,10 +7870,13 @@
         <v>2</v>
       </c>
       <c r="H194" s="26" t="s">
-        <v>228</v>
+        <v>226</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="J194" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K194" s="4">
         <v>100</v>
@@ -7894,29 +7884,28 @@
     </row>
     <row r="195" s="4" customFormat="1" spans="1:11">
       <c r="A195" s="4">
-        <v>10200013</v>
+        <v>10200012</v>
       </c>
       <c r="B195" s="4">
         <v>102000</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D195" s="26">
-        <v>4020650</v>
+        <v>4020644</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G195" s="4">
         <v>2</v>
       </c>
-      <c r="H195" s="26"/>
-      <c r="I195" s="4" t="s">
-        <v>73</v>
+      <c r="H195" s="26" t="s">
+        <v>227</v>
       </c>
       <c r="J195" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K195" s="4">
         <v>100</v>
@@ -7924,16 +7913,16 @@
     </row>
     <row r="196" s="4" customFormat="1" spans="1:11">
       <c r="A196" s="4">
-        <v>10200014</v>
+        <v>10200013</v>
       </c>
       <c r="B196" s="4">
         <v>102000</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D196" s="26">
-        <v>4020653</v>
+        <v>4020650</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>72</v>
@@ -7941,14 +7930,12 @@
       <c r="G196" s="4">
         <v>2</v>
       </c>
-      <c r="H196" s="26" t="s">
-        <v>229</v>
-      </c>
+      <c r="H196" s="26"/>
       <c r="I196" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J196" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K196" s="4">
         <v>100</v>
@@ -7956,16 +7943,16 @@
     </row>
     <row r="197" s="4" customFormat="1" spans="1:11">
       <c r="A197" s="4">
-        <v>10200015</v>
+        <v>10200014</v>
       </c>
       <c r="B197" s="4">
         <v>102000</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D197" s="26">
-        <v>4020654</v>
+        <v>4020653</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>72</v>
@@ -7974,10 +7961,13 @@
         <v>2</v>
       </c>
       <c r="H197" s="26" t="s">
-        <v>230</v>
+        <v>228</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="J197" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K197" s="4">
         <v>100</v>
@@ -7985,31 +7975,28 @@
     </row>
     <row r="198" s="4" customFormat="1" spans="1:11">
       <c r="A198" s="4">
-        <v>10200016</v>
+        <v>10200015</v>
       </c>
       <c r="B198" s="4">
         <v>102000</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D198" s="26">
-        <v>4020655</v>
+        <v>4020654</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G198" s="4">
         <v>2</v>
       </c>
       <c r="H198" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="I198" s="4" t="s">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="J198" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K198" s="4">
         <v>100</v>
@@ -8017,16 +8004,16 @@
     </row>
     <row r="199" s="4" customFormat="1" spans="1:11">
       <c r="A199" s="4">
-        <v>10200017</v>
+        <v>10200016</v>
       </c>
       <c r="B199" s="4">
         <v>102000</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D199" s="26">
-        <v>4020656</v>
+        <v>4020655</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>80</v>
@@ -8035,10 +8022,13 @@
         <v>2</v>
       </c>
       <c r="H199" s="26" t="s">
-        <v>232</v>
+        <v>230</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="J199" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K199" s="4">
         <v>100</v>
@@ -8046,28 +8036,28 @@
     </row>
     <row r="200" s="4" customFormat="1" spans="1:11">
       <c r="A200" s="4">
-        <v>10200018</v>
+        <v>10200017</v>
       </c>
       <c r="B200" s="4">
         <v>102000</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D200" s="26">
-        <v>4020657</v>
+        <v>4020656</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="G200" s="4">
+        <v>2</v>
       </c>
       <c r="H200" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="J200" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K200" s="4">
         <v>100</v>
@@ -8075,28 +8065,28 @@
     </row>
     <row r="201" s="4" customFormat="1" spans="1:11">
       <c r="A201" s="4">
-        <v>10200019</v>
+        <v>10200018</v>
       </c>
       <c r="B201" s="4">
         <v>102000</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D201" s="26">
-        <v>4020658</v>
+        <v>4020657</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G201" s="4">
-        <v>2</v>
-      </c>
       <c r="H201" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="J201" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K201" s="4">
         <v>100</v>
@@ -8104,118 +8094,118 @@
     </row>
     <row r="202" s="4" customFormat="1" spans="1:11">
       <c r="A202" s="4">
-        <v>10200020</v>
+        <v>10200019</v>
       </c>
       <c r="B202" s="4">
         <v>102000</v>
       </c>
       <c r="C202" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D202" s="26">
+        <v>4020658</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G202" s="4">
+        <v>2</v>
+      </c>
+      <c r="H202" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="J202" s="4">
+        <v>18</v>
+      </c>
+      <c r="K202" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="203" s="4" customFormat="1" spans="1:11">
+      <c r="A203" s="4">
+        <v>10200020</v>
+      </c>
+      <c r="B203" s="4">
+        <v>102000</v>
+      </c>
+      <c r="C203" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D202" s="26">
+      <c r="D203" s="26">
         <v>4020651</v>
       </c>
-      <c r="E202" s="4" t="s">
+      <c r="E203" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G202" s="4">
-        <v>2</v>
-      </c>
-      <c r="H202" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="I202" s="4" t="s">
+      <c r="G203" s="4">
+        <v>2</v>
+      </c>
+      <c r="H203" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="I203" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J202" s="4">
+      <c r="J203" s="4">
         <v>19</v>
       </c>
-      <c r="K202" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="203" s="5" customFormat="1" spans="1:11">
-      <c r="A203" s="5">
-        <v>10270001</v>
-      </c>
-      <c r="B203" s="5">
-        <v>102700</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D203" s="30">
-        <v>4020002</v>
-      </c>
-      <c r="E203" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F203" s="5">
-        <v>1</v>
-      </c>
-      <c r="G203" s="5">
-        <v>2</v>
-      </c>
-      <c r="J203" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K203" s="5">
-        <v>0</v>
+      <c r="K203" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="204" s="5" customFormat="1" spans="1:11">
       <c r="A204" s="5">
-        <v>10270003</v>
+        <v>10270001</v>
       </c>
       <c r="B204" s="5">
         <v>102700</v>
       </c>
-      <c r="C204" s="38" t="s">
-        <v>27</v>
+      <c r="C204" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="D204" s="30">
-        <v>4020645</v>
+        <v>4020002</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>236</v>
+        <v>25</v>
+      </c>
+      <c r="F204" s="5">
+        <v>1</v>
       </c>
       <c r="G204" s="5">
         <v>2</v>
       </c>
-      <c r="I204" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="J204" s="5">
-        <v>2</v>
+      <c r="J204" s="20">
+        <v>-1</v>
       </c>
       <c r="K204" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" s="5" customFormat="1" spans="1:11">
       <c r="A205" s="5">
-        <v>10270004</v>
+        <v>10270003</v>
       </c>
       <c r="B205" s="5">
         <v>102700</v>
       </c>
       <c r="C205" s="38" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D205" s="30">
-        <v>4020640</v>
+        <v>4020645</v>
       </c>
       <c r="E205" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G205" s="5">
+        <v>2</v>
+      </c>
+      <c r="I205" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G205" s="5">
-        <v>2</v>
-      </c>
-      <c r="H205" s="5" t="s">
-        <v>238</v>
-      </c>
       <c r="J205" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K205" s="5">
         <v>100</v>
@@ -8223,31 +8213,28 @@
     </row>
     <row r="206" s="5" customFormat="1" spans="1:11">
       <c r="A206" s="5">
-        <v>10270005</v>
+        <v>10270004</v>
       </c>
       <c r="B206" s="5">
         <v>102700</v>
       </c>
       <c r="C206" s="38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D206" s="30">
-        <v>4020646</v>
+        <v>4020640</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="G206" s="5">
         <v>2</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="I206" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J206" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K206" s="5">
         <v>100</v>
@@ -8255,16 +8242,16 @@
     </row>
     <row r="207" s="5" customFormat="1" spans="1:11">
       <c r="A207" s="5">
-        <v>10270006</v>
+        <v>10270005</v>
       </c>
       <c r="B207" s="5">
         <v>102700</v>
       </c>
       <c r="C207" s="38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D207" s="30">
-        <v>4020641</v>
+        <v>4020646</v>
       </c>
       <c r="E207" s="5" t="s">
         <v>34</v>
@@ -8273,10 +8260,13 @@
         <v>2</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
+      </c>
+      <c r="I207" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="J207" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K207" s="5">
         <v>100</v>
@@ -8284,77 +8274,74 @@
     </row>
     <row r="208" s="5" customFormat="1" spans="1:11">
       <c r="A208" s="5">
-        <v>10270002</v>
+        <v>10270006</v>
       </c>
       <c r="B208" s="5">
         <v>102700</v>
       </c>
-      <c r="C208" s="5" t="s">
-        <v>63</v>
+      <c r="C208" s="38" t="s">
+        <v>37</v>
       </c>
       <c r="D208" s="30">
-        <v>4020003</v>
+        <v>4020641</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G208" s="5">
         <v>2</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="J208" s="20">
-        <v>-1</v>
+        <v>240</v>
+      </c>
+      <c r="J208" s="5">
+        <v>5</v>
       </c>
       <c r="K208" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="209" s="5" customFormat="1" ht="20" customHeight="1" spans="1:11">
+    <row r="209" s="5" customFormat="1" spans="1:11">
       <c r="A209" s="5">
-        <v>10270007</v>
+        <v>10270002</v>
       </c>
       <c r="B209" s="5">
         <v>102700</v>
       </c>
-      <c r="C209" s="38" t="s">
-        <v>39</v>
+      <c r="C209" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="D209" s="30">
-        <v>4020647</v>
+        <v>4020003</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G209" s="5">
         <v>2</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I209" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="J209" s="5">
-        <v>6</v>
+        <v>241</v>
+      </c>
+      <c r="J209" s="20">
+        <v>-1</v>
       </c>
       <c r="K209" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="210" s="5" customFormat="1" spans="1:11">
+    <row r="210" s="5" customFormat="1" ht="20" customHeight="1" spans="1:11">
       <c r="A210" s="5">
-        <v>10270008</v>
+        <v>10270007</v>
       </c>
       <c r="B210" s="5">
         <v>102700</v>
       </c>
       <c r="C210" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D210" s="30">
-        <v>4020642</v>
+        <v>4020647</v>
       </c>
       <c r="E210" s="5" t="s">
         <v>40</v>
@@ -8363,10 +8350,13 @@
         <v>2</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
+      </c>
+      <c r="I210" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="J210" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K210" s="5">
         <v>100</v>
@@ -8374,31 +8364,28 @@
     </row>
     <row r="211" s="5" customFormat="1" spans="1:11">
       <c r="A211" s="5">
-        <v>10270009</v>
+        <v>10270008</v>
       </c>
       <c r="B211" s="5">
         <v>102700</v>
       </c>
       <c r="C211" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D211" s="30">
-        <v>4020648</v>
+        <v>4020642</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G211" s="5">
         <v>2</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I211" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="J211" s="20">
-        <v>-1</v>
+        <v>243</v>
+      </c>
+      <c r="J211" s="5">
+        <v>7</v>
       </c>
       <c r="K211" s="5">
         <v>100</v>
@@ -8406,16 +8393,16 @@
     </row>
     <row r="212" s="5" customFormat="1" spans="1:11">
       <c r="A212" s="5">
-        <v>10270010</v>
+        <v>10270009</v>
       </c>
       <c r="B212" s="5">
         <v>102700</v>
       </c>
       <c r="C212" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D212" s="30">
-        <v>4020643</v>
+        <v>4020648</v>
       </c>
       <c r="E212" s="5" t="s">
         <v>44</v>
@@ -8424,7 +8411,10 @@
         <v>2</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
+      </c>
+      <c r="I212" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="J212" s="20">
         <v>-1</v>
@@ -8435,28 +8425,25 @@
     </row>
     <row r="213" s="5" customFormat="1" spans="1:11">
       <c r="A213" s="5">
-        <v>10270011</v>
+        <v>10270010</v>
       </c>
       <c r="B213" s="5">
         <v>102700</v>
       </c>
       <c r="C213" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D213" s="30">
-        <v>4020649</v>
+        <v>4020643</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G213" s="5">
         <v>2</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="I213" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J213" s="20">
         <v>-1</v>
@@ -8467,16 +8454,16 @@
     </row>
     <row r="214" s="5" customFormat="1" spans="1:11">
       <c r="A214" s="5">
-        <v>10270012</v>
+        <v>10270011</v>
       </c>
       <c r="B214" s="5">
         <v>102700</v>
       </c>
       <c r="C214" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D214" s="30">
-        <v>4020644</v>
+        <v>4020649</v>
       </c>
       <c r="E214" s="5" t="s">
         <v>48</v>
@@ -8485,7 +8472,10 @@
         <v>2</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="I214" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="J214" s="20">
         <v>-1</v>
@@ -8496,28 +8486,28 @@
     </row>
     <row r="215" s="5" customFormat="1" spans="1:11">
       <c r="A215" s="5">
-        <v>10270013</v>
+        <v>10270012</v>
       </c>
       <c r="B215" s="5">
         <v>102700</v>
       </c>
       <c r="C215" s="38" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D215" s="30">
-        <v>4020650</v>
+        <v>4020644</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G215" s="5">
         <v>2</v>
       </c>
-      <c r="I215" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="J215" s="5">
-        <v>12</v>
+      <c r="H215" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="J215" s="20">
+        <v>-1</v>
       </c>
       <c r="K215" s="5">
         <v>100</v>
@@ -8525,16 +8515,16 @@
     </row>
     <row r="216" s="5" customFormat="1" spans="1:11">
       <c r="A216" s="5">
-        <v>10270014</v>
+        <v>10270013</v>
       </c>
       <c r="B216" s="5">
         <v>102700</v>
       </c>
-      <c r="C216" s="5" t="s">
-        <v>74</v>
+      <c r="C216" s="38" t="s">
+        <v>71</v>
       </c>
       <c r="D216" s="30">
-        <v>4020653</v>
+        <v>4020650</v>
       </c>
       <c r="E216" s="5" t="s">
         <v>72</v>
@@ -8542,14 +8532,11 @@
       <c r="G216" s="5">
         <v>2</v>
       </c>
-      <c r="H216" s="5" t="s">
-        <v>252</v>
-      </c>
       <c r="I216" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J216" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K216" s="5">
         <v>100</v>
@@ -8557,16 +8544,16 @@
     </row>
     <row r="217" s="5" customFormat="1" spans="1:11">
       <c r="A217" s="5">
-        <v>10270015</v>
+        <v>10270014</v>
       </c>
       <c r="B217" s="5">
         <v>102700</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D217" s="30">
-        <v>4020654</v>
+        <v>4020653</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>72</v>
@@ -8575,10 +8562,13 @@
         <v>2</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="J217" s="20">
-        <v>-1</v>
+        <v>251</v>
+      </c>
+      <c r="I217" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J217" s="5">
+        <v>13</v>
       </c>
       <c r="K217" s="5">
         <v>100</v>
@@ -8586,28 +8576,25 @@
     </row>
     <row r="218" s="5" customFormat="1" spans="1:11">
       <c r="A218" s="5">
-        <v>10270016</v>
+        <v>10270015</v>
       </c>
       <c r="B218" s="5">
         <v>102700</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D218" s="30">
-        <v>4020655</v>
+        <v>4020654</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G218" s="5">
         <v>2</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I218" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J218" s="20">
         <v>-1</v>
@@ -8618,16 +8605,16 @@
     </row>
     <row r="219" s="5" customFormat="1" spans="1:11">
       <c r="A219" s="5">
-        <v>10270017</v>
+        <v>10270016</v>
       </c>
       <c r="B219" s="5">
         <v>102700</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D219" s="30">
-        <v>4020656</v>
+        <v>4020655</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>80</v>
@@ -8636,7 +8623,10 @@
         <v>2</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
+      </c>
+      <c r="I219" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="J219" s="20">
         <v>-1</v>
@@ -8647,29 +8637,25 @@
     </row>
     <row r="220" s="5" customFormat="1" spans="1:11">
       <c r="A220" s="5">
-        <v>10270018</v>
+        <v>10270017</v>
       </c>
       <c r="B220" s="5">
         <v>102700</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D220" s="30">
-        <v>4020657</v>
+        <v>4020656</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F220" s="38"/>
+        <v>80</v>
+      </c>
       <c r="G220" s="5">
         <v>2</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="I220" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J220" s="20">
         <v>-1</v>
@@ -8680,25 +8666,29 @@
     </row>
     <row r="221" s="5" customFormat="1" spans="1:11">
       <c r="A221" s="5">
-        <v>10270019</v>
+        <v>10270018</v>
       </c>
       <c r="B221" s="5">
         <v>102700</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D221" s="30">
-        <v>4020658</v>
+        <v>4020657</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>86</v>
       </c>
+      <c r="F221" s="38"/>
       <c r="G221" s="5">
         <v>2</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
+      </c>
+      <c r="I221" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="J221" s="20">
         <v>-1</v>
@@ -8709,31 +8699,28 @@
     </row>
     <row r="222" s="5" customFormat="1" spans="1:11">
       <c r="A222" s="5">
-        <v>10270020</v>
+        <v>10270019</v>
       </c>
       <c r="B222" s="5">
         <v>102700</v>
       </c>
-      <c r="C222" s="38" t="s">
-        <v>53</v>
+      <c r="C222" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="D222" s="30">
-        <v>4020651</v>
+        <v>4020658</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="G222" s="5">
         <v>2</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="I222" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="J222" s="5">
-        <v>19</v>
+        <v>259</v>
+      </c>
+      <c r="J222" s="20">
+        <v>-1</v>
       </c>
       <c r="K222" s="5">
         <v>100</v>
@@ -8741,108 +8728,111 @@
     </row>
     <row r="223" s="5" customFormat="1" spans="1:11">
       <c r="A223" s="5">
-        <v>10270021</v>
+        <v>10270020</v>
       </c>
       <c r="B223" s="5">
         <v>102700</v>
       </c>
-      <c r="C223" s="39" t="s">
+      <c r="C223" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D223" s="30">
+        <v>4020651</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G223" s="5">
+        <v>2</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I223" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="J223" s="5">
+        <v>19</v>
+      </c>
+      <c r="K223" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="224" s="5" customFormat="1" spans="1:11">
+      <c r="A224" s="5">
+        <v>10270021</v>
+      </c>
+      <c r="B224" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C224" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="D223" s="30"/>
-      <c r="G223" s="5">
-        <v>2</v>
-      </c>
-      <c r="J223" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K223" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" s="1" customFormat="1" spans="1:11">
-      <c r="A224" s="1">
-        <v>10150001</v>
-      </c>
-      <c r="B224" s="1">
-        <v>101500</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D224" s="16">
-        <v>4020002</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F224" s="1">
-        <v>1</v>
-      </c>
-      <c r="G224" s="1">
+      <c r="D224" s="30"/>
+      <c r="G224" s="5">
         <v>2</v>
       </c>
       <c r="J224" s="20">
         <v>-1</v>
       </c>
-      <c r="K224" s="1">
+      <c r="K224" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" spans="1:11">
       <c r="A225" s="1">
-        <v>10150003</v>
+        <v>10150001</v>
       </c>
       <c r="B225" s="1">
         <v>101500</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D225" s="16">
-        <v>4020645</v>
+        <v>4020002</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>236</v>
+        <v>25</v>
+      </c>
+      <c r="F225" s="1">
+        <v>1</v>
       </c>
       <c r="G225" s="1">
         <v>2</v>
       </c>
-      <c r="H225" s="1"/>
-      <c r="I225" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J225" s="5">
-        <v>2</v>
+      <c r="J225" s="20">
+        <v>-1</v>
       </c>
       <c r="K225" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" spans="1:11">
       <c r="A226" s="1">
-        <v>10150004</v>
+        <v>10150003</v>
       </c>
       <c r="B226" s="1">
         <v>101500</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D226" s="16">
-        <v>4020640</v>
+        <v>4020645</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G226" s="1">
         <v>2</v>
       </c>
-      <c r="H226" s="1" t="s">
-        <v>263</v>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="J226" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K226" s="1">
         <v>100</v>
@@ -8850,31 +8840,28 @@
     </row>
     <row r="227" s="1" customFormat="1" spans="1:11">
       <c r="A227" s="1">
-        <v>10150005</v>
+        <v>10150004</v>
       </c>
       <c r="B227" s="1">
         <v>101500</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D227" s="16">
-        <v>4020646</v>
+        <v>4020640</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="G227" s="1">
         <v>2</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="I227" s="1" t="s">
-        <v>36</v>
+        <v>262</v>
       </c>
       <c r="J227" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K227" s="1">
         <v>100</v>
@@ -8882,16 +8869,16 @@
     </row>
     <row r="228" s="1" customFormat="1" spans="1:11">
       <c r="A228" s="1">
-        <v>10150006</v>
+        <v>10150005</v>
       </c>
       <c r="B228" s="1">
         <v>101500</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D228" s="16">
-        <v>4020641</v>
+        <v>4020646</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>34</v>
@@ -8900,10 +8887,13 @@
         <v>2</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="J228" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K228" s="1">
         <v>100</v>
@@ -8911,28 +8901,28 @@
     </row>
     <row r="229" s="1" customFormat="1" spans="1:11">
       <c r="A229" s="1">
-        <v>10150002</v>
+        <v>10150006</v>
       </c>
       <c r="B229" s="1">
         <v>101500</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D229" s="16">
-        <v>4020003</v>
+        <v>4020641</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G229" s="1">
         <v>2</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J229" s="20">
-        <v>-1</v>
+        <v>264</v>
+      </c>
+      <c r="J229" s="5">
+        <v>5</v>
       </c>
       <c r="K229" s="1">
         <v>100</v>
@@ -8940,31 +8930,28 @@
     </row>
     <row r="230" s="1" customFormat="1" spans="1:11">
       <c r="A230" s="1">
-        <v>10150007</v>
+        <v>10150002</v>
       </c>
       <c r="B230" s="1">
         <v>101500</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D230" s="16">
-        <v>4020647</v>
+        <v>4020003</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G230" s="1">
         <v>2</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I230" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J230" s="5">
-        <v>6</v>
+        <v>265</v>
+      </c>
+      <c r="J230" s="20">
+        <v>-1</v>
       </c>
       <c r="K230" s="1">
         <v>100</v>
@@ -8972,16 +8959,16 @@
     </row>
     <row r="231" s="1" customFormat="1" spans="1:11">
       <c r="A231" s="1">
-        <v>10150008</v>
+        <v>10150007</v>
       </c>
       <c r="B231" s="1">
         <v>101500</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D231" s="16">
-        <v>4020642</v>
+        <v>4020647</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>40</v>
@@ -8990,10 +8977,13 @@
         <v>2</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J231" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>
@@ -9001,31 +8991,28 @@
     </row>
     <row r="232" s="1" customFormat="1" spans="1:11">
       <c r="A232" s="1">
-        <v>10150009</v>
+        <v>10150008</v>
       </c>
       <c r="B232" s="1">
         <v>101500</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D232" s="16">
-        <v>4020648</v>
+        <v>4020642</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G232" s="1">
         <v>2</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I232" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J232" s="20">
-        <v>-1</v>
+        <v>266</v>
+      </c>
+      <c r="J232" s="5">
+        <v>7</v>
       </c>
       <c r="K232" s="1">
         <v>100</v>
@@ -9033,16 +9020,16 @@
     </row>
     <row r="233" s="1" customFormat="1" spans="1:11">
       <c r="A233" s="1">
-        <v>10150010</v>
+        <v>10150009</v>
       </c>
       <c r="B233" s="1">
         <v>101500</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D233" s="16">
-        <v>4020643</v>
+        <v>4020648</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>44</v>
@@ -9051,7 +9038,10 @@
         <v>2</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="J233" s="20">
         <v>-1</v>
@@ -9062,28 +9052,25 @@
     </row>
     <row r="234" s="1" customFormat="1" spans="1:11">
       <c r="A234" s="1">
-        <v>10150011</v>
+        <v>10150010</v>
       </c>
       <c r="B234" s="1">
         <v>101500</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D234" s="16">
-        <v>4020649</v>
+        <v>4020643</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G234" s="1">
         <v>2</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="I234" s="1" t="s">
-        <v>49</v>
+        <v>268</v>
       </c>
       <c r="J234" s="20">
         <v>-1</v>
@@ -9094,16 +9081,16 @@
     </row>
     <row r="235" s="1" customFormat="1" spans="1:11">
       <c r="A235" s="1">
-        <v>10150012</v>
+        <v>10150011</v>
       </c>
       <c r="B235" s="1">
         <v>101500</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D235" s="16">
-        <v>4020644</v>
+        <v>4020649</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>48</v>
@@ -9112,7 +9099,10 @@
         <v>2</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="J235" s="20">
         <v>-1</v>
@@ -9123,29 +9113,28 @@
     </row>
     <row r="236" s="1" customFormat="1" spans="1:11">
       <c r="A236" s="1">
-        <v>10150013</v>
+        <v>10150012</v>
       </c>
       <c r="B236" s="1">
         <v>101500</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D236" s="16">
-        <v>4020650</v>
+        <v>4020644</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G236" s="1">
         <v>2</v>
       </c>
-      <c r="H236" s="1"/>
-      <c r="I236" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J236" s="5">
-        <v>12</v>
+      <c r="H236" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J236" s="20">
+        <v>-1</v>
       </c>
       <c r="K236" s="1">
         <v>100</v>
@@ -9153,16 +9142,16 @@
     </row>
     <row r="237" s="1" customFormat="1" spans="1:11">
       <c r="A237" s="1">
-        <v>10150014</v>
+        <v>10150013</v>
       </c>
       <c r="B237" s="1">
         <v>101500</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D237" s="16">
-        <v>4020653</v>
+        <v>4020650</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>72</v>
@@ -9170,14 +9159,12 @@
       <c r="G237" s="1">
         <v>2</v>
       </c>
-      <c r="H237" s="1" t="s">
-        <v>272</v>
-      </c>
+      <c r="H237" s="1"/>
       <c r="I237" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J237" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K237" s="1">
         <v>100</v>
@@ -9185,16 +9172,16 @@
     </row>
     <row r="238" s="1" customFormat="1" spans="1:11">
       <c r="A238" s="1">
-        <v>10150015</v>
+        <v>10150014</v>
       </c>
       <c r="B238" s="1">
         <v>101500</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D238" s="16">
-        <v>4020654</v>
+        <v>4020653</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>72</v>
@@ -9203,10 +9190,13 @@
         <v>2</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="J238" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K238" s="1">
         <v>100</v>
@@ -9214,31 +9204,28 @@
     </row>
     <row r="239" s="1" customFormat="1" spans="1:11">
       <c r="A239" s="1">
-        <v>10150016</v>
+        <v>10150015</v>
       </c>
       <c r="B239" s="1">
         <v>101500</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D239" s="16">
-        <v>4020655</v>
+        <v>4020654</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G239" s="1">
         <v>2</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I239" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J239" s="20">
-        <v>-1</v>
+        <v>272</v>
+      </c>
+      <c r="J239" s="5">
+        <v>14</v>
       </c>
       <c r="K239" s="1">
         <v>100</v>
@@ -9246,16 +9233,16 @@
     </row>
     <row r="240" s="1" customFormat="1" spans="1:11">
       <c r="A240" s="1">
-        <v>10150017</v>
+        <v>10150016</v>
       </c>
       <c r="B240" s="1">
         <v>101500</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D240" s="16">
-        <v>4020656</v>
+        <v>4020655</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>80</v>
@@ -9264,7 +9251,10 @@
         <v>2</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="J240" s="20">
         <v>-1</v>
@@ -9275,28 +9265,25 @@
     </row>
     <row r="241" s="1" customFormat="1" spans="1:11">
       <c r="A241" s="1">
-        <v>10150018</v>
+        <v>10150017</v>
       </c>
       <c r="B241" s="1">
         <v>101500</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D241" s="16">
-        <v>4020657</v>
+        <v>4020656</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G241" s="1">
         <v>2</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I241" s="1" t="s">
-        <v>88</v>
+        <v>274</v>
       </c>
       <c r="J241" s="20">
         <v>-1</v>
@@ -9307,16 +9294,16 @@
     </row>
     <row r="242" s="1" customFormat="1" spans="1:11">
       <c r="A242" s="1">
-        <v>10150019</v>
+        <v>10150018</v>
       </c>
       <c r="B242" s="1">
         <v>101500</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D242" s="16">
-        <v>4020658</v>
+        <v>4020657</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>86</v>
@@ -9325,7 +9312,10 @@
         <v>2</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="J242" s="20">
         <v>-1</v>
@@ -9336,33 +9326,62 @@
     </row>
     <row r="243" s="1" customFormat="1" spans="1:11">
       <c r="A243" s="1">
-        <v>10150020</v>
+        <v>10150019</v>
       </c>
       <c r="B243" s="1">
         <v>101500</v>
       </c>
       <c r="C243" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D243" s="16">
+        <v>4020658</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G243" s="1">
+        <v>2</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J243" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K243" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="244" s="1" customFormat="1" spans="1:11">
+      <c r="A244" s="1">
+        <v>10150020</v>
+      </c>
+      <c r="B244" s="1">
+        <v>101500</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D243" s="16">
+      <c r="D244" s="16">
         <v>4020651</v>
       </c>
-      <c r="E243" s="1" t="s">
+      <c r="E244" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G243" s="1">
-        <v>2</v>
-      </c>
-      <c r="H243" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="I243" s="1" t="s">
+      <c r="G244" s="1">
+        <v>2</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I244" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J243" s="5">
+      <c r="J244" s="5">
         <v>19</v>
       </c>
-      <c r="K243" s="1">
+      <c r="K244" s="1">
         <v>100</v>
       </c>
     </row>
